--- a/lcoe_plots/synthetic_ethylene_lcoe/LCOE_SYNTHETIC_Ethylene.xlsx
+++ b/lcoe_plots/synthetic_ethylene_lcoe/LCOE_SYNTHETIC_Ethylene.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/MacroEnergy-Abbie.jl/MacroEnergyExamples/lcoe_plots/synthetic_ethylene_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028B3B37-9581-DF4F-9A1E-60ADDC5D8560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFCDA25-4E66-5C49-AB40-1F00B1ECA7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="lc_detailed" sheetId="1" r:id="rId1"/>
+    <sheet name="lc_summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="95">
   <si>
     <t>Asset Parameters (normalized by commodity feedstock)</t>
   </si>
@@ -77,12 +78,18 @@
     <t>Carbon Outputs</t>
   </si>
   <si>
+    <t>Assumptions</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
     <t>commodity</t>
   </si>
   <si>
+    <t>CCS</t>
+  </si>
+  <si>
     <t>h2_consumption (MWh/t-CO2Captured)</t>
   </si>
   <si>
@@ -95,6 +102,9 @@
     <t>natgas_production (MWh/t-CO2Captured)</t>
   </si>
   <si>
+    <t>gasoline_production (MWh/t-CO2Captured)</t>
+  </si>
+  <si>
     <t>emission_rate (t-CO2/t-CO2Captured)</t>
   </si>
   <si>
@@ -194,6 +204,9 @@
     <t>natgas_production</t>
   </si>
   <si>
+    <t>gasoline_production</t>
+  </si>
+  <si>
     <t>investment_cost</t>
   </si>
   <si>
@@ -215,94 +228,97 @@
     <t>Ethylene (t-CO2/t-ethylene)</t>
   </si>
   <si>
+    <t>Gasoline (t-CO2/MWh-gasoline)</t>
+  </si>
+  <si>
     <t>NG (t-CO2/MWh-NG)</t>
   </si>
   <si>
-    <t>CA_Synthetic_Ethylene_Non_CCS</t>
-  </si>
-  <si>
-    <t>CA_Synthetic_Ethylene_CCS_90</t>
+    <t>LPG (t-CO2/t-LPG)</t>
+  </si>
+  <si>
+    <t>CO2Captured (t-CO2/t-CO2Captured)</t>
+  </si>
+  <si>
+    <t>CO2Captured - RECYCLE ADJUSTED  (t-CO2/t-CO2Captured)</t>
+  </si>
+  <si>
+    <t>Ethylene (t-CO2/t-CO2Captured)</t>
+  </si>
+  <si>
+    <t>NG (t-CO2/t-CO2Captured)</t>
+  </si>
+  <si>
+    <t>Emissions (t-CO2/t-CO2Captured)</t>
+  </si>
+  <si>
+    <t>Captured (t-CO2/t-CO2Captured)</t>
+  </si>
+  <si>
+    <t>Gasoline (t-CO2/t-CO2Captured)</t>
+  </si>
+  <si>
+    <t>RECYCLED Output (t-CO2/t-CO2Captured)</t>
+  </si>
+  <si>
+    <t>STORED Output (t-CO2/t-CO2Captured)</t>
+  </si>
+  <si>
+    <t>Ethylene Carbon Content</t>
+  </si>
+  <si>
+    <t>t-CO2/t-ethylene</t>
+  </si>
+  <si>
+    <t>Synthetic_Ethylene_Non_CCS</t>
   </si>
   <si>
     <t>CO2Captured</t>
   </si>
   <si>
-    <t>gasoline_production (MWh/t-CO2Captured)</t>
-  </si>
-  <si>
-    <t>gasoline_production</t>
-  </si>
-  <si>
-    <t>Gasoline (t-CO2/MWh-gasoline)</t>
-  </si>
-  <si>
-    <t>Assumptions</t>
-  </si>
-  <si>
-    <t>Ethylene Carbon Content</t>
-  </si>
-  <si>
-    <t>t-CO2/t-ethylene</t>
-  </si>
-  <si>
     <t>Gasoline Carbon Content</t>
   </si>
   <si>
+    <t>t-CO2/MWh-gasoline</t>
+  </si>
+  <si>
+    <t>Synthetic_Ethylene_CCS_90</t>
+  </si>
+  <si>
     <t>Natural Gas Carbon Content</t>
   </si>
   <si>
+    <t>t-CO2/MWh-natgas</t>
+  </si>
+  <si>
+    <t>LPG Carbon Content</t>
+  </si>
+  <si>
+    <t>t-CO2/t-LPG</t>
+  </si>
+  <si>
     <t>Capacity Factor</t>
   </si>
   <si>
-    <t>t-CO2/MWh-gasoline</t>
-  </si>
-  <si>
-    <t>t-CO2/MWh-natgas</t>
-  </si>
-  <si>
-    <t>LPG (t-CO2/t-LPG)</t>
-  </si>
-  <si>
-    <t>LPG Carbon Content</t>
-  </si>
-  <si>
-    <t>t-CO2/t-LPG</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
-    <t>CO2Captured (t-CO2/t-CO2Captured)</t>
-  </si>
-  <si>
-    <t>CO2Captured - ADJUSTED FEEDSTOCK (t-CO2/t-CO2Captured)</t>
-  </si>
-  <si>
-    <t>Ethylene (t-CO2/t-CO2Captured)</t>
-  </si>
-  <si>
-    <t>NG (t-CO2/t-CO2Captured)</t>
-  </si>
-  <si>
-    <t>Emissions (t-CO2/t-CO2Captured)</t>
-  </si>
-  <si>
-    <t>Captured (t-CO2/t-CO2Captured)</t>
-  </si>
-  <si>
-    <t>LPG (t-CO2/t-CO2Captured)</t>
-  </si>
-  <si>
-    <t>Gasoline (t-CO2/t-CO2Captured)</t>
-  </si>
-  <si>
-    <t>Total Output (t-CO2/t-CO2Captured)</t>
-  </si>
-  <si>
-    <t>LPG (t-LPG/t-CO2Captured)</t>
-  </si>
-  <si>
-    <t>LPG (t-LPG/t-ethylene)</t>
+    <t>LCOE ($/GJ-ethylene)</t>
+  </si>
+  <si>
+    <t>Levelized cost for Synthetic Ethylene Production - $/GJ-ethylene - no chemicals CO2 sequestration</t>
+  </si>
+  <si>
+    <t>Levelized cost for Synthetic Ethylene Production - $/GJ-ethylene - chemicals CO2 sequestration</t>
+  </si>
+  <si>
+    <t>Ethylene LHV</t>
+  </si>
+  <si>
+    <t>GJ/t-ethylene</t>
+  </si>
+  <si>
+    <t>CHECK LCOE ($/GJ-ethylene)</t>
   </si>
 </sst>
 </file>
@@ -312,7 +328,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -351,6 +367,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -455,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -481,6 +505,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -795,790 +830,838 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:CG108"/>
+  <dimension ref="B2:CF108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="13.83203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="12" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.83203125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5" style="1" customWidth="1"/>
-    <col min="23" max="23" width="14.33203125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="11" style="1" customWidth="1"/>
-    <col min="25" max="25" width="9.33203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="10.83203125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="14.83203125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5" style="1" customWidth="1"/>
-    <col min="29" max="30" width="12.5" style="1" customWidth="1"/>
-    <col min="31" max="31" width="12.1640625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="13.1640625" style="1" customWidth="1"/>
-    <col min="33" max="33" width="9.6640625" style="1" customWidth="1"/>
-    <col min="34" max="34" width="9.83203125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5" style="1" customWidth="1"/>
-    <col min="36" max="36" width="15.33203125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="3.33203125" customWidth="1"/>
-    <col min="38" max="38" width="18.83203125" style="1" customWidth="1"/>
-    <col min="39" max="39" width="19.83203125" style="1" customWidth="1"/>
-    <col min="40" max="40" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.6640625" style="1" customWidth="1"/>
-    <col min="42" max="42" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="44" width="15.6640625" style="1" customWidth="1"/>
-    <col min="45" max="45" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.5" style="1" customWidth="1"/>
-    <col min="50" max="50" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="10.5" style="1" customWidth="1"/>
-    <col min="55" max="55" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="12.1640625" style="1" customWidth="1"/>
-    <col min="58" max="58" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="18" style="1" customWidth="1"/>
-    <col min="61" max="61" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="9.6640625" style="1" customWidth="1"/>
-    <col min="64" max="64" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="3.33203125" style="1" customWidth="1"/>
-    <col min="67" max="67" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="25.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="17.33203125" style="1" customWidth="1"/>
-    <col min="71" max="71" width="3.6640625" style="1" customWidth="1"/>
-    <col min="72" max="72" width="29.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="47.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="3.33203125" style="1" customWidth="1"/>
-    <col min="75" max="75" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="23.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="18.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="18.5" style="1" customWidth="1"/>
-    <col min="81" max="81" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="10.83203125" style="1" customWidth="1"/>
-    <col min="83" max="83" width="22.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="10.83203125" style="1" customWidth="1"/>
-    <col min="85" max="85" width="17.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="86" max="91" width="10.83203125" style="1" customWidth="1"/>
-    <col min="92" max="16384" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="12.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="13.83203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.83203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="11" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.83203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="15" style="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5" style="1" customWidth="1"/>
+    <col min="28" max="29" width="12.5" style="1" customWidth="1"/>
+    <col min="30" max="30" width="12.1640625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="13.1640625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="9.6640625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="9.83203125" style="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5" style="1" customWidth="1"/>
+    <col min="35" max="35" width="15.33203125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="3.33203125" customWidth="1"/>
+    <col min="37" max="37" width="18.83203125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="19.83203125" style="1" customWidth="1"/>
+    <col min="39" max="39" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.6640625" style="1" customWidth="1"/>
+    <col min="41" max="41" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="15.6640625" style="1" customWidth="1"/>
+    <col min="44" max="44" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.5" style="1" customWidth="1"/>
+    <col min="49" max="49" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="14.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="10.5" style="1" customWidth="1"/>
+    <col min="54" max="54" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.1640625" style="1" customWidth="1"/>
+    <col min="57" max="57" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18" style="1" customWidth="1"/>
+    <col min="60" max="60" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="9.6640625" style="1" customWidth="1"/>
+    <col min="63" max="63" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="3.33203125" style="1" customWidth="1"/>
+    <col min="66" max="66" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="25.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="17.33203125" style="1" customWidth="1"/>
+    <col min="70" max="70" width="3.6640625" style="1" customWidth="1"/>
+    <col min="71" max="71" width="29.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="45.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="3.33203125" style="1" customWidth="1"/>
+    <col min="74" max="74" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="17.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="23.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="31.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="10.83203125" style="1" customWidth="1"/>
+    <col min="82" max="82" width="22.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="10.83203125" style="1" customWidth="1"/>
+    <col min="84" max="84" width="17.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="85" max="92" width="10.83203125" style="1" customWidth="1"/>
+    <col min="93" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:85" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="AM2" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="AN2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO2" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AP2" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="AQ2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BA2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BG2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="BO2" s="1" t="s">
+      <c r="BN2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BT2" s="1" t="s">
+      <c r="BS2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="BW2" s="1" t="s">
+      <c r="BV2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="CE2" s="18" t="s">
+      <c r="CD2" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="V3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="X3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z3" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA3" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB3" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC3" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD3" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE3" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF3" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG3" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH3" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI3" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AS3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AT3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AU3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AV3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AW3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AZ3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="BA3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="BD3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="BE3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="BF3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="BJ3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="BK3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="BL3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="BN3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BO3" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="BP3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="BQ3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="BS3" s="7" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="3" spans="2:85" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="R3" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="S3" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="X3" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y3" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z3" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA3" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB3" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC3" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD3" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE3" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF3" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG3" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH3" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI3" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="AJ3" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AM3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AN3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AP3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AS3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AT3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AU3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AV3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AW3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AX3" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AY3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AZ3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="BA3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="BB3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="BC3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="BD3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="BE3" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG3" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="BI3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="BJ3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="BK3" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="BL3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BM3" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="BP3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="BQ3" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="BR3" s="7" t="s">
+      <c r="BT3" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="BV3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="BW3" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="BX3" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="BY3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="BZ3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="CA3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="CB3" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="BT3" s="7" t="s">
+      <c r="CD3" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="CE3" s="19">
+        <v>3.14</v>
+      </c>
+      <c r="CF3" s="19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="2:84" x14ac:dyDescent="0.2">
+      <c r="B4" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="BU3" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="BW3" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="BX3" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="BY3" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="BZ3" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="CA3" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="CB3" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="CC3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="CE3" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="CF3" s="19">
-        <v>3.14</v>
-      </c>
-      <c r="CG3" s="19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="2:85" x14ac:dyDescent="0.2">
-      <c r="B4" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="D4" s="13">
+        <v>0</v>
+      </c>
+      <c r="E4" s="13">
         <v>5.4424706709999997</v>
       </c>
-      <c r="E4" s="13">
+      <c r="F4" s="13">
         <v>0.17633674630000001</v>
       </c>
-      <c r="F4" s="13">
+      <c r="G4" s="13">
         <v>0.1137656428</v>
       </c>
-      <c r="G4" s="13">
+      <c r="H4" s="13">
         <v>0.15787734950000001</v>
       </c>
-      <c r="H4" s="13"/>
       <c r="I4" s="13">
+        <v>0.76475307729999997</v>
+      </c>
+      <c r="J4" s="13">
         <v>0.42937955880000001</v>
       </c>
-      <c r="J4" s="13">
+      <c r="K4" s="13">
         <v>174237.6587</v>
       </c>
-      <c r="K4" s="13">
+      <c r="L4" s="13">
         <v>95841.654150000002</v>
       </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
         <v>2.9463016839999998</v>
       </c>
-      <c r="M4" s="13">
-        <f>1/(CA4/BR4)</f>
-        <v>8.5028075192604816E-2</v>
-      </c>
-      <c r="N4" s="13">
-        <f>M4/F4</f>
-        <v>0.74739678078454819</v>
-      </c>
-      <c r="P4" s="16">
+      <c r="O4" s="16">
         <v>122.135409</v>
       </c>
-      <c r="Q4" s="16">
-        <v>-6.4965359999999999</v>
-      </c>
-      <c r="R4" s="16">
-        <v>117.625038</v>
-      </c>
-      <c r="S4" s="16">
-        <v>88.648826</v>
-      </c>
-      <c r="T4" s="16">
-        <v>72.811197000000007</v>
-      </c>
-      <c r="U4" s="11">
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="11">
         <v>21.986353300000001</v>
       </c>
+      <c r="U4" s="17"/>
       <c r="V4" s="17"/>
-      <c r="W4" s="17"/>
-      <c r="X4" s="16">
-        <v>25.313632999999999</v>
-      </c>
-      <c r="Y4" s="16">
-        <v>8.8090729999999997</v>
-      </c>
-      <c r="Z4" s="16"/>
-      <c r="AA4" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="17">
-        <v>0</v>
-      </c>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="17"/>
+      <c r="AA4" s="17"/>
+      <c r="AB4" s="17"/>
       <c r="AC4" s="17"/>
       <c r="AD4" s="17"/>
       <c r="AE4" s="17"/>
-      <c r="AF4" s="17"/>
-      <c r="AG4" s="16">
-        <v>11.573017</v>
-      </c>
-      <c r="AH4" s="16">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="16">
-        <v>576.81126900000004</v>
-      </c>
-      <c r="AJ4" s="16">
-        <v>0</v>
+      <c r="AF4" s="16"/>
+      <c r="AG4" s="16"/>
+      <c r="AH4" s="16"/>
+      <c r="AI4" s="16"/>
+      <c r="AK4" s="1" t="str">
+        <f>B4</f>
+        <v>Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="AL4" s="1" t="str">
-        <f>B4</f>
-        <v>CA_Synthetic_Ethylene_Non_CCS</v>
-      </c>
-      <c r="AM4" s="1" t="str">
         <f>C4</f>
         <v>CO2Captured</v>
       </c>
+      <c r="AM4" s="12">
+        <f>SUM(AS4:AZ4)+BB4+BC4</f>
+        <v>476.64414784303057</v>
+      </c>
       <c r="AN4" s="12">
-        <f>SUM(AT4:BA4)+BC4+BD4</f>
-        <v>964.86966954612205</v>
-      </c>
-      <c r="AO4" s="12">
-        <f>SUM(AT4:BA4)+BF4+BG4</f>
-        <v>964.86966954612205</v>
-      </c>
-      <c r="AP4" s="5">
-        <f t="shared" ref="AP4:AP5" si="0">AN4-AO4</f>
+        <f>SUM(AS4:AZ4)+BE4+BF4</f>
+        <v>476.64414784303057</v>
+      </c>
+      <c r="AO4" s="5">
+        <f>AM4-AN4</f>
         <v>0</v>
       </c>
+      <c r="AP4" s="12">
+        <f>SUM(AS4:AZ4)+BH4+BI4</f>
+        <v>520.27386164750192</v>
+      </c>
       <c r="AQ4" s="12">
-        <f>SUM(AT4:BA4)+BI4+BJ4</f>
-        <v>964.86966954612205</v>
-      </c>
-      <c r="AR4" s="12">
-        <f>SUM(AT4:BA4)+BL4+BM4</f>
-        <v>964.86966954612205</v>
+        <f>SUM(AS4:AZ4)+BK4+BL4</f>
+        <v>520.27386164750192</v>
+      </c>
+      <c r="AR4" s="5">
+        <f>AP4-AQ4</f>
+        <v>0</v>
       </c>
       <c r="AS4" s="5">
-        <f t="shared" ref="AS4:AS5" si="1">AQ4-AR4</f>
+        <f>E4/G4*X4</f>
         <v>0</v>
       </c>
-      <c r="AT4" s="5">
-        <f>D4/F4*Y4</f>
-        <v>421.42003737878917</v>
+      <c r="AT4" s="1">
+        <f>F4/G4*W4</f>
+        <v>0</v>
       </c>
       <c r="AU4" s="1">
-        <f>E4/F4*X4</f>
-        <v>39.236131141099733</v>
+        <f>1/G4*T4</f>
+        <v>193.26004546602891</v>
       </c>
       <c r="AV4" s="1">
-        <f>1/F4*U4</f>
-        <v>193.26004546602891</v>
+        <f>H4/G4*AF4*-1</f>
+        <v>0</v>
       </c>
       <c r="AW4" s="1">
-        <f>G4/F4*AG4*-1</f>
-        <v>-16.060360621268707</v>
+        <f>I4/G4*Z4</f>
+        <v>0</v>
       </c>
       <c r="AX4" s="1">
-        <f>H4/F4*AA4</f>
+        <f>K4/G4/(0.9*8760)</f>
+        <v>194.26040330394619</v>
+      </c>
+      <c r="AY4" s="1">
+        <f>L4/G4/(0.9*8760)</f>
+        <v>106.85542108065717</v>
+      </c>
+      <c r="AZ4" s="1">
+        <f>M4/G4</f>
+        <v>25.897991796869626</v>
+      </c>
+      <c r="BA4" s="1">
+        <f>BW4+BX4+BZ4-BT4</f>
+        <v>-0.35722411839199997</v>
+      </c>
+      <c r="BB4" s="1">
         <v>0</v>
       </c>
-      <c r="AY4" s="1">
-        <f>J4/F4/(0.9*8760)</f>
-        <v>194.26040330394619</v>
-      </c>
-      <c r="AZ4" s="1">
-        <f>K4/F4/(0.9*8760)</f>
-        <v>106.85542108065717</v>
-      </c>
-      <c r="BA4" s="1">
-        <f>L4/F4</f>
-        <v>25.897991796869626</v>
-      </c>
-      <c r="BO4" s="9">
-        <f>$CF$3</f>
+      <c r="BC4" s="1">
+        <f>BA4*O4</f>
+        <v>-43.629713804471336</v>
+      </c>
+      <c r="BD4" s="1">
+        <f>BW4+BX4+BZ4-BT4</f>
+        <v>-0.35722411839199997</v>
+      </c>
+      <c r="BE4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="1">
+        <f>BD4*O4</f>
+        <v>-43.629713804471336</v>
+      </c>
+      <c r="BG4" s="1">
+        <f>BV4+BW4+BX4+BZ4-BT4</f>
+        <v>0</v>
+      </c>
+      <c r="BH4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="1">
+        <f>BG4*O4</f>
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="1">
+        <f>BV4+BW4+BX4+BZ4-BT4</f>
+        <v>0</v>
+      </c>
+      <c r="BK4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL4" s="1">
+        <f>BJ4*O4</f>
+        <v>0</v>
+      </c>
+      <c r="BN4" s="9">
+        <f>$CE$3</f>
         <v>3.14</v>
       </c>
-      <c r="BP4" s="10">
-        <f>$CF$4</f>
+      <c r="BO4" s="10">
+        <f>$CE$4</f>
         <v>0.24123847100000001</v>
       </c>
+      <c r="BP4" s="9">
+        <f>$CE$5</f>
+        <v>0.18104824</v>
+      </c>
       <c r="BQ4" s="9">
-        <f>$CF$5</f>
-        <v>0.18104824</v>
-      </c>
-      <c r="BR4" s="9">
-        <f>$CF$6</f>
+        <f>$CE$6</f>
         <v>1.5714285714285715E-2</v>
       </c>
+      <c r="BS4" s="10">
+        <v>1</v>
+      </c>
       <c r="BT4" s="10">
+        <f>BS4-BY4</f>
         <v>1</v>
       </c>
-      <c r="BU4" s="10"/>
+      <c r="BV4" s="10">
+        <f>BN4*G4</f>
+        <v>0.35722411839200002</v>
+      </c>
       <c r="BW4" s="10">
-        <f>BO4*F4</f>
-        <v>0.35722411839200002</v>
+        <f>BP4*H4</f>
+        <v>2.8583416262839882E-2</v>
       </c>
       <c r="BX4" s="10">
-        <f>BQ4*G4</f>
-        <v>2.8583416262839882E-2</v>
+        <f>(BS4-BV4-BW4-BZ4)*(1-D4)</f>
+        <v>0.42970460228476337</v>
       </c>
       <c r="BY4" s="10">
-        <f>I4</f>
-        <v>0.42937955880000001</v>
-      </c>
-      <c r="BZ4" s="10"/>
+        <f>(BS4-BV4-BW4-BZ4)*(D4)</f>
+        <v>0</v>
+      </c>
+      <c r="BZ4" s="10">
+        <f>BO4*I4</f>
+        <v>0.1844878630603968</v>
+      </c>
       <c r="CA4" s="10">
-        <f>BT4-SUM(BW4:BY4)</f>
-        <v>0.18481290654516003</v>
+        <f>BV4+BW4+BX4+BZ4</f>
+        <v>1</v>
       </c>
       <c r="CB4" s="10">
-        <f>BP4*H4</f>
-        <v>0</v>
-      </c>
-      <c r="CC4" s="10"/>
-      <c r="CE4" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="CF4" s="19">
+        <f>SUM(BV4:BZ4)</f>
+        <v>1</v>
+      </c>
+      <c r="CD4" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="CE4" s="19">
         <v>0.24123847100000001</v>
       </c>
-      <c r="CG4" s="19" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="2:85" x14ac:dyDescent="0.2">
+      <c r="CF4" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B5" s="14" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D5" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="E5" s="13">
         <v>5.9243674339999997</v>
       </c>
-      <c r="E5" s="13">
+      <c r="F5" s="13">
         <v>0.24466847410000001</v>
       </c>
-      <c r="F5" s="13">
+      <c r="G5" s="13">
         <v>0.1238388794</v>
       </c>
-      <c r="G5" s="13">
+      <c r="H5" s="13">
         <v>0.1718564021</v>
       </c>
-      <c r="H5" s="13"/>
       <c r="I5" s="13">
+        <v>0.83246718269999997</v>
+      </c>
+      <c r="J5" s="13">
         <v>0.37885468500000002</v>
       </c>
-      <c r="J5" s="13">
+      <c r="K5" s="13">
         <v>209498.31779999999</v>
       </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>115165.852</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>3.542547876</v>
       </c>
-      <c r="M5" s="13">
-        <f>1/(CA5/BR5)</f>
-        <v>7.8111766387896325E-2</v>
-      </c>
-      <c r="N5" s="13">
-        <f>M5/F5</f>
-        <v>0.63075317514457674</v>
-      </c>
-      <c r="P5" s="16">
+      <c r="O5" s="16">
         <v>122.135409</v>
       </c>
-      <c r="Q5" s="16">
-        <v>-6.4965359999999999</v>
-      </c>
-      <c r="R5" s="16">
-        <v>117.625038</v>
-      </c>
-      <c r="S5" s="16">
-        <v>88.648826</v>
-      </c>
-      <c r="T5" s="16">
-        <v>72.811197000000007</v>
-      </c>
-      <c r="U5" s="11">
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="11">
         <v>21.986353300000001</v>
       </c>
+      <c r="U5" s="17"/>
       <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="16">
-        <v>25.313632999999999</v>
-      </c>
-      <c r="Y5" s="16">
-        <v>8.8090729999999997</v>
-      </c>
-      <c r="Z5" s="16"/>
-      <c r="AA5" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="17">
-        <v>0</v>
-      </c>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="17"/>
       <c r="AC5" s="17"/>
       <c r="AD5" s="17"/>
       <c r="AE5" s="17"/>
-      <c r="AF5" s="17"/>
-      <c r="AG5" s="16">
-        <v>11.573017</v>
-      </c>
-      <c r="AH5" s="16">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="16">
-        <v>576.81126900000004</v>
-      </c>
-      <c r="AJ5" s="16">
-        <v>0</v>
+      <c r="AF5" s="16"/>
+      <c r="AG5" s="16"/>
+      <c r="AH5" s="16"/>
+      <c r="AI5" s="16"/>
+      <c r="AK5" s="1" t="str">
+        <f>B5</f>
+        <v>Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="AL5" s="1" t="str">
-        <f>B5</f>
-        <v>CA_Synthetic_Ethylene_CCS_90</v>
-      </c>
-      <c r="AM5" s="1" t="str">
         <f>C5</f>
         <v>CO2Captured</v>
       </c>
+      <c r="AM5" s="12">
+        <f>SUM(AS5:AZ5)+BB5+BC5</f>
+        <v>491.18316495374813</v>
+      </c>
       <c r="AN5" s="12">
-        <f>SUM(AT5:BA5)+BC5+BD5</f>
-        <v>994.04783885392965</v>
-      </c>
-      <c r="AO5" s="12">
-        <f>SUM(AT5:BA5)+BF5+BG5</f>
-        <v>994.04783885392965</v>
-      </c>
-      <c r="AP5" s="5">
-        <f t="shared" si="0"/>
+        <f>SUM(AS5:AZ5)+BE5+BF5</f>
+        <v>491.18316495374813</v>
+      </c>
+      <c r="AO5" s="5">
+        <f>AM5-AN5</f>
         <v>0</v>
       </c>
+      <c r="AP5" s="12">
+        <f>SUM(AS5:AZ5)+BH5+BI5</f>
+        <v>538.67601721659707</v>
+      </c>
       <c r="AQ5" s="12">
-        <f>SUM(AT5:BA5)+BI5+BJ5</f>
-        <v>994.04783885392965</v>
-      </c>
-      <c r="AR5" s="12">
-        <f>SUM(AT5:BA5)+BL5+BM5</f>
-        <v>994.04783885392965</v>
+        <f>SUM(AS5:AZ5)+BK5+BL5</f>
+        <v>538.67601721659707</v>
+      </c>
+      <c r="AR5" s="5">
+        <f>AP5-AQ5</f>
+        <v>0</v>
       </c>
       <c r="AS5" s="5">
-        <f t="shared" si="1"/>
+        <f>E5/G5*X5</f>
         <v>0</v>
       </c>
-      <c r="AT5" s="5">
-        <f>D5/F5*Y5</f>
-        <v>421.42003753409836</v>
+      <c r="AT5" s="1">
+        <f>F5/G5*W5</f>
+        <v>0</v>
       </c>
       <c r="AU5" s="1">
-        <f>E5/F5*X5</f>
-        <v>50.01214473228999</v>
+        <f>1/G5*T5</f>
+        <v>177.53998910942985</v>
       </c>
       <c r="AV5" s="1">
-        <f>1/F5*U5</f>
-        <v>177.53998910942985</v>
+        <f>H5/G5*AF5*-1</f>
+        <v>0</v>
       </c>
       <c r="AW5" s="1">
-        <f>G5/F5*AG5*-1</f>
-        <v>-16.06036062905569</v>
+        <f>I5/G5*Z5</f>
+        <v>0</v>
       </c>
       <c r="AX5" s="1">
-        <f>H5/F5*AA5</f>
+        <f>K5/G5/(0.9*8760)</f>
+        <v>214.57390798665784</v>
+      </c>
+      <c r="AY5" s="1">
+        <f>L5/G5/(0.9*8760)</f>
+        <v>117.95601601844012</v>
+      </c>
+      <c r="AZ5" s="1">
+        <f>M5/G5</f>
+        <v>28.606104102069256</v>
+      </c>
+      <c r="BA5" s="1">
+        <f>BW5+BX5+BZ5-BT5</f>
+        <v>-0.38885408131599997</v>
+      </c>
+      <c r="BB5" s="1">
         <v>0</v>
       </c>
-      <c r="AY5" s="1">
-        <f>J5/F5/(0.9*8760)</f>
-        <v>214.57390798665784</v>
-      </c>
-      <c r="AZ5" s="1">
-        <f>K5/F5/(0.9*8760)</f>
-        <v>117.95601601844012</v>
-      </c>
-      <c r="BA5" s="1">
-        <f>L5/F5</f>
-        <v>28.606104102069256</v>
-      </c>
-      <c r="BO5" s="9">
-        <f>$CF$3</f>
+      <c r="BC5" s="1">
+        <f>BA5*O5</f>
+        <v>-47.492852262848913</v>
+      </c>
+      <c r="BD5" s="1">
+        <f>BW5+BX5+BZ5-BT5</f>
+        <v>-0.38885408131599997</v>
+      </c>
+      <c r="BE5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="1">
+        <f>BD5*O5</f>
+        <v>-47.492852262848913</v>
+      </c>
+      <c r="BG5" s="1">
+        <f>BV5+BW5+BX5+BZ5-BT5</f>
+        <v>0</v>
+      </c>
+      <c r="BH5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="1">
+        <f>BG5*O5</f>
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="1">
+        <f>BV5+BW5+BX5+BZ5-BT5</f>
+        <v>0</v>
+      </c>
+      <c r="BK5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL5" s="1">
+        <f>BJ5*O5</f>
+        <v>0</v>
+      </c>
+      <c r="BN5" s="9">
+        <f>$CE$3</f>
         <v>3.14</v>
       </c>
-      <c r="BP5" s="10">
-        <f>$CF$4</f>
+      <c r="BO5" s="10">
+        <f>$CE$4</f>
         <v>0.24123847100000001</v>
       </c>
+      <c r="BP5" s="9">
+        <f>$CE$5</f>
+        <v>0.18104824</v>
+      </c>
       <c r="BQ5" s="9">
-        <f>$CF$5</f>
+        <f>$CE$6</f>
+        <v>1.5714285714285715E-2</v>
+      </c>
+      <c r="BS5" s="10">
+        <v>1</v>
+      </c>
+      <c r="BT5" s="10">
+        <f>BS5-BY5</f>
+        <v>0.65871234168504667</v>
+      </c>
+      <c r="BV5" s="10">
+        <f>BN5*G5</f>
+        <v>0.38885408131600002</v>
+      </c>
+      <c r="BW5" s="10">
+        <f>BP5*H5</f>
+        <v>3.1114299132937305E-2</v>
+      </c>
+      <c r="BX5" s="10">
+        <f>(BS5-BV5-BW5-BZ5)*(1-D5)</f>
+        <v>3.7920850923883698E-2</v>
+      </c>
+      <c r="BY5" s="10">
+        <f>(BS5-BV5-BW5-BZ5)*(D5)</f>
+        <v>0.34128765831495339</v>
+      </c>
+      <c r="BZ5" s="10">
+        <f>BO5*I5</f>
+        <v>0.20082311031222566</v>
+      </c>
+      <c r="CA5" s="10">
+        <f>BV5+BW5+BX5+BZ5</f>
+        <v>0.65871234168504667</v>
+      </c>
+      <c r="CB5" s="10">
+        <f>SUM(BV5:BZ5)</f>
+        <v>1</v>
+      </c>
+      <c r="CD5" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="CE5" s="19">
         <v>0.18104824</v>
       </c>
-      <c r="BR5" s="9">
-        <f>$CF$6</f>
-        <v>1.5714285714285715E-2</v>
-      </c>
-      <c r="BT5" s="10">
-        <v>1</v>
-      </c>
-      <c r="BU5" s="10"/>
-      <c r="BW5" s="10">
-        <f>BO5*F5</f>
-        <v>0.38885408131600002</v>
-      </c>
-      <c r="BX5" s="10">
-        <f>BQ5*G5</f>
-        <v>3.1114299132937305E-2</v>
-      </c>
-      <c r="BY5" s="10">
-        <f>I5</f>
-        <v>0.37885468500000002</v>
-      </c>
-      <c r="BZ5" s="10"/>
-      <c r="CA5" s="10">
-        <f>BT5-SUM(BW5:BY5)</f>
-        <v>0.20117693455106267</v>
-      </c>
-      <c r="CB5" s="10">
-        <f>BP5*H5</f>
-        <v>0</v>
-      </c>
-      <c r="CC5" s="10"/>
-      <c r="CE5" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="CF5" s="19">
-        <v>0.18104824</v>
-      </c>
-      <c r="CG5" s="19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="2:85" x14ac:dyDescent="0.2">
+      <c r="CF5" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B6" s="14"/>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -1591,60 +1674,59 @@
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
       <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
+      <c r="O6" s="16"/>
       <c r="P6" s="16"/>
       <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
       <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="17"/>
       <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
+      <c r="W6" s="16"/>
       <c r="X6" s="16"/>
       <c r="Y6" s="16"/>
-      <c r="Z6" s="16"/>
+      <c r="Z6" s="17"/>
       <c r="AA6" s="17"/>
       <c r="AB6" s="17"/>
       <c r="AC6" s="17"/>
       <c r="AD6" s="17"/>
       <c r="AE6" s="17"/>
-      <c r="AF6" s="17"/>
+      <c r="AF6" s="16"/>
       <c r="AG6" s="16"/>
       <c r="AH6" s="16"/>
       <c r="AI6" s="16"/>
-      <c r="AJ6" s="16"/>
+      <c r="AM6" s="12"/>
       <c r="AN6" s="12"/>
-      <c r="AO6" s="12"/>
-      <c r="AP6" s="5"/>
+      <c r="AO6" s="5"/>
+      <c r="AP6" s="12"/>
       <c r="AQ6" s="12"/>
-      <c r="AR6" s="12"/>
+      <c r="AR6" s="5"/>
       <c r="AS6" s="5"/>
-      <c r="AT6" s="5"/>
-      <c r="BO6" s="9"/>
-      <c r="BP6" s="10"/>
+      <c r="BN6" s="9"/>
+      <c r="BO6" s="10"/>
+      <c r="BP6" s="9"/>
       <c r="BQ6" s="9"/>
-      <c r="BR6" s="9"/>
+      <c r="BS6" s="10"/>
       <c r="BT6" s="10"/>
-      <c r="BU6" s="10"/>
+      <c r="BV6" s="10"/>
       <c r="BW6" s="10"/>
       <c r="BX6" s="10"/>
       <c r="BY6" s="10"/>
       <c r="BZ6" s="10"/>
       <c r="CA6" s="10"/>
       <c r="CB6" s="10"/>
-      <c r="CC6" s="10"/>
-      <c r="CE6" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="CF6" s="19">
+      <c r="CD6" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="CE6" s="19">
         <f>0.22/14</f>
         <v>1.5714285714285715E-2</v>
       </c>
-      <c r="CG6" s="19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="2:85" x14ac:dyDescent="0.2">
+      <c r="CF6" s="19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B7" s="14"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -1657,59 +1739,58 @@
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
       <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
+      <c r="O7" s="16"/>
       <c r="P7" s="16"/>
       <c r="Q7" s="16"/>
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="17"/>
       <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
+      <c r="W7" s="16"/>
       <c r="X7" s="16"/>
       <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
+      <c r="Z7" s="17"/>
       <c r="AA7" s="17"/>
       <c r="AB7" s="17"/>
       <c r="AC7" s="17"/>
       <c r="AD7" s="17"/>
       <c r="AE7" s="17"/>
-      <c r="AF7" s="17"/>
+      <c r="AF7" s="16"/>
       <c r="AG7" s="16"/>
       <c r="AH7" s="16"/>
       <c r="AI7" s="16"/>
-      <c r="AJ7" s="16"/>
+      <c r="AM7" s="12"/>
       <c r="AN7" s="12"/>
-      <c r="AO7" s="12"/>
-      <c r="AP7" s="5"/>
+      <c r="AO7" s="5"/>
+      <c r="AP7" s="12"/>
       <c r="AQ7" s="12"/>
-      <c r="AR7" s="12"/>
+      <c r="AR7" s="5"/>
       <c r="AS7" s="5"/>
-      <c r="AT7" s="5"/>
-      <c r="BO7" s="9"/>
-      <c r="BP7" s="10"/>
+      <c r="BN7" s="9"/>
+      <c r="BO7" s="10"/>
+      <c r="BP7" s="9"/>
       <c r="BQ7" s="9"/>
-      <c r="BR7" s="9"/>
+      <c r="BS7" s="10"/>
       <c r="BT7" s="10"/>
-      <c r="BU7" s="10"/>
+      <c r="BV7" s="10"/>
       <c r="BW7" s="10"/>
       <c r="BX7" s="10"/>
       <c r="BY7" s="10"/>
       <c r="BZ7" s="10"/>
       <c r="CA7" s="10"/>
       <c r="CB7" s="10"/>
-      <c r="CC7" s="10"/>
-      <c r="CE7" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="CF7" s="19">
+      <c r="CD7" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="CE7" s="19">
         <v>0.9</v>
       </c>
-      <c r="CG7" s="19" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="2:85" x14ac:dyDescent="0.2">
+      <c r="CF7" s="19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B8" s="14"/>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -1722,50 +1803,49 @@
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
+      <c r="O8" s="16"/>
       <c r="P8" s="16"/>
       <c r="Q8" s="16"/>
       <c r="R8" s="16"/>
       <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="17"/>
       <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
+      <c r="W8" s="16"/>
       <c r="X8" s="16"/>
       <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
+      <c r="Z8" s="17"/>
       <c r="AA8" s="17"/>
       <c r="AB8" s="17"/>
       <c r="AC8" s="17"/>
       <c r="AD8" s="17"/>
       <c r="AE8" s="17"/>
-      <c r="AF8" s="17"/>
+      <c r="AF8" s="16"/>
       <c r="AG8" s="16"/>
       <c r="AH8" s="16"/>
       <c r="AI8" s="16"/>
-      <c r="AJ8" s="16"/>
+      <c r="AM8" s="12"/>
       <c r="AN8" s="12"/>
-      <c r="AO8" s="12"/>
-      <c r="AP8" s="5"/>
+      <c r="AO8" s="5"/>
+      <c r="AP8" s="12"/>
       <c r="AQ8" s="12"/>
-      <c r="AR8" s="12"/>
+      <c r="AR8" s="5"/>
       <c r="AS8" s="5"/>
-      <c r="AT8" s="5"/>
-      <c r="BO8" s="9"/>
-      <c r="BP8" s="10"/>
+      <c r="BN8" s="9"/>
+      <c r="BO8" s="10"/>
+      <c r="BP8" s="9"/>
       <c r="BQ8" s="9"/>
-      <c r="BR8" s="9"/>
+      <c r="BS8" s="10"/>
       <c r="BT8" s="10"/>
-      <c r="BU8" s="10"/>
+      <c r="BV8" s="10"/>
       <c r="BW8" s="10"/>
       <c r="BX8" s="10"/>
       <c r="BY8" s="10"/>
       <c r="BZ8" s="10"/>
       <c r="CA8" s="10"/>
       <c r="CB8" s="10"/>
-      <c r="CC8" s="10"/>
-    </row>
-    <row r="9" spans="2:85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B9" s="14"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -1778,50 +1858,49 @@
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
+      <c r="O9" s="16"/>
       <c r="P9" s="16"/>
       <c r="Q9" s="16"/>
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="17"/>
       <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
+      <c r="W9" s="16"/>
       <c r="X9" s="16"/>
       <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
+      <c r="Z9" s="17"/>
       <c r="AA9" s="17"/>
       <c r="AB9" s="17"/>
       <c r="AC9" s="17"/>
       <c r="AD9" s="17"/>
       <c r="AE9" s="17"/>
-      <c r="AF9" s="17"/>
+      <c r="AF9" s="16"/>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AI9" s="16"/>
-      <c r="AJ9" s="16"/>
+      <c r="AM9" s="12"/>
       <c r="AN9" s="12"/>
-      <c r="AO9" s="12"/>
-      <c r="AP9" s="5"/>
+      <c r="AO9" s="5"/>
+      <c r="AP9" s="12"/>
       <c r="AQ9" s="12"/>
-      <c r="AR9" s="12"/>
+      <c r="AR9" s="5"/>
       <c r="AS9" s="5"/>
-      <c r="AT9" s="5"/>
-      <c r="BO9" s="9"/>
-      <c r="BP9" s="10"/>
+      <c r="BN9" s="9"/>
+      <c r="BO9" s="10"/>
+      <c r="BP9" s="9"/>
       <c r="BQ9" s="9"/>
-      <c r="BR9" s="9"/>
+      <c r="BS9" s="10"/>
       <c r="BT9" s="10"/>
-      <c r="BU9" s="10"/>
+      <c r="BV9" s="10"/>
       <c r="BW9" s="10"/>
       <c r="BX9" s="10"/>
       <c r="BY9" s="10"/>
       <c r="BZ9" s="10"/>
       <c r="CA9" s="10"/>
       <c r="CB9" s="10"/>
-      <c r="CC9" s="10"/>
-    </row>
-    <row r="10" spans="2:85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B10" s="14"/>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
@@ -1834,50 +1913,49 @@
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
+      <c r="O10" s="16"/>
       <c r="P10" s="16"/>
       <c r="Q10" s="16"/>
       <c r="R10" s="16"/>
       <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="17"/>
       <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
+      <c r="W10" s="16"/>
       <c r="X10" s="16"/>
       <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
+      <c r="Z10" s="17"/>
       <c r="AA10" s="17"/>
       <c r="AB10" s="17"/>
       <c r="AC10" s="17"/>
       <c r="AD10" s="17"/>
       <c r="AE10" s="17"/>
-      <c r="AF10" s="17"/>
+      <c r="AF10" s="16"/>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AI10" s="16"/>
-      <c r="AJ10" s="16"/>
+      <c r="AM10" s="12"/>
       <c r="AN10" s="12"/>
-      <c r="AO10" s="12"/>
-      <c r="AP10" s="5"/>
+      <c r="AO10" s="5"/>
+      <c r="AP10" s="12"/>
       <c r="AQ10" s="12"/>
-      <c r="AR10" s="12"/>
+      <c r="AR10" s="5"/>
       <c r="AS10" s="5"/>
-      <c r="AT10" s="5"/>
-      <c r="BO10" s="9"/>
-      <c r="BP10" s="10"/>
+      <c r="BN10" s="9"/>
+      <c r="BO10" s="10"/>
+      <c r="BP10" s="9"/>
       <c r="BQ10" s="9"/>
-      <c r="BR10" s="9"/>
+      <c r="BS10" s="10"/>
       <c r="BT10" s="10"/>
-      <c r="BU10" s="10"/>
+      <c r="BV10" s="10"/>
       <c r="BW10" s="10"/>
       <c r="BX10" s="10"/>
       <c r="BY10" s="10"/>
       <c r="BZ10" s="10"/>
       <c r="CA10" s="10"/>
       <c r="CB10" s="10"/>
-      <c r="CC10" s="10"/>
-    </row>
-    <row r="11" spans="2:85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B11" s="14"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
@@ -1890,50 +1968,49 @@
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
       <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
+      <c r="O11" s="16"/>
       <c r="P11" s="16"/>
       <c r="Q11" s="16"/>
       <c r="R11" s="16"/>
       <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="17"/>
       <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
+      <c r="W11" s="16"/>
       <c r="X11" s="16"/>
       <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
+      <c r="Z11" s="17"/>
       <c r="AA11" s="17"/>
       <c r="AB11" s="17"/>
       <c r="AC11" s="17"/>
       <c r="AD11" s="17"/>
       <c r="AE11" s="17"/>
-      <c r="AF11" s="17"/>
+      <c r="AF11" s="16"/>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AI11" s="16"/>
-      <c r="AJ11" s="16"/>
+      <c r="AM11" s="12"/>
       <c r="AN11" s="12"/>
-      <c r="AO11" s="12"/>
-      <c r="AP11" s="5"/>
+      <c r="AO11" s="5"/>
+      <c r="AP11" s="12"/>
       <c r="AQ11" s="12"/>
-      <c r="AR11" s="12"/>
+      <c r="AR11" s="5"/>
       <c r="AS11" s="5"/>
-      <c r="AT11" s="5"/>
-      <c r="BO11" s="9"/>
-      <c r="BP11" s="10"/>
+      <c r="BN11" s="9"/>
+      <c r="BO11" s="10"/>
+      <c r="BP11" s="9"/>
       <c r="BQ11" s="9"/>
-      <c r="BR11" s="9"/>
+      <c r="BS11" s="10"/>
       <c r="BT11" s="10"/>
-      <c r="BU11" s="10"/>
+      <c r="BV11" s="10"/>
       <c r="BW11" s="10"/>
       <c r="BX11" s="10"/>
       <c r="BY11" s="10"/>
       <c r="BZ11" s="10"/>
       <c r="CA11" s="10"/>
       <c r="CB11" s="10"/>
-      <c r="CC11" s="10"/>
-    </row>
-    <row r="12" spans="2:85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B12" s="14"/>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -1946,50 +2023,49 @@
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
+      <c r="O12" s="16"/>
       <c r="P12" s="16"/>
       <c r="Q12" s="16"/>
       <c r="R12" s="16"/>
       <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="17"/>
       <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
+      <c r="W12" s="16"/>
       <c r="X12" s="16"/>
       <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
+      <c r="Z12" s="17"/>
       <c r="AA12" s="17"/>
       <c r="AB12" s="17"/>
       <c r="AC12" s="17"/>
       <c r="AD12" s="17"/>
       <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
+      <c r="AF12" s="16"/>
       <c r="AG12" s="16"/>
       <c r="AH12" s="16"/>
       <c r="AI12" s="16"/>
-      <c r="AJ12" s="16"/>
+      <c r="AM12" s="12"/>
       <c r="AN12" s="12"/>
-      <c r="AO12" s="12"/>
-      <c r="AP12" s="5"/>
+      <c r="AO12" s="5"/>
+      <c r="AP12" s="12"/>
       <c r="AQ12" s="12"/>
-      <c r="AR12" s="12"/>
+      <c r="AR12" s="5"/>
       <c r="AS12" s="5"/>
-      <c r="AT12" s="5"/>
-      <c r="BO12" s="9"/>
-      <c r="BP12" s="10"/>
+      <c r="BN12" s="9"/>
+      <c r="BO12" s="10"/>
+      <c r="BP12" s="9"/>
       <c r="BQ12" s="9"/>
-      <c r="BR12" s="9"/>
+      <c r="BS12" s="10"/>
       <c r="BT12" s="10"/>
-      <c r="BU12" s="10"/>
+      <c r="BV12" s="10"/>
       <c r="BW12" s="10"/>
       <c r="BX12" s="10"/>
       <c r="BY12" s="10"/>
       <c r="BZ12" s="10"/>
       <c r="CA12" s="10"/>
       <c r="CB12" s="10"/>
-      <c r="CC12" s="10"/>
-    </row>
-    <row r="13" spans="2:85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B13" s="14"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -2002,50 +2078,49 @@
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
+      <c r="O13" s="16"/>
       <c r="P13" s="16"/>
       <c r="Q13" s="16"/>
       <c r="R13" s="16"/>
       <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="17"/>
       <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
+      <c r="W13" s="16"/>
       <c r="X13" s="16"/>
       <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
+      <c r="Z13" s="17"/>
       <c r="AA13" s="17"/>
       <c r="AB13" s="17"/>
       <c r="AC13" s="17"/>
       <c r="AD13" s="17"/>
       <c r="AE13" s="17"/>
-      <c r="AF13" s="17"/>
+      <c r="AF13" s="16"/>
       <c r="AG13" s="16"/>
       <c r="AH13" s="16"/>
       <c r="AI13" s="16"/>
-      <c r="AJ13" s="16"/>
+      <c r="AM13" s="12"/>
       <c r="AN13" s="12"/>
-      <c r="AO13" s="12"/>
-      <c r="AP13" s="5"/>
+      <c r="AO13" s="5"/>
+      <c r="AP13" s="12"/>
       <c r="AQ13" s="12"/>
-      <c r="AR13" s="12"/>
+      <c r="AR13" s="5"/>
       <c r="AS13" s="5"/>
-      <c r="AT13" s="5"/>
-      <c r="BO13" s="9"/>
-      <c r="BP13" s="10"/>
+      <c r="BN13" s="9"/>
+      <c r="BO13" s="10"/>
+      <c r="BP13" s="9"/>
       <c r="BQ13" s="9"/>
-      <c r="BR13" s="9"/>
+      <c r="BS13" s="10"/>
       <c r="BT13" s="10"/>
-      <c r="BU13" s="10"/>
+      <c r="BV13" s="10"/>
       <c r="BW13" s="10"/>
       <c r="BX13" s="10"/>
       <c r="BY13" s="10"/>
       <c r="BZ13" s="10"/>
       <c r="CA13" s="10"/>
       <c r="CB13" s="10"/>
-      <c r="CC13" s="10"/>
-    </row>
-    <row r="14" spans="2:85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B14" s="14"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -2058,50 +2133,49 @@
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
       <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
+      <c r="O14" s="16"/>
       <c r="P14" s="16"/>
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="17"/>
       <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
+      <c r="W14" s="16"/>
       <c r="X14" s="16"/>
       <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
+      <c r="Z14" s="17"/>
       <c r="AA14" s="17"/>
       <c r="AB14" s="17"/>
       <c r="AC14" s="17"/>
       <c r="AD14" s="17"/>
       <c r="AE14" s="17"/>
-      <c r="AF14" s="17"/>
+      <c r="AF14" s="16"/>
       <c r="AG14" s="16"/>
       <c r="AH14" s="16"/>
       <c r="AI14" s="16"/>
-      <c r="AJ14" s="16"/>
+      <c r="AM14" s="12"/>
       <c r="AN14" s="12"/>
-      <c r="AO14" s="12"/>
-      <c r="AP14" s="5"/>
+      <c r="AO14" s="5"/>
+      <c r="AP14" s="12"/>
       <c r="AQ14" s="12"/>
-      <c r="AR14" s="12"/>
+      <c r="AR14" s="5"/>
       <c r="AS14" s="5"/>
-      <c r="AT14" s="5"/>
-      <c r="BO14" s="9"/>
-      <c r="BP14" s="10"/>
+      <c r="BN14" s="9"/>
+      <c r="BO14" s="10"/>
+      <c r="BP14" s="9"/>
       <c r="BQ14" s="9"/>
-      <c r="BR14" s="9"/>
+      <c r="BS14" s="10"/>
       <c r="BT14" s="10"/>
-      <c r="BU14" s="10"/>
+      <c r="BV14" s="10"/>
       <c r="BW14" s="10"/>
       <c r="BX14" s="10"/>
       <c r="BY14" s="10"/>
       <c r="BZ14" s="10"/>
       <c r="CA14" s="10"/>
       <c r="CB14" s="10"/>
-      <c r="CC14" s="10"/>
-    </row>
-    <row r="15" spans="2:85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B15" s="14"/>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
@@ -2114,50 +2188,49 @@
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
+      <c r="O15" s="16"/>
       <c r="P15" s="16"/>
       <c r="Q15" s="16"/>
       <c r="R15" s="16"/>
       <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="17"/>
       <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
+      <c r="W15" s="16"/>
       <c r="X15" s="16"/>
       <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
+      <c r="Z15" s="17"/>
       <c r="AA15" s="17"/>
       <c r="AB15" s="17"/>
       <c r="AC15" s="17"/>
       <c r="AD15" s="17"/>
       <c r="AE15" s="17"/>
-      <c r="AF15" s="17"/>
+      <c r="AF15" s="16"/>
       <c r="AG15" s="16"/>
       <c r="AH15" s="16"/>
       <c r="AI15" s="16"/>
-      <c r="AJ15" s="16"/>
+      <c r="AM15" s="12"/>
       <c r="AN15" s="12"/>
-      <c r="AO15" s="12"/>
-      <c r="AP15" s="5"/>
+      <c r="AO15" s="5"/>
+      <c r="AP15" s="12"/>
       <c r="AQ15" s="12"/>
-      <c r="AR15" s="12"/>
+      <c r="AR15" s="5"/>
       <c r="AS15" s="5"/>
-      <c r="AT15" s="5"/>
-      <c r="BO15" s="9"/>
-      <c r="BP15" s="10"/>
+      <c r="BN15" s="9"/>
+      <c r="BO15" s="10"/>
+      <c r="BP15" s="9"/>
       <c r="BQ15" s="9"/>
-      <c r="BR15" s="9"/>
+      <c r="BS15" s="10"/>
       <c r="BT15" s="10"/>
-      <c r="BU15" s="10"/>
+      <c r="BV15" s="10"/>
       <c r="BW15" s="10"/>
       <c r="BX15" s="10"/>
       <c r="BY15" s="10"/>
       <c r="BZ15" s="10"/>
       <c r="CA15" s="10"/>
       <c r="CB15" s="10"/>
-      <c r="CC15" s="10"/>
-    </row>
-    <row r="16" spans="2:85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B16" s="14"/>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
@@ -2170,50 +2243,49 @@
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
+      <c r="O16" s="16"/>
       <c r="P16" s="16"/>
       <c r="Q16" s="16"/>
       <c r="R16" s="16"/>
       <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="17"/>
       <c r="V16" s="17"/>
-      <c r="W16" s="17"/>
+      <c r="W16" s="16"/>
       <c r="X16" s="16"/>
       <c r="Y16" s="16"/>
-      <c r="Z16" s="16"/>
+      <c r="Z16" s="17"/>
       <c r="AA16" s="17"/>
       <c r="AB16" s="17"/>
       <c r="AC16" s="17"/>
       <c r="AD16" s="17"/>
       <c r="AE16" s="17"/>
-      <c r="AF16" s="17"/>
+      <c r="AF16" s="16"/>
       <c r="AG16" s="16"/>
       <c r="AH16" s="16"/>
       <c r="AI16" s="16"/>
-      <c r="AJ16" s="16"/>
+      <c r="AM16" s="12"/>
       <c r="AN16" s="12"/>
-      <c r="AO16" s="12"/>
-      <c r="AP16" s="5"/>
+      <c r="AO16" s="5"/>
+      <c r="AP16" s="12"/>
       <c r="AQ16" s="12"/>
-      <c r="AR16" s="12"/>
+      <c r="AR16" s="5"/>
       <c r="AS16" s="5"/>
-      <c r="AT16" s="5"/>
-      <c r="BO16" s="9"/>
-      <c r="BP16" s="10"/>
+      <c r="BN16" s="9"/>
+      <c r="BO16" s="10"/>
+      <c r="BP16" s="9"/>
       <c r="BQ16" s="9"/>
-      <c r="BR16" s="9"/>
+      <c r="BS16" s="10"/>
       <c r="BT16" s="10"/>
-      <c r="BU16" s="10"/>
+      <c r="BV16" s="10"/>
       <c r="BW16" s="10"/>
       <c r="BX16" s="10"/>
       <c r="BY16" s="10"/>
       <c r="BZ16" s="10"/>
       <c r="CA16" s="10"/>
       <c r="CB16" s="10"/>
-      <c r="CC16" s="10"/>
-    </row>
-    <row r="17" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B17" s="14"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
@@ -2226,50 +2298,49 @@
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
+      <c r="O17" s="16"/>
       <c r="P17" s="16"/>
       <c r="Q17" s="16"/>
       <c r="R17" s="16"/>
       <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="17"/>
       <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
+      <c r="W17" s="16"/>
       <c r="X17" s="16"/>
       <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
+      <c r="Z17" s="17"/>
       <c r="AA17" s="17"/>
       <c r="AB17" s="17"/>
       <c r="AC17" s="17"/>
       <c r="AD17" s="17"/>
       <c r="AE17" s="17"/>
-      <c r="AF17" s="17"/>
+      <c r="AF17" s="16"/>
       <c r="AG17" s="16"/>
       <c r="AH17" s="16"/>
       <c r="AI17" s="16"/>
-      <c r="AJ17" s="16"/>
+      <c r="AM17" s="12"/>
       <c r="AN17" s="12"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="5"/>
+      <c r="AO17" s="5"/>
+      <c r="AP17" s="12"/>
       <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
+      <c r="AR17" s="5"/>
       <c r="AS17" s="5"/>
-      <c r="AT17" s="5"/>
-      <c r="BO17" s="9"/>
-      <c r="BP17" s="10"/>
+      <c r="BN17" s="9"/>
+      <c r="BO17" s="10"/>
+      <c r="BP17" s="9"/>
       <c r="BQ17" s="9"/>
-      <c r="BR17" s="9"/>
+      <c r="BS17" s="10"/>
       <c r="BT17" s="10"/>
-      <c r="BU17" s="10"/>
+      <c r="BV17" s="10"/>
       <c r="BW17" s="10"/>
       <c r="BX17" s="10"/>
       <c r="BY17" s="10"/>
       <c r="BZ17" s="10"/>
       <c r="CA17" s="10"/>
       <c r="CB17" s="10"/>
-      <c r="CC17" s="10"/>
-    </row>
-    <row r="18" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B18" s="14"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -2282,50 +2353,49 @@
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
+      <c r="O18" s="16"/>
       <c r="P18" s="16"/>
       <c r="Q18" s="16"/>
       <c r="R18" s="16"/>
       <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="17"/>
       <c r="V18" s="17"/>
-      <c r="W18" s="17"/>
+      <c r="W18" s="16"/>
       <c r="X18" s="16"/>
       <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
+      <c r="Z18" s="17"/>
       <c r="AA18" s="17"/>
       <c r="AB18" s="17"/>
       <c r="AC18" s="17"/>
       <c r="AD18" s="17"/>
       <c r="AE18" s="17"/>
-      <c r="AF18" s="17"/>
+      <c r="AF18" s="16"/>
       <c r="AG18" s="16"/>
       <c r="AH18" s="16"/>
       <c r="AI18" s="16"/>
-      <c r="AJ18" s="16"/>
+      <c r="AM18" s="12"/>
       <c r="AN18" s="12"/>
-      <c r="AO18" s="12"/>
-      <c r="AP18" s="5"/>
+      <c r="AO18" s="5"/>
+      <c r="AP18" s="12"/>
       <c r="AQ18" s="12"/>
-      <c r="AR18" s="12"/>
+      <c r="AR18" s="5"/>
       <c r="AS18" s="5"/>
-      <c r="AT18" s="5"/>
-      <c r="BO18" s="9"/>
-      <c r="BP18" s="10"/>
+      <c r="BN18" s="9"/>
+      <c r="BO18" s="10"/>
+      <c r="BP18" s="9"/>
       <c r="BQ18" s="9"/>
-      <c r="BR18" s="9"/>
+      <c r="BS18" s="10"/>
       <c r="BT18" s="10"/>
-      <c r="BU18" s="10"/>
+      <c r="BV18" s="10"/>
       <c r="BW18" s="10"/>
       <c r="BX18" s="10"/>
       <c r="BY18" s="10"/>
       <c r="BZ18" s="10"/>
       <c r="CA18" s="10"/>
       <c r="CB18" s="10"/>
-      <c r="CC18" s="10"/>
-    </row>
-    <row r="19" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B19" s="14"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -2338,50 +2408,49 @@
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
+      <c r="O19" s="16"/>
       <c r="P19" s="16"/>
       <c r="Q19" s="16"/>
       <c r="R19" s="16"/>
       <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="17"/>
       <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
+      <c r="W19" s="16"/>
       <c r="X19" s="16"/>
       <c r="Y19" s="16"/>
-      <c r="Z19" s="16"/>
+      <c r="Z19" s="17"/>
       <c r="AA19" s="17"/>
       <c r="AB19" s="17"/>
       <c r="AC19" s="17"/>
       <c r="AD19" s="17"/>
       <c r="AE19" s="17"/>
-      <c r="AF19" s="17"/>
+      <c r="AF19" s="16"/>
       <c r="AG19" s="16"/>
       <c r="AH19" s="16"/>
       <c r="AI19" s="16"/>
-      <c r="AJ19" s="16"/>
+      <c r="AM19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AO19" s="12"/>
-      <c r="AP19" s="5"/>
+      <c r="AO19" s="5"/>
+      <c r="AP19" s="12"/>
       <c r="AQ19" s="12"/>
-      <c r="AR19" s="12"/>
+      <c r="AR19" s="5"/>
       <c r="AS19" s="5"/>
-      <c r="AT19" s="5"/>
-      <c r="BO19" s="9"/>
-      <c r="BP19" s="10"/>
+      <c r="BN19" s="9"/>
+      <c r="BO19" s="10"/>
+      <c r="BP19" s="9"/>
       <c r="BQ19" s="9"/>
-      <c r="BR19" s="9"/>
+      <c r="BS19" s="10"/>
       <c r="BT19" s="10"/>
-      <c r="BU19" s="10"/>
+      <c r="BV19" s="10"/>
       <c r="BW19" s="10"/>
       <c r="BX19" s="10"/>
       <c r="BY19" s="10"/>
       <c r="BZ19" s="10"/>
       <c r="CA19" s="10"/>
       <c r="CB19" s="10"/>
-      <c r="CC19" s="10"/>
-    </row>
-    <row r="20" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B20" s="14"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -2394,50 +2463,49 @@
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
+      <c r="O20" s="16"/>
       <c r="P20" s="16"/>
       <c r="Q20" s="16"/>
       <c r="R20" s="16"/>
       <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="11"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="17"/>
       <c r="V20" s="17"/>
-      <c r="W20" s="17"/>
+      <c r="W20" s="16"/>
       <c r="X20" s="16"/>
       <c r="Y20" s="16"/>
-      <c r="Z20" s="16"/>
+      <c r="Z20" s="17"/>
       <c r="AA20" s="17"/>
       <c r="AB20" s="17"/>
       <c r="AC20" s="17"/>
       <c r="AD20" s="17"/>
       <c r="AE20" s="17"/>
-      <c r="AF20" s="17"/>
+      <c r="AF20" s="16"/>
       <c r="AG20" s="16"/>
       <c r="AH20" s="16"/>
       <c r="AI20" s="16"/>
-      <c r="AJ20" s="16"/>
+      <c r="AM20" s="12"/>
       <c r="AN20" s="12"/>
-      <c r="AO20" s="12"/>
-      <c r="AP20" s="5"/>
+      <c r="AO20" s="5"/>
+      <c r="AP20" s="12"/>
       <c r="AQ20" s="12"/>
-      <c r="AR20" s="12"/>
+      <c r="AR20" s="5"/>
       <c r="AS20" s="5"/>
-      <c r="AT20" s="5"/>
-      <c r="BO20" s="9"/>
-      <c r="BP20" s="10"/>
+      <c r="BN20" s="9"/>
+      <c r="BO20" s="10"/>
+      <c r="BP20" s="9"/>
       <c r="BQ20" s="9"/>
-      <c r="BR20" s="9"/>
+      <c r="BS20" s="10"/>
       <c r="BT20" s="10"/>
-      <c r="BU20" s="10"/>
+      <c r="BV20" s="10"/>
       <c r="BW20" s="10"/>
       <c r="BX20" s="10"/>
       <c r="BY20" s="10"/>
       <c r="BZ20" s="10"/>
       <c r="CA20" s="10"/>
       <c r="CB20" s="10"/>
-      <c r="CC20" s="10"/>
-    </row>
-    <row r="21" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B21" s="14"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -2450,50 +2518,49 @@
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
+      <c r="O21" s="16"/>
       <c r="P21" s="16"/>
       <c r="Q21" s="16"/>
       <c r="R21" s="16"/>
       <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="11"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="17"/>
       <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
+      <c r="W21" s="16"/>
       <c r="X21" s="16"/>
       <c r="Y21" s="16"/>
-      <c r="Z21" s="16"/>
+      <c r="Z21" s="17"/>
       <c r="AA21" s="17"/>
       <c r="AB21" s="17"/>
       <c r="AC21" s="17"/>
       <c r="AD21" s="17"/>
       <c r="AE21" s="17"/>
-      <c r="AF21" s="17"/>
+      <c r="AF21" s="16"/>
       <c r="AG21" s="16"/>
       <c r="AH21" s="16"/>
       <c r="AI21" s="16"/>
-      <c r="AJ21" s="16"/>
+      <c r="AM21" s="12"/>
       <c r="AN21" s="12"/>
-      <c r="AO21" s="12"/>
-      <c r="AP21" s="5"/>
+      <c r="AO21" s="5"/>
+      <c r="AP21" s="12"/>
       <c r="AQ21" s="12"/>
-      <c r="AR21" s="12"/>
+      <c r="AR21" s="5"/>
       <c r="AS21" s="5"/>
-      <c r="AT21" s="5"/>
-      <c r="BO21" s="9"/>
-      <c r="BP21" s="10"/>
+      <c r="BN21" s="9"/>
+      <c r="BO21" s="10"/>
+      <c r="BP21" s="9"/>
       <c r="BQ21" s="9"/>
-      <c r="BR21" s="9"/>
+      <c r="BS21" s="10"/>
       <c r="BT21" s="10"/>
-      <c r="BU21" s="10"/>
+      <c r="BV21" s="10"/>
       <c r="BW21" s="10"/>
       <c r="BX21" s="10"/>
       <c r="BY21" s="10"/>
       <c r="BZ21" s="10"/>
       <c r="CA21" s="10"/>
       <c r="CB21" s="10"/>
-      <c r="CC21" s="10"/>
-    </row>
-    <row r="22" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B22" s="14"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -2506,50 +2573,49 @@
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
+      <c r="O22" s="16"/>
       <c r="P22" s="16"/>
       <c r="Q22" s="16"/>
       <c r="R22" s="16"/>
       <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="17"/>
       <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
+      <c r="W22" s="16"/>
       <c r="X22" s="16"/>
       <c r="Y22" s="16"/>
-      <c r="Z22" s="16"/>
+      <c r="Z22" s="17"/>
       <c r="AA22" s="17"/>
       <c r="AB22" s="17"/>
       <c r="AC22" s="17"/>
       <c r="AD22" s="17"/>
       <c r="AE22" s="17"/>
-      <c r="AF22" s="17"/>
+      <c r="AF22" s="16"/>
       <c r="AG22" s="16"/>
       <c r="AH22" s="16"/>
       <c r="AI22" s="16"/>
-      <c r="AJ22" s="16"/>
+      <c r="AM22" s="12"/>
       <c r="AN22" s="12"/>
-      <c r="AO22" s="12"/>
-      <c r="AP22" s="5"/>
+      <c r="AO22" s="5"/>
+      <c r="AP22" s="12"/>
       <c r="AQ22" s="12"/>
-      <c r="AR22" s="12"/>
+      <c r="AR22" s="5"/>
       <c r="AS22" s="5"/>
-      <c r="AT22" s="5"/>
-      <c r="BO22" s="9"/>
-      <c r="BP22" s="10"/>
+      <c r="BN22" s="9"/>
+      <c r="BO22" s="10"/>
+      <c r="BP22" s="9"/>
       <c r="BQ22" s="9"/>
-      <c r="BR22" s="9"/>
+      <c r="BS22" s="10"/>
       <c r="BT22" s="10"/>
-      <c r="BU22" s="10"/>
+      <c r="BV22" s="10"/>
       <c r="BW22" s="10"/>
       <c r="BX22" s="10"/>
       <c r="BY22" s="10"/>
       <c r="BZ22" s="10"/>
       <c r="CA22" s="10"/>
       <c r="CB22" s="10"/>
-      <c r="CC22" s="10"/>
-    </row>
-    <row r="23" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B23" s="14"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -2562,50 +2628,49 @@
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
+      <c r="O23" s="16"/>
       <c r="P23" s="16"/>
       <c r="Q23" s="16"/>
       <c r="R23" s="16"/>
       <c r="S23" s="16"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="17"/>
       <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
+      <c r="W23" s="16"/>
       <c r="X23" s="16"/>
       <c r="Y23" s="16"/>
-      <c r="Z23" s="16"/>
+      <c r="Z23" s="17"/>
       <c r="AA23" s="17"/>
       <c r="AB23" s="17"/>
       <c r="AC23" s="17"/>
       <c r="AD23" s="17"/>
       <c r="AE23" s="17"/>
-      <c r="AF23" s="17"/>
+      <c r="AF23" s="16"/>
       <c r="AG23" s="16"/>
       <c r="AH23" s="16"/>
       <c r="AI23" s="16"/>
-      <c r="AJ23" s="16"/>
+      <c r="AM23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AO23" s="12"/>
-      <c r="AP23" s="5"/>
+      <c r="AO23" s="5"/>
+      <c r="AP23" s="12"/>
       <c r="AQ23" s="12"/>
-      <c r="AR23" s="12"/>
+      <c r="AR23" s="5"/>
       <c r="AS23" s="5"/>
-      <c r="AT23" s="5"/>
-      <c r="BO23" s="9"/>
-      <c r="BP23" s="10"/>
+      <c r="BN23" s="9"/>
+      <c r="BO23" s="10"/>
+      <c r="BP23" s="9"/>
       <c r="BQ23" s="9"/>
-      <c r="BR23" s="9"/>
+      <c r="BS23" s="10"/>
       <c r="BT23" s="10"/>
-      <c r="BU23" s="10"/>
+      <c r="BV23" s="10"/>
       <c r="BW23" s="10"/>
       <c r="BX23" s="10"/>
       <c r="BY23" s="10"/>
       <c r="BZ23" s="10"/>
       <c r="CA23" s="10"/>
       <c r="CB23" s="10"/>
-      <c r="CC23" s="10"/>
-    </row>
-    <row r="24" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B24" s="14"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -2618,50 +2683,49 @@
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
+      <c r="O24" s="16"/>
       <c r="P24" s="16"/>
       <c r="Q24" s="16"/>
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="17"/>
       <c r="V24" s="17"/>
-      <c r="W24" s="17"/>
+      <c r="W24" s="16"/>
       <c r="X24" s="16"/>
       <c r="Y24" s="16"/>
-      <c r="Z24" s="16"/>
+      <c r="Z24" s="17"/>
       <c r="AA24" s="17"/>
       <c r="AB24" s="17"/>
       <c r="AC24" s="17"/>
       <c r="AD24" s="17"/>
       <c r="AE24" s="17"/>
-      <c r="AF24" s="17"/>
+      <c r="AF24" s="16"/>
       <c r="AG24" s="16"/>
       <c r="AH24" s="16"/>
       <c r="AI24" s="16"/>
-      <c r="AJ24" s="16"/>
+      <c r="AM24" s="12"/>
       <c r="AN24" s="12"/>
-      <c r="AO24" s="12"/>
-      <c r="AP24" s="5"/>
+      <c r="AO24" s="5"/>
+      <c r="AP24" s="12"/>
       <c r="AQ24" s="12"/>
-      <c r="AR24" s="12"/>
+      <c r="AR24" s="5"/>
       <c r="AS24" s="5"/>
-      <c r="AT24" s="5"/>
-      <c r="BO24" s="9"/>
-      <c r="BP24" s="10"/>
+      <c r="BN24" s="9"/>
+      <c r="BO24" s="10"/>
+      <c r="BP24" s="9"/>
       <c r="BQ24" s="9"/>
-      <c r="BR24" s="9"/>
+      <c r="BS24" s="10"/>
       <c r="BT24" s="10"/>
-      <c r="BU24" s="10"/>
+      <c r="BV24" s="10"/>
       <c r="BW24" s="10"/>
       <c r="BX24" s="10"/>
       <c r="BY24" s="10"/>
       <c r="BZ24" s="10"/>
       <c r="CA24" s="10"/>
       <c r="CB24" s="10"/>
-      <c r="CC24" s="10"/>
-    </row>
-    <row r="25" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B25" s="14"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -2674,50 +2738,49 @@
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
+      <c r="O25" s="16"/>
       <c r="P25" s="16"/>
       <c r="Q25" s="16"/>
       <c r="R25" s="16"/>
       <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="17"/>
       <c r="V25" s="17"/>
-      <c r="W25" s="17"/>
+      <c r="W25" s="16"/>
       <c r="X25" s="16"/>
       <c r="Y25" s="16"/>
-      <c r="Z25" s="16"/>
+      <c r="Z25" s="17"/>
       <c r="AA25" s="17"/>
       <c r="AB25" s="17"/>
       <c r="AC25" s="17"/>
       <c r="AD25" s="17"/>
       <c r="AE25" s="17"/>
-      <c r="AF25" s="17"/>
+      <c r="AF25" s="16"/>
       <c r="AG25" s="16"/>
       <c r="AH25" s="16"/>
       <c r="AI25" s="16"/>
-      <c r="AJ25" s="16"/>
+      <c r="AM25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AO25" s="12"/>
-      <c r="AP25" s="5"/>
+      <c r="AO25" s="5"/>
+      <c r="AP25" s="12"/>
       <c r="AQ25" s="12"/>
-      <c r="AR25" s="12"/>
+      <c r="AR25" s="5"/>
       <c r="AS25" s="5"/>
-      <c r="AT25" s="5"/>
-      <c r="BO25" s="9"/>
-      <c r="BP25" s="10"/>
+      <c r="BN25" s="9"/>
+      <c r="BO25" s="10"/>
+      <c r="BP25" s="9"/>
       <c r="BQ25" s="9"/>
-      <c r="BR25" s="9"/>
+      <c r="BS25" s="10"/>
       <c r="BT25" s="10"/>
-      <c r="BU25" s="10"/>
+      <c r="BV25" s="10"/>
       <c r="BW25" s="10"/>
       <c r="BX25" s="10"/>
       <c r="BY25" s="10"/>
       <c r="BZ25" s="10"/>
       <c r="CA25" s="10"/>
       <c r="CB25" s="10"/>
-      <c r="CC25" s="10"/>
-    </row>
-    <row r="26" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B26" s="14"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -2730,50 +2793,49 @@
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
       <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
+      <c r="O26" s="16"/>
       <c r="P26" s="16"/>
       <c r="Q26" s="16"/>
       <c r="R26" s="16"/>
       <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="11"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="17"/>
       <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
+      <c r="W26" s="16"/>
       <c r="X26" s="16"/>
       <c r="Y26" s="16"/>
-      <c r="Z26" s="16"/>
+      <c r="Z26" s="17"/>
       <c r="AA26" s="17"/>
       <c r="AB26" s="17"/>
       <c r="AC26" s="17"/>
       <c r="AD26" s="17"/>
       <c r="AE26" s="17"/>
-      <c r="AF26" s="17"/>
+      <c r="AF26" s="16"/>
       <c r="AG26" s="16"/>
       <c r="AH26" s="16"/>
       <c r="AI26" s="16"/>
-      <c r="AJ26" s="16"/>
+      <c r="AM26" s="12"/>
       <c r="AN26" s="12"/>
-      <c r="AO26" s="12"/>
-      <c r="AP26" s="5"/>
+      <c r="AO26" s="5"/>
+      <c r="AP26" s="12"/>
       <c r="AQ26" s="12"/>
-      <c r="AR26" s="12"/>
+      <c r="AR26" s="5"/>
       <c r="AS26" s="5"/>
-      <c r="AT26" s="5"/>
-      <c r="BO26" s="9"/>
-      <c r="BP26" s="10"/>
+      <c r="BN26" s="9"/>
+      <c r="BO26" s="10"/>
+      <c r="BP26" s="9"/>
       <c r="BQ26" s="9"/>
-      <c r="BR26" s="9"/>
+      <c r="BS26" s="10"/>
       <c r="BT26" s="10"/>
-      <c r="BU26" s="10"/>
+      <c r="BV26" s="10"/>
       <c r="BW26" s="10"/>
       <c r="BX26" s="10"/>
       <c r="BY26" s="10"/>
       <c r="BZ26" s="10"/>
       <c r="CA26" s="10"/>
       <c r="CB26" s="10"/>
-      <c r="CC26" s="10"/>
-    </row>
-    <row r="27" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B27" s="14"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -2786,50 +2848,49 @@
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
       <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
+      <c r="O27" s="16"/>
       <c r="P27" s="16"/>
       <c r="Q27" s="16"/>
       <c r="R27" s="16"/>
       <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="11"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="17"/>
       <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
+      <c r="W27" s="16"/>
       <c r="X27" s="16"/>
       <c r="Y27" s="16"/>
-      <c r="Z27" s="16"/>
+      <c r="Z27" s="17"/>
       <c r="AA27" s="17"/>
       <c r="AB27" s="17"/>
       <c r="AC27" s="17"/>
       <c r="AD27" s="17"/>
       <c r="AE27" s="17"/>
-      <c r="AF27" s="17"/>
+      <c r="AF27" s="16"/>
       <c r="AG27" s="16"/>
       <c r="AH27" s="16"/>
       <c r="AI27" s="16"/>
-      <c r="AJ27" s="16"/>
+      <c r="AM27" s="12"/>
       <c r="AN27" s="12"/>
-      <c r="AO27" s="12"/>
-      <c r="AP27" s="5"/>
+      <c r="AO27" s="5"/>
+      <c r="AP27" s="12"/>
       <c r="AQ27" s="12"/>
-      <c r="AR27" s="12"/>
+      <c r="AR27" s="5"/>
       <c r="AS27" s="5"/>
-      <c r="AT27" s="5"/>
-      <c r="BO27" s="9"/>
-      <c r="BP27" s="10"/>
+      <c r="BN27" s="9"/>
+      <c r="BO27" s="10"/>
+      <c r="BP27" s="9"/>
       <c r="BQ27" s="9"/>
-      <c r="BR27" s="9"/>
+      <c r="BS27" s="10"/>
       <c r="BT27" s="10"/>
-      <c r="BU27" s="10"/>
+      <c r="BV27" s="10"/>
       <c r="BW27" s="10"/>
       <c r="BX27" s="10"/>
       <c r="BY27" s="10"/>
       <c r="BZ27" s="10"/>
       <c r="CA27" s="10"/>
       <c r="CB27" s="10"/>
-      <c r="CC27" s="10"/>
-    </row>
-    <row r="28" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B28" s="14"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -2842,50 +2903,49 @@
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
+      <c r="O28" s="16"/>
       <c r="P28" s="16"/>
       <c r="Q28" s="16"/>
       <c r="R28" s="16"/>
       <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="11"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="17"/>
       <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
+      <c r="W28" s="16"/>
       <c r="X28" s="16"/>
       <c r="Y28" s="16"/>
-      <c r="Z28" s="16"/>
+      <c r="Z28" s="17"/>
       <c r="AA28" s="17"/>
       <c r="AB28" s="17"/>
       <c r="AC28" s="17"/>
       <c r="AD28" s="17"/>
       <c r="AE28" s="17"/>
-      <c r="AF28" s="17"/>
+      <c r="AF28" s="16"/>
       <c r="AG28" s="16"/>
       <c r="AH28" s="16"/>
       <c r="AI28" s="16"/>
-      <c r="AJ28" s="16"/>
+      <c r="AM28" s="12"/>
       <c r="AN28" s="12"/>
-      <c r="AO28" s="12"/>
-      <c r="AP28" s="5"/>
+      <c r="AO28" s="5"/>
+      <c r="AP28" s="12"/>
       <c r="AQ28" s="12"/>
-      <c r="AR28" s="12"/>
+      <c r="AR28" s="5"/>
       <c r="AS28" s="5"/>
-      <c r="AT28" s="5"/>
-      <c r="BO28" s="9"/>
-      <c r="BP28" s="10"/>
+      <c r="BN28" s="9"/>
+      <c r="BO28" s="10"/>
+      <c r="BP28" s="9"/>
       <c r="BQ28" s="9"/>
-      <c r="BR28" s="9"/>
+      <c r="BS28" s="10"/>
       <c r="BT28" s="10"/>
-      <c r="BU28" s="10"/>
+      <c r="BV28" s="10"/>
       <c r="BW28" s="10"/>
       <c r="BX28" s="10"/>
       <c r="BY28" s="10"/>
       <c r="BZ28" s="10"/>
       <c r="CA28" s="10"/>
       <c r="CB28" s="10"/>
-      <c r="CC28" s="10"/>
-    </row>
-    <row r="29" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B29" s="14"/>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -2898,50 +2958,49 @@
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
+      <c r="O29" s="16"/>
       <c r="P29" s="16"/>
       <c r="Q29" s="16"/>
       <c r="R29" s="16"/>
       <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="17"/>
       <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
+      <c r="W29" s="16"/>
       <c r="X29" s="16"/>
       <c r="Y29" s="16"/>
-      <c r="Z29" s="16"/>
+      <c r="Z29" s="17"/>
       <c r="AA29" s="17"/>
       <c r="AB29" s="17"/>
       <c r="AC29" s="17"/>
       <c r="AD29" s="17"/>
       <c r="AE29" s="17"/>
-      <c r="AF29" s="17"/>
+      <c r="AF29" s="16"/>
       <c r="AG29" s="16"/>
       <c r="AH29" s="16"/>
       <c r="AI29" s="16"/>
-      <c r="AJ29" s="16"/>
+      <c r="AM29" s="12"/>
       <c r="AN29" s="12"/>
-      <c r="AO29" s="12"/>
-      <c r="AP29" s="5"/>
+      <c r="AO29" s="5"/>
+      <c r="AP29" s="12"/>
       <c r="AQ29" s="12"/>
-      <c r="AR29" s="12"/>
+      <c r="AR29" s="5"/>
       <c r="AS29" s="5"/>
-      <c r="AT29" s="5"/>
-      <c r="BO29" s="9"/>
-      <c r="BP29" s="10"/>
+      <c r="BN29" s="9"/>
+      <c r="BO29" s="10"/>
+      <c r="BP29" s="9"/>
       <c r="BQ29" s="9"/>
-      <c r="BR29" s="9"/>
+      <c r="BS29" s="10"/>
       <c r="BT29" s="10"/>
-      <c r="BU29" s="10"/>
+      <c r="BV29" s="10"/>
       <c r="BW29" s="10"/>
       <c r="BX29" s="10"/>
       <c r="BY29" s="10"/>
       <c r="BZ29" s="10"/>
       <c r="CA29" s="10"/>
       <c r="CB29" s="10"/>
-      <c r="CC29" s="10"/>
-    </row>
-    <row r="30" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B30" s="14"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -2954,50 +3013,49 @@
       <c r="K30" s="13"/>
       <c r="L30" s="13"/>
       <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
+      <c r="O30" s="16"/>
       <c r="P30" s="16"/>
       <c r="Q30" s="16"/>
       <c r="R30" s="16"/>
       <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="11"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="17"/>
       <c r="V30" s="17"/>
-      <c r="W30" s="17"/>
+      <c r="W30" s="16"/>
       <c r="X30" s="16"/>
       <c r="Y30" s="16"/>
-      <c r="Z30" s="16"/>
+      <c r="Z30" s="17"/>
       <c r="AA30" s="17"/>
       <c r="AB30" s="17"/>
       <c r="AC30" s="17"/>
       <c r="AD30" s="17"/>
       <c r="AE30" s="17"/>
-      <c r="AF30" s="17"/>
+      <c r="AF30" s="16"/>
       <c r="AG30" s="16"/>
       <c r="AH30" s="16"/>
       <c r="AI30" s="16"/>
-      <c r="AJ30" s="16"/>
+      <c r="AM30" s="12"/>
       <c r="AN30" s="12"/>
-      <c r="AO30" s="12"/>
-      <c r="AP30" s="5"/>
+      <c r="AO30" s="5"/>
+      <c r="AP30" s="12"/>
       <c r="AQ30" s="12"/>
-      <c r="AR30" s="12"/>
+      <c r="AR30" s="5"/>
       <c r="AS30" s="5"/>
-      <c r="AT30" s="5"/>
-      <c r="BO30" s="9"/>
-      <c r="BP30" s="10"/>
+      <c r="BN30" s="9"/>
+      <c r="BO30" s="10"/>
+      <c r="BP30" s="9"/>
       <c r="BQ30" s="9"/>
-      <c r="BR30" s="9"/>
+      <c r="BS30" s="10"/>
       <c r="BT30" s="10"/>
-      <c r="BU30" s="10"/>
+      <c r="BV30" s="10"/>
       <c r="BW30" s="10"/>
       <c r="BX30" s="10"/>
       <c r="BY30" s="10"/>
       <c r="BZ30" s="10"/>
       <c r="CA30" s="10"/>
       <c r="CB30" s="10"/>
-      <c r="CC30" s="10"/>
-    </row>
-    <row r="31" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B31" s="14"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
@@ -3010,50 +3068,49 @@
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
+      <c r="O31" s="16"/>
       <c r="P31" s="16"/>
       <c r="Q31" s="16"/>
       <c r="R31" s="16"/>
       <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="11"/>
+      <c r="T31" s="11"/>
+      <c r="U31" s="17"/>
       <c r="V31" s="17"/>
-      <c r="W31" s="17"/>
+      <c r="W31" s="16"/>
       <c r="X31" s="16"/>
       <c r="Y31" s="16"/>
-      <c r="Z31" s="16"/>
+      <c r="Z31" s="17"/>
       <c r="AA31" s="17"/>
       <c r="AB31" s="17"/>
       <c r="AC31" s="17"/>
       <c r="AD31" s="17"/>
       <c r="AE31" s="17"/>
-      <c r="AF31" s="17"/>
+      <c r="AF31" s="16"/>
       <c r="AG31" s="16"/>
       <c r="AH31" s="16"/>
       <c r="AI31" s="16"/>
-      <c r="AJ31" s="16"/>
+      <c r="AM31" s="12"/>
       <c r="AN31" s="12"/>
-      <c r="AO31" s="12"/>
-      <c r="AP31" s="5"/>
+      <c r="AO31" s="5"/>
+      <c r="AP31" s="12"/>
       <c r="AQ31" s="12"/>
-      <c r="AR31" s="12"/>
+      <c r="AR31" s="5"/>
       <c r="AS31" s="5"/>
-      <c r="AT31" s="5"/>
-      <c r="BO31" s="9"/>
-      <c r="BP31" s="10"/>
+      <c r="BN31" s="9"/>
+      <c r="BO31" s="10"/>
+      <c r="BP31" s="9"/>
       <c r="BQ31" s="9"/>
-      <c r="BR31" s="9"/>
+      <c r="BS31" s="10"/>
       <c r="BT31" s="10"/>
-      <c r="BU31" s="10"/>
+      <c r="BV31" s="10"/>
       <c r="BW31" s="10"/>
       <c r="BX31" s="10"/>
       <c r="BY31" s="10"/>
       <c r="BZ31" s="10"/>
       <c r="CA31" s="10"/>
       <c r="CB31" s="10"/>
-      <c r="CC31" s="10"/>
-    </row>
-    <row r="32" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B32" s="14"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -3066,50 +3123,49 @@
       <c r="K32" s="13"/>
       <c r="L32" s="13"/>
       <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
+      <c r="O32" s="16"/>
       <c r="P32" s="16"/>
       <c r="Q32" s="16"/>
       <c r="R32" s="16"/>
       <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="17"/>
       <c r="V32" s="17"/>
-      <c r="W32" s="17"/>
+      <c r="W32" s="16"/>
       <c r="X32" s="16"/>
       <c r="Y32" s="16"/>
-      <c r="Z32" s="16"/>
+      <c r="Z32" s="17"/>
       <c r="AA32" s="17"/>
       <c r="AB32" s="17"/>
       <c r="AC32" s="17"/>
       <c r="AD32" s="17"/>
       <c r="AE32" s="17"/>
-      <c r="AF32" s="17"/>
+      <c r="AF32" s="16"/>
       <c r="AG32" s="16"/>
       <c r="AH32" s="16"/>
       <c r="AI32" s="16"/>
-      <c r="AJ32" s="16"/>
+      <c r="AM32" s="12"/>
       <c r="AN32" s="12"/>
-      <c r="AO32" s="12"/>
-      <c r="AP32" s="5"/>
+      <c r="AO32" s="5"/>
+      <c r="AP32" s="12"/>
       <c r="AQ32" s="12"/>
-      <c r="AR32" s="12"/>
+      <c r="AR32" s="5"/>
       <c r="AS32" s="5"/>
-      <c r="AT32" s="5"/>
-      <c r="BO32" s="9"/>
-      <c r="BP32" s="10"/>
+      <c r="BN32" s="9"/>
+      <c r="BO32" s="10"/>
+      <c r="BP32" s="9"/>
       <c r="BQ32" s="9"/>
-      <c r="BR32" s="9"/>
+      <c r="BS32" s="10"/>
       <c r="BT32" s="10"/>
-      <c r="BU32" s="10"/>
+      <c r="BV32" s="10"/>
       <c r="BW32" s="10"/>
       <c r="BX32" s="10"/>
       <c r="BY32" s="10"/>
       <c r="BZ32" s="10"/>
       <c r="CA32" s="10"/>
       <c r="CB32" s="10"/>
-      <c r="CC32" s="10"/>
-    </row>
-    <row r="33" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B33" s="14"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -3122,50 +3178,49 @@
       <c r="K33" s="13"/>
       <c r="L33" s="13"/>
       <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
+      <c r="O33" s="16"/>
       <c r="P33" s="16"/>
       <c r="Q33" s="16"/>
       <c r="R33" s="16"/>
       <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="11"/>
+      <c r="T33" s="11"/>
+      <c r="U33" s="17"/>
       <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
+      <c r="W33" s="16"/>
       <c r="X33" s="16"/>
       <c r="Y33" s="16"/>
-      <c r="Z33" s="16"/>
+      <c r="Z33" s="17"/>
       <c r="AA33" s="17"/>
       <c r="AB33" s="17"/>
       <c r="AC33" s="17"/>
       <c r="AD33" s="17"/>
       <c r="AE33" s="17"/>
-      <c r="AF33" s="17"/>
+      <c r="AF33" s="16"/>
       <c r="AG33" s="16"/>
       <c r="AH33" s="16"/>
       <c r="AI33" s="16"/>
-      <c r="AJ33" s="16"/>
+      <c r="AM33" s="12"/>
       <c r="AN33" s="12"/>
-      <c r="AO33" s="12"/>
-      <c r="AP33" s="5"/>
+      <c r="AO33" s="5"/>
+      <c r="AP33" s="12"/>
       <c r="AQ33" s="12"/>
-      <c r="AR33" s="12"/>
+      <c r="AR33" s="5"/>
       <c r="AS33" s="5"/>
-      <c r="AT33" s="5"/>
-      <c r="BO33" s="9"/>
-      <c r="BP33" s="10"/>
+      <c r="BN33" s="9"/>
+      <c r="BO33" s="10"/>
+      <c r="BP33" s="9"/>
       <c r="BQ33" s="9"/>
-      <c r="BR33" s="9"/>
+      <c r="BS33" s="10"/>
       <c r="BT33" s="10"/>
-      <c r="BU33" s="10"/>
+      <c r="BV33" s="10"/>
       <c r="BW33" s="10"/>
       <c r="BX33" s="10"/>
       <c r="BY33" s="10"/>
       <c r="BZ33" s="10"/>
       <c r="CA33" s="10"/>
       <c r="CB33" s="10"/>
-      <c r="CC33" s="10"/>
-    </row>
-    <row r="34" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B34" s="14"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -3178,50 +3233,49 @@
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
+      <c r="O34" s="16"/>
       <c r="P34" s="16"/>
       <c r="Q34" s="16"/>
       <c r="R34" s="16"/>
       <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="11"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="17"/>
       <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
+      <c r="W34" s="16"/>
       <c r="X34" s="16"/>
       <c r="Y34" s="16"/>
-      <c r="Z34" s="16"/>
+      <c r="Z34" s="17"/>
       <c r="AA34" s="17"/>
       <c r="AB34" s="17"/>
       <c r="AC34" s="17"/>
       <c r="AD34" s="17"/>
       <c r="AE34" s="17"/>
-      <c r="AF34" s="17"/>
+      <c r="AF34" s="16"/>
       <c r="AG34" s="16"/>
       <c r="AH34" s="16"/>
       <c r="AI34" s="16"/>
-      <c r="AJ34" s="16"/>
+      <c r="AM34" s="12"/>
       <c r="AN34" s="12"/>
-      <c r="AO34" s="12"/>
-      <c r="AP34" s="5"/>
+      <c r="AO34" s="5"/>
+      <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AR34" s="12"/>
+      <c r="AR34" s="5"/>
       <c r="AS34" s="5"/>
-      <c r="AT34" s="5"/>
-      <c r="BO34" s="9"/>
-      <c r="BP34" s="10"/>
+      <c r="BN34" s="9"/>
+      <c r="BO34" s="10"/>
+      <c r="BP34" s="9"/>
       <c r="BQ34" s="9"/>
-      <c r="BR34" s="9"/>
+      <c r="BS34" s="10"/>
       <c r="BT34" s="10"/>
-      <c r="BU34" s="10"/>
+      <c r="BV34" s="10"/>
       <c r="BW34" s="10"/>
       <c r="BX34" s="10"/>
       <c r="BY34" s="10"/>
       <c r="BZ34" s="10"/>
       <c r="CA34" s="10"/>
       <c r="CB34" s="10"/>
-      <c r="CC34" s="10"/>
-    </row>
-    <row r="35" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B35" s="14"/>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
@@ -3234,50 +3288,49 @@
       <c r="K35" s="13"/>
       <c r="L35" s="13"/>
       <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
+      <c r="O35" s="16"/>
       <c r="P35" s="16"/>
       <c r="Q35" s="16"/>
       <c r="R35" s="16"/>
       <c r="S35" s="16"/>
-      <c r="T35" s="16"/>
-      <c r="U35" s="11"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="17"/>
       <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
+      <c r="W35" s="16"/>
       <c r="X35" s="16"/>
       <c r="Y35" s="16"/>
-      <c r="Z35" s="16"/>
+      <c r="Z35" s="17"/>
       <c r="AA35" s="17"/>
       <c r="AB35" s="17"/>
       <c r="AC35" s="17"/>
       <c r="AD35" s="17"/>
       <c r="AE35" s="17"/>
-      <c r="AF35" s="17"/>
+      <c r="AF35" s="16"/>
       <c r="AG35" s="16"/>
       <c r="AH35" s="16"/>
       <c r="AI35" s="16"/>
-      <c r="AJ35" s="16"/>
+      <c r="AM35" s="12"/>
       <c r="AN35" s="12"/>
-      <c r="AO35" s="12"/>
-      <c r="AP35" s="5"/>
+      <c r="AO35" s="5"/>
+      <c r="AP35" s="12"/>
       <c r="AQ35" s="12"/>
-      <c r="AR35" s="12"/>
+      <c r="AR35" s="5"/>
       <c r="AS35" s="5"/>
-      <c r="AT35" s="5"/>
-      <c r="BO35" s="9"/>
-      <c r="BP35" s="10"/>
+      <c r="BN35" s="9"/>
+      <c r="BO35" s="10"/>
+      <c r="BP35" s="9"/>
       <c r="BQ35" s="9"/>
-      <c r="BR35" s="9"/>
+      <c r="BS35" s="10"/>
       <c r="BT35" s="10"/>
-      <c r="BU35" s="10"/>
+      <c r="BV35" s="10"/>
       <c r="BW35" s="10"/>
       <c r="BX35" s="10"/>
       <c r="BY35" s="10"/>
       <c r="BZ35" s="10"/>
       <c r="CA35" s="10"/>
       <c r="CB35" s="10"/>
-      <c r="CC35" s="10"/>
-    </row>
-    <row r="36" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B36" s="14"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -3290,50 +3343,49 @@
       <c r="K36" s="13"/>
       <c r="L36" s="13"/>
       <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
+      <c r="O36" s="16"/>
       <c r="P36" s="16"/>
       <c r="Q36" s="16"/>
       <c r="R36" s="16"/>
       <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="11"/>
+      <c r="T36" s="11"/>
+      <c r="U36" s="17"/>
       <c r="V36" s="17"/>
-      <c r="W36" s="17"/>
+      <c r="W36" s="16"/>
       <c r="X36" s="16"/>
       <c r="Y36" s="16"/>
-      <c r="Z36" s="16"/>
+      <c r="Z36" s="17"/>
       <c r="AA36" s="17"/>
       <c r="AB36" s="17"/>
       <c r="AC36" s="17"/>
       <c r="AD36" s="17"/>
       <c r="AE36" s="17"/>
-      <c r="AF36" s="17"/>
+      <c r="AF36" s="16"/>
       <c r="AG36" s="16"/>
       <c r="AH36" s="16"/>
       <c r="AI36" s="16"/>
-      <c r="AJ36" s="16"/>
+      <c r="AM36" s="12"/>
       <c r="AN36" s="12"/>
-      <c r="AO36" s="12"/>
-      <c r="AP36" s="5"/>
+      <c r="AO36" s="5"/>
+      <c r="AP36" s="12"/>
       <c r="AQ36" s="12"/>
-      <c r="AR36" s="12"/>
+      <c r="AR36" s="5"/>
       <c r="AS36" s="5"/>
-      <c r="AT36" s="5"/>
-      <c r="BO36" s="9"/>
-      <c r="BP36" s="10"/>
+      <c r="BN36" s="9"/>
+      <c r="BO36" s="10"/>
+      <c r="BP36" s="9"/>
       <c r="BQ36" s="9"/>
-      <c r="BR36" s="9"/>
+      <c r="BS36" s="10"/>
       <c r="BT36" s="10"/>
-      <c r="BU36" s="10"/>
+      <c r="BV36" s="10"/>
       <c r="BW36" s="10"/>
       <c r="BX36" s="10"/>
       <c r="BY36" s="10"/>
       <c r="BZ36" s="10"/>
       <c r="CA36" s="10"/>
       <c r="CB36" s="10"/>
-      <c r="CC36" s="10"/>
-    </row>
-    <row r="37" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B37" s="14"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -3346,50 +3398,49 @@
       <c r="K37" s="13"/>
       <c r="L37" s="13"/>
       <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
+      <c r="O37" s="16"/>
       <c r="P37" s="16"/>
       <c r="Q37" s="16"/>
       <c r="R37" s="16"/>
       <c r="S37" s="16"/>
-      <c r="T37" s="16"/>
-      <c r="U37" s="11"/>
+      <c r="T37" s="11"/>
+      <c r="U37" s="17"/>
       <c r="V37" s="17"/>
-      <c r="W37" s="17"/>
+      <c r="W37" s="16"/>
       <c r="X37" s="16"/>
       <c r="Y37" s="16"/>
-      <c r="Z37" s="16"/>
+      <c r="Z37" s="17"/>
       <c r="AA37" s="17"/>
       <c r="AB37" s="17"/>
       <c r="AC37" s="17"/>
       <c r="AD37" s="17"/>
       <c r="AE37" s="17"/>
-      <c r="AF37" s="17"/>
+      <c r="AF37" s="16"/>
       <c r="AG37" s="16"/>
       <c r="AH37" s="16"/>
       <c r="AI37" s="16"/>
-      <c r="AJ37" s="16"/>
+      <c r="AM37" s="12"/>
       <c r="AN37" s="12"/>
-      <c r="AO37" s="12"/>
-      <c r="AP37" s="5"/>
+      <c r="AO37" s="5"/>
+      <c r="AP37" s="12"/>
       <c r="AQ37" s="12"/>
-      <c r="AR37" s="12"/>
+      <c r="AR37" s="5"/>
       <c r="AS37" s="5"/>
-      <c r="AT37" s="5"/>
-      <c r="BO37" s="9"/>
-      <c r="BP37" s="10"/>
+      <c r="BN37" s="9"/>
+      <c r="BO37" s="10"/>
+      <c r="BP37" s="9"/>
       <c r="BQ37" s="9"/>
-      <c r="BR37" s="9"/>
+      <c r="BS37" s="10"/>
       <c r="BT37" s="10"/>
-      <c r="BU37" s="10"/>
+      <c r="BV37" s="10"/>
       <c r="BW37" s="10"/>
       <c r="BX37" s="10"/>
       <c r="BY37" s="10"/>
       <c r="BZ37" s="10"/>
       <c r="CA37" s="10"/>
       <c r="CB37" s="10"/>
-      <c r="CC37" s="10"/>
-    </row>
-    <row r="38" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B38" s="14"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -3402,50 +3453,49 @@
       <c r="K38" s="13"/>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
+      <c r="O38" s="16"/>
       <c r="P38" s="16"/>
       <c r="Q38" s="16"/>
       <c r="R38" s="16"/>
       <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="11"/>
+      <c r="T38" s="11"/>
+      <c r="U38" s="17"/>
       <c r="V38" s="17"/>
-      <c r="W38" s="17"/>
+      <c r="W38" s="16"/>
       <c r="X38" s="16"/>
       <c r="Y38" s="16"/>
-      <c r="Z38" s="16"/>
+      <c r="Z38" s="17"/>
       <c r="AA38" s="17"/>
       <c r="AB38" s="17"/>
       <c r="AC38" s="17"/>
       <c r="AD38" s="17"/>
       <c r="AE38" s="17"/>
-      <c r="AF38" s="17"/>
+      <c r="AF38" s="16"/>
       <c r="AG38" s="16"/>
       <c r="AH38" s="16"/>
       <c r="AI38" s="16"/>
-      <c r="AJ38" s="16"/>
+      <c r="AM38" s="12"/>
       <c r="AN38" s="12"/>
-      <c r="AO38" s="12"/>
-      <c r="AP38" s="5"/>
+      <c r="AO38" s="5"/>
+      <c r="AP38" s="12"/>
       <c r="AQ38" s="12"/>
-      <c r="AR38" s="12"/>
+      <c r="AR38" s="5"/>
       <c r="AS38" s="5"/>
-      <c r="AT38" s="5"/>
-      <c r="BO38" s="9"/>
-      <c r="BP38" s="10"/>
+      <c r="BN38" s="9"/>
+      <c r="BO38" s="10"/>
+      <c r="BP38" s="9"/>
       <c r="BQ38" s="9"/>
-      <c r="BR38" s="9"/>
+      <c r="BS38" s="10"/>
       <c r="BT38" s="10"/>
-      <c r="BU38" s="10"/>
+      <c r="BV38" s="10"/>
       <c r="BW38" s="10"/>
       <c r="BX38" s="10"/>
       <c r="BY38" s="10"/>
       <c r="BZ38" s="10"/>
       <c r="CA38" s="10"/>
       <c r="CB38" s="10"/>
-      <c r="CC38" s="10"/>
-    </row>
-    <row r="39" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B39" s="14"/>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
@@ -3458,50 +3508,49 @@
       <c r="K39" s="13"/>
       <c r="L39" s="13"/>
       <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
+      <c r="O39" s="16"/>
       <c r="P39" s="16"/>
       <c r="Q39" s="16"/>
       <c r="R39" s="16"/>
       <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="11"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="17"/>
       <c r="V39" s="17"/>
-      <c r="W39" s="17"/>
+      <c r="W39" s="16"/>
       <c r="X39" s="16"/>
       <c r="Y39" s="16"/>
-      <c r="Z39" s="16"/>
+      <c r="Z39" s="17"/>
       <c r="AA39" s="17"/>
       <c r="AB39" s="17"/>
       <c r="AC39" s="17"/>
       <c r="AD39" s="17"/>
       <c r="AE39" s="17"/>
-      <c r="AF39" s="17"/>
+      <c r="AF39" s="16"/>
       <c r="AG39" s="16"/>
       <c r="AH39" s="16"/>
       <c r="AI39" s="16"/>
-      <c r="AJ39" s="16"/>
+      <c r="AM39" s="12"/>
       <c r="AN39" s="12"/>
-      <c r="AO39" s="12"/>
-      <c r="AP39" s="5"/>
+      <c r="AO39" s="5"/>
+      <c r="AP39" s="12"/>
       <c r="AQ39" s="12"/>
-      <c r="AR39" s="12"/>
+      <c r="AR39" s="5"/>
       <c r="AS39" s="5"/>
-      <c r="AT39" s="5"/>
-      <c r="BO39" s="9"/>
-      <c r="BP39" s="10"/>
+      <c r="BN39" s="9"/>
+      <c r="BO39" s="10"/>
+      <c r="BP39" s="9"/>
       <c r="BQ39" s="9"/>
-      <c r="BR39" s="9"/>
+      <c r="BS39" s="10"/>
       <c r="BT39" s="10"/>
-      <c r="BU39" s="10"/>
+      <c r="BV39" s="10"/>
       <c r="BW39" s="10"/>
       <c r="BX39" s="10"/>
       <c r="BY39" s="10"/>
       <c r="BZ39" s="10"/>
       <c r="CA39" s="10"/>
       <c r="CB39" s="10"/>
-      <c r="CC39" s="10"/>
-    </row>
-    <row r="40" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B40" s="14"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -3514,50 +3563,49 @@
       <c r="K40" s="13"/>
       <c r="L40" s="13"/>
       <c r="M40" s="13"/>
-      <c r="N40" s="13"/>
+      <c r="O40" s="16"/>
       <c r="P40" s="16"/>
       <c r="Q40" s="16"/>
       <c r="R40" s="16"/>
       <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
-      <c r="U40" s="11"/>
+      <c r="T40" s="11"/>
+      <c r="U40" s="17"/>
       <c r="V40" s="17"/>
-      <c r="W40" s="17"/>
+      <c r="W40" s="16"/>
       <c r="X40" s="16"/>
       <c r="Y40" s="16"/>
-      <c r="Z40" s="16"/>
+      <c r="Z40" s="17"/>
       <c r="AA40" s="17"/>
       <c r="AB40" s="17"/>
       <c r="AC40" s="17"/>
       <c r="AD40" s="17"/>
       <c r="AE40" s="17"/>
-      <c r="AF40" s="17"/>
+      <c r="AF40" s="16"/>
       <c r="AG40" s="16"/>
       <c r="AH40" s="16"/>
       <c r="AI40" s="16"/>
-      <c r="AJ40" s="16"/>
+      <c r="AM40" s="12"/>
       <c r="AN40" s="12"/>
-      <c r="AO40" s="12"/>
-      <c r="AP40" s="5"/>
+      <c r="AO40" s="5"/>
+      <c r="AP40" s="12"/>
       <c r="AQ40" s="12"/>
-      <c r="AR40" s="12"/>
+      <c r="AR40" s="5"/>
       <c r="AS40" s="5"/>
-      <c r="AT40" s="5"/>
-      <c r="BO40" s="9"/>
-      <c r="BP40" s="10"/>
+      <c r="BN40" s="9"/>
+      <c r="BO40" s="10"/>
+      <c r="BP40" s="9"/>
       <c r="BQ40" s="9"/>
-      <c r="BR40" s="9"/>
+      <c r="BS40" s="10"/>
       <c r="BT40" s="10"/>
-      <c r="BU40" s="10"/>
+      <c r="BV40" s="10"/>
       <c r="BW40" s="10"/>
       <c r="BX40" s="10"/>
       <c r="BY40" s="10"/>
       <c r="BZ40" s="10"/>
       <c r="CA40" s="10"/>
       <c r="CB40" s="10"/>
-      <c r="CC40" s="10"/>
-    </row>
-    <row r="41" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B41" s="14"/>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
@@ -3570,50 +3618,49 @@
       <c r="K41" s="13"/>
       <c r="L41" s="13"/>
       <c r="M41" s="13"/>
-      <c r="N41" s="13"/>
+      <c r="O41" s="16"/>
       <c r="P41" s="16"/>
       <c r="Q41" s="16"/>
       <c r="R41" s="16"/>
       <c r="S41" s="16"/>
-      <c r="T41" s="16"/>
-      <c r="U41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="17"/>
       <c r="V41" s="17"/>
-      <c r="W41" s="17"/>
+      <c r="W41" s="16"/>
       <c r="X41" s="16"/>
       <c r="Y41" s="16"/>
-      <c r="Z41" s="16"/>
+      <c r="Z41" s="17"/>
       <c r="AA41" s="17"/>
       <c r="AB41" s="17"/>
       <c r="AC41" s="17"/>
       <c r="AD41" s="17"/>
       <c r="AE41" s="17"/>
-      <c r="AF41" s="17"/>
+      <c r="AF41" s="16"/>
       <c r="AG41" s="16"/>
       <c r="AH41" s="16"/>
       <c r="AI41" s="16"/>
-      <c r="AJ41" s="16"/>
+      <c r="AM41" s="12"/>
       <c r="AN41" s="12"/>
-      <c r="AO41" s="12"/>
-      <c r="AP41" s="5"/>
+      <c r="AO41" s="5"/>
+      <c r="AP41" s="12"/>
       <c r="AQ41" s="12"/>
-      <c r="AR41" s="12"/>
+      <c r="AR41" s="5"/>
       <c r="AS41" s="5"/>
-      <c r="AT41" s="5"/>
-      <c r="BO41" s="9"/>
-      <c r="BP41" s="10"/>
+      <c r="BN41" s="9"/>
+      <c r="BO41" s="10"/>
+      <c r="BP41" s="9"/>
       <c r="BQ41" s="9"/>
-      <c r="BR41" s="9"/>
+      <c r="BS41" s="10"/>
       <c r="BT41" s="10"/>
-      <c r="BU41" s="10"/>
+      <c r="BV41" s="10"/>
       <c r="BW41" s="10"/>
       <c r="BX41" s="10"/>
       <c r="BY41" s="10"/>
       <c r="BZ41" s="10"/>
       <c r="CA41" s="10"/>
       <c r="CB41" s="10"/>
-      <c r="CC41" s="10"/>
-    </row>
-    <row r="42" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B42" s="14"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -3626,50 +3673,49 @@
       <c r="K42" s="13"/>
       <c r="L42" s="13"/>
       <c r="M42" s="13"/>
-      <c r="N42" s="13"/>
+      <c r="O42" s="16"/>
       <c r="P42" s="16"/>
       <c r="Q42" s="16"/>
       <c r="R42" s="16"/>
       <c r="S42" s="16"/>
-      <c r="T42" s="16"/>
-      <c r="U42" s="11"/>
+      <c r="T42" s="11"/>
+      <c r="U42" s="17"/>
       <c r="V42" s="17"/>
-      <c r="W42" s="17"/>
+      <c r="W42" s="16"/>
       <c r="X42" s="16"/>
       <c r="Y42" s="16"/>
-      <c r="Z42" s="16"/>
+      <c r="Z42" s="17"/>
       <c r="AA42" s="17"/>
       <c r="AB42" s="17"/>
       <c r="AC42" s="17"/>
       <c r="AD42" s="17"/>
       <c r="AE42" s="17"/>
-      <c r="AF42" s="17"/>
+      <c r="AF42" s="16"/>
       <c r="AG42" s="16"/>
       <c r="AH42" s="16"/>
       <c r="AI42" s="16"/>
-      <c r="AJ42" s="16"/>
+      <c r="AM42" s="12"/>
       <c r="AN42" s="12"/>
-      <c r="AO42" s="12"/>
-      <c r="AP42" s="5"/>
+      <c r="AO42" s="5"/>
+      <c r="AP42" s="12"/>
       <c r="AQ42" s="12"/>
-      <c r="AR42" s="12"/>
+      <c r="AR42" s="5"/>
       <c r="AS42" s="5"/>
-      <c r="AT42" s="5"/>
-      <c r="BO42" s="9"/>
-      <c r="BP42" s="10"/>
+      <c r="BN42" s="9"/>
+      <c r="BO42" s="10"/>
+      <c r="BP42" s="9"/>
       <c r="BQ42" s="9"/>
-      <c r="BR42" s="9"/>
+      <c r="BS42" s="10"/>
       <c r="BT42" s="10"/>
-      <c r="BU42" s="10"/>
+      <c r="BV42" s="10"/>
       <c r="BW42" s="10"/>
       <c r="BX42" s="10"/>
       <c r="BY42" s="10"/>
       <c r="BZ42" s="10"/>
       <c r="CA42" s="10"/>
       <c r="CB42" s="10"/>
-      <c r="CC42" s="10"/>
-    </row>
-    <row r="43" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B43" s="14"/>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
@@ -3682,50 +3728,49 @@
       <c r="K43" s="13"/>
       <c r="L43" s="13"/>
       <c r="M43" s="13"/>
-      <c r="N43" s="13"/>
+      <c r="O43" s="16"/>
       <c r="P43" s="16"/>
       <c r="Q43" s="16"/>
       <c r="R43" s="16"/>
       <c r="S43" s="16"/>
-      <c r="T43" s="16"/>
-      <c r="U43" s="11"/>
+      <c r="T43" s="11"/>
+      <c r="U43" s="17"/>
       <c r="V43" s="17"/>
-      <c r="W43" s="17"/>
+      <c r="W43" s="16"/>
       <c r="X43" s="16"/>
       <c r="Y43" s="16"/>
-      <c r="Z43" s="16"/>
+      <c r="Z43" s="17"/>
       <c r="AA43" s="17"/>
       <c r="AB43" s="17"/>
       <c r="AC43" s="17"/>
       <c r="AD43" s="17"/>
       <c r="AE43" s="17"/>
-      <c r="AF43" s="17"/>
+      <c r="AF43" s="16"/>
       <c r="AG43" s="16"/>
       <c r="AH43" s="16"/>
       <c r="AI43" s="16"/>
-      <c r="AJ43" s="16"/>
+      <c r="AM43" s="12"/>
       <c r="AN43" s="12"/>
-      <c r="AO43" s="12"/>
-      <c r="AP43" s="5"/>
+      <c r="AO43" s="5"/>
+      <c r="AP43" s="12"/>
       <c r="AQ43" s="12"/>
-      <c r="AR43" s="12"/>
+      <c r="AR43" s="5"/>
       <c r="AS43" s="5"/>
-      <c r="AT43" s="5"/>
-      <c r="BO43" s="9"/>
-      <c r="BP43" s="10"/>
+      <c r="BN43" s="9"/>
+      <c r="BO43" s="10"/>
+      <c r="BP43" s="9"/>
       <c r="BQ43" s="9"/>
-      <c r="BR43" s="9"/>
+      <c r="BS43" s="10"/>
       <c r="BT43" s="10"/>
-      <c r="BU43" s="10"/>
+      <c r="BV43" s="10"/>
       <c r="BW43" s="10"/>
       <c r="BX43" s="10"/>
       <c r="BY43" s="10"/>
       <c r="BZ43" s="10"/>
       <c r="CA43" s="10"/>
       <c r="CB43" s="10"/>
-      <c r="CC43" s="10"/>
-    </row>
-    <row r="44" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B44" s="14"/>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -3738,50 +3783,49 @@
       <c r="K44" s="13"/>
       <c r="L44" s="13"/>
       <c r="M44" s="13"/>
-      <c r="N44" s="13"/>
+      <c r="O44" s="16"/>
       <c r="P44" s="16"/>
       <c r="Q44" s="16"/>
       <c r="R44" s="16"/>
       <c r="S44" s="16"/>
-      <c r="T44" s="16"/>
-      <c r="U44" s="11"/>
+      <c r="T44" s="11"/>
+      <c r="U44" s="17"/>
       <c r="V44" s="17"/>
-      <c r="W44" s="17"/>
+      <c r="W44" s="16"/>
       <c r="X44" s="16"/>
       <c r="Y44" s="16"/>
-      <c r="Z44" s="16"/>
+      <c r="Z44" s="17"/>
       <c r="AA44" s="17"/>
       <c r="AB44" s="17"/>
       <c r="AC44" s="17"/>
       <c r="AD44" s="17"/>
       <c r="AE44" s="17"/>
-      <c r="AF44" s="17"/>
+      <c r="AF44" s="16"/>
       <c r="AG44" s="16"/>
       <c r="AH44" s="16"/>
       <c r="AI44" s="16"/>
-      <c r="AJ44" s="16"/>
+      <c r="AM44" s="12"/>
       <c r="AN44" s="12"/>
-      <c r="AO44" s="12"/>
-      <c r="AP44" s="5"/>
+      <c r="AO44" s="5"/>
+      <c r="AP44" s="12"/>
       <c r="AQ44" s="12"/>
-      <c r="AR44" s="12"/>
+      <c r="AR44" s="5"/>
       <c r="AS44" s="5"/>
-      <c r="AT44" s="5"/>
-      <c r="BO44" s="9"/>
-      <c r="BP44" s="10"/>
+      <c r="BN44" s="9"/>
+      <c r="BO44" s="10"/>
+      <c r="BP44" s="9"/>
       <c r="BQ44" s="9"/>
-      <c r="BR44" s="9"/>
+      <c r="BS44" s="10"/>
       <c r="BT44" s="10"/>
-      <c r="BU44" s="10"/>
+      <c r="BV44" s="10"/>
       <c r="BW44" s="10"/>
       <c r="BX44" s="10"/>
       <c r="BY44" s="10"/>
       <c r="BZ44" s="10"/>
       <c r="CA44" s="10"/>
       <c r="CB44" s="10"/>
-      <c r="CC44" s="10"/>
-    </row>
-    <row r="45" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B45" s="14"/>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -3794,50 +3838,49 @@
       <c r="K45" s="13"/>
       <c r="L45" s="13"/>
       <c r="M45" s="13"/>
-      <c r="N45" s="13"/>
+      <c r="O45" s="16"/>
       <c r="P45" s="16"/>
       <c r="Q45" s="16"/>
       <c r="R45" s="16"/>
       <c r="S45" s="16"/>
-      <c r="T45" s="16"/>
-      <c r="U45" s="11"/>
+      <c r="T45" s="11"/>
+      <c r="U45" s="17"/>
       <c r="V45" s="17"/>
-      <c r="W45" s="17"/>
+      <c r="W45" s="16"/>
       <c r="X45" s="16"/>
       <c r="Y45" s="16"/>
-      <c r="Z45" s="16"/>
+      <c r="Z45" s="17"/>
       <c r="AA45" s="17"/>
       <c r="AB45" s="17"/>
       <c r="AC45" s="17"/>
       <c r="AD45" s="17"/>
       <c r="AE45" s="17"/>
-      <c r="AF45" s="17"/>
+      <c r="AF45" s="16"/>
       <c r="AG45" s="16"/>
       <c r="AH45" s="16"/>
       <c r="AI45" s="16"/>
-      <c r="AJ45" s="16"/>
+      <c r="AM45" s="12"/>
       <c r="AN45" s="12"/>
-      <c r="AO45" s="12"/>
-      <c r="AP45" s="5"/>
+      <c r="AO45" s="5"/>
+      <c r="AP45" s="12"/>
       <c r="AQ45" s="12"/>
-      <c r="AR45" s="12"/>
+      <c r="AR45" s="5"/>
       <c r="AS45" s="5"/>
-      <c r="AT45" s="5"/>
-      <c r="BO45" s="9"/>
-      <c r="BP45" s="10"/>
+      <c r="BN45" s="9"/>
+      <c r="BO45" s="10"/>
+      <c r="BP45" s="9"/>
       <c r="BQ45" s="9"/>
-      <c r="BR45" s="9"/>
+      <c r="BS45" s="10"/>
       <c r="BT45" s="10"/>
-      <c r="BU45" s="10"/>
+      <c r="BV45" s="10"/>
       <c r="BW45" s="10"/>
       <c r="BX45" s="10"/>
       <c r="BY45" s="10"/>
       <c r="BZ45" s="10"/>
       <c r="CA45" s="10"/>
       <c r="CB45" s="10"/>
-      <c r="CC45" s="10"/>
-    </row>
-    <row r="46" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B46" s="14"/>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -3850,50 +3893,49 @@
       <c r="K46" s="13"/>
       <c r="L46" s="13"/>
       <c r="M46" s="13"/>
-      <c r="N46" s="13"/>
+      <c r="O46" s="16"/>
       <c r="P46" s="16"/>
       <c r="Q46" s="16"/>
       <c r="R46" s="16"/>
       <c r="S46" s="16"/>
-      <c r="T46" s="16"/>
-      <c r="U46" s="11"/>
+      <c r="T46" s="11"/>
+      <c r="U46" s="17"/>
       <c r="V46" s="17"/>
-      <c r="W46" s="17"/>
+      <c r="W46" s="16"/>
       <c r="X46" s="16"/>
       <c r="Y46" s="16"/>
-      <c r="Z46" s="16"/>
+      <c r="Z46" s="17"/>
       <c r="AA46" s="17"/>
       <c r="AB46" s="17"/>
       <c r="AC46" s="17"/>
       <c r="AD46" s="17"/>
       <c r="AE46" s="17"/>
-      <c r="AF46" s="17"/>
+      <c r="AF46" s="16"/>
       <c r="AG46" s="16"/>
       <c r="AH46" s="16"/>
       <c r="AI46" s="16"/>
-      <c r="AJ46" s="16"/>
+      <c r="AM46" s="12"/>
       <c r="AN46" s="12"/>
-      <c r="AO46" s="12"/>
-      <c r="AP46" s="5"/>
+      <c r="AO46" s="5"/>
+      <c r="AP46" s="12"/>
       <c r="AQ46" s="12"/>
-      <c r="AR46" s="12"/>
+      <c r="AR46" s="5"/>
       <c r="AS46" s="5"/>
-      <c r="AT46" s="5"/>
-      <c r="BO46" s="9"/>
-      <c r="BP46" s="10"/>
+      <c r="BN46" s="9"/>
+      <c r="BO46" s="10"/>
+      <c r="BP46" s="9"/>
       <c r="BQ46" s="9"/>
-      <c r="BR46" s="9"/>
+      <c r="BS46" s="10"/>
       <c r="BT46" s="10"/>
-      <c r="BU46" s="10"/>
+      <c r="BV46" s="10"/>
       <c r="BW46" s="10"/>
       <c r="BX46" s="10"/>
       <c r="BY46" s="10"/>
       <c r="BZ46" s="10"/>
       <c r="CA46" s="10"/>
       <c r="CB46" s="10"/>
-      <c r="CC46" s="10"/>
-    </row>
-    <row r="47" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B47" s="14"/>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -3906,50 +3948,49 @@
       <c r="K47" s="13"/>
       <c r="L47" s="13"/>
       <c r="M47" s="13"/>
-      <c r="N47" s="13"/>
+      <c r="O47" s="16"/>
       <c r="P47" s="16"/>
       <c r="Q47" s="16"/>
       <c r="R47" s="16"/>
       <c r="S47" s="16"/>
-      <c r="T47" s="16"/>
-      <c r="U47" s="11"/>
+      <c r="T47" s="11"/>
+      <c r="U47" s="17"/>
       <c r="V47" s="17"/>
-      <c r="W47" s="17"/>
+      <c r="W47" s="16"/>
       <c r="X47" s="16"/>
       <c r="Y47" s="16"/>
-      <c r="Z47" s="16"/>
+      <c r="Z47" s="17"/>
       <c r="AA47" s="17"/>
       <c r="AB47" s="17"/>
       <c r="AC47" s="17"/>
       <c r="AD47" s="17"/>
       <c r="AE47" s="17"/>
-      <c r="AF47" s="17"/>
+      <c r="AF47" s="16"/>
       <c r="AG47" s="16"/>
       <c r="AH47" s="16"/>
       <c r="AI47" s="16"/>
-      <c r="AJ47" s="16"/>
+      <c r="AM47" s="12"/>
       <c r="AN47" s="12"/>
-      <c r="AO47" s="12"/>
-      <c r="AP47" s="5"/>
+      <c r="AO47" s="5"/>
+      <c r="AP47" s="12"/>
       <c r="AQ47" s="12"/>
-      <c r="AR47" s="12"/>
+      <c r="AR47" s="5"/>
       <c r="AS47" s="5"/>
-      <c r="AT47" s="5"/>
-      <c r="BO47" s="9"/>
-      <c r="BP47" s="10"/>
+      <c r="BN47" s="9"/>
+      <c r="BO47" s="10"/>
+      <c r="BP47" s="9"/>
       <c r="BQ47" s="9"/>
-      <c r="BR47" s="9"/>
+      <c r="BS47" s="10"/>
       <c r="BT47" s="10"/>
-      <c r="BU47" s="10"/>
+      <c r="BV47" s="10"/>
       <c r="BW47" s="10"/>
       <c r="BX47" s="10"/>
       <c r="BY47" s="10"/>
       <c r="BZ47" s="10"/>
       <c r="CA47" s="10"/>
       <c r="CB47" s="10"/>
-      <c r="CC47" s="10"/>
-    </row>
-    <row r="48" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B48" s="14"/>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -3962,50 +4003,49 @@
       <c r="K48" s="13"/>
       <c r="L48" s="13"/>
       <c r="M48" s="13"/>
-      <c r="N48" s="13"/>
+      <c r="O48" s="16"/>
       <c r="P48" s="16"/>
       <c r="Q48" s="16"/>
       <c r="R48" s="16"/>
       <c r="S48" s="16"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="11"/>
+      <c r="T48" s="11"/>
+      <c r="U48" s="17"/>
       <c r="V48" s="17"/>
-      <c r="W48" s="17"/>
+      <c r="W48" s="16"/>
       <c r="X48" s="16"/>
       <c r="Y48" s="16"/>
-      <c r="Z48" s="16"/>
+      <c r="Z48" s="17"/>
       <c r="AA48" s="17"/>
       <c r="AB48" s="17"/>
       <c r="AC48" s="17"/>
       <c r="AD48" s="17"/>
       <c r="AE48" s="17"/>
-      <c r="AF48" s="17"/>
+      <c r="AF48" s="16"/>
       <c r="AG48" s="16"/>
       <c r="AH48" s="16"/>
       <c r="AI48" s="16"/>
-      <c r="AJ48" s="16"/>
+      <c r="AM48" s="12"/>
       <c r="AN48" s="12"/>
-      <c r="AO48" s="12"/>
-      <c r="AP48" s="5"/>
+      <c r="AO48" s="5"/>
+      <c r="AP48" s="12"/>
       <c r="AQ48" s="12"/>
-      <c r="AR48" s="12"/>
+      <c r="AR48" s="5"/>
       <c r="AS48" s="5"/>
-      <c r="AT48" s="5"/>
-      <c r="BO48" s="9"/>
-      <c r="BP48" s="10"/>
+      <c r="BN48" s="9"/>
+      <c r="BO48" s="10"/>
+      <c r="BP48" s="9"/>
       <c r="BQ48" s="9"/>
-      <c r="BR48" s="9"/>
+      <c r="BS48" s="10"/>
       <c r="BT48" s="10"/>
-      <c r="BU48" s="10"/>
+      <c r="BV48" s="10"/>
       <c r="BW48" s="10"/>
       <c r="BX48" s="10"/>
       <c r="BY48" s="10"/>
       <c r="BZ48" s="10"/>
       <c r="CA48" s="10"/>
       <c r="CB48" s="10"/>
-      <c r="CC48" s="10"/>
-    </row>
-    <row r="49" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B49" s="14"/>
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
@@ -4018,50 +4058,49 @@
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
+      <c r="O49" s="16"/>
       <c r="P49" s="16"/>
       <c r="Q49" s="16"/>
       <c r="R49" s="16"/>
       <c r="S49" s="16"/>
-      <c r="T49" s="16"/>
-      <c r="U49" s="11"/>
+      <c r="T49" s="11"/>
+      <c r="U49" s="17"/>
       <c r="V49" s="17"/>
-      <c r="W49" s="17"/>
+      <c r="W49" s="16"/>
       <c r="X49" s="16"/>
       <c r="Y49" s="16"/>
-      <c r="Z49" s="16"/>
+      <c r="Z49" s="17"/>
       <c r="AA49" s="17"/>
       <c r="AB49" s="17"/>
       <c r="AC49" s="17"/>
       <c r="AD49" s="17"/>
       <c r="AE49" s="17"/>
-      <c r="AF49" s="17"/>
+      <c r="AF49" s="16"/>
       <c r="AG49" s="16"/>
       <c r="AH49" s="16"/>
       <c r="AI49" s="16"/>
-      <c r="AJ49" s="16"/>
+      <c r="AM49" s="12"/>
       <c r="AN49" s="12"/>
-      <c r="AO49" s="12"/>
-      <c r="AP49" s="5"/>
+      <c r="AO49" s="5"/>
+      <c r="AP49" s="12"/>
       <c r="AQ49" s="12"/>
-      <c r="AR49" s="12"/>
+      <c r="AR49" s="5"/>
       <c r="AS49" s="5"/>
-      <c r="AT49" s="5"/>
-      <c r="BO49" s="9"/>
-      <c r="BP49" s="10"/>
+      <c r="BN49" s="9"/>
+      <c r="BO49" s="10"/>
+      <c r="BP49" s="9"/>
       <c r="BQ49" s="9"/>
-      <c r="BR49" s="9"/>
+      <c r="BS49" s="10"/>
       <c r="BT49" s="10"/>
-      <c r="BU49" s="10"/>
+      <c r="BV49" s="10"/>
       <c r="BW49" s="10"/>
       <c r="BX49" s="10"/>
       <c r="BY49" s="10"/>
       <c r="BZ49" s="10"/>
       <c r="CA49" s="10"/>
       <c r="CB49" s="10"/>
-      <c r="CC49" s="10"/>
-    </row>
-    <row r="50" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B50" s="14"/>
       <c r="C50" s="13"/>
       <c r="D50" s="13"/>
@@ -4074,50 +4113,49 @@
       <c r="K50" s="13"/>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
+      <c r="O50" s="16"/>
       <c r="P50" s="16"/>
       <c r="Q50" s="16"/>
       <c r="R50" s="16"/>
       <c r="S50" s="16"/>
-      <c r="T50" s="16"/>
-      <c r="U50" s="11"/>
+      <c r="T50" s="11"/>
+      <c r="U50" s="17"/>
       <c r="V50" s="17"/>
-      <c r="W50" s="17"/>
+      <c r="W50" s="16"/>
       <c r="X50" s="16"/>
       <c r="Y50" s="16"/>
-      <c r="Z50" s="16"/>
+      <c r="Z50" s="17"/>
       <c r="AA50" s="17"/>
       <c r="AB50" s="17"/>
       <c r="AC50" s="17"/>
       <c r="AD50" s="17"/>
       <c r="AE50" s="17"/>
-      <c r="AF50" s="17"/>
+      <c r="AF50" s="16"/>
       <c r="AG50" s="16"/>
       <c r="AH50" s="16"/>
       <c r="AI50" s="16"/>
-      <c r="AJ50" s="16"/>
+      <c r="AM50" s="12"/>
       <c r="AN50" s="12"/>
-      <c r="AO50" s="12"/>
-      <c r="AP50" s="5"/>
+      <c r="AO50" s="5"/>
+      <c r="AP50" s="12"/>
       <c r="AQ50" s="12"/>
-      <c r="AR50" s="12"/>
+      <c r="AR50" s="5"/>
       <c r="AS50" s="5"/>
-      <c r="AT50" s="5"/>
-      <c r="BO50" s="9"/>
-      <c r="BP50" s="10"/>
+      <c r="BN50" s="9"/>
+      <c r="BO50" s="10"/>
+      <c r="BP50" s="9"/>
       <c r="BQ50" s="9"/>
-      <c r="BR50" s="9"/>
+      <c r="BS50" s="10"/>
       <c r="BT50" s="10"/>
-      <c r="BU50" s="10"/>
+      <c r="BV50" s="10"/>
       <c r="BW50" s="10"/>
       <c r="BX50" s="10"/>
       <c r="BY50" s="10"/>
       <c r="BZ50" s="10"/>
       <c r="CA50" s="10"/>
       <c r="CB50" s="10"/>
-      <c r="CC50" s="10"/>
-    </row>
-    <row r="51" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B51" s="14"/>
       <c r="C51" s="13"/>
       <c r="D51" s="13"/>
@@ -4130,50 +4168,49 @@
       <c r="K51" s="13"/>
       <c r="L51" s="13"/>
       <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
+      <c r="O51" s="16"/>
       <c r="P51" s="16"/>
       <c r="Q51" s="16"/>
       <c r="R51" s="16"/>
       <c r="S51" s="16"/>
-      <c r="T51" s="16"/>
-      <c r="U51" s="11"/>
+      <c r="T51" s="11"/>
+      <c r="U51" s="17"/>
       <c r="V51" s="17"/>
-      <c r="W51" s="17"/>
+      <c r="W51" s="16"/>
       <c r="X51" s="16"/>
       <c r="Y51" s="16"/>
-      <c r="Z51" s="16"/>
+      <c r="Z51" s="17"/>
       <c r="AA51" s="17"/>
       <c r="AB51" s="17"/>
       <c r="AC51" s="17"/>
       <c r="AD51" s="17"/>
       <c r="AE51" s="17"/>
-      <c r="AF51" s="17"/>
+      <c r="AF51" s="16"/>
       <c r="AG51" s="16"/>
       <c r="AH51" s="16"/>
       <c r="AI51" s="16"/>
-      <c r="AJ51" s="16"/>
+      <c r="AM51" s="12"/>
       <c r="AN51" s="12"/>
-      <c r="AO51" s="12"/>
-      <c r="AP51" s="5"/>
+      <c r="AO51" s="5"/>
+      <c r="AP51" s="12"/>
       <c r="AQ51" s="12"/>
-      <c r="AR51" s="12"/>
+      <c r="AR51" s="5"/>
       <c r="AS51" s="5"/>
-      <c r="AT51" s="5"/>
-      <c r="BO51" s="9"/>
-      <c r="BP51" s="10"/>
+      <c r="BN51" s="9"/>
+      <c r="BO51" s="10"/>
+      <c r="BP51" s="9"/>
       <c r="BQ51" s="9"/>
-      <c r="BR51" s="9"/>
+      <c r="BS51" s="10"/>
       <c r="BT51" s="10"/>
-      <c r="BU51" s="10"/>
+      <c r="BV51" s="10"/>
       <c r="BW51" s="10"/>
       <c r="BX51" s="10"/>
       <c r="BY51" s="10"/>
       <c r="BZ51" s="10"/>
       <c r="CA51" s="10"/>
       <c r="CB51" s="10"/>
-      <c r="CC51" s="10"/>
-    </row>
-    <row r="52" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B52" s="14"/>
       <c r="C52" s="13"/>
       <c r="D52" s="13"/>
@@ -4186,50 +4223,49 @@
       <c r="K52" s="13"/>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
-      <c r="N52" s="13"/>
+      <c r="O52" s="16"/>
       <c r="P52" s="16"/>
       <c r="Q52" s="16"/>
       <c r="R52" s="16"/>
       <c r="S52" s="16"/>
-      <c r="T52" s="16"/>
-      <c r="U52" s="11"/>
+      <c r="T52" s="11"/>
+      <c r="U52" s="17"/>
       <c r="V52" s="17"/>
-      <c r="W52" s="17"/>
+      <c r="W52" s="16"/>
       <c r="X52" s="16"/>
       <c r="Y52" s="16"/>
-      <c r="Z52" s="16"/>
+      <c r="Z52" s="17"/>
       <c r="AA52" s="17"/>
       <c r="AB52" s="17"/>
       <c r="AC52" s="17"/>
       <c r="AD52" s="17"/>
       <c r="AE52" s="17"/>
-      <c r="AF52" s="17"/>
+      <c r="AF52" s="16"/>
       <c r="AG52" s="16"/>
       <c r="AH52" s="16"/>
       <c r="AI52" s="16"/>
-      <c r="AJ52" s="16"/>
+      <c r="AM52" s="12"/>
       <c r="AN52" s="12"/>
-      <c r="AO52" s="12"/>
-      <c r="AP52" s="5"/>
+      <c r="AO52" s="5"/>
+      <c r="AP52" s="12"/>
       <c r="AQ52" s="12"/>
-      <c r="AR52" s="12"/>
+      <c r="AR52" s="5"/>
       <c r="AS52" s="5"/>
-      <c r="AT52" s="5"/>
-      <c r="BO52" s="9"/>
-      <c r="BP52" s="10"/>
+      <c r="BN52" s="9"/>
+      <c r="BO52" s="10"/>
+      <c r="BP52" s="9"/>
       <c r="BQ52" s="9"/>
-      <c r="BR52" s="9"/>
+      <c r="BS52" s="10"/>
       <c r="BT52" s="10"/>
-      <c r="BU52" s="10"/>
+      <c r="BV52" s="10"/>
       <c r="BW52" s="10"/>
       <c r="BX52" s="10"/>
       <c r="BY52" s="10"/>
       <c r="BZ52" s="10"/>
       <c r="CA52" s="10"/>
       <c r="CB52" s="10"/>
-      <c r="CC52" s="10"/>
-    </row>
-    <row r="53" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B53" s="14"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -4242,50 +4278,49 @@
       <c r="K53" s="13"/>
       <c r="L53" s="13"/>
       <c r="M53" s="13"/>
-      <c r="N53" s="13"/>
+      <c r="O53" s="16"/>
       <c r="P53" s="16"/>
       <c r="Q53" s="16"/>
       <c r="R53" s="16"/>
       <c r="S53" s="16"/>
-      <c r="T53" s="16"/>
-      <c r="U53" s="11"/>
+      <c r="T53" s="11"/>
+      <c r="U53" s="17"/>
       <c r="V53" s="17"/>
-      <c r="W53" s="17"/>
+      <c r="W53" s="16"/>
       <c r="X53" s="16"/>
       <c r="Y53" s="16"/>
-      <c r="Z53" s="16"/>
+      <c r="Z53" s="17"/>
       <c r="AA53" s="17"/>
       <c r="AB53" s="17"/>
       <c r="AC53" s="17"/>
       <c r="AD53" s="17"/>
       <c r="AE53" s="17"/>
-      <c r="AF53" s="17"/>
+      <c r="AF53" s="16"/>
       <c r="AG53" s="16"/>
       <c r="AH53" s="16"/>
       <c r="AI53" s="16"/>
-      <c r="AJ53" s="16"/>
+      <c r="AM53" s="12"/>
       <c r="AN53" s="12"/>
-      <c r="AO53" s="12"/>
-      <c r="AP53" s="5"/>
+      <c r="AO53" s="5"/>
+      <c r="AP53" s="12"/>
       <c r="AQ53" s="12"/>
-      <c r="AR53" s="12"/>
+      <c r="AR53" s="5"/>
       <c r="AS53" s="5"/>
-      <c r="AT53" s="5"/>
-      <c r="BO53" s="9"/>
-      <c r="BP53" s="10"/>
+      <c r="BN53" s="9"/>
+      <c r="BO53" s="10"/>
+      <c r="BP53" s="9"/>
       <c r="BQ53" s="9"/>
-      <c r="BR53" s="9"/>
+      <c r="BS53" s="10"/>
       <c r="BT53" s="10"/>
-      <c r="BU53" s="10"/>
+      <c r="BV53" s="10"/>
       <c r="BW53" s="10"/>
       <c r="BX53" s="10"/>
       <c r="BY53" s="10"/>
       <c r="BZ53" s="10"/>
       <c r="CA53" s="10"/>
       <c r="CB53" s="10"/>
-      <c r="CC53" s="10"/>
-    </row>
-    <row r="54" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B54" s="14"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
@@ -4298,50 +4333,49 @@
       <c r="K54" s="13"/>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
-      <c r="N54" s="13"/>
+      <c r="O54" s="16"/>
       <c r="P54" s="16"/>
       <c r="Q54" s="16"/>
       <c r="R54" s="16"/>
       <c r="S54" s="16"/>
-      <c r="T54" s="16"/>
-      <c r="U54" s="11"/>
+      <c r="T54" s="11"/>
+      <c r="U54" s="17"/>
       <c r="V54" s="17"/>
-      <c r="W54" s="17"/>
+      <c r="W54" s="16"/>
       <c r="X54" s="16"/>
       <c r="Y54" s="16"/>
-      <c r="Z54" s="16"/>
+      <c r="Z54" s="17"/>
       <c r="AA54" s="17"/>
       <c r="AB54" s="17"/>
       <c r="AC54" s="17"/>
       <c r="AD54" s="17"/>
       <c r="AE54" s="17"/>
-      <c r="AF54" s="17"/>
+      <c r="AF54" s="16"/>
       <c r="AG54" s="16"/>
       <c r="AH54" s="16"/>
       <c r="AI54" s="16"/>
-      <c r="AJ54" s="16"/>
+      <c r="AM54" s="12"/>
       <c r="AN54" s="12"/>
-      <c r="AO54" s="12"/>
-      <c r="AP54" s="5"/>
+      <c r="AO54" s="5"/>
+      <c r="AP54" s="12"/>
       <c r="AQ54" s="12"/>
-      <c r="AR54" s="12"/>
+      <c r="AR54" s="5"/>
       <c r="AS54" s="5"/>
-      <c r="AT54" s="5"/>
-      <c r="BO54" s="9"/>
-      <c r="BP54" s="10"/>
+      <c r="BN54" s="9"/>
+      <c r="BO54" s="10"/>
+      <c r="BP54" s="9"/>
       <c r="BQ54" s="9"/>
-      <c r="BR54" s="9"/>
+      <c r="BS54" s="10"/>
       <c r="BT54" s="10"/>
-      <c r="BU54" s="10"/>
+      <c r="BV54" s="10"/>
       <c r="BW54" s="10"/>
       <c r="BX54" s="10"/>
       <c r="BY54" s="10"/>
       <c r="BZ54" s="10"/>
       <c r="CA54" s="10"/>
       <c r="CB54" s="10"/>
-      <c r="CC54" s="10"/>
-    </row>
-    <row r="55" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B55" s="14"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
@@ -4354,50 +4388,49 @@
       <c r="K55" s="13"/>
       <c r="L55" s="13"/>
       <c r="M55" s="13"/>
-      <c r="N55" s="13"/>
+      <c r="O55" s="16"/>
       <c r="P55" s="16"/>
       <c r="Q55" s="16"/>
       <c r="R55" s="16"/>
       <c r="S55" s="16"/>
-      <c r="T55" s="16"/>
-      <c r="U55" s="11"/>
+      <c r="T55" s="11"/>
+      <c r="U55" s="17"/>
       <c r="V55" s="17"/>
-      <c r="W55" s="17"/>
+      <c r="W55" s="16"/>
       <c r="X55" s="16"/>
       <c r="Y55" s="16"/>
-      <c r="Z55" s="16"/>
+      <c r="Z55" s="17"/>
       <c r="AA55" s="17"/>
       <c r="AB55" s="17"/>
       <c r="AC55" s="17"/>
       <c r="AD55" s="17"/>
       <c r="AE55" s="17"/>
-      <c r="AF55" s="17"/>
+      <c r="AF55" s="16"/>
       <c r="AG55" s="16"/>
       <c r="AH55" s="16"/>
       <c r="AI55" s="16"/>
-      <c r="AJ55" s="16"/>
+      <c r="AM55" s="12"/>
       <c r="AN55" s="12"/>
-      <c r="AO55" s="12"/>
-      <c r="AP55" s="5"/>
+      <c r="AO55" s="5"/>
+      <c r="AP55" s="12"/>
       <c r="AQ55" s="12"/>
-      <c r="AR55" s="12"/>
+      <c r="AR55" s="5"/>
       <c r="AS55" s="5"/>
-      <c r="AT55" s="5"/>
-      <c r="BO55" s="9"/>
-      <c r="BP55" s="10"/>
+      <c r="BN55" s="9"/>
+      <c r="BO55" s="10"/>
+      <c r="BP55" s="9"/>
       <c r="BQ55" s="9"/>
-      <c r="BR55" s="9"/>
+      <c r="BS55" s="10"/>
       <c r="BT55" s="10"/>
-      <c r="BU55" s="10"/>
+      <c r="BV55" s="10"/>
       <c r="BW55" s="10"/>
       <c r="BX55" s="10"/>
       <c r="BY55" s="10"/>
       <c r="BZ55" s="10"/>
       <c r="CA55" s="10"/>
       <c r="CB55" s="10"/>
-      <c r="CC55" s="10"/>
-    </row>
-    <row r="56" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B56" s="14"/>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
@@ -4410,50 +4443,49 @@
       <c r="K56" s="13"/>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
-      <c r="N56" s="13"/>
+      <c r="O56" s="16"/>
       <c r="P56" s="16"/>
       <c r="Q56" s="16"/>
       <c r="R56" s="16"/>
       <c r="S56" s="16"/>
-      <c r="T56" s="16"/>
-      <c r="U56" s="11"/>
+      <c r="T56" s="11"/>
+      <c r="U56" s="17"/>
       <c r="V56" s="17"/>
-      <c r="W56" s="17"/>
+      <c r="W56" s="16"/>
       <c r="X56" s="16"/>
       <c r="Y56" s="16"/>
-      <c r="Z56" s="16"/>
+      <c r="Z56" s="17"/>
       <c r="AA56" s="17"/>
       <c r="AB56" s="17"/>
       <c r="AC56" s="17"/>
       <c r="AD56" s="17"/>
       <c r="AE56" s="17"/>
-      <c r="AF56" s="17"/>
+      <c r="AF56" s="16"/>
       <c r="AG56" s="16"/>
       <c r="AH56" s="16"/>
       <c r="AI56" s="16"/>
-      <c r="AJ56" s="16"/>
+      <c r="AM56" s="12"/>
       <c r="AN56" s="12"/>
-      <c r="AO56" s="12"/>
-      <c r="AP56" s="5"/>
+      <c r="AO56" s="5"/>
+      <c r="AP56" s="12"/>
       <c r="AQ56" s="12"/>
-      <c r="AR56" s="12"/>
+      <c r="AR56" s="5"/>
       <c r="AS56" s="5"/>
-      <c r="AT56" s="5"/>
-      <c r="BO56" s="9"/>
-      <c r="BP56" s="10"/>
+      <c r="BN56" s="9"/>
+      <c r="BO56" s="10"/>
+      <c r="BP56" s="9"/>
       <c r="BQ56" s="9"/>
-      <c r="BR56" s="9"/>
+      <c r="BS56" s="10"/>
       <c r="BT56" s="10"/>
-      <c r="BU56" s="10"/>
+      <c r="BV56" s="10"/>
       <c r="BW56" s="10"/>
       <c r="BX56" s="10"/>
       <c r="BY56" s="10"/>
       <c r="BZ56" s="10"/>
       <c r="CA56" s="10"/>
       <c r="CB56" s="10"/>
-      <c r="CC56" s="10"/>
-    </row>
-    <row r="57" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B57" s="14"/>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
@@ -4466,50 +4498,49 @@
       <c r="K57" s="13"/>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
-      <c r="N57" s="13"/>
+      <c r="O57" s="16"/>
       <c r="P57" s="16"/>
       <c r="Q57" s="16"/>
       <c r="R57" s="16"/>
       <c r="S57" s="16"/>
-      <c r="T57" s="16"/>
-      <c r="U57" s="11"/>
+      <c r="T57" s="11"/>
+      <c r="U57" s="17"/>
       <c r="V57" s="17"/>
-      <c r="W57" s="17"/>
+      <c r="W57" s="16"/>
       <c r="X57" s="16"/>
       <c r="Y57" s="16"/>
-      <c r="Z57" s="16"/>
+      <c r="Z57" s="17"/>
       <c r="AA57" s="17"/>
       <c r="AB57" s="17"/>
       <c r="AC57" s="17"/>
       <c r="AD57" s="17"/>
       <c r="AE57" s="17"/>
-      <c r="AF57" s="17"/>
+      <c r="AF57" s="16"/>
       <c r="AG57" s="16"/>
       <c r="AH57" s="16"/>
       <c r="AI57" s="16"/>
-      <c r="AJ57" s="16"/>
+      <c r="AM57" s="12"/>
       <c r="AN57" s="12"/>
-      <c r="AO57" s="12"/>
-      <c r="AP57" s="5"/>
+      <c r="AO57" s="5"/>
+      <c r="AP57" s="12"/>
       <c r="AQ57" s="12"/>
-      <c r="AR57" s="12"/>
+      <c r="AR57" s="5"/>
       <c r="AS57" s="5"/>
-      <c r="AT57" s="5"/>
-      <c r="BO57" s="9"/>
-      <c r="BP57" s="10"/>
+      <c r="BN57" s="9"/>
+      <c r="BO57" s="10"/>
+      <c r="BP57" s="9"/>
       <c r="BQ57" s="9"/>
-      <c r="BR57" s="9"/>
+      <c r="BS57" s="10"/>
       <c r="BT57" s="10"/>
-      <c r="BU57" s="10"/>
+      <c r="BV57" s="10"/>
       <c r="BW57" s="10"/>
       <c r="BX57" s="10"/>
       <c r="BY57" s="10"/>
       <c r="BZ57" s="10"/>
       <c r="CA57" s="10"/>
       <c r="CB57" s="10"/>
-      <c r="CC57" s="10"/>
-    </row>
-    <row r="58" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B58" s="14"/>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
@@ -4522,50 +4553,49 @@
       <c r="K58" s="13"/>
       <c r="L58" s="13"/>
       <c r="M58" s="13"/>
-      <c r="N58" s="13"/>
+      <c r="O58" s="17"/>
       <c r="P58" s="17"/>
-      <c r="Q58" s="17"/>
+      <c r="Q58" s="16"/>
       <c r="R58" s="16"/>
       <c r="S58" s="16"/>
-      <c r="T58" s="16"/>
-      <c r="U58" s="11"/>
+      <c r="T58" s="11"/>
+      <c r="U58" s="17"/>
       <c r="V58" s="17"/>
-      <c r="W58" s="17"/>
+      <c r="W58" s="16"/>
       <c r="X58" s="16"/>
-      <c r="Y58" s="16"/>
+      <c r="Y58" s="17"/>
       <c r="Z58" s="17"/>
       <c r="AA58" s="17"/>
       <c r="AB58" s="17"/>
       <c r="AC58" s="17"/>
       <c r="AD58" s="17"/>
       <c r="AE58" s="17"/>
-      <c r="AF58" s="17"/>
+      <c r="AF58" s="16"/>
       <c r="AG58" s="16"/>
       <c r="AH58" s="16"/>
       <c r="AI58" s="16"/>
-      <c r="AJ58" s="16"/>
+      <c r="AM58" s="12"/>
       <c r="AN58" s="12"/>
-      <c r="AO58" s="12"/>
-      <c r="AP58" s="5"/>
+      <c r="AO58" s="5"/>
+      <c r="AP58" s="12"/>
       <c r="AQ58" s="12"/>
-      <c r="AR58" s="12"/>
+      <c r="AR58" s="5"/>
       <c r="AS58" s="5"/>
-      <c r="AT58" s="5"/>
-      <c r="BO58" s="9"/>
-      <c r="BP58" s="10"/>
+      <c r="BN58" s="9"/>
+      <c r="BO58" s="10"/>
+      <c r="BP58" s="9"/>
       <c r="BQ58" s="9"/>
-      <c r="BR58" s="9"/>
+      <c r="BS58" s="10"/>
       <c r="BT58" s="10"/>
-      <c r="BU58" s="10"/>
+      <c r="BV58" s="10"/>
       <c r="BW58" s="10"/>
       <c r="BX58" s="10"/>
       <c r="BY58" s="10"/>
       <c r="BZ58" s="10"/>
       <c r="CA58" s="10"/>
       <c r="CB58" s="10"/>
-      <c r="CC58" s="10"/>
-    </row>
-    <row r="59" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B59" s="14"/>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
@@ -4578,50 +4608,49 @@
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
       <c r="M59" s="13"/>
-      <c r="N59" s="13"/>
+      <c r="O59" s="17"/>
       <c r="P59" s="17"/>
-      <c r="Q59" s="17"/>
+      <c r="Q59" s="16"/>
       <c r="R59" s="16"/>
       <c r="S59" s="16"/>
-      <c r="T59" s="16"/>
-      <c r="U59" s="11"/>
+      <c r="T59" s="11"/>
+      <c r="U59" s="17"/>
       <c r="V59" s="17"/>
-      <c r="W59" s="17"/>
+      <c r="W59" s="16"/>
       <c r="X59" s="16"/>
-      <c r="Y59" s="16"/>
+      <c r="Y59" s="17"/>
       <c r="Z59" s="17"/>
       <c r="AA59" s="17"/>
       <c r="AB59" s="17"/>
       <c r="AC59" s="17"/>
       <c r="AD59" s="17"/>
       <c r="AE59" s="17"/>
-      <c r="AF59" s="17"/>
+      <c r="AF59" s="16"/>
       <c r="AG59" s="16"/>
       <c r="AH59" s="16"/>
       <c r="AI59" s="16"/>
-      <c r="AJ59" s="16"/>
+      <c r="AM59" s="12"/>
       <c r="AN59" s="12"/>
-      <c r="AO59" s="12"/>
-      <c r="AP59" s="5"/>
+      <c r="AO59" s="5"/>
+      <c r="AP59" s="12"/>
       <c r="AQ59" s="12"/>
-      <c r="AR59" s="12"/>
+      <c r="AR59" s="5"/>
       <c r="AS59" s="5"/>
-      <c r="AT59" s="5"/>
-      <c r="BO59" s="9"/>
-      <c r="BP59" s="10"/>
+      <c r="BN59" s="9"/>
+      <c r="BO59" s="10"/>
+      <c r="BP59" s="9"/>
       <c r="BQ59" s="9"/>
-      <c r="BR59" s="9"/>
+      <c r="BS59" s="10"/>
       <c r="BT59" s="10"/>
-      <c r="BU59" s="10"/>
+      <c r="BV59" s="10"/>
       <c r="BW59" s="10"/>
       <c r="BX59" s="10"/>
       <c r="BY59" s="10"/>
       <c r="BZ59" s="10"/>
       <c r="CA59" s="10"/>
       <c r="CB59" s="10"/>
-      <c r="CC59" s="10"/>
-    </row>
-    <row r="60" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B60" s="14"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
@@ -4634,50 +4663,49 @@
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
       <c r="M60" s="13"/>
-      <c r="N60" s="13"/>
+      <c r="O60" s="17"/>
       <c r="P60" s="17"/>
-      <c r="Q60" s="17"/>
+      <c r="Q60" s="16"/>
       <c r="R60" s="16"/>
       <c r="S60" s="16"/>
-      <c r="T60" s="16"/>
-      <c r="U60" s="11"/>
+      <c r="T60" s="11"/>
+      <c r="U60" s="17"/>
       <c r="V60" s="17"/>
-      <c r="W60" s="17"/>
+      <c r="W60" s="16"/>
       <c r="X60" s="16"/>
-      <c r="Y60" s="16"/>
+      <c r="Y60" s="17"/>
       <c r="Z60" s="17"/>
       <c r="AA60" s="17"/>
       <c r="AB60" s="17"/>
       <c r="AC60" s="17"/>
       <c r="AD60" s="17"/>
       <c r="AE60" s="17"/>
-      <c r="AF60" s="17"/>
+      <c r="AF60" s="16"/>
       <c r="AG60" s="16"/>
       <c r="AH60" s="16"/>
       <c r="AI60" s="16"/>
-      <c r="AJ60" s="16"/>
+      <c r="AM60" s="12"/>
       <c r="AN60" s="12"/>
-      <c r="AO60" s="12"/>
-      <c r="AP60" s="5"/>
+      <c r="AO60" s="5"/>
+      <c r="AP60" s="12"/>
       <c r="AQ60" s="12"/>
-      <c r="AR60" s="12"/>
+      <c r="AR60" s="5"/>
       <c r="AS60" s="5"/>
-      <c r="AT60" s="5"/>
-      <c r="BO60" s="9"/>
-      <c r="BP60" s="10"/>
+      <c r="BN60" s="9"/>
+      <c r="BO60" s="10"/>
+      <c r="BP60" s="9"/>
       <c r="BQ60" s="9"/>
-      <c r="BR60" s="9"/>
+      <c r="BS60" s="10"/>
       <c r="BT60" s="10"/>
-      <c r="BU60" s="10"/>
+      <c r="BV60" s="10"/>
       <c r="BW60" s="10"/>
       <c r="BX60" s="10"/>
       <c r="BY60" s="10"/>
       <c r="BZ60" s="10"/>
       <c r="CA60" s="10"/>
       <c r="CB60" s="10"/>
-      <c r="CC60" s="10"/>
-    </row>
-    <row r="61" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B61" s="14"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
@@ -4690,50 +4718,49 @@
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
-      <c r="N61" s="13"/>
+      <c r="O61" s="17"/>
       <c r="P61" s="17"/>
-      <c r="Q61" s="17"/>
+      <c r="Q61" s="16"/>
       <c r="R61" s="16"/>
       <c r="S61" s="16"/>
-      <c r="T61" s="16"/>
-      <c r="U61" s="11"/>
+      <c r="T61" s="11"/>
+      <c r="U61" s="17"/>
       <c r="V61" s="17"/>
-      <c r="W61" s="17"/>
+      <c r="W61" s="16"/>
       <c r="X61" s="16"/>
-      <c r="Y61" s="16"/>
+      <c r="Y61" s="17"/>
       <c r="Z61" s="17"/>
       <c r="AA61" s="17"/>
       <c r="AB61" s="17"/>
       <c r="AC61" s="17"/>
       <c r="AD61" s="17"/>
       <c r="AE61" s="17"/>
-      <c r="AF61" s="17"/>
+      <c r="AF61" s="16"/>
       <c r="AG61" s="16"/>
       <c r="AH61" s="16"/>
       <c r="AI61" s="16"/>
-      <c r="AJ61" s="16"/>
+      <c r="AM61" s="12"/>
       <c r="AN61" s="12"/>
-      <c r="AO61" s="12"/>
-      <c r="AP61" s="5"/>
+      <c r="AO61" s="5"/>
+      <c r="AP61" s="12"/>
       <c r="AQ61" s="12"/>
-      <c r="AR61" s="12"/>
+      <c r="AR61" s="5"/>
       <c r="AS61" s="5"/>
-      <c r="AT61" s="5"/>
-      <c r="BO61" s="9"/>
-      <c r="BP61" s="10"/>
+      <c r="BN61" s="9"/>
+      <c r="BO61" s="10"/>
+      <c r="BP61" s="9"/>
       <c r="BQ61" s="9"/>
-      <c r="BR61" s="9"/>
+      <c r="BS61" s="10"/>
       <c r="BT61" s="10"/>
-      <c r="BU61" s="10"/>
+      <c r="BV61" s="10"/>
       <c r="BW61" s="10"/>
       <c r="BX61" s="10"/>
       <c r="BY61" s="10"/>
       <c r="BZ61" s="10"/>
       <c r="CA61" s="10"/>
       <c r="CB61" s="10"/>
-      <c r="CC61" s="10"/>
-    </row>
-    <row r="62" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B62" s="14"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
@@ -4746,50 +4773,49 @@
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
-      <c r="N62" s="13"/>
+      <c r="O62" s="17"/>
       <c r="P62" s="17"/>
-      <c r="Q62" s="17"/>
+      <c r="Q62" s="16"/>
       <c r="R62" s="16"/>
       <c r="S62" s="16"/>
-      <c r="T62" s="16"/>
-      <c r="U62" s="11"/>
+      <c r="T62" s="11"/>
+      <c r="U62" s="17"/>
       <c r="V62" s="17"/>
-      <c r="W62" s="17"/>
+      <c r="W62" s="16"/>
       <c r="X62" s="16"/>
-      <c r="Y62" s="16"/>
+      <c r="Y62" s="17"/>
       <c r="Z62" s="17"/>
       <c r="AA62" s="17"/>
       <c r="AB62" s="17"/>
       <c r="AC62" s="17"/>
       <c r="AD62" s="17"/>
       <c r="AE62" s="17"/>
-      <c r="AF62" s="17"/>
+      <c r="AF62" s="16"/>
       <c r="AG62" s="16"/>
       <c r="AH62" s="16"/>
       <c r="AI62" s="16"/>
-      <c r="AJ62" s="16"/>
+      <c r="AM62" s="12"/>
       <c r="AN62" s="12"/>
-      <c r="AO62" s="12"/>
-      <c r="AP62" s="5"/>
+      <c r="AO62" s="5"/>
+      <c r="AP62" s="12"/>
       <c r="AQ62" s="12"/>
-      <c r="AR62" s="12"/>
+      <c r="AR62" s="5"/>
       <c r="AS62" s="5"/>
-      <c r="AT62" s="5"/>
-      <c r="BO62" s="9"/>
-      <c r="BP62" s="10"/>
+      <c r="BN62" s="9"/>
+      <c r="BO62" s="10"/>
+      <c r="BP62" s="9"/>
       <c r="BQ62" s="9"/>
-      <c r="BR62" s="9"/>
+      <c r="BS62" s="10"/>
       <c r="BT62" s="10"/>
-      <c r="BU62" s="10"/>
+      <c r="BV62" s="10"/>
       <c r="BW62" s="10"/>
       <c r="BX62" s="10"/>
       <c r="BY62" s="10"/>
       <c r="BZ62" s="10"/>
       <c r="CA62" s="10"/>
       <c r="CB62" s="10"/>
-      <c r="CC62" s="10"/>
-    </row>
-    <row r="63" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B63" s="14"/>
       <c r="C63" s="13"/>
       <c r="D63" s="13"/>
@@ -4802,50 +4828,49 @@
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
-      <c r="N63" s="13"/>
+      <c r="O63" s="17"/>
       <c r="P63" s="17"/>
-      <c r="Q63" s="17"/>
+      <c r="Q63" s="16"/>
       <c r="R63" s="16"/>
       <c r="S63" s="16"/>
-      <c r="T63" s="16"/>
-      <c r="U63" s="11"/>
+      <c r="T63" s="11"/>
+      <c r="U63" s="17"/>
       <c r="V63" s="17"/>
-      <c r="W63" s="17"/>
+      <c r="W63" s="16"/>
       <c r="X63" s="16"/>
-      <c r="Y63" s="16"/>
+      <c r="Y63" s="17"/>
       <c r="Z63" s="17"/>
       <c r="AA63" s="17"/>
       <c r="AB63" s="17"/>
       <c r="AC63" s="17"/>
       <c r="AD63" s="17"/>
       <c r="AE63" s="17"/>
-      <c r="AF63" s="17"/>
+      <c r="AF63" s="16"/>
       <c r="AG63" s="16"/>
       <c r="AH63" s="16"/>
       <c r="AI63" s="16"/>
-      <c r="AJ63" s="16"/>
+      <c r="AM63" s="12"/>
       <c r="AN63" s="12"/>
-      <c r="AO63" s="12"/>
-      <c r="AP63" s="5"/>
+      <c r="AO63" s="5"/>
+      <c r="AP63" s="12"/>
       <c r="AQ63" s="12"/>
-      <c r="AR63" s="12"/>
+      <c r="AR63" s="5"/>
       <c r="AS63" s="5"/>
-      <c r="AT63" s="5"/>
-      <c r="BO63" s="9"/>
-      <c r="BP63" s="10"/>
+      <c r="BN63" s="9"/>
+      <c r="BO63" s="10"/>
+      <c r="BP63" s="9"/>
       <c r="BQ63" s="9"/>
-      <c r="BR63" s="9"/>
+      <c r="BS63" s="10"/>
       <c r="BT63" s="10"/>
-      <c r="BU63" s="10"/>
+      <c r="BV63" s="10"/>
       <c r="BW63" s="10"/>
       <c r="BX63" s="10"/>
       <c r="BY63" s="10"/>
       <c r="BZ63" s="10"/>
       <c r="CA63" s="10"/>
       <c r="CB63" s="10"/>
-      <c r="CC63" s="10"/>
-    </row>
-    <row r="64" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B64" s="14"/>
       <c r="C64" s="13"/>
       <c r="D64" s="13"/>
@@ -4858,50 +4883,49 @@
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
       <c r="M64" s="13"/>
-      <c r="N64" s="13"/>
+      <c r="O64" s="17"/>
       <c r="P64" s="17"/>
-      <c r="Q64" s="17"/>
+      <c r="Q64" s="16"/>
       <c r="R64" s="16"/>
       <c r="S64" s="16"/>
-      <c r="T64" s="16"/>
-      <c r="U64" s="11"/>
+      <c r="T64" s="11"/>
+      <c r="U64" s="17"/>
       <c r="V64" s="17"/>
-      <c r="W64" s="17"/>
+      <c r="W64" s="16"/>
       <c r="X64" s="16"/>
-      <c r="Y64" s="16"/>
+      <c r="Y64" s="17"/>
       <c r="Z64" s="17"/>
       <c r="AA64" s="17"/>
       <c r="AB64" s="17"/>
       <c r="AC64" s="17"/>
       <c r="AD64" s="17"/>
       <c r="AE64" s="17"/>
-      <c r="AF64" s="17"/>
+      <c r="AF64" s="16"/>
       <c r="AG64" s="16"/>
       <c r="AH64" s="16"/>
       <c r="AI64" s="16"/>
-      <c r="AJ64" s="16"/>
+      <c r="AM64" s="12"/>
       <c r="AN64" s="12"/>
-      <c r="AO64" s="12"/>
-      <c r="AP64" s="5"/>
+      <c r="AO64" s="5"/>
+      <c r="AP64" s="12"/>
       <c r="AQ64" s="12"/>
-      <c r="AR64" s="12"/>
+      <c r="AR64" s="5"/>
       <c r="AS64" s="5"/>
-      <c r="AT64" s="5"/>
-      <c r="BO64" s="9"/>
-      <c r="BP64" s="10"/>
+      <c r="BN64" s="9"/>
+      <c r="BO64" s="10"/>
+      <c r="BP64" s="9"/>
       <c r="BQ64" s="9"/>
-      <c r="BR64" s="9"/>
+      <c r="BS64" s="10"/>
       <c r="BT64" s="10"/>
-      <c r="BU64" s="10"/>
+      <c r="BV64" s="10"/>
       <c r="BW64" s="10"/>
       <c r="BX64" s="10"/>
       <c r="BY64" s="10"/>
       <c r="BZ64" s="10"/>
       <c r="CA64" s="10"/>
       <c r="CB64" s="10"/>
-      <c r="CC64" s="10"/>
-    </row>
-    <row r="65" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B65" s="14"/>
       <c r="C65" s="13"/>
       <c r="D65" s="13"/>
@@ -4914,50 +4938,49 @@
       <c r="K65" s="13"/>
       <c r="L65" s="13"/>
       <c r="M65" s="13"/>
-      <c r="N65" s="13"/>
+      <c r="O65" s="17"/>
       <c r="P65" s="17"/>
-      <c r="Q65" s="17"/>
+      <c r="Q65" s="16"/>
       <c r="R65" s="16"/>
       <c r="S65" s="16"/>
-      <c r="T65" s="16"/>
-      <c r="U65" s="11"/>
+      <c r="T65" s="11"/>
+      <c r="U65" s="17"/>
       <c r="V65" s="17"/>
-      <c r="W65" s="17"/>
+      <c r="W65" s="16"/>
       <c r="X65" s="16"/>
-      <c r="Y65" s="16"/>
+      <c r="Y65" s="17"/>
       <c r="Z65" s="17"/>
       <c r="AA65" s="17"/>
       <c r="AB65" s="17"/>
       <c r="AC65" s="17"/>
       <c r="AD65" s="17"/>
       <c r="AE65" s="17"/>
-      <c r="AF65" s="17"/>
+      <c r="AF65" s="16"/>
       <c r="AG65" s="16"/>
       <c r="AH65" s="16"/>
       <c r="AI65" s="16"/>
-      <c r="AJ65" s="16"/>
+      <c r="AM65" s="12"/>
       <c r="AN65" s="12"/>
-      <c r="AO65" s="12"/>
-      <c r="AP65" s="5"/>
+      <c r="AO65" s="5"/>
+      <c r="AP65" s="12"/>
       <c r="AQ65" s="12"/>
-      <c r="AR65" s="12"/>
+      <c r="AR65" s="5"/>
       <c r="AS65" s="5"/>
-      <c r="AT65" s="5"/>
-      <c r="BO65" s="9"/>
-      <c r="BP65" s="10"/>
+      <c r="BN65" s="9"/>
+      <c r="BO65" s="10"/>
+      <c r="BP65" s="9"/>
       <c r="BQ65" s="9"/>
-      <c r="BR65" s="9"/>
+      <c r="BS65" s="10"/>
       <c r="BT65" s="10"/>
-      <c r="BU65" s="10"/>
+      <c r="BV65" s="10"/>
       <c r="BW65" s="10"/>
       <c r="BX65" s="10"/>
       <c r="BY65" s="10"/>
       <c r="BZ65" s="10"/>
       <c r="CA65" s="10"/>
       <c r="CB65" s="10"/>
-      <c r="CC65" s="10"/>
-    </row>
-    <row r="66" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="2:80" x14ac:dyDescent="0.2">
       <c r="B66" s="14"/>
       <c r="C66" s="13"/>
       <c r="D66" s="13"/>
@@ -4970,534 +4993,957 @@
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
       <c r="M66" s="13"/>
-      <c r="N66" s="13"/>
+      <c r="O66" s="17"/>
       <c r="P66" s="17"/>
-      <c r="Q66" s="17"/>
+      <c r="Q66" s="16"/>
       <c r="R66" s="16"/>
       <c r="S66" s="16"/>
-      <c r="T66" s="16"/>
-      <c r="U66" s="11"/>
+      <c r="T66" s="11"/>
+      <c r="U66" s="17"/>
       <c r="V66" s="17"/>
-      <c r="W66" s="17"/>
+      <c r="W66" s="16"/>
       <c r="X66" s="16"/>
-      <c r="Y66" s="16"/>
+      <c r="Y66" s="17"/>
       <c r="Z66" s="17"/>
       <c r="AA66" s="17"/>
       <c r="AB66" s="17"/>
       <c r="AC66" s="17"/>
       <c r="AD66" s="17"/>
       <c r="AE66" s="17"/>
-      <c r="AF66" s="17"/>
+      <c r="AF66" s="16"/>
       <c r="AG66" s="16"/>
       <c r="AH66" s="16"/>
       <c r="AI66" s="16"/>
-      <c r="AJ66" s="16"/>
+      <c r="AM66" s="12"/>
       <c r="AN66" s="12"/>
-      <c r="AO66" s="12"/>
-      <c r="AP66" s="5"/>
+      <c r="AO66" s="5"/>
+      <c r="AP66" s="12"/>
       <c r="AQ66" s="12"/>
-      <c r="AR66" s="12"/>
+      <c r="AR66" s="5"/>
       <c r="AS66" s="5"/>
-      <c r="AT66" s="5"/>
-      <c r="BO66" s="9"/>
-      <c r="BP66" s="10"/>
+      <c r="BN66" s="9"/>
+      <c r="BO66" s="10"/>
+      <c r="BP66" s="9"/>
       <c r="BQ66" s="9"/>
-      <c r="BR66" s="9"/>
+      <c r="BS66" s="10"/>
       <c r="BT66" s="10"/>
-      <c r="BU66" s="10"/>
+      <c r="BV66" s="10"/>
       <c r="BW66" s="10"/>
       <c r="BX66" s="10"/>
       <c r="BY66" s="10"/>
       <c r="BZ66" s="10"/>
       <c r="CA66" s="10"/>
       <c r="CB66" s="10"/>
-      <c r="CC66" s="10"/>
-    </row>
-    <row r="67" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM67" s="5"/>
       <c r="AN67" s="5"/>
       <c r="AO67" s="5"/>
       <c r="AP67" s="5"/>
       <c r="AQ67" s="5"/>
       <c r="AR67" s="5"/>
       <c r="AS67" s="5"/>
-      <c r="AT67" s="5"/>
-      <c r="BO67" s="8"/>
+      <c r="BN67" s="8"/>
+      <c r="BP67" s="8"/>
       <c r="BQ67" s="8"/>
-      <c r="BR67" s="8"/>
-    </row>
-    <row r="68" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM68" s="5"/>
       <c r="AN68" s="5"/>
       <c r="AO68" s="5"/>
       <c r="AP68" s="5"/>
       <c r="AQ68" s="5"/>
       <c r="AR68" s="5"/>
       <c r="AS68" s="5"/>
-      <c r="AT68" s="5"/>
-      <c r="BO68" s="8"/>
+      <c r="BN68" s="8"/>
+      <c r="BP68" s="8"/>
       <c r="BQ68" s="8"/>
-      <c r="BR68" s="8"/>
-    </row>
-    <row r="69" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM69" s="5"/>
       <c r="AN69" s="5"/>
       <c r="AO69" s="5"/>
       <c r="AP69" s="5"/>
       <c r="AQ69" s="5"/>
       <c r="AR69" s="5"/>
       <c r="AS69" s="5"/>
-      <c r="AT69" s="5"/>
-      <c r="BO69" s="8"/>
+      <c r="BN69" s="8"/>
+      <c r="BP69" s="8"/>
       <c r="BQ69" s="8"/>
-      <c r="BR69" s="8"/>
-    </row>
-    <row r="70" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM70" s="5"/>
       <c r="AN70" s="5"/>
       <c r="AO70" s="5"/>
       <c r="AP70" s="5"/>
       <c r="AQ70" s="5"/>
       <c r="AR70" s="5"/>
       <c r="AS70" s="5"/>
-      <c r="AT70" s="5"/>
-      <c r="BO70" s="8"/>
+      <c r="BN70" s="8"/>
+      <c r="BP70" s="8"/>
       <c r="BQ70" s="8"/>
-      <c r="BR70" s="8"/>
-    </row>
-    <row r="71" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM71" s="5"/>
       <c r="AN71" s="5"/>
       <c r="AO71" s="5"/>
       <c r="AP71" s="5"/>
       <c r="AQ71" s="5"/>
       <c r="AR71" s="5"/>
       <c r="AS71" s="5"/>
-      <c r="AT71" s="5"/>
-      <c r="BO71" s="8"/>
+      <c r="BN71" s="8"/>
+      <c r="BP71" s="8"/>
       <c r="BQ71" s="8"/>
-      <c r="BR71" s="8"/>
-    </row>
-    <row r="72" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM72" s="5"/>
       <c r="AN72" s="5"/>
       <c r="AO72" s="5"/>
       <c r="AP72" s="5"/>
       <c r="AQ72" s="5"/>
       <c r="AR72" s="5"/>
       <c r="AS72" s="5"/>
-      <c r="AT72" s="5"/>
-      <c r="BO72" s="8"/>
+      <c r="BN72" s="8"/>
+      <c r="BP72" s="8"/>
       <c r="BQ72" s="8"/>
-      <c r="BR72" s="8"/>
-    </row>
-    <row r="73" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM73" s="5"/>
       <c r="AN73" s="5"/>
       <c r="AO73" s="5"/>
       <c r="AP73" s="5"/>
       <c r="AQ73" s="5"/>
       <c r="AR73" s="5"/>
       <c r="AS73" s="5"/>
-      <c r="AT73" s="5"/>
-      <c r="BO73" s="8"/>
+      <c r="BN73" s="8"/>
+      <c r="BP73" s="8"/>
       <c r="BQ73" s="8"/>
-      <c r="BR73" s="8"/>
-    </row>
-    <row r="74" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM74" s="5"/>
       <c r="AN74" s="5"/>
       <c r="AO74" s="5"/>
       <c r="AP74" s="5"/>
       <c r="AQ74" s="5"/>
       <c r="AR74" s="5"/>
       <c r="AS74" s="5"/>
-      <c r="AT74" s="5"/>
-      <c r="BO74" s="8"/>
+      <c r="BN74" s="8"/>
+      <c r="BP74" s="8"/>
       <c r="BQ74" s="8"/>
-      <c r="BR74" s="8"/>
-    </row>
-    <row r="75" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM75" s="5"/>
       <c r="AN75" s="5"/>
       <c r="AO75" s="5"/>
       <c r="AP75" s="5"/>
       <c r="AQ75" s="5"/>
       <c r="AR75" s="5"/>
       <c r="AS75" s="5"/>
-      <c r="AT75" s="5"/>
-      <c r="BO75" s="8"/>
+      <c r="BN75" s="8"/>
+      <c r="BP75" s="8"/>
       <c r="BQ75" s="8"/>
-      <c r="BR75" s="8"/>
-    </row>
-    <row r="76" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM76" s="5"/>
       <c r="AN76" s="5"/>
       <c r="AO76" s="5"/>
       <c r="AP76" s="5"/>
       <c r="AQ76" s="5"/>
       <c r="AR76" s="5"/>
       <c r="AS76" s="5"/>
-      <c r="AT76" s="5"/>
-      <c r="BO76" s="8"/>
+      <c r="BN76" s="8"/>
+      <c r="BP76" s="8"/>
       <c r="BQ76" s="8"/>
-      <c r="BR76" s="8"/>
-    </row>
-    <row r="77" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM77" s="5"/>
       <c r="AN77" s="5"/>
       <c r="AO77" s="5"/>
       <c r="AP77" s="5"/>
       <c r="AQ77" s="5"/>
       <c r="AR77" s="5"/>
       <c r="AS77" s="5"/>
-      <c r="AT77" s="5"/>
-      <c r="BO77" s="8"/>
+      <c r="BN77" s="8"/>
+      <c r="BP77" s="8"/>
       <c r="BQ77" s="8"/>
-      <c r="BR77" s="8"/>
-    </row>
-    <row r="78" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM78" s="5"/>
       <c r="AN78" s="5"/>
       <c r="AO78" s="5"/>
       <c r="AP78" s="5"/>
       <c r="AQ78" s="5"/>
       <c r="AR78" s="5"/>
       <c r="AS78" s="5"/>
-      <c r="AT78" s="5"/>
-      <c r="BO78" s="8"/>
+      <c r="BN78" s="8"/>
+      <c r="BP78" s="8"/>
       <c r="BQ78" s="8"/>
-      <c r="BR78" s="8"/>
-    </row>
-    <row r="79" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM79" s="5"/>
       <c r="AN79" s="5"/>
       <c r="AO79" s="5"/>
       <c r="AP79" s="5"/>
       <c r="AQ79" s="5"/>
       <c r="AR79" s="5"/>
       <c r="AS79" s="5"/>
-      <c r="AT79" s="5"/>
-      <c r="BO79" s="8"/>
+      <c r="BN79" s="8"/>
+      <c r="BP79" s="8"/>
       <c r="BQ79" s="8"/>
-      <c r="BR79" s="8"/>
-    </row>
-    <row r="80" spans="2:81" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="AM80" s="5"/>
       <c r="AN80" s="5"/>
       <c r="AO80" s="5"/>
       <c r="AP80" s="5"/>
       <c r="AQ80" s="5"/>
       <c r="AR80" s="5"/>
       <c r="AS80" s="5"/>
-      <c r="AT80" s="5"/>
-      <c r="BO80" s="8"/>
+      <c r="BN80" s="8"/>
+      <c r="BP80" s="8"/>
       <c r="BQ80" s="8"/>
-      <c r="BR80" s="8"/>
-    </row>
-    <row r="81" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM81" s="5"/>
       <c r="AN81" s="5"/>
       <c r="AO81" s="5"/>
       <c r="AP81" s="5"/>
       <c r="AQ81" s="5"/>
       <c r="AR81" s="5"/>
       <c r="AS81" s="5"/>
-      <c r="AT81" s="5"/>
-      <c r="BO81" s="8"/>
+      <c r="BN81" s="8"/>
+      <c r="BP81" s="8"/>
       <c r="BQ81" s="8"/>
-      <c r="BR81" s="8"/>
-    </row>
-    <row r="82" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM82" s="5"/>
       <c r="AN82" s="5"/>
       <c r="AO82" s="5"/>
       <c r="AP82" s="5"/>
       <c r="AQ82" s="5"/>
       <c r="AR82" s="5"/>
       <c r="AS82" s="5"/>
-      <c r="AT82" s="5"/>
-      <c r="BO82" s="8"/>
+      <c r="BN82" s="8"/>
+      <c r="BP82" s="8"/>
       <c r="BQ82" s="8"/>
-      <c r="BR82" s="8"/>
-    </row>
-    <row r="83" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM83" s="5"/>
       <c r="AN83" s="5"/>
       <c r="AO83" s="5"/>
       <c r="AP83" s="5"/>
       <c r="AQ83" s="5"/>
       <c r="AR83" s="5"/>
       <c r="AS83" s="5"/>
-      <c r="AT83" s="5"/>
-      <c r="BO83" s="8"/>
+      <c r="BN83" s="8"/>
+      <c r="BP83" s="8"/>
       <c r="BQ83" s="8"/>
-      <c r="BR83" s="8"/>
-    </row>
-    <row r="84" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM84" s="5"/>
       <c r="AN84" s="5"/>
       <c r="AO84" s="5"/>
       <c r="AP84" s="5"/>
       <c r="AQ84" s="5"/>
       <c r="AR84" s="5"/>
       <c r="AS84" s="5"/>
-      <c r="AT84" s="5"/>
-      <c r="BO84" s="8"/>
+      <c r="BN84" s="8"/>
+      <c r="BP84" s="8"/>
       <c r="BQ84" s="8"/>
-      <c r="BR84" s="8"/>
-    </row>
-    <row r="85" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM85" s="5"/>
       <c r="AN85" s="5"/>
       <c r="AO85" s="5"/>
       <c r="AP85" s="5"/>
       <c r="AQ85" s="5"/>
       <c r="AR85" s="5"/>
       <c r="AS85" s="5"/>
-      <c r="AT85" s="5"/>
-      <c r="BO85" s="8"/>
+      <c r="BN85" s="8"/>
+      <c r="BP85" s="8"/>
       <c r="BQ85" s="8"/>
-      <c r="BR85" s="8"/>
-    </row>
-    <row r="86" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM86" s="5"/>
       <c r="AN86" s="5"/>
       <c r="AO86" s="5"/>
       <c r="AP86" s="5"/>
       <c r="AQ86" s="5"/>
       <c r="AR86" s="5"/>
       <c r="AS86" s="5"/>
-      <c r="AT86" s="5"/>
-      <c r="BO86" s="8"/>
+      <c r="BN86" s="8"/>
+      <c r="BP86" s="8"/>
       <c r="BQ86" s="8"/>
-      <c r="BR86" s="8"/>
-    </row>
-    <row r="87" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM87" s="5"/>
       <c r="AN87" s="5"/>
       <c r="AO87" s="5"/>
       <c r="AP87" s="5"/>
       <c r="AQ87" s="5"/>
       <c r="AR87" s="5"/>
       <c r="AS87" s="5"/>
-      <c r="AT87" s="5"/>
-      <c r="BO87" s="8"/>
+      <c r="BN87" s="8"/>
+      <c r="BP87" s="8"/>
       <c r="BQ87" s="8"/>
-      <c r="BR87" s="8"/>
-    </row>
-    <row r="88" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM88" s="5"/>
       <c r="AN88" s="5"/>
       <c r="AO88" s="5"/>
       <c r="AP88" s="5"/>
       <c r="AQ88" s="5"/>
       <c r="AR88" s="5"/>
       <c r="AS88" s="5"/>
-      <c r="AT88" s="5"/>
-      <c r="BO88" s="8"/>
+      <c r="BN88" s="8"/>
+      <c r="BP88" s="8"/>
       <c r="BQ88" s="8"/>
-      <c r="BR88" s="8"/>
-    </row>
-    <row r="89" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM89" s="5"/>
       <c r="AN89" s="5"/>
       <c r="AO89" s="5"/>
       <c r="AP89" s="5"/>
       <c r="AQ89" s="5"/>
       <c r="AR89" s="5"/>
       <c r="AS89" s="5"/>
-      <c r="AT89" s="5"/>
-      <c r="BO89" s="8"/>
+      <c r="BN89" s="8"/>
+      <c r="BP89" s="8"/>
       <c r="BQ89" s="8"/>
-      <c r="BR89" s="8"/>
-    </row>
-    <row r="90" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM90" s="5"/>
       <c r="AN90" s="5"/>
       <c r="AO90" s="5"/>
       <c r="AP90" s="5"/>
       <c r="AQ90" s="5"/>
       <c r="AR90" s="5"/>
       <c r="AS90" s="5"/>
-      <c r="AT90" s="5"/>
-      <c r="BO90" s="8"/>
+      <c r="BN90" s="8"/>
+      <c r="BP90" s="8"/>
       <c r="BQ90" s="8"/>
-      <c r="BR90" s="8"/>
-    </row>
-    <row r="91" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM91" s="5"/>
       <c r="AN91" s="5"/>
       <c r="AO91" s="5"/>
       <c r="AP91" s="5"/>
       <c r="AQ91" s="5"/>
       <c r="AR91" s="5"/>
       <c r="AS91" s="5"/>
-      <c r="AT91" s="5"/>
-      <c r="BO91" s="8"/>
+      <c r="BN91" s="8"/>
+      <c r="BP91" s="8"/>
       <c r="BQ91" s="8"/>
-      <c r="BR91" s="8"/>
-    </row>
-    <row r="92" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM92" s="5"/>
       <c r="AN92" s="5"/>
       <c r="AO92" s="5"/>
       <c r="AP92" s="5"/>
       <c r="AQ92" s="5"/>
       <c r="AR92" s="5"/>
       <c r="AS92" s="5"/>
-      <c r="AT92" s="5"/>
-      <c r="BO92" s="8"/>
+      <c r="BN92" s="8"/>
+      <c r="BP92" s="8"/>
       <c r="BQ92" s="8"/>
-      <c r="BR92" s="8"/>
-    </row>
-    <row r="93" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM93" s="5"/>
       <c r="AN93" s="5"/>
       <c r="AO93" s="5"/>
       <c r="AP93" s="5"/>
       <c r="AQ93" s="5"/>
       <c r="AR93" s="5"/>
       <c r="AS93" s="5"/>
-      <c r="AT93" s="5"/>
-      <c r="BO93" s="8"/>
+      <c r="BN93" s="8"/>
+      <c r="BP93" s="8"/>
       <c r="BQ93" s="8"/>
-      <c r="BR93" s="8"/>
-    </row>
-    <row r="94" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM94" s="5"/>
       <c r="AN94" s="5"/>
       <c r="AO94" s="5"/>
       <c r="AP94" s="5"/>
       <c r="AQ94" s="5"/>
       <c r="AR94" s="5"/>
       <c r="AS94" s="5"/>
-      <c r="AT94" s="5"/>
-      <c r="BO94" s="8"/>
+      <c r="BN94" s="8"/>
+      <c r="BP94" s="8"/>
       <c r="BQ94" s="8"/>
-      <c r="BR94" s="8"/>
-    </row>
-    <row r="95" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM95" s="5"/>
       <c r="AN95" s="5"/>
       <c r="AO95" s="5"/>
       <c r="AP95" s="5"/>
       <c r="AQ95" s="5"/>
       <c r="AR95" s="5"/>
       <c r="AS95" s="5"/>
-      <c r="AT95" s="5"/>
-      <c r="BO95" s="8"/>
+      <c r="BN95" s="8"/>
+      <c r="BP95" s="8"/>
       <c r="BQ95" s="8"/>
-      <c r="BR95" s="8"/>
-    </row>
-    <row r="96" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM96" s="5"/>
       <c r="AN96" s="5"/>
       <c r="AO96" s="5"/>
       <c r="AP96" s="5"/>
       <c r="AQ96" s="5"/>
       <c r="AR96" s="5"/>
       <c r="AS96" s="5"/>
-      <c r="AT96" s="5"/>
-      <c r="BO96" s="8"/>
+      <c r="BN96" s="8"/>
+      <c r="BP96" s="8"/>
       <c r="BQ96" s="8"/>
-      <c r="BR96" s="8"/>
-    </row>
-    <row r="97" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM97" s="5"/>
       <c r="AN97" s="5"/>
       <c r="AO97" s="5"/>
       <c r="AP97" s="5"/>
       <c r="AQ97" s="5"/>
       <c r="AR97" s="5"/>
       <c r="AS97" s="5"/>
-      <c r="AT97" s="5"/>
-      <c r="BO97" s="8"/>
+      <c r="BN97" s="8"/>
+      <c r="BP97" s="8"/>
       <c r="BQ97" s="8"/>
-      <c r="BR97" s="8"/>
-    </row>
-    <row r="98" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM98" s="5"/>
       <c r="AN98" s="5"/>
       <c r="AO98" s="5"/>
       <c r="AP98" s="5"/>
       <c r="AQ98" s="5"/>
       <c r="AR98" s="5"/>
       <c r="AS98" s="5"/>
-      <c r="AT98" s="5"/>
-      <c r="BO98" s="8"/>
+      <c r="BN98" s="8"/>
+      <c r="BP98" s="8"/>
       <c r="BQ98" s="8"/>
-      <c r="BR98" s="8"/>
-    </row>
-    <row r="99" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM99" s="5"/>
       <c r="AN99" s="5"/>
       <c r="AO99" s="5"/>
       <c r="AP99" s="5"/>
       <c r="AQ99" s="5"/>
       <c r="AR99" s="5"/>
       <c r="AS99" s="5"/>
-      <c r="AT99" s="5"/>
-      <c r="BO99" s="8"/>
+      <c r="BN99" s="8"/>
+      <c r="BP99" s="8"/>
       <c r="BQ99" s="8"/>
-      <c r="BR99" s="8"/>
-    </row>
-    <row r="100" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM100" s="5"/>
       <c r="AN100" s="5"/>
       <c r="AO100" s="5"/>
       <c r="AP100" s="5"/>
       <c r="AQ100" s="5"/>
       <c r="AR100" s="5"/>
       <c r="AS100" s="5"/>
-      <c r="AT100" s="5"/>
-      <c r="BO100" s="8"/>
+      <c r="BN100" s="8"/>
+      <c r="BP100" s="8"/>
       <c r="BQ100" s="8"/>
-      <c r="BR100" s="8"/>
-    </row>
-    <row r="101" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM101" s="5"/>
       <c r="AN101" s="5"/>
       <c r="AO101" s="5"/>
       <c r="AP101" s="5"/>
       <c r="AQ101" s="5"/>
       <c r="AR101" s="5"/>
       <c r="AS101" s="5"/>
-      <c r="AT101" s="5"/>
-      <c r="BO101" s="8"/>
+      <c r="BN101" s="8"/>
+      <c r="BP101" s="8"/>
       <c r="BQ101" s="8"/>
-      <c r="BR101" s="8"/>
-    </row>
-    <row r="102" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM102" s="5"/>
       <c r="AN102" s="5"/>
       <c r="AO102" s="5"/>
       <c r="AP102" s="5"/>
       <c r="AQ102" s="5"/>
       <c r="AR102" s="5"/>
       <c r="AS102" s="5"/>
-      <c r="AT102" s="5"/>
-      <c r="BO102" s="8"/>
+      <c r="BN102" s="8"/>
+      <c r="BP102" s="8"/>
       <c r="BQ102" s="8"/>
-      <c r="BR102" s="8"/>
-    </row>
-    <row r="103" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM103" s="5"/>
       <c r="AN103" s="5"/>
       <c r="AO103" s="5"/>
       <c r="AP103" s="5"/>
       <c r="AQ103" s="5"/>
       <c r="AR103" s="5"/>
       <c r="AS103" s="5"/>
-      <c r="AT103" s="5"/>
-      <c r="BO103" s="8"/>
+      <c r="BN103" s="8"/>
+      <c r="BP103" s="8"/>
       <c r="BQ103" s="8"/>
-      <c r="BR103" s="8"/>
-    </row>
-    <row r="104" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM104" s="5"/>
       <c r="AN104" s="5"/>
       <c r="AO104" s="5"/>
       <c r="AP104" s="5"/>
       <c r="AQ104" s="5"/>
       <c r="AR104" s="5"/>
       <c r="AS104" s="5"/>
-      <c r="AT104" s="5"/>
-      <c r="BO104" s="8"/>
+      <c r="BN104" s="8"/>
+      <c r="BP104" s="8"/>
       <c r="BQ104" s="8"/>
-      <c r="BR104" s="8"/>
-    </row>
-    <row r="105" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM105" s="5"/>
       <c r="AN105" s="5"/>
       <c r="AO105" s="5"/>
       <c r="AP105" s="5"/>
       <c r="AQ105" s="5"/>
       <c r="AR105" s="5"/>
       <c r="AS105" s="5"/>
-      <c r="AT105" s="5"/>
-    </row>
-    <row r="106" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM106" s="5"/>
       <c r="AN106" s="5"/>
       <c r="AO106" s="5"/>
       <c r="AP106" s="5"/>
       <c r="AQ106" s="5"/>
       <c r="AR106" s="5"/>
       <c r="AS106" s="5"/>
-      <c r="AT106" s="5"/>
-    </row>
-    <row r="107" spans="40:70" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AM107" s="5"/>
       <c r="AN107" s="5"/>
       <c r="AO107" s="5"/>
       <c r="AP107" s="5"/>
       <c r="AQ107" s="5"/>
       <c r="AR107" s="5"/>
       <c r="AS107" s="5"/>
-      <c r="AT107" s="5"/>
-    </row>
-    <row r="108" spans="40:70" x14ac:dyDescent="0.2">
-      <c r="AT108" s="5"/>
+    </row>
+    <row r="108" spans="39:69" x14ac:dyDescent="0.2">
+      <c r="AS108" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F389C78-28A3-1242-8015-D6A42DDB2312}">
+  <dimension ref="B2:AL5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.5" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2.33203125" customWidth="1"/>
+    <col min="21" max="21" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="2.6640625" customWidth="1"/>
+    <col min="36" max="36" width="11.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="B2" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="S2" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ2" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:38" ht="32" x14ac:dyDescent="0.2">
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="O3" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC3" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD3" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE3" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF3" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG3" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK3">
+        <v>45.6</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="B4" t="str">
+        <f>lc_detailed!AK4</f>
+        <v>Synthetic_Ethylene_Non_CCS</v>
+      </c>
+      <c r="C4" t="str">
+        <f>lc_detailed!AL4</f>
+        <v>CO2Captured</v>
+      </c>
+      <c r="D4" s="25">
+        <f>lc_detailed!AS4/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="25">
+        <f>lc_detailed!AT4/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="25">
+        <f>lc_detailed!AU4/$AK$3</f>
+        <v>4.2381588917988795</v>
+      </c>
+      <c r="G4" s="25">
+        <f>lc_detailed!AV4/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="25">
+        <f>lc_detailed!AW4/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="25">
+        <f>lc_detailed!AX4/$AK$3</f>
+        <v>4.2600965636830308</v>
+      </c>
+      <c r="J4" s="25">
+        <f>lc_detailed!AY4/$AK$3</f>
+        <v>2.3433206377337097</v>
+      </c>
+      <c r="K4" s="25">
+        <f>lc_detailed!AZ4/$AK$3</f>
+        <v>0.56793841659801814</v>
+      </c>
+      <c r="L4" s="25">
+        <f>lc_detailed!BH4/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="25">
+        <f>lc_detailed!BI4/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="25">
+        <f>lc_detailed!BG4</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="25">
+        <f>lc_detailed!AP4</f>
+        <v>520.27386164750192</v>
+      </c>
+      <c r="P4" s="25">
+        <f>O4/$AK$3</f>
+        <v>11.409514509813638</v>
+      </c>
+      <c r="Q4" s="25">
+        <f>SUM(D4:M4)</f>
+        <v>11.409514509813638</v>
+      </c>
+      <c r="S4" t="str">
+        <f>lc_detailed!AK4</f>
+        <v>Synthetic_Ethylene_Non_CCS</v>
+      </c>
+      <c r="T4" t="str">
+        <f>lc_detailed!AL4</f>
+        <v>CO2Captured</v>
+      </c>
+      <c r="U4" s="25">
+        <f>lc_detailed!AS4/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="V4" s="25">
+        <f>lc_detailed!AT4/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="25">
+        <f>lc_detailed!AU4/$AK$3</f>
+        <v>4.2381588917988795</v>
+      </c>
+      <c r="X4" s="25">
+        <f>lc_detailed!AV4/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="25">
+        <f>lc_detailed!AW4/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="25">
+        <f>lc_detailed!AX4/$AK$3</f>
+        <v>4.2600965636830308</v>
+      </c>
+      <c r="AA4" s="25">
+        <f>lc_detailed!AY4/$AK$3</f>
+        <v>2.3433206377337097</v>
+      </c>
+      <c r="AB4" s="25">
+        <f>lc_detailed!AZ4/$AK$3</f>
+        <v>0.56793841659801814</v>
+      </c>
+      <c r="AC4" s="25">
+        <f>lc_detailed!BB4/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="AD4" s="25">
+        <f>lc_detailed!BC4/$AK$3</f>
+        <v>-0.95679196939630118</v>
+      </c>
+      <c r="AE4" s="25">
+        <f>lc_detailed!BD4</f>
+        <v>-0.35722411839199997</v>
+      </c>
+      <c r="AF4" s="25">
+        <f>lc_detailed!AM4</f>
+        <v>476.64414784303057</v>
+      </c>
+      <c r="AG4" s="25">
+        <f>AF4/$AK$3</f>
+        <v>10.452722540417337</v>
+      </c>
+      <c r="AH4" s="25">
+        <f>SUM(U4:AD4)</f>
+        <v>10.452722540417337</v>
+      </c>
+    </row>
+    <row r="5" spans="2:38" x14ac:dyDescent="0.2">
+      <c r="B5" t="str">
+        <f>lc_detailed!AK5</f>
+        <v>Synthetic_Ethylene_CCS_90</v>
+      </c>
+      <c r="C5" t="str">
+        <f>lc_detailed!AL5</f>
+        <v>CO2Captured</v>
+      </c>
+      <c r="D5" s="25">
+        <f>lc_detailed!AS5/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="25">
+        <f>lc_detailed!AT5/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="25">
+        <f>lc_detailed!AU5/$AK$3</f>
+        <v>3.893420813803286</v>
+      </c>
+      <c r="G5" s="25">
+        <f>lc_detailed!AV5/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="25">
+        <f>lc_detailed!AW5/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="25">
+        <f>lc_detailed!AX5/$AK$3</f>
+        <v>4.705568157602146</v>
+      </c>
+      <c r="J5" s="25">
+        <f>lc_detailed!AY5/$AK$3</f>
+        <v>2.5867547372464941</v>
+      </c>
+      <c r="K5" s="25">
+        <f>lc_detailed!AZ5/$AK$3</f>
+        <v>0.62732684434362407</v>
+      </c>
+      <c r="L5" s="25">
+        <f>lc_detailed!BH5/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="25">
+        <f>lc_detailed!BI5/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="25">
+        <f>lc_detailed!BG5</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="25">
+        <f>lc_detailed!AP5</f>
+        <v>538.67601721659707</v>
+      </c>
+      <c r="P5" s="25">
+        <f>O5/$AK$3</f>
+        <v>11.81307055299555</v>
+      </c>
+      <c r="Q5" s="25">
+        <f>SUM(D5:M5)</f>
+        <v>11.813070552995551</v>
+      </c>
+      <c r="S5" t="str">
+        <f>lc_detailed!AK5</f>
+        <v>Synthetic_Ethylene_CCS_90</v>
+      </c>
+      <c r="T5" t="str">
+        <f>lc_detailed!AL5</f>
+        <v>CO2Captured</v>
+      </c>
+      <c r="U5" s="25">
+        <f>lc_detailed!AS5/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="25">
+        <f>lc_detailed!AT5/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="25">
+        <f>lc_detailed!AU5/$AK$3</f>
+        <v>3.893420813803286</v>
+      </c>
+      <c r="X5" s="25">
+        <f>lc_detailed!AV5/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="25">
+        <f>lc_detailed!AW5/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="25">
+        <f>lc_detailed!AX5/$AK$3</f>
+        <v>4.705568157602146</v>
+      </c>
+      <c r="AA5" s="25">
+        <f>lc_detailed!AY5/$AK$3</f>
+        <v>2.5867547372464941</v>
+      </c>
+      <c r="AB5" s="25">
+        <f>lc_detailed!AZ5/$AK$3</f>
+        <v>0.62732684434362407</v>
+      </c>
+      <c r="AC5" s="25">
+        <f>lc_detailed!BB5/$AK$3</f>
+        <v>0</v>
+      </c>
+      <c r="AD5" s="25">
+        <f>lc_detailed!BC5/$AK$3</f>
+        <v>-1.0415099180449323</v>
+      </c>
+      <c r="AE5" s="25">
+        <f>lc_detailed!BD5</f>
+        <v>-0.38885408131599997</v>
+      </c>
+      <c r="AF5" s="25">
+        <f>lc_detailed!AM5</f>
+        <v>491.18316495374813</v>
+      </c>
+      <c r="AG5" s="25">
+        <f>AF5/$AK$3</f>
+        <v>10.771560634950617</v>
+      </c>
+      <c r="AH5" s="25">
+        <f>SUM(U5:AD5)</f>
+        <v>10.771560634950619</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lcoe_plots/synthetic_ethylene_lcoe/LCOE_SYNTHETIC_Ethylene.xlsx
+++ b/lcoe_plots/synthetic_ethylene_lcoe/LCOE_SYNTHETIC_Ethylene.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/MacroEnergy-Abbie.jl/MacroEnergyExamples/lcoe_plots/synthetic_ethylene_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFCDA25-4E66-5C49-AB40-1F00B1ECA7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB35CF9-A81C-D44E-9ABF-AAB53455FB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lc_detailed" sheetId="1" r:id="rId1"/>
-    <sheet name="lc_summary" sheetId="2" r:id="rId2"/>
+    <sheet name="lc_summary_noseq" sheetId="2" r:id="rId2"/>
+    <sheet name="lc_summary_seq" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="95">
   <si>
     <t>Asset Parameters (normalized by commodity feedstock)</t>
   </si>
@@ -198,7 +199,7 @@
     <t>elec_consumption</t>
   </si>
   <si>
-    <t>ethane_consumption</t>
+    <t>co2captured_consumption</t>
   </si>
   <si>
     <t>natgas_production</t>
@@ -270,7 +271,7 @@
     <t>t-CO2/t-ethylene</t>
   </si>
   <si>
-    <t>Synthetic_Ethylene_Non_CCS</t>
+    <t>SE_Synthetic_Ethylene_Non_CCS</t>
   </si>
   <si>
     <t>CO2Captured</t>
@@ -282,7 +283,7 @@
     <t>t-CO2/MWh-gasoline</t>
   </si>
   <si>
-    <t>Synthetic_Ethylene_CCS_90</t>
+    <t>SE_Synthetic_Ethylene_CCS_90</t>
   </si>
   <si>
     <t>Natural Gas Carbon Content</t>
@@ -303,22 +304,22 @@
     <t>%</t>
   </si>
   <si>
+    <t>Levelized cost for Synthetic Ethylene Production - $/GJ-ethylene - no chemicals CO2 sequestration</t>
+  </si>
+  <si>
     <t>LCOE ($/GJ-ethylene)</t>
   </si>
   <si>
-    <t>Levelized cost for Synthetic Ethylene Production - $/GJ-ethylene - no chemicals CO2 sequestration</t>
+    <t>CHECK LCOE ($/GJ-ethylene)</t>
+  </si>
+  <si>
+    <t>Ethylene LHV</t>
+  </si>
+  <si>
+    <t>GJ/t-ethylene</t>
   </si>
   <si>
     <t>Levelized cost for Synthetic Ethylene Production - $/GJ-ethylene - chemicals CO2 sequestration</t>
-  </si>
-  <si>
-    <t>Ethylene LHV</t>
-  </si>
-  <si>
-    <t>GJ/t-ethylene</t>
-  </si>
-  <si>
-    <t>CHECK LCOE ($/GJ-ethylene)</t>
   </si>
 </sst>
 </file>
@@ -915,8 +916,8 @@
     <col min="82" max="82" width="22.5" style="1" bestFit="1" customWidth="1"/>
     <col min="83" max="83" width="10.83203125" style="1" customWidth="1"/>
     <col min="84" max="84" width="17.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="85" max="92" width="10.83203125" style="1" customWidth="1"/>
-    <col min="93" max="16384" width="10.83203125" style="1"/>
+    <col min="85" max="95" width="10.83203125" style="1" customWidth="1"/>
+    <col min="96" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:84" x14ac:dyDescent="0.2">
@@ -1239,31 +1240,55 @@
       <c r="O4" s="16">
         <v>122.135409</v>
       </c>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
+      <c r="P4" s="16">
+        <v>-10.071578000000001</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>73.297528</v>
+      </c>
+      <c r="R4" s="16">
+        <v>77.158259999999999</v>
+      </c>
+      <c r="S4" s="16">
+        <v>59.694023999999999</v>
+      </c>
       <c r="T4" s="11">
         <v>21.986353300000001</v>
       </c>
       <c r="U4" s="17"/>
       <c r="V4" s="17"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="16"/>
+      <c r="W4" s="16">
+        <v>26.556269</v>
+      </c>
+      <c r="X4" s="16">
+        <v>8.6278919999999992</v>
+      </c>
       <c r="Y4" s="16"/>
-      <c r="Z4" s="17"/>
-      <c r="AA4" s="17"/>
+      <c r="Z4" s="17">
+        <v>-96.133976000000004</v>
+      </c>
+      <c r="AA4" s="17">
+        <v>-96.133976000000004</v>
+      </c>
       <c r="AB4" s="17"/>
       <c r="AC4" s="17"/>
       <c r="AD4" s="17"/>
       <c r="AE4" s="17"/>
-      <c r="AF4" s="16"/>
-      <c r="AG4" s="16"/>
-      <c r="AH4" s="16"/>
-      <c r="AI4" s="16"/>
+      <c r="AF4" s="16">
+        <v>4.7546840000000001</v>
+      </c>
+      <c r="AG4" s="16">
+        <v>-0.13628299999999999</v>
+      </c>
+      <c r="AH4" s="16">
+        <v>576.81126900000004</v>
+      </c>
+      <c r="AI4" s="16">
+        <v>576.81126900000004</v>
+      </c>
       <c r="AK4" s="1" t="str">
         <f>B4</f>
-        <v>Synthetic_Ethylene_Non_CCS</v>
+        <v>SE_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="AL4" s="1" t="str">
         <f>C4</f>
@@ -1271,11 +1296,11 @@
       </c>
       <c r="AM4" s="12">
         <f>SUM(AS4:AZ4)+BB4+BC4</f>
-        <v>476.64414784303057</v>
+        <v>1069.5117340943755</v>
       </c>
       <c r="AN4" s="12">
         <f>SUM(AS4:AZ4)+BE4+BF4</f>
-        <v>476.64414784303057</v>
+        <v>1069.5117340943755</v>
       </c>
       <c r="AO4" s="5">
         <f>AM4-AN4</f>
@@ -1283,11 +1308,11 @@
       </c>
       <c r="AP4" s="12">
         <f>SUM(AS4:AZ4)+BH4+BI4</f>
-        <v>520.27386164750192</v>
+        <v>1113.1414478988468</v>
       </c>
       <c r="AQ4" s="12">
         <f>SUM(AS4:AZ4)+BK4+BL4</f>
-        <v>520.27386164750192</v>
+        <v>1113.1414478988468</v>
       </c>
       <c r="AR4" s="5">
         <f>AP4-AQ4</f>
@@ -1295,23 +1320,23 @@
       </c>
       <c r="AS4" s="5">
         <f>E4/G4*X4</f>
-        <v>0</v>
+        <v>412.75246205135954</v>
       </c>
       <c r="AT4" s="1">
         <f>F4/G4*W4</f>
-        <v>0</v>
+        <v>41.162216940662823</v>
       </c>
       <c r="AU4" s="1">
-        <f>1/G4*T4</f>
-        <v>193.26004546602891</v>
+        <f>1/G4*(O4+P4)</f>
+        <v>985.04107428117129</v>
       </c>
       <c r="AV4" s="1">
         <f>H4/G4*AF4*-1</f>
-        <v>0</v>
+        <v>-6.5982742166693766</v>
       </c>
       <c r="AW4" s="1">
         <f>I4/G4*Z4</f>
-        <v>0</v>
+        <v>-646.22984733915064</v>
       </c>
       <c r="AX4" s="1">
         <f>K4/G4/(0.9*8760)</f>
@@ -1470,31 +1495,55 @@
       <c r="O5" s="16">
         <v>122.135409</v>
       </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
+      <c r="P5" s="16">
+        <v>-10.071578000000001</v>
+      </c>
+      <c r="Q5" s="16">
+        <v>73.297528</v>
+      </c>
+      <c r="R5" s="16">
+        <v>77.158259999999999</v>
+      </c>
+      <c r="S5" s="16">
+        <v>59.694023999999999</v>
+      </c>
       <c r="T5" s="11">
         <v>21.986353300000001</v>
       </c>
       <c r="U5" s="17"/>
       <c r="V5" s="17"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
+      <c r="W5" s="16">
+        <v>26.556269</v>
+      </c>
+      <c r="X5" s="16">
+        <v>8.6278919999999992</v>
+      </c>
       <c r="Y5" s="16"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="17"/>
+      <c r="Z5" s="17">
+        <v>-96.133976000000004</v>
+      </c>
+      <c r="AA5" s="17">
+        <v>-96.133976000000004</v>
+      </c>
       <c r="AB5" s="17"/>
       <c r="AC5" s="17"/>
       <c r="AD5" s="17"/>
       <c r="AE5" s="17"/>
-      <c r="AF5" s="16"/>
-      <c r="AG5" s="16"/>
-      <c r="AH5" s="16"/>
-      <c r="AI5" s="16"/>
+      <c r="AF5" s="16">
+        <v>4.7546840000000001</v>
+      </c>
+      <c r="AG5" s="16">
+        <v>-0.13628299999999999</v>
+      </c>
+      <c r="AH5" s="16">
+        <v>576.81126900000004</v>
+      </c>
+      <c r="AI5" s="16">
+        <v>576.81126900000004</v>
+      </c>
       <c r="AK5" s="1" t="str">
         <f>B5</f>
-        <v>Synthetic_Ethylene_CCS_90</v>
+        <v>SE_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="AL5" s="1" t="str">
         <f>C5</f>
@@ -1502,11 +1551,11 @@
       </c>
       <c r="AM5" s="12">
         <f>SUM(AS5:AZ5)+BB5+BC5</f>
-        <v>491.18316495374813</v>
+        <v>1030.9511213412507</v>
       </c>
       <c r="AN5" s="12">
         <f>SUM(AS5:AZ5)+BE5+BF5</f>
-        <v>491.18316495374813</v>
+        <v>1030.9511213412507</v>
       </c>
       <c r="AO5" s="5">
         <f>AM5-AN5</f>
@@ -1514,11 +1563,11 @@
       </c>
       <c r="AP5" s="12">
         <f>SUM(AS5:AZ5)+BH5+BI5</f>
-        <v>538.67601721659707</v>
+        <v>1078.4439736040995</v>
       </c>
       <c r="AQ5" s="12">
         <f>SUM(AS5:AZ5)+BK5+BL5</f>
-        <v>538.67601721659707</v>
+        <v>1078.4439736040995</v>
       </c>
       <c r="AR5" s="5">
         <f>AP5-AQ5</f>
@@ -1526,23 +1575,23 @@
       </c>
       <c r="AS5" s="5">
         <f>E5/G5*X5</f>
-        <v>0</v>
+        <v>412.75246220347435</v>
       </c>
       <c r="AT5" s="1">
         <f>F5/G5*W5</f>
-        <v>0</v>
+        <v>52.467220678186571</v>
       </c>
       <c r="AU5" s="1">
-        <f>1/G5*T5</f>
-        <v>177.53998910942985</v>
+        <f>1/G5*(O5+P5)</f>
+        <v>904.91638444202511</v>
       </c>
       <c r="AV5" s="1">
         <f>H5/G5*AF5*-1</f>
-        <v>0</v>
+        <v>-6.598274219868598</v>
       </c>
       <c r="AW5" s="1">
         <f>I5/G5*Z5</f>
-        <v>0</v>
+        <v>-646.22984760688507</v>
       </c>
       <c r="AX5" s="1">
         <f>K5/G5/(0.9*8760)</f>
@@ -5527,422 +5576,436 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F389C78-28A3-1242-8015-D6A42DDB2312}">
-  <dimension ref="B2:AL5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B2:T5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="26.5" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="2.33203125" customWidth="1"/>
-    <col min="21" max="21" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="2.6640625" customWidth="1"/>
-    <col min="36" max="36" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="2.6640625" customWidth="1"/>
+    <col min="18" max="18" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B2" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="S2" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ2" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="R2" s="24" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:38" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:20" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" s="4" t="s">
         <v>59</v>
       </c>
+      <c r="K3" s="22" t="s">
+        <v>61</v>
+      </c>
       <c r="L3" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M3" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="N3" s="22" t="s">
         <v>60</v>
       </c>
+      <c r="N3" s="23" t="s">
+        <v>50</v>
+      </c>
       <c r="O3" s="23" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="P3" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q3" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC3" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD3" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE3" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF3" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG3" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH3" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="AJ3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R3" t="s">
         <v>92</v>
       </c>
-      <c r="AK3">
+      <c r="S3">
         <v>45.6</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="T3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B4" t="str">
         <f>lc_detailed!AK4</f>
-        <v>Synthetic_Ethylene_Non_CCS</v>
-      </c>
-      <c r="C4" t="str">
-        <f>lc_detailed!AL4</f>
-        <v>CO2Captured</v>
+        <v>SE_Synthetic_Ethylene_Non_CCS</v>
+      </c>
+      <c r="C4" s="25">
+        <f>lc_detailed!AS4/$S$3</f>
+        <v>9.0515890800736738</v>
       </c>
       <c r="D4" s="25">
-        <f>lc_detailed!AS4/$AK$3</f>
+        <f>lc_detailed!AT4/$S$3</f>
+        <v>0.9026801960671671</v>
+      </c>
+      <c r="E4" s="25">
+        <f>lc_detailed!AU4/$S$3</f>
+        <v>21.601777944762528</v>
+      </c>
+      <c r="F4" s="25">
+        <f>lc_detailed!AV4/$S$3</f>
+        <v>-0.1446989959795916</v>
+      </c>
+      <c r="G4" s="25">
+        <f>lc_detailed!AW4/$S$3</f>
+        <v>-14.171707178490145</v>
+      </c>
+      <c r="H4" s="25">
+        <f>lc_detailed!AX4/$S$3</f>
+        <v>4.2600965636830308</v>
+      </c>
+      <c r="I4" s="25">
+        <f>lc_detailed!AY4/$S$3</f>
+        <v>2.3433206377337097</v>
+      </c>
+      <c r="J4" s="25">
+        <f>lc_detailed!AZ4/$S$3</f>
+        <v>0.56793841659801814</v>
+      </c>
+      <c r="K4" s="25">
+        <f>lc_detailed!BH4/$S$3</f>
         <v>0</v>
       </c>
-      <c r="E4" s="25">
-        <f>lc_detailed!AT4/$AK$3</f>
+      <c r="L4" s="25">
+        <f>lc_detailed!BI4/$S$3</f>
         <v>0</v>
       </c>
-      <c r="F4" s="25">
-        <f>lc_detailed!AU4/$AK$3</f>
-        <v>4.2381588917988795</v>
-      </c>
-      <c r="G4" s="25">
-        <f>lc_detailed!AV4/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="25">
-        <f>lc_detailed!AW4/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="25">
-        <f>lc_detailed!AX4/$AK$3</f>
-        <v>4.2600965636830308</v>
-      </c>
-      <c r="J4" s="25">
-        <f>lc_detailed!AY4/$AK$3</f>
-        <v>2.3433206377337097</v>
-      </c>
-      <c r="K4" s="25">
-        <f>lc_detailed!AZ4/$AK$3</f>
-        <v>0.56793841659801814</v>
-      </c>
-      <c r="L4" s="25">
-        <f>lc_detailed!BH4/$AK$3</f>
-        <v>0</v>
-      </c>
       <c r="M4" s="25">
-        <f>lc_detailed!BI4/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="25">
         <f>lc_detailed!BG4</f>
         <v>0</v>
       </c>
+      <c r="N4" s="25">
+        <f>lc_detailed!AP4</f>
+        <v>1113.1414478988468</v>
+      </c>
       <c r="O4" s="25">
-        <f>lc_detailed!AP4</f>
-        <v>520.27386164750192</v>
+        <f>N4/$S$3</f>
+        <v>24.410996664448394</v>
       </c>
       <c r="P4" s="25">
-        <f>O4/$AK$3</f>
-        <v>11.409514509813638</v>
-      </c>
-      <c r="Q4" s="25">
-        <f>SUM(D4:M4)</f>
-        <v>11.409514509813638</v>
-      </c>
-      <c r="S4" t="str">
+        <f>SUM(C4:L4)</f>
+        <v>24.41099666444839</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B5" t="str">
+        <f>lc_detailed!AK5</f>
+        <v>SE_Synthetic_Ethylene_CCS_90</v>
+      </c>
+      <c r="C5" s="25">
+        <f>lc_detailed!AS5/$S$3</f>
+        <v>9.0515890834095245</v>
+      </c>
+      <c r="D5" s="25">
+        <f>lc_detailed!AT5/$S$3</f>
+        <v>1.1505969446970739</v>
+      </c>
+      <c r="E5" s="25">
+        <f>lc_detailed!AU5/$S$3</f>
+        <v>19.84465755355318</v>
+      </c>
+      <c r="F5" s="25">
+        <f>lc_detailed!AV5/$S$3</f>
+        <v>-0.14469899604974995</v>
+      </c>
+      <c r="G5" s="25">
+        <f>lc_detailed!AW5/$S$3</f>
+        <v>-14.171707184361514</v>
+      </c>
+      <c r="H5" s="25">
+        <f>lc_detailed!AX5/$S$3</f>
+        <v>4.705568157602146</v>
+      </c>
+      <c r="I5" s="25">
+        <f>lc_detailed!AY5/$S$3</f>
+        <v>2.5867547372464941</v>
+      </c>
+      <c r="J5" s="25">
+        <f>lc_detailed!AZ5/$S$3</f>
+        <v>0.62732684434362407</v>
+      </c>
+      <c r="K5" s="25">
+        <f>lc_detailed!BH5/$S$3</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="25">
+        <f>lc_detailed!BI5/$S$3</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="25">
+        <f>lc_detailed!BG5</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="25">
+        <f>lc_detailed!AP5</f>
+        <v>1078.4439736040995</v>
+      </c>
+      <c r="O5" s="25">
+        <f>N5/$S$3</f>
+        <v>23.650087140440778</v>
+      </c>
+      <c r="P5" s="25">
+        <f>SUM(C5:L5)</f>
+        <v>23.650087140440778</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B2:T5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="2.33203125" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B2" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="R2" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="N3" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="P3" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="R3" t="s">
+        <v>92</v>
+      </c>
+      <c r="S3">
+        <v>45.6</v>
+      </c>
+      <c r="T3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B4" t="str">
         <f>lc_detailed!AK4</f>
-        <v>Synthetic_Ethylene_Non_CCS</v>
-      </c>
-      <c r="T4" t="str">
-        <f>lc_detailed!AL4</f>
-        <v>CO2Captured</v>
-      </c>
-      <c r="U4" s="25">
-        <f>lc_detailed!AS4/$AK$3</f>
+        <v>SE_Synthetic_Ethylene_Non_CCS</v>
+      </c>
+      <c r="C4" s="25">
+        <f>lc_detailed!AS4/$S$3</f>
+        <v>9.0515890800736738</v>
+      </c>
+      <c r="D4" s="25">
+        <f>lc_detailed!AT4/$S$3</f>
+        <v>0.9026801960671671</v>
+      </c>
+      <c r="E4" s="25">
+        <f>lc_detailed!AU4/$S$3</f>
+        <v>21.601777944762528</v>
+      </c>
+      <c r="F4" s="25">
+        <f>lc_detailed!AV4/$S$3</f>
+        <v>-0.1446989959795916</v>
+      </c>
+      <c r="G4" s="25">
+        <f>lc_detailed!AW4/$S$3</f>
+        <v>-14.171707178490145</v>
+      </c>
+      <c r="H4" s="25">
+        <f>lc_detailed!AX4/$S$3</f>
+        <v>4.2600965636830308</v>
+      </c>
+      <c r="I4" s="25">
+        <f>lc_detailed!AY4/$S$3</f>
+        <v>2.3433206377337097</v>
+      </c>
+      <c r="J4" s="25">
+        <f>lc_detailed!AZ4/$S$3</f>
+        <v>0.56793841659801814</v>
+      </c>
+      <c r="K4" s="25">
+        <f>lc_detailed!BB4/$S$3</f>
         <v>0</v>
       </c>
-      <c r="V4" s="25">
-        <f>lc_detailed!AT4/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="W4" s="25">
-        <f>lc_detailed!AU4/$AK$3</f>
-        <v>4.2381588917988795</v>
-      </c>
-      <c r="X4" s="25">
-        <f>lc_detailed!AV4/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="Y4" s="25">
-        <f>lc_detailed!AW4/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="Z4" s="25">
-        <f>lc_detailed!AX4/$AK$3</f>
-        <v>4.2600965636830308</v>
-      </c>
-      <c r="AA4" s="25">
-        <f>lc_detailed!AY4/$AK$3</f>
-        <v>2.3433206377337097</v>
-      </c>
-      <c r="AB4" s="25">
-        <f>lc_detailed!AZ4/$AK$3</f>
-        <v>0.56793841659801814</v>
-      </c>
-      <c r="AC4" s="25">
-        <f>lc_detailed!BB4/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD4" s="25">
-        <f>lc_detailed!BC4/$AK$3</f>
+      <c r="L4" s="25">
+        <f>lc_detailed!BC4/$S$3</f>
         <v>-0.95679196939630118</v>
       </c>
-      <c r="AE4" s="25">
+      <c r="M4" s="25">
         <f>lc_detailed!BD4</f>
         <v>-0.35722411839199997</v>
       </c>
-      <c r="AF4" s="25">
+      <c r="N4" s="25">
         <f>lc_detailed!AM4</f>
-        <v>476.64414784303057</v>
-      </c>
-      <c r="AG4" s="25">
-        <f>AF4/$AK$3</f>
-        <v>10.452722540417337</v>
-      </c>
-      <c r="AH4" s="25">
-        <f>SUM(U4:AD4)</f>
-        <v>10.452722540417337</v>
-      </c>
-    </row>
-    <row r="5" spans="2:38" x14ac:dyDescent="0.2">
+        <v>1069.5117340943755</v>
+      </c>
+      <c r="O4" s="25">
+        <f>N4/$S$3</f>
+        <v>23.454204695052091</v>
+      </c>
+      <c r="P4" s="25">
+        <f>SUM(C4:L4)</f>
+        <v>23.454204695052088</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B5" t="str">
         <f>lc_detailed!AK5</f>
-        <v>Synthetic_Ethylene_CCS_90</v>
-      </c>
-      <c r="C5" t="str">
-        <f>lc_detailed!AL5</f>
-        <v>CO2Captured</v>
+        <v>SE_Synthetic_Ethylene_CCS_90</v>
+      </c>
+      <c r="C5" s="25">
+        <f>lc_detailed!AS5/$S$3</f>
+        <v>9.0515890834095245</v>
       </c>
       <c r="D5" s="25">
-        <f>lc_detailed!AS5/$AK$3</f>
+        <f>lc_detailed!AT5/$S$3</f>
+        <v>1.1505969446970739</v>
+      </c>
+      <c r="E5" s="25">
+        <f>lc_detailed!AU5/$S$3</f>
+        <v>19.84465755355318</v>
+      </c>
+      <c r="F5" s="25">
+        <f>lc_detailed!AV5/$S$3</f>
+        <v>-0.14469899604974995</v>
+      </c>
+      <c r="G5" s="25">
+        <f>lc_detailed!AW5/$S$3</f>
+        <v>-14.171707184361514</v>
+      </c>
+      <c r="H5" s="25">
+        <f>lc_detailed!AX5/$S$3</f>
+        <v>4.705568157602146</v>
+      </c>
+      <c r="I5" s="25">
+        <f>lc_detailed!AY5/$S$3</f>
+        <v>2.5867547372464941</v>
+      </c>
+      <c r="J5" s="25">
+        <f>lc_detailed!AZ5/$S$3</f>
+        <v>0.62732684434362407</v>
+      </c>
+      <c r="K5" s="25">
+        <f>lc_detailed!BB5/$S$3</f>
         <v>0</v>
       </c>
-      <c r="E5" s="25">
-        <f>lc_detailed!AT5/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="25">
-        <f>lc_detailed!AU5/$AK$3</f>
-        <v>3.893420813803286</v>
-      </c>
-      <c r="G5" s="25">
-        <f>lc_detailed!AV5/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="25">
-        <f>lc_detailed!AW5/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="25">
-        <f>lc_detailed!AX5/$AK$3</f>
-        <v>4.705568157602146</v>
-      </c>
-      <c r="J5" s="25">
-        <f>lc_detailed!AY5/$AK$3</f>
-        <v>2.5867547372464941</v>
-      </c>
-      <c r="K5" s="25">
-        <f>lc_detailed!AZ5/$AK$3</f>
-        <v>0.62732684434362407</v>
-      </c>
       <c r="L5" s="25">
-        <f>lc_detailed!BH5/$AK$3</f>
-        <v>0</v>
+        <f>lc_detailed!BC5/$S$3</f>
+        <v>-1.0415099180449323</v>
       </c>
       <c r="M5" s="25">
-        <f>lc_detailed!BI5/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="25">
-        <f>lc_detailed!BG5</f>
-        <v>0</v>
-      </c>
-      <c r="O5" s="25">
-        <f>lc_detailed!AP5</f>
-        <v>538.67601721659707</v>
-      </c>
-      <c r="P5" s="25">
-        <f>O5/$AK$3</f>
-        <v>11.81307055299555</v>
-      </c>
-      <c r="Q5" s="25">
-        <f>SUM(D5:M5)</f>
-        <v>11.813070552995551</v>
-      </c>
-      <c r="S5" t="str">
-        <f>lc_detailed!AK5</f>
-        <v>Synthetic_Ethylene_CCS_90</v>
-      </c>
-      <c r="T5" t="str">
-        <f>lc_detailed!AL5</f>
-        <v>CO2Captured</v>
-      </c>
-      <c r="U5" s="25">
-        <f>lc_detailed!AS5/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="V5" s="25">
-        <f>lc_detailed!AT5/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="W5" s="25">
-        <f>lc_detailed!AU5/$AK$3</f>
-        <v>3.893420813803286</v>
-      </c>
-      <c r="X5" s="25">
-        <f>lc_detailed!AV5/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="25">
-        <f>lc_detailed!AW5/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="Z5" s="25">
-        <f>lc_detailed!AX5/$AK$3</f>
-        <v>4.705568157602146</v>
-      </c>
-      <c r="AA5" s="25">
-        <f>lc_detailed!AY5/$AK$3</f>
-        <v>2.5867547372464941</v>
-      </c>
-      <c r="AB5" s="25">
-        <f>lc_detailed!AZ5/$AK$3</f>
-        <v>0.62732684434362407</v>
-      </c>
-      <c r="AC5" s="25">
-        <f>lc_detailed!BB5/$AK$3</f>
-        <v>0</v>
-      </c>
-      <c r="AD5" s="25">
-        <f>lc_detailed!BC5/$AK$3</f>
-        <v>-1.0415099180449323</v>
-      </c>
-      <c r="AE5" s="25">
         <f>lc_detailed!BD5</f>
         <v>-0.38885408131599997</v>
       </c>
-      <c r="AF5" s="25">
+      <c r="N5" s="25">
         <f>lc_detailed!AM5</f>
-        <v>491.18316495374813</v>
-      </c>
-      <c r="AG5" s="25">
-        <f>AF5/$AK$3</f>
-        <v>10.771560634950617</v>
-      </c>
-      <c r="AH5" s="25">
-        <f>SUM(U5:AD5)</f>
-        <v>10.771560634950619</v>
+        <v>1030.9511213412507</v>
+      </c>
+      <c r="O5" s="25">
+        <f>N5/$S$3</f>
+        <v>22.608577222395848</v>
+      </c>
+      <c r="P5" s="25">
+        <f>SUM(C5:L5)</f>
+        <v>22.608577222395844</v>
       </c>
     </row>
   </sheetData>

--- a/lcoe_plots/synthetic_ethylene_lcoe/LCOE_SYNTHETIC_Ethylene.xlsx
+++ b/lcoe_plots/synthetic_ethylene_lcoe/LCOE_SYNTHETIC_Ethylene.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/MacroEnergy-Abbie.jl/MacroEnergyExamples/lcoe_plots/synthetic_ethylene_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EA4A17-3B6E-8D4B-86D4-8EA43FBB915B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A205A4C-6B30-2347-8A9E-EE10120F2E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,28 +32,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -392,6 +370,9 @@
     <t>Levelized cost for Synthetic Ethylene Production - $/GJ-ethylene - no chemicals CO2 sequestration</t>
   </si>
   <si>
+    <t>Levelized cost for Synthetic Ethylene Production - $/GJ-ethylene - no chemicals CO2 sequestration - SORTED</t>
+  </si>
+  <si>
     <t>LCOE ($/GJ-ethylene)</t>
   </si>
   <si>
@@ -405,9 +386,6 @@
   </si>
   <si>
     <t>Levelized cost for Synthetic Ethylene Production - $/GJ-ethylene - chemicals CO2 sequestration</t>
-  </si>
-  <si>
-    <t>Levelized cost for Synthetic Ethylene Production - $/GJ-ethylene - no chemicals CO2 sequestration - SORTED</t>
   </si>
   <si>
     <t>Levelized cost for Synthetic Ethylene Production - $/GJ-ethylene - chemicals CO2 sequestration - SORTED</t>
@@ -1026,8 +1004,8 @@
     <col min="87" max="87" width="22.5" style="1" bestFit="1" customWidth="1"/>
     <col min="88" max="88" width="10.83203125" style="1" customWidth="1"/>
     <col min="89" max="89" width="17.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="90" max="105" width="10.83203125" style="1" customWidth="1"/>
-    <col min="106" max="16384" width="10.83203125" style="1"/>
+    <col min="90" max="106" width="10.83203125" style="1" customWidth="1"/>
+    <col min="107" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:89" x14ac:dyDescent="0.2">
@@ -1354,7 +1332,7 @@
         <v>0.41383317400000003</v>
       </c>
       <c r="K3" s="27">
-        <f>BY3-SUM(CA3+CD3+CB3+CF3)</f>
+        <f t="shared" ref="K3:K20" si="0">BY3-SUM(CA3+CD3+CB3+CF3)</f>
         <v>0.41383317371333472</v>
       </c>
       <c r="L3" s="13">
@@ -1367,30 +1345,30 @@
         <v>2.9463016839999998</v>
       </c>
       <c r="O3" s="13">
-        <f>N3-(Q3*X3)</f>
+        <f t="shared" ref="O3:O20" si="1">N3-(Q3*X3)</f>
         <v>-45.313083991760003</v>
       </c>
       <c r="P3" s="26">
         <v>1.01</v>
       </c>
       <c r="Q3" s="26">
-        <f>P3*G3</f>
+        <f t="shared" ref="Q3:Q20" si="2">P3*G3</f>
         <v>0.11490329922799999</v>
       </c>
       <c r="S3" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T3" s="16">
-        <v>-6.0933450000000002</v>
+        <v>-6.0910019999999996</v>
       </c>
       <c r="U3" s="16">
-        <v>63.965595</v>
+        <v>59.252833000000003</v>
       </c>
       <c r="V3" s="16">
-        <v>44.054146000000003</v>
+        <v>23.691089000000002</v>
       </c>
       <c r="W3" s="16">
-        <v>38.296242999999997</v>
+        <v>31.789762</v>
       </c>
       <c r="X3" s="26">
         <v>420</v>
@@ -1398,194 +1376,196 @@
       <c r="Y3" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z3" s="17"/>
+      <c r="Z3" s="17">
+        <v>-8.0072700000000001</v>
+      </c>
       <c r="AA3" s="17"/>
       <c r="AB3" s="16">
-        <v>22.027436000000002</v>
+        <v>21.266241000000001</v>
       </c>
       <c r="AC3" s="16">
-        <v>7.1289699999999998</v>
+        <v>7.267779</v>
       </c>
       <c r="AD3" s="16"/>
       <c r="AE3" s="17">
-        <v>0</v>
+        <v>-128.077631</v>
       </c>
       <c r="AF3" s="17">
-        <v>0</v>
+        <v>-128.077631</v>
       </c>
       <c r="AG3" s="17"/>
       <c r="AH3" s="17"/>
       <c r="AI3" s="17"/>
       <c r="AJ3" s="17"/>
       <c r="AK3" s="16">
-        <v>12.1478</v>
+        <v>7.9635800000000003</v>
       </c>
       <c r="AL3" s="16">
         <v>0</v>
       </c>
       <c r="AM3" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN3" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AP3" s="1" t="str">
-        <f>B3</f>
+        <f t="shared" ref="AP3:AP20" si="3">B3</f>
         <v>SE_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="AQ3" s="1" t="str">
-        <f>C3</f>
+        <f t="shared" ref="AQ3:AQ20" si="4">C3</f>
         <v>CO2Captured</v>
       </c>
       <c r="AR3" s="12">
-        <f>SUM(AX3:BE3)+BG3+BH3</f>
-        <v>1392.9294985009017</v>
+        <f t="shared" ref="AR3:AR20" si="5">SUM(AX3:BE3)+BG3+BH3</f>
+        <v>331.38329840666216</v>
       </c>
       <c r="AS3" s="12">
-        <f>SUM(AX3:BE3)+BJ3+BK3</f>
-        <v>1392.9294985009017</v>
+        <f t="shared" ref="AS3:AS20" si="6">SUM(AX3:BE3)+BJ3+BK3</f>
+        <v>331.38329840666216</v>
       </c>
       <c r="AT3" s="5">
-        <f>AR3-AS3</f>
+        <f t="shared" ref="AT3:AT20" si="7">AR3-AS3</f>
         <v>0</v>
       </c>
       <c r="AU3" s="12">
-        <f>SUM(AX3:BE3)+BM3+BN3</f>
-        <v>1429.8253607507204</v>
+        <f t="shared" ref="AU3:AU20" si="8">SUM(AX3:BE3)+BM3+BN3</f>
+        <v>358.88746933797165</v>
       </c>
       <c r="AV3" s="12">
-        <f>SUM(AX3:BE3)+BP3+BQ3</f>
-        <v>1429.8253607507204</v>
+        <f t="shared" ref="AV3:AV20" si="9">SUM(AX3:BE3)+BP3+BQ3</f>
+        <v>358.88746933797165</v>
       </c>
       <c r="AW3" s="5">
-        <f>AU3-AV3</f>
+        <f t="shared" ref="AW3:AW20" si="10">AU3-AV3</f>
         <v>0</v>
       </c>
       <c r="AX3" s="5">
-        <f>E3/G3*AC3</f>
-        <v>341.04505705336607</v>
+        <f t="shared" ref="AX3:AX20" si="11">E3/G3*AC3</f>
+        <v>347.68558483290798</v>
       </c>
       <c r="AY3" s="1">
-        <f>F3/G3*AB3</f>
-        <v>34.142525792255157</v>
+        <f t="shared" ref="AY3:AY20" si="12">F3/G3*AB3</f>
+        <v>32.962673542522793</v>
       </c>
       <c r="AZ3" s="1">
-        <f>1/G3*(S3+T3)</f>
-        <v>815.69304858707312</v>
+        <f t="shared" ref="AZ3:AZ20" si="13">1/G3*(S3+T3)</f>
+        <v>594.44869589397695</v>
       </c>
       <c r="BA3" s="1">
-        <f>H3/G3*AK3*-1</f>
-        <v>-16.858011074817224</v>
+        <f t="shared" ref="BA3:BA20" si="14">H3/G3*AK3*-1</f>
+        <v>-11.051393654422442</v>
       </c>
       <c r="BB3" s="1">
-        <f>I3/G3*AE3</f>
-        <v>0</v>
+        <f t="shared" ref="BB3:BB20" si="15">I3/G3*AE3</f>
+        <v>-860.96083166985693</v>
       </c>
       <c r="BC3" s="1">
-        <f>L3/G3/(0.9*8760)</f>
+        <f t="shared" ref="BC3:BC20" si="16">L3/G3/(0.9*8760)</f>
         <v>194.26040330394619</v>
       </c>
       <c r="BD3" s="1">
-        <f>M3/G3/(0.9*8760)</f>
+        <f t="shared" ref="BD3:BD20" si="17">M3/G3/(0.9*8760)</f>
         <v>106.85542108065717</v>
       </c>
       <c r="BE3" s="1">
-        <f>O3</f>
+        <f t="shared" ref="BE3:BE20" si="18">O3</f>
         <v>-45.313083991760003</v>
       </c>
       <c r="BF3" s="1">
-        <f>CG3-BY3-CA3-CD3</f>
+        <f t="shared" ref="BF3:BF20" si="19">CG3-BY3-CA3-CD3</f>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BG3" s="1">
         <v>0</v>
       </c>
       <c r="BH3" s="1">
-        <f>BF3*S3</f>
-        <v>-36.895862249818791</v>
+        <f t="shared" ref="BH3:BH20" si="20">BF3*S3</f>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BI3" s="1">
-        <f>BY3-CG3-CA3-CD3</f>
+        <f t="shared" ref="BI3:BI20" si="21">BY3-CG3-CA3-CD3</f>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BJ3" s="1">
         <v>0</v>
       </c>
       <c r="BK3" s="1">
-        <f>BI3*S3</f>
-        <v>-36.895862249818791</v>
+        <f t="shared" ref="BK3:BK20" si="22">BI3*S3</f>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BL3" s="1">
-        <f>BY3-CG3</f>
+        <f t="shared" ref="BL3:BL20" si="23">BY3-CG3</f>
         <v>0</v>
       </c>
       <c r="BM3" s="1">
         <v>0</v>
       </c>
       <c r="BN3" s="1">
-        <f>BL3*S3</f>
+        <f t="shared" ref="BN3:BN20" si="24">BL3*S3</f>
         <v>0</v>
       </c>
       <c r="BO3" s="1">
-        <f>BY3-CG3</f>
+        <f t="shared" ref="BO3:BO20" si="25">BY3-CG3</f>
         <v>0</v>
       </c>
       <c r="BP3" s="1">
         <v>0</v>
       </c>
       <c r="BQ3" s="1">
-        <f>BO3*S3</f>
+        <f t="shared" ref="BQ3:BQ20" si="26">BO3*S3</f>
         <v>0</v>
       </c>
       <c r="BS3" s="9">
-        <f>$CJ$2</f>
+        <f t="shared" ref="BS3:BS20" si="27">$CJ$2</f>
         <v>3.14</v>
       </c>
       <c r="BT3" s="10">
-        <f>$CJ$3</f>
+        <f t="shared" ref="BT3:BT20" si="28">$CJ$3</f>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU3" s="9">
-        <f>$CJ$4</f>
+        <f t="shared" ref="BU3:BU20" si="29">$CJ$4</f>
         <v>0.18104824</v>
       </c>
       <c r="BV3" s="9">
-        <f>$CJ$5</f>
+        <f t="shared" ref="BV3:BV20" si="30">$CJ$5</f>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX3" s="10">
         <v>1</v>
       </c>
       <c r="BY3" s="10">
-        <f>BX3-CE3</f>
+        <f t="shared" ref="BY3:BY20" si="31">BX3-CE3</f>
         <v>1</v>
       </c>
       <c r="CA3" s="10">
-        <f>BS3*G3</f>
+        <f t="shared" ref="CA3:CA20" si="32">BS3*G3</f>
         <v>0.35722411839200002</v>
       </c>
       <c r="CB3" s="10">
-        <f>BU3*H3</f>
+        <f t="shared" ref="CB3:CB20" si="33">BU3*H3</f>
         <v>2.8583416262839882E-2</v>
       </c>
       <c r="CC3" s="10">
-        <f>(BX3-CA3-CB3-CF3-CD3)*(1-D3)</f>
+        <f t="shared" ref="CC3:CC20" si="34">(BX3-CA3-CB3-CF3-CD3)*(1-D3)</f>
         <v>0.41383317371333478</v>
       </c>
       <c r="CD3" s="10">
-        <f>BV3*P3</f>
+        <f t="shared" ref="CD3:CD20" si="35">BV3*P3</f>
         <v>1.5871428571428571E-2</v>
       </c>
       <c r="CE3" s="10">
-        <f>(BX3-CA3-CB3-CF3-CD3)*(D3)</f>
+        <f t="shared" ref="CE3:CE20" si="36">(BX3-CA3-CB3-CF3-CD3)*(D3)</f>
         <v>0</v>
       </c>
       <c r="CF3" s="10">
-        <f>BT3*I3</f>
+        <f t="shared" ref="CF3:CF20" si="37">BT3*I3</f>
         <v>0.1844878630603968</v>
       </c>
       <c r="CG3" s="10">
-        <f>SUM(CA3:CF3)-CE3</f>
+        <f t="shared" ref="CG3:CG20" si="38">SUM(CA3:CF3)-CE3</f>
         <v>1</v>
       </c>
       <c r="CI3" s="20" t="s">
@@ -1627,7 +1607,7 @@
         <v>3.6333707999999999E-2</v>
       </c>
       <c r="K4" s="27">
-        <f>BY4-SUM(CA4+CD4+CB4+CF4)</f>
+        <f t="shared" si="0"/>
         <v>3.6333708066740855E-2</v>
       </c>
       <c r="L4" s="13">
@@ -1640,30 +1620,30 @@
         <v>3.542547876</v>
       </c>
       <c r="O4" s="13">
-        <f>N4-(Q4*X4)</f>
+        <f t="shared" si="1"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="P4" s="26">
         <v>1.01</v>
       </c>
       <c r="Q4" s="26">
-        <f>P4*G4</f>
+        <f t="shared" si="2"/>
         <v>0.125077268194</v>
       </c>
       <c r="S4" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T4" s="16">
-        <v>-6.0933450000000002</v>
+        <v>-6.0910019999999996</v>
       </c>
       <c r="U4" s="16">
-        <v>63.965595</v>
+        <v>59.252833000000003</v>
       </c>
       <c r="V4" s="16">
-        <v>44.054146000000003</v>
+        <v>23.691089000000002</v>
       </c>
       <c r="W4" s="16">
-        <v>38.296242999999997</v>
+        <v>31.789762</v>
       </c>
       <c r="X4" s="26">
         <v>420</v>
@@ -1671,194 +1651,196 @@
       <c r="Y4" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z4" s="17"/>
+      <c r="Z4" s="17">
+        <v>-8.0072700000000001</v>
+      </c>
       <c r="AA4" s="17"/>
       <c r="AB4" s="16">
-        <v>22.027436000000002</v>
+        <v>21.266241000000001</v>
       </c>
       <c r="AC4" s="16">
-        <v>7.1289699999999998</v>
+        <v>7.267779</v>
       </c>
       <c r="AD4" s="16"/>
       <c r="AE4" s="17">
-        <v>0</v>
+        <v>-128.077631</v>
       </c>
       <c r="AF4" s="17">
-        <v>0</v>
+        <v>-128.077631</v>
       </c>
       <c r="AG4" s="17"/>
       <c r="AH4" s="17"/>
       <c r="AI4" s="17"/>
       <c r="AJ4" s="17"/>
       <c r="AK4" s="16">
-        <v>12.1478</v>
+        <v>7.9635800000000003</v>
       </c>
       <c r="AL4" s="16">
         <v>0</v>
       </c>
       <c r="AM4" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN4" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AP4" s="1" t="str">
-        <f>B4</f>
+        <f t="shared" si="3"/>
         <v>SE_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="AQ4" s="1" t="str">
-        <f>C4</f>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR4" s="12">
-        <f>SUM(AX4:BE4)+BG4+BH4</f>
-        <v>1360.5662600068829</v>
+        <f t="shared" si="5"/>
+        <v>317.48856038202962</v>
       </c>
       <c r="AS4" s="12">
-        <f>SUM(AX4:BE4)+BJ4+BK4</f>
-        <v>1360.5662600068829</v>
+        <f t="shared" si="6"/>
+        <v>317.48856038202962</v>
       </c>
       <c r="AT4" s="5">
-        <f>AR4-AS4</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU4" s="12">
-        <f>SUM(AX4:BE4)+BM4+BN4</f>
-        <v>1400.590046898282</v>
+        <f t="shared" si="8"/>
+        <v>347.32445548933936</v>
       </c>
       <c r="AV4" s="12">
-        <f>SUM(AX4:BE4)+BP4+BQ4</f>
-        <v>1400.590046898282</v>
+        <f t="shared" si="9"/>
+        <v>347.32445548933936</v>
       </c>
       <c r="AW4" s="5">
-        <f>AU4-AV4</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX4" s="5">
-        <f>E4/G4*AC4</f>
-        <v>341.04505717905403</v>
+        <f t="shared" si="11"/>
+        <v>347.68558496104322</v>
       </c>
       <c r="AY4" s="1">
-        <f>F4/G4*AB4</f>
-        <v>43.519605317547864</v>
+        <f t="shared" si="12"/>
+        <v>42.015712355621154</v>
       </c>
       <c r="AZ4" s="1">
-        <f>1/G4*(S4+T4)</f>
-        <v>749.34337624505338</v>
+        <f t="shared" si="13"/>
+        <v>546.09536461939263</v>
       </c>
       <c r="BA4" s="1">
-        <f>H4/G4*AK4*-1</f>
-        <v>-16.858011082990952</v>
+        <f t="shared" si="14"/>
+        <v>-11.051393659780791</v>
       </c>
       <c r="BB4" s="1">
-        <f>I4/G4*AE4</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-860.96083202655484</v>
       </c>
       <c r="BC4" s="1">
-        <f>L4/G4/(0.9*8760)</f>
+        <f t="shared" si="16"/>
         <v>214.57390798665784</v>
       </c>
       <c r="BD4" s="1">
-        <f>M4/G4/(0.9*8760)</f>
+        <f t="shared" si="17"/>
         <v>117.95601601844012</v>
       </c>
       <c r="BE4" s="1">
-        <f>O4</f>
+        <f t="shared" si="18"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="BF4" s="1">
-        <f>CG4-BY4-CA4-CD4</f>
+        <f t="shared" si="19"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BG4" s="1">
         <v>0</v>
       </c>
       <c r="BH4" s="1">
-        <f>BF4*S4</f>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="20"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BI4" s="1">
-        <f>BY4-CG4-CA4-CD4</f>
+        <f t="shared" si="21"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BJ4" s="1">
         <v>0</v>
       </c>
       <c r="BK4" s="1">
-        <f>BI4*S4</f>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="22"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BL4" s="1">
-        <f>BY4-CG4</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM4" s="1">
         <v>0</v>
       </c>
       <c r="BN4" s="1">
-        <f>BL4*S4</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO4" s="1">
-        <f>BY4-CG4</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP4" s="1">
         <v>0</v>
       </c>
       <c r="BQ4" s="1">
-        <f>BO4*S4</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS4" s="9">
-        <f>$CJ$2</f>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT4" s="10">
-        <f>$CJ$3</f>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU4" s="9">
-        <f>$CJ$4</f>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV4" s="9">
-        <f>$CJ$5</f>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX4" s="10">
         <v>1</v>
       </c>
       <c r="BY4" s="10">
-        <f>BX4-CE4</f>
+        <f t="shared" si="31"/>
         <v>0.67299662739933241</v>
       </c>
       <c r="CA4" s="10">
-        <f>BS4*G4</f>
+        <f t="shared" si="32"/>
         <v>0.38885408131600002</v>
       </c>
       <c r="CB4" s="10">
-        <f>BU4*H4</f>
+        <f t="shared" si="33"/>
         <v>3.1114299132937305E-2</v>
       </c>
       <c r="CC4" s="10">
-        <f>(BX4-CA4-CB4-CF4-CD4)*(1-D4)</f>
+        <f t="shared" si="34"/>
         <v>3.6333708066740841E-2</v>
       </c>
       <c r="CD4" s="10">
-        <f>BV4*P4</f>
+        <f t="shared" si="35"/>
         <v>1.5871428571428571E-2</v>
       </c>
       <c r="CE4" s="10">
-        <f>(BX4-CA4-CB4-CF4-CD4)*(D4)</f>
+        <f t="shared" si="36"/>
         <v>0.32700337260066764</v>
       </c>
       <c r="CF4" s="10">
-        <f>BT4*I4</f>
+        <f t="shared" si="37"/>
         <v>0.20082311031222566</v>
       </c>
       <c r="CG4" s="10">
-        <f>SUM(CA4:CF4)-CE4</f>
+        <f t="shared" si="38"/>
         <v>0.67299662739933241</v>
       </c>
       <c r="CI4" s="20" t="s">
@@ -1900,7 +1882,7 @@
         <v>0.41383317400000003</v>
       </c>
       <c r="K5" s="27">
-        <f t="shared" ref="K5:K20" si="0">BY5-SUM(CA5+CD5+CB5+CF5)</f>
+        <f t="shared" si="0"/>
         <v>0.41383317371333472</v>
       </c>
       <c r="L5" s="13">
@@ -1913,30 +1895,30 @@
         <v>2.9463016839999998</v>
       </c>
       <c r="O5" s="13">
-        <f>N5-(Q5*X5)</f>
+        <f t="shared" si="1"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="P5" s="26">
         <v>1.01</v>
       </c>
       <c r="Q5" s="26">
-        <f t="shared" ref="Q5:Q20" si="1">P5*G5</f>
+        <f t="shared" si="2"/>
         <v>0.11490329922799999</v>
       </c>
       <c r="S5" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T5" s="16">
-        <v>-16.195074999999999</v>
+        <v>-16.179127999999999</v>
       </c>
       <c r="U5" s="16">
-        <v>64.592955000000003</v>
+        <v>58.461202</v>
       </c>
       <c r="V5" s="16">
-        <v>40.280831999999997</v>
+        <v>19.647223</v>
       </c>
       <c r="W5" s="16">
-        <v>41.334845999999999</v>
+        <v>40.820307</v>
       </c>
       <c r="X5" s="26">
         <v>420</v>
@@ -1944,194 +1926,196 @@
       <c r="Y5" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z5" s="17"/>
+      <c r="Z5" s="17">
+        <v>-2.2030439999999998</v>
+      </c>
       <c r="AA5" s="17"/>
       <c r="AB5" s="16">
-        <v>22.722069000000001</v>
+        <v>21.500722</v>
       </c>
       <c r="AC5" s="16">
-        <v>10.932268000000001</v>
+        <v>7.5324369999999998</v>
       </c>
       <c r="AD5" s="16"/>
       <c r="AE5" s="17">
-        <v>0</v>
+        <v>-140.74133399999999</v>
       </c>
       <c r="AF5" s="17">
-        <v>0</v>
+        <v>-140.74133399999999</v>
       </c>
       <c r="AG5" s="17"/>
       <c r="AH5" s="17"/>
       <c r="AI5" s="17"/>
       <c r="AJ5" s="17"/>
       <c r="AK5" s="16">
-        <v>12.157551</v>
+        <v>5.4076719999999998</v>
       </c>
       <c r="AL5" s="16">
         <v>0</v>
       </c>
       <c r="AM5" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN5" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AP5" s="1" t="str">
-        <f t="shared" ref="AP5:AP17" si="2">B5</f>
+        <f t="shared" si="3"/>
         <v>MIDAT_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="AQ5" s="1" t="str">
-        <f t="shared" ref="AQ5:AQ17" si="3">C5</f>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR5" s="12">
-        <f t="shared" ref="AR5:AR17" si="4">SUM(AX5:BE5)+BG5+BH5</f>
-        <v>1487.1456204804856</v>
+        <f t="shared" si="5"/>
+        <v>174.15242976340338</v>
       </c>
       <c r="AS5" s="12">
-        <f t="shared" ref="AS5:AS17" si="5">SUM(AX5:BE5)+BJ5+BK5</f>
-        <v>1487.1456204804856</v>
+        <f t="shared" si="6"/>
+        <v>174.15242976340338</v>
       </c>
       <c r="AT5" s="5">
-        <f t="shared" ref="AT5:AT17" si="6">AR5-AS5</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU5" s="12">
-        <f t="shared" ref="AU5:AU17" si="7">SUM(AX5:BE5)+BM5+BN5</f>
-        <v>1524.0414827303043</v>
+        <f t="shared" si="8"/>
+        <v>201.65660069471286</v>
       </c>
       <c r="AV5" s="12">
-        <f t="shared" ref="AV5:AV17" si="8">SUM(AX5:BE5)+BP5+BQ5</f>
-        <v>1524.0414827303043</v>
+        <f t="shared" si="9"/>
+        <v>201.65660069471286</v>
       </c>
       <c r="AW5" s="5">
-        <f t="shared" ref="AW5:AW17" si="9">AU5-AV5</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX5" s="5">
-        <f t="shared" ref="AX5:AX17" si="10">E5/G5*AC5</f>
-        <v>522.9922364356546</v>
+        <f t="shared" si="11"/>
+        <v>360.34664284123591</v>
       </c>
       <c r="AY5" s="1">
-        <f t="shared" ref="AY5:AY17" si="11">F5/G5*AB5</f>
-        <v>35.219206942010928</v>
+        <f t="shared" si="12"/>
+        <v>33.326119092440351</v>
       </c>
       <c r="AZ5" s="1">
-        <f t="shared" ref="AZ5:AZ17" si="12">1/G5*(S5+T5)</f>
-        <v>726.89884190589748</v>
+        <f t="shared" si="13"/>
+        <v>505.77406837277596</v>
       </c>
       <c r="BA5" s="1">
-        <f t="shared" ref="BA5:BA17" si="13">H5/G5*AK5*-1</f>
-        <v>-16.87154294610178</v>
+        <f t="shared" si="14"/>
+        <v>-7.5044530256490054</v>
       </c>
       <c r="BB5" s="1">
-        <f t="shared" ref="BB5:BB17" si="14">I5/G5*AE5</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-946.08851697893374</v>
       </c>
       <c r="BC5" s="1">
-        <f t="shared" ref="BC5:BC17" si="15">L5/G5/(0.9*8760)</f>
+        <f t="shared" si="16"/>
         <v>194.26040330394619</v>
       </c>
       <c r="BD5" s="1">
-        <f t="shared" ref="BD5:BD17" si="16">M5/G5/(0.9*8760)</f>
+        <f t="shared" si="17"/>
         <v>106.85542108065717</v>
       </c>
       <c r="BE5" s="1">
-        <f t="shared" ref="BE5:BE17" si="17">O5</f>
+        <f t="shared" si="18"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="BF5" s="1">
-        <f t="shared" ref="BF5:BF17" si="18">CG5-BY5-CA5-CD5</f>
+        <f t="shared" si="19"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BG5" s="1">
         <v>0</v>
       </c>
       <c r="BH5" s="1">
-        <f t="shared" ref="BH5:BH17" si="19">BF5*S5</f>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="20"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BI5" s="1">
-        <f t="shared" ref="BI5:BI17" si="20">BY5-CG5-CA5-CD5</f>
+        <f t="shared" si="21"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BJ5" s="1">
         <v>0</v>
       </c>
       <c r="BK5" s="1">
-        <f t="shared" ref="BK5:BK17" si="21">BI5*S5</f>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="22"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BL5" s="1">
-        <f t="shared" ref="BL5:BL17" si="22">BY5-CG5</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM5" s="1">
         <v>0</v>
       </c>
       <c r="BN5" s="1">
-        <f t="shared" ref="BN5:BN17" si="23">BL5*S5</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO5" s="1">
-        <f t="shared" ref="BO5:BO17" si="24">BY5-CG5</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP5" s="1">
         <v>0</v>
       </c>
       <c r="BQ5" s="1">
-        <f t="shared" ref="BQ5:BQ17" si="25">BO5*S5</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS5" s="9">
-        <f t="shared" ref="BS5:BS19" si="26">$CJ$2</f>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT5" s="10">
-        <f t="shared" ref="BT5:BT19" si="27">$CJ$3</f>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU5" s="9">
-        <f t="shared" ref="BU5:BU19" si="28">$CJ$4</f>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV5" s="9">
-        <f t="shared" ref="BV5:BV19" si="29">$CJ$5</f>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX5" s="10">
         <v>1</v>
       </c>
       <c r="BY5" s="10">
-        <f>BX5-CE5</f>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="CA5" s="10">
-        <f t="shared" ref="CA5:CA17" si="30">BS5*G5</f>
+        <f t="shared" si="32"/>
         <v>0.35722411839200002</v>
       </c>
       <c r="CB5" s="10">
-        <f t="shared" ref="CB5:CB17" si="31">BU5*H5</f>
+        <f t="shared" si="33"/>
         <v>2.8583416262839882E-2</v>
       </c>
       <c r="CC5" s="10">
-        <f t="shared" ref="CC5:CC17" si="32">(BX5-CA5-CB5-CF5-CD5)*(1-D5)</f>
+        <f t="shared" si="34"/>
         <v>0.41383317371333478</v>
       </c>
       <c r="CD5" s="10">
-        <f t="shared" ref="CD5:CD17" si="33">BV5*P5</f>
+        <f t="shared" si="35"/>
         <v>1.5871428571428571E-2</v>
       </c>
       <c r="CE5" s="10">
-        <f t="shared" ref="CE5:CE17" si="34">(BX5-CA5-CB5-CF5-CD5)*(D5)</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CF5" s="10">
-        <f t="shared" ref="CF5:CF17" si="35">BT5*I5</f>
+        <f t="shared" si="37"/>
         <v>0.1844878630603968</v>
       </c>
       <c r="CG5" s="10">
-        <f t="shared" ref="CG5:CG17" si="36">SUM(CA5:CF5)-CE5</f>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="CI5" s="20" t="s">
@@ -2187,30 +2171,30 @@
         <v>3.542547876</v>
       </c>
       <c r="O6" s="13">
-        <f t="shared" ref="O5:O20" si="37">N6-(Q6*X6)</f>
+        <f t="shared" si="1"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="P6" s="26">
         <v>1.01</v>
       </c>
       <c r="Q6" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125077268194</v>
       </c>
       <c r="S6" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T6" s="16">
-        <v>-16.195074999999999</v>
+        <v>-16.179127999999999</v>
       </c>
       <c r="U6" s="16">
-        <v>64.592955000000003</v>
+        <v>58.461202</v>
       </c>
       <c r="V6" s="16">
-        <v>40.280831999999997</v>
+        <v>19.647223</v>
       </c>
       <c r="W6" s="16">
-        <v>41.334845999999999</v>
+        <v>40.820307</v>
       </c>
       <c r="X6" s="26">
         <v>420</v>
@@ -2218,194 +2202,196 @@
       <c r="Y6" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z6" s="17"/>
+      <c r="Z6" s="17">
+        <v>-2.2030439999999998</v>
+      </c>
       <c r="AA6" s="17"/>
       <c r="AB6" s="16">
-        <v>22.722069000000001</v>
+        <v>21.500722</v>
       </c>
       <c r="AC6" s="16">
-        <v>10.932268000000001</v>
+        <v>7.5324369999999998</v>
       </c>
       <c r="AD6" s="16"/>
       <c r="AE6" s="17">
-        <v>0</v>
+        <v>-140.74133399999999</v>
       </c>
       <c r="AF6" s="17">
-        <v>0</v>
+        <v>-140.74133399999999</v>
       </c>
       <c r="AG6" s="17"/>
       <c r="AH6" s="17"/>
       <c r="AI6" s="17"/>
       <c r="AJ6" s="17"/>
       <c r="AK6" s="16">
-        <v>12.157551</v>
+        <v>5.4076719999999998</v>
       </c>
       <c r="AL6" s="16">
         <v>0</v>
       </c>
       <c r="AM6" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN6" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AP6" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>MIDAT_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="AQ6" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR6" s="12">
-        <f t="shared" si="4"/>
-        <v>1462.3007386975059</v>
+        <f t="shared" si="5"/>
+        <v>167.57043490230325</v>
       </c>
       <c r="AS6" s="12">
-        <f t="shared" si="5"/>
-        <v>1462.3007386975059</v>
+        <f t="shared" si="6"/>
+        <v>167.57043490230325</v>
       </c>
       <c r="AT6" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU6" s="12">
-        <f t="shared" si="7"/>
-        <v>1502.3245255889051</v>
+        <f t="shared" si="8"/>
+        <v>197.40633000961301</v>
       </c>
       <c r="AV6" s="12">
-        <f t="shared" si="8"/>
-        <v>1502.3245255889051</v>
+        <f t="shared" si="9"/>
+        <v>197.40633000961301</v>
       </c>
       <c r="AW6" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX6" s="5">
-        <f t="shared" si="10"/>
-        <v>522.992236628397</v>
+        <f t="shared" si="11"/>
+        <v>360.34664297403725</v>
       </c>
       <c r="AY6" s="1">
-        <f t="shared" si="11"/>
-        <v>44.891991736037248</v>
+        <f t="shared" si="12"/>
+        <v>42.478976467452597</v>
       </c>
       <c r="AZ6" s="1">
-        <f t="shared" si="12"/>
-        <v>667.77182093913541</v>
+        <f t="shared" si="13"/>
+        <v>464.63366172869286</v>
       </c>
       <c r="BA6" s="1">
-        <f t="shared" si="13"/>
-        <v>-16.87154295428207</v>
+        <f t="shared" si="14"/>
+        <v>-7.5044530292875953</v>
       </c>
       <c r="BB6" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-946.08851737090015</v>
       </c>
       <c r="BC6" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>214.57390798665784</v>
       </c>
       <c r="BD6" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>117.95601601844012</v>
       </c>
       <c r="BE6" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="BF6" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BG6" s="1">
         <v>0</v>
       </c>
       <c r="BH6" s="1">
-        <f t="shared" si="19"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="20"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BI6" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BJ6" s="1">
         <v>0</v>
       </c>
       <c r="BK6" s="1">
-        <f t="shared" si="21"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="22"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BL6" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM6" s="1">
         <v>0</v>
       </c>
       <c r="BN6" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO6" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP6" s="1">
         <v>0</v>
       </c>
       <c r="BQ6" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS6" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT6" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU6" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV6" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX6" s="10">
         <v>1</v>
       </c>
       <c r="BY6" s="10">
-        <f t="shared" ref="BY5:BY17" si="38">BX6-CE6</f>
+        <f t="shared" si="31"/>
         <v>0.67299662739933241</v>
       </c>
       <c r="CA6" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.38885408131600002</v>
       </c>
       <c r="CB6" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>3.1114299132937305E-2</v>
       </c>
       <c r="CC6" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.6333708066740841E-2</v>
       </c>
       <c r="CD6" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1.5871428571428571E-2</v>
       </c>
       <c r="CE6" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.32700337260066764</v>
       </c>
       <c r="CF6" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.20082311031222566</v>
       </c>
       <c r="CG6" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.67299662739933241</v>
       </c>
       <c r="CI6" s="20" t="s">
@@ -2460,30 +2446,30 @@
         <v>2.9463016839999998</v>
       </c>
       <c r="O7" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="P7" s="26">
         <v>1.01</v>
       </c>
       <c r="Q7" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11490329922799999</v>
       </c>
       <c r="S7" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T7" s="16">
-        <v>-23.197887000000001</v>
+        <v>-23.276809</v>
       </c>
       <c r="U7" s="16">
-        <v>65.789889000000002</v>
+        <v>60.47681</v>
       </c>
       <c r="V7" s="16">
-        <v>36.475603</v>
+        <v>28.904357999999998</v>
       </c>
       <c r="W7" s="16">
-        <v>41.353130999999998</v>
+        <v>39.957475000000002</v>
       </c>
       <c r="X7" s="26">
         <v>420</v>
@@ -2491,194 +2477,196 @@
       <c r="Y7" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z7" s="17"/>
+      <c r="Z7" s="17">
+        <v>-2.703157</v>
+      </c>
       <c r="AA7" s="17"/>
       <c r="AB7" s="16">
-        <v>21.945748999999999</v>
+        <v>20.789991000000001</v>
       </c>
       <c r="AC7" s="16">
-        <v>10.100218</v>
+        <v>9.1959800000000005</v>
       </c>
       <c r="AD7" s="16"/>
       <c r="AE7" s="17">
-        <v>0</v>
+        <v>-150.75578899999999</v>
       </c>
       <c r="AF7" s="17">
-        <v>0</v>
+        <v>-150.75578899999999</v>
       </c>
       <c r="AG7" s="17"/>
       <c r="AH7" s="17"/>
       <c r="AI7" s="17"/>
       <c r="AJ7" s="17"/>
       <c r="AK7" s="16">
-        <v>11.105559</v>
+        <v>8.9604540000000004</v>
       </c>
       <c r="AL7" s="16">
         <v>0</v>
       </c>
       <c r="AM7" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN7" s="16">
         <v>0</v>
       </c>
       <c r="AP7" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>NE_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="AQ7" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR7" s="12">
-        <f t="shared" si="4"/>
-        <v>1386.0427965263459</v>
+        <f t="shared" si="5"/>
+        <v>117.99563293448526</v>
       </c>
       <c r="AS7" s="12">
-        <f t="shared" si="5"/>
-        <v>1386.0427965263459</v>
+        <f t="shared" si="6"/>
+        <v>117.99563293448526</v>
       </c>
       <c r="AT7" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU7" s="12">
-        <f t="shared" si="7"/>
-        <v>1422.9386587761646</v>
+        <f t="shared" si="8"/>
+        <v>145.49980386579475</v>
       </c>
       <c r="AV7" s="12">
-        <f t="shared" si="8"/>
-        <v>1422.9386587761646</v>
+        <f t="shared" si="9"/>
+        <v>145.49980386579475</v>
       </c>
       <c r="AW7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX7" s="5">
-        <f t="shared" si="10"/>
-        <v>483.18753256942239</v>
+        <f t="shared" si="11"/>
+        <v>439.92940407402665</v>
       </c>
       <c r="AY7" s="1">
-        <f t="shared" si="11"/>
-        <v>34.015910942283881</v>
+        <f t="shared" si="12"/>
+        <v>32.224486042690245</v>
       </c>
       <c r="AZ7" s="1">
-        <f t="shared" si="12"/>
-        <v>665.34412443894701</v>
+        <f t="shared" si="13"/>
+        <v>443.38545239600234</v>
       </c>
       <c r="BA7" s="1">
-        <f t="shared" si="13"/>
-        <v>-15.411649567332033</v>
+        <f t="shared" si="14"/>
+        <v>-12.43479747504818</v>
       </c>
       <c r="BB7" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-1013.4074815647197</v>
       </c>
       <c r="BC7" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>194.26040330394619</v>
       </c>
       <c r="BD7" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>106.85542108065717</v>
       </c>
       <c r="BE7" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="BF7" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BG7" s="1">
         <v>0</v>
       </c>
       <c r="BH7" s="1">
-        <f t="shared" si="19"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="20"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BI7" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BJ7" s="1">
         <v>0</v>
       </c>
       <c r="BK7" s="1">
-        <f t="shared" si="21"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="22"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BL7" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM7" s="1">
         <v>0</v>
       </c>
       <c r="BN7" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO7" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP7" s="1">
         <v>0</v>
       </c>
       <c r="BQ7" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS7" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT7" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU7" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV7" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX7" s="10">
         <v>1</v>
       </c>
       <c r="BY7" s="10">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="CA7" s="10">
+        <f t="shared" si="32"/>
+        <v>0.35722411839200002</v>
+      </c>
+      <c r="CB7" s="10">
+        <f t="shared" si="33"/>
+        <v>2.8583416262839882E-2</v>
+      </c>
+      <c r="CC7" s="10">
+        <f t="shared" si="34"/>
+        <v>0.41383317371333478</v>
+      </c>
+      <c r="CD7" s="10">
+        <f t="shared" si="35"/>
+        <v>1.5871428571428571E-2</v>
+      </c>
+      <c r="CE7" s="10">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="CF7" s="10">
+        <f t="shared" si="37"/>
+        <v>0.1844878630603968</v>
+      </c>
+      <c r="CG7" s="10">
         <f t="shared" si="38"/>
-        <v>1</v>
-      </c>
-      <c r="CA7" s="10">
-        <f t="shared" si="30"/>
-        <v>0.35722411839200002</v>
-      </c>
-      <c r="CB7" s="10">
-        <f t="shared" si="31"/>
-        <v>2.8583416262839882E-2</v>
-      </c>
-      <c r="CC7" s="10">
-        <f t="shared" si="32"/>
-        <v>0.41383317371333478</v>
-      </c>
-      <c r="CD7" s="10">
-        <f t="shared" si="33"/>
-        <v>1.5871428571428571E-2</v>
-      </c>
-      <c r="CE7" s="10">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="CF7" s="10">
-        <f t="shared" si="35"/>
-        <v>0.1844878630603968</v>
-      </c>
-      <c r="CG7" s="10">
-        <f t="shared" si="36"/>
         <v>1</v>
       </c>
     </row>
@@ -2724,30 +2712,30 @@
         <v>3.542547876</v>
       </c>
       <c r="O8" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="P8" s="26">
         <v>1.01</v>
       </c>
       <c r="Q8" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125077268194</v>
       </c>
       <c r="S8" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T8" s="16">
-        <v>-23.197887000000001</v>
+        <v>-23.276809</v>
       </c>
       <c r="U8" s="16">
-        <v>65.789889000000002</v>
+        <v>60.47681</v>
       </c>
       <c r="V8" s="16">
-        <v>36.475603</v>
+        <v>28.904357999999998</v>
       </c>
       <c r="W8" s="16">
-        <v>41.353130999999998</v>
+        <v>39.957475000000002</v>
       </c>
       <c r="X8" s="26">
         <v>420</v>
@@ -2755,194 +2743,196 @@
       <c r="Y8" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z8" s="17"/>
+      <c r="Z8" s="17">
+        <v>-2.703157</v>
+      </c>
       <c r="AA8" s="17"/>
       <c r="AB8" s="16">
-        <v>21.945748999999999</v>
+        <v>20.789991000000001</v>
       </c>
       <c r="AC8" s="16">
-        <v>10.100218</v>
+        <v>9.1959800000000005</v>
       </c>
       <c r="AD8" s="16"/>
       <c r="AE8" s="17">
-        <v>0</v>
+        <v>-150.75578899999999</v>
       </c>
       <c r="AF8" s="17">
-        <v>0</v>
+        <v>-150.75578899999999</v>
       </c>
       <c r="AG8" s="17"/>
       <c r="AH8" s="17"/>
       <c r="AI8" s="17"/>
       <c r="AJ8" s="17"/>
       <c r="AK8" s="16">
-        <v>11.105559</v>
+        <v>8.9604540000000004</v>
       </c>
       <c r="AL8" s="16">
         <v>0</v>
       </c>
       <c r="AM8" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN8" s="16">
         <v>0</v>
       </c>
       <c r="AP8" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>NE_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="AQ8" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR8" s="12">
-        <f t="shared" si="4"/>
-        <v>1365.8743865618048</v>
+        <f t="shared" si="5"/>
+        <v>116.18586167353027</v>
       </c>
       <c r="AS8" s="12">
-        <f t="shared" si="5"/>
-        <v>1365.8743865618048</v>
+        <f t="shared" si="6"/>
+        <v>116.18586167353027</v>
       </c>
       <c r="AT8" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU8" s="12">
-        <f t="shared" si="7"/>
-        <v>1405.898173453204</v>
+        <f t="shared" si="8"/>
+        <v>146.02175678084004</v>
       </c>
       <c r="AV8" s="12">
-        <f t="shared" si="8"/>
-        <v>1405.898173453204</v>
+        <f t="shared" si="9"/>
+        <v>146.02175678084004</v>
       </c>
       <c r="AW8" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX8" s="5">
-        <f t="shared" si="10"/>
-        <v>483.1875327474952</v>
+        <f t="shared" si="11"/>
+        <v>439.92940423615721</v>
       </c>
       <c r="AY8" s="1">
-        <f t="shared" si="11"/>
-        <v>43.358216311602064</v>
+        <f t="shared" si="12"/>
+        <v>41.074785230354188</v>
       </c>
       <c r="AZ8" s="1">
-        <f t="shared" si="12"/>
-        <v>611.22405472929347</v>
+        <f t="shared" si="13"/>
+        <v>407.31982754036449</v>
       </c>
       <c r="BA8" s="1">
-        <f t="shared" si="13"/>
-        <v>-15.411649574804484</v>
+        <f t="shared" si="14"/>
+        <v>-12.434797481077283</v>
       </c>
       <c r="BB8" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-1013.4074819845765</v>
       </c>
       <c r="BC8" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>214.57390798665784</v>
       </c>
       <c r="BD8" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>117.95601601844012</v>
       </c>
       <c r="BE8" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="BF8" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BG8" s="1">
         <v>0</v>
       </c>
       <c r="BH8" s="1">
-        <f t="shared" si="19"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="20"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BI8" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BJ8" s="1">
         <v>0</v>
       </c>
       <c r="BK8" s="1">
-        <f t="shared" si="21"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="22"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BL8" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM8" s="1">
         <v>0</v>
       </c>
       <c r="BN8" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO8" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP8" s="1">
         <v>0</v>
       </c>
       <c r="BQ8" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS8" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT8" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU8" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV8" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX8" s="10">
         <v>1</v>
       </c>
       <c r="BY8" s="10">
+        <f t="shared" si="31"/>
+        <v>0.67299662739933241</v>
+      </c>
+      <c r="CA8" s="10">
+        <f t="shared" si="32"/>
+        <v>0.38885408131600002</v>
+      </c>
+      <c r="CB8" s="10">
+        <f t="shared" si="33"/>
+        <v>3.1114299132937305E-2</v>
+      </c>
+      <c r="CC8" s="10">
+        <f t="shared" si="34"/>
+        <v>3.6333708066740841E-2</v>
+      </c>
+      <c r="CD8" s="10">
+        <f t="shared" si="35"/>
+        <v>1.5871428571428571E-2</v>
+      </c>
+      <c r="CE8" s="10">
+        <f t="shared" si="36"/>
+        <v>0.32700337260066764</v>
+      </c>
+      <c r="CF8" s="10">
+        <f t="shared" si="37"/>
+        <v>0.20082311031222566</v>
+      </c>
+      <c r="CG8" s="10">
         <f t="shared" si="38"/>
-        <v>0.67299662739933241</v>
-      </c>
-      <c r="CA8" s="10">
-        <f t="shared" si="30"/>
-        <v>0.38885408131600002</v>
-      </c>
-      <c r="CB8" s="10">
-        <f t="shared" si="31"/>
-        <v>3.1114299132937305E-2</v>
-      </c>
-      <c r="CC8" s="10">
-        <f t="shared" si="32"/>
-        <v>3.6333708066740841E-2</v>
-      </c>
-      <c r="CD8" s="10">
-        <f t="shared" si="33"/>
-        <v>1.5871428571428571E-2</v>
-      </c>
-      <c r="CE8" s="10">
-        <f t="shared" si="34"/>
-        <v>0.32700337260066764</v>
-      </c>
-      <c r="CF8" s="10">
-        <f t="shared" si="35"/>
-        <v>0.20082311031222566</v>
-      </c>
-      <c r="CG8" s="10">
-        <f t="shared" si="36"/>
         <v>0.67299662739933241</v>
       </c>
     </row>
@@ -2988,30 +2978,30 @@
         <v>2.9463016839999998</v>
       </c>
       <c r="O9" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="P9" s="26">
         <v>1.01</v>
       </c>
       <c r="Q9" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11490329922799999</v>
       </c>
       <c r="S9" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T9" s="16">
-        <v>-4.8339619999999996</v>
+        <v>3.8282379999999998</v>
       </c>
       <c r="U9" s="16">
-        <v>74.769733000000002</v>
+        <v>70.666427999999996</v>
       </c>
       <c r="V9" s="16">
-        <v>43.970934</v>
+        <v>35.615270000000002</v>
       </c>
       <c r="W9" s="16">
-        <v>38.884405999999998</v>
+        <v>32.098216000000001</v>
       </c>
       <c r="X9" s="26">
         <v>420</v>
@@ -3019,194 +3009,196 @@
       <c r="Y9" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z9" s="17"/>
+      <c r="Z9" s="17">
+        <v>-9.0114289999999997</v>
+      </c>
       <c r="AA9" s="17"/>
       <c r="AB9" s="16">
-        <v>20.221685000000001</v>
+        <v>20.274927999999999</v>
       </c>
       <c r="AC9" s="16">
-        <v>5.0428329999999999</v>
+        <v>8.4664520000000003</v>
       </c>
       <c r="AD9" s="16"/>
       <c r="AE9" s="17">
-        <v>0</v>
+        <v>-116.150516</v>
       </c>
       <c r="AF9" s="17">
-        <v>0</v>
+        <v>-116.150516</v>
       </c>
       <c r="AG9" s="17"/>
       <c r="AH9" s="17"/>
       <c r="AI9" s="17"/>
       <c r="AJ9" s="17"/>
       <c r="AK9" s="16">
-        <v>8.5585660000000008</v>
+        <v>12.963217999999999</v>
       </c>
       <c r="AL9" s="16">
         <v>0</v>
       </c>
       <c r="AM9" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN9" s="16">
         <v>0</v>
       </c>
       <c r="AP9" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>CA_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="AQ9" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR9" s="12">
-        <f t="shared" si="4"/>
-        <v>1306.3821217958791</v>
+        <f t="shared" si="5"/>
+        <v>547.61858206381407</v>
       </c>
       <c r="AS9" s="12">
-        <f t="shared" si="5"/>
-        <v>1306.3821217958791</v>
+        <f t="shared" si="6"/>
+        <v>547.61858206381407</v>
       </c>
       <c r="AT9" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU9" s="12">
-        <f t="shared" si="7"/>
-        <v>1343.2779840456978</v>
+        <f t="shared" si="8"/>
+        <v>575.12275299512351</v>
       </c>
       <c r="AV9" s="12">
-        <f t="shared" si="8"/>
-        <v>1343.2779840456978</v>
+        <f t="shared" si="9"/>
+        <v>575.12275299512351</v>
       </c>
       <c r="AW9" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX9" s="5">
-        <f t="shared" si="10"/>
-        <v>241.24568741285168</v>
+        <f t="shared" si="11"/>
+        <v>405.02928268453724</v>
       </c>
       <c r="AY9" s="1">
-        <f t="shared" si="11"/>
-        <v>31.343611742890062</v>
+        <f t="shared" si="12"/>
+        <v>31.426138392871337</v>
       </c>
       <c r="AZ9" s="1">
-        <f t="shared" si="12"/>
-        <v>826.76302515472628</v>
+        <f t="shared" si="13"/>
+        <v>681.63881547549261</v>
       </c>
       <c r="BA9" s="1">
-        <f t="shared" si="13"/>
-        <v>-11.877080657613241</v>
+        <f t="shared" si="14"/>
+        <v>-17.989600800907979</v>
       </c>
       <c r="BB9" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-780.78462314971318</v>
       </c>
       <c r="BC9" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>194.26040330394619</v>
       </c>
       <c r="BD9" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>106.85542108065717</v>
       </c>
       <c r="BE9" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="BF9" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BG9" s="1">
         <v>0</v>
       </c>
       <c r="BH9" s="1">
-        <f t="shared" si="19"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="20"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BI9" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BJ9" s="1">
         <v>0</v>
       </c>
       <c r="BK9" s="1">
-        <f t="shared" si="21"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="22"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BL9" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM9" s="1">
         <v>0</v>
       </c>
       <c r="BN9" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO9" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP9" s="1">
         <v>0</v>
       </c>
       <c r="BQ9" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS9" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT9" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU9" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV9" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX9" s="10">
         <v>1</v>
       </c>
       <c r="BY9" s="10">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="CA9" s="10">
+        <f t="shared" si="32"/>
+        <v>0.35722411839200002</v>
+      </c>
+      <c r="CB9" s="10">
+        <f t="shared" si="33"/>
+        <v>2.8583416262839882E-2</v>
+      </c>
+      <c r="CC9" s="10">
+        <f t="shared" si="34"/>
+        <v>0.41383317371333478</v>
+      </c>
+      <c r="CD9" s="10">
+        <f t="shared" si="35"/>
+        <v>1.5871428571428571E-2</v>
+      </c>
+      <c r="CE9" s="10">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="CF9" s="10">
+        <f t="shared" si="37"/>
+        <v>0.1844878630603968</v>
+      </c>
+      <c r="CG9" s="10">
         <f t="shared" si="38"/>
-        <v>1</v>
-      </c>
-      <c r="CA9" s="10">
-        <f t="shared" si="30"/>
-        <v>0.35722411839200002</v>
-      </c>
-      <c r="CB9" s="10">
-        <f t="shared" si="31"/>
-        <v>2.8583416262839882E-2</v>
-      </c>
-      <c r="CC9" s="10">
-        <f t="shared" si="32"/>
-        <v>0.41383317371333478</v>
-      </c>
-      <c r="CD9" s="10">
-        <f t="shared" si="33"/>
-        <v>1.5871428571428571E-2</v>
-      </c>
-      <c r="CE9" s="10">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="CF9" s="10">
-        <f t="shared" si="35"/>
-        <v>0.1844878630603968</v>
-      </c>
-      <c r="CG9" s="10">
-        <f t="shared" si="36"/>
         <v>1</v>
       </c>
     </row>
@@ -3252,30 +3244,30 @@
         <v>3.542547876</v>
       </c>
       <c r="O10" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="P10" s="26">
         <v>1.01</v>
       </c>
       <c r="Q10" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125077268194</v>
       </c>
       <c r="S10" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T10" s="16">
-        <v>-4.8339619999999996</v>
+        <v>3.8282379999999998</v>
       </c>
       <c r="U10" s="16">
-        <v>74.769733000000002</v>
+        <v>70.666427999999996</v>
       </c>
       <c r="V10" s="16">
-        <v>43.970934</v>
+        <v>35.615270000000002</v>
       </c>
       <c r="W10" s="16">
-        <v>38.884405999999998</v>
+        <v>32.098216000000001</v>
       </c>
       <c r="X10" s="26">
         <v>420</v>
@@ -3283,194 +3275,196 @@
       <c r="Y10" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z10" s="17"/>
+      <c r="Z10" s="17">
+        <v>-9.0114289999999997</v>
+      </c>
       <c r="AA10" s="17"/>
       <c r="AB10" s="16">
-        <v>20.221685000000001</v>
+        <v>20.274927999999999</v>
       </c>
       <c r="AC10" s="16">
-        <v>5.0428329999999999</v>
+        <v>8.4664520000000003</v>
       </c>
       <c r="AD10" s="16"/>
       <c r="AE10" s="17">
-        <v>0</v>
+        <v>-116.150516</v>
       </c>
       <c r="AF10" s="17">
-        <v>0</v>
+        <v>-116.150516</v>
       </c>
       <c r="AG10" s="17"/>
       <c r="AH10" s="17"/>
       <c r="AI10" s="17"/>
       <c r="AJ10" s="17"/>
       <c r="AK10" s="16">
-        <v>8.5585660000000008</v>
+        <v>12.963217999999999</v>
       </c>
       <c r="AL10" s="16">
         <v>0</v>
       </c>
       <c r="AM10" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN10" s="16">
         <v>0</v>
       </c>
       <c r="AP10" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>CA_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="AQ10" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR10" s="12">
-        <f t="shared" si="4"/>
-        <v>1272.3497268887545</v>
+        <f t="shared" si="5"/>
+        <v>526.209669573979</v>
       </c>
       <c r="AS10" s="12">
-        <f t="shared" si="5"/>
-        <v>1272.3497268887545</v>
+        <f t="shared" si="6"/>
+        <v>526.209669573979</v>
       </c>
       <c r="AT10" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU10" s="12">
-        <f t="shared" si="7"/>
-        <v>1312.3735137801536</v>
+        <f t="shared" si="8"/>
+        <v>556.04556468128874</v>
       </c>
       <c r="AV10" s="12">
-        <f t="shared" si="8"/>
-        <v>1312.3735137801536</v>
+        <f t="shared" si="9"/>
+        <v>556.04556468128874</v>
       </c>
       <c r="AW10" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX10" s="5">
-        <f t="shared" si="10"/>
-        <v>241.24568750175982</v>
+        <f t="shared" si="11"/>
+        <v>405.02928283380578</v>
       </c>
       <c r="AY10" s="1">
-        <f t="shared" si="11"/>
-        <v>39.951983065835613</v>
+        <f t="shared" si="12"/>
+        <v>40.057175260965458</v>
       </c>
       <c r="AZ10" s="1">
-        <f t="shared" si="12"/>
-        <v>759.51290463631233</v>
+        <f t="shared" si="13"/>
+        <v>626.19331162972389</v>
       </c>
       <c r="BA10" s="1">
-        <f t="shared" si="13"/>
-        <v>-11.877080663371933</v>
+        <f t="shared" si="14"/>
+        <v>-17.989600809630371</v>
       </c>
       <c r="BB10" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-780.78462347319385</v>
       </c>
       <c r="BC10" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>214.57390798665784</v>
       </c>
       <c r="BD10" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>117.95601601844012</v>
       </c>
       <c r="BE10" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="BF10" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BG10" s="1">
         <v>0</v>
       </c>
       <c r="BH10" s="1">
-        <f t="shared" si="19"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="20"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BI10" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BJ10" s="1">
         <v>0</v>
       </c>
       <c r="BK10" s="1">
-        <f t="shared" si="21"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="22"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BL10" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM10" s="1">
         <v>0</v>
       </c>
       <c r="BN10" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO10" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP10" s="1">
         <v>0</v>
       </c>
       <c r="BQ10" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS10" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT10" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU10" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV10" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX10" s="10">
         <v>1</v>
       </c>
       <c r="BY10" s="10">
+        <f t="shared" si="31"/>
+        <v>0.67299662739933241</v>
+      </c>
+      <c r="CA10" s="10">
+        <f t="shared" si="32"/>
+        <v>0.38885408131600002</v>
+      </c>
+      <c r="CB10" s="10">
+        <f t="shared" si="33"/>
+        <v>3.1114299132937305E-2</v>
+      </c>
+      <c r="CC10" s="10">
+        <f t="shared" si="34"/>
+        <v>3.6333708066740841E-2</v>
+      </c>
+      <c r="CD10" s="10">
+        <f t="shared" si="35"/>
+        <v>1.5871428571428571E-2</v>
+      </c>
+      <c r="CE10" s="10">
+        <f t="shared" si="36"/>
+        <v>0.32700337260066764</v>
+      </c>
+      <c r="CF10" s="10">
+        <f t="shared" si="37"/>
+        <v>0.20082311031222566</v>
+      </c>
+      <c r="CG10" s="10">
         <f t="shared" si="38"/>
-        <v>0.67299662739933241</v>
-      </c>
-      <c r="CA10" s="10">
-        <f t="shared" si="30"/>
-        <v>0.38885408131600002</v>
-      </c>
-      <c r="CB10" s="10">
-        <f t="shared" si="31"/>
-        <v>3.1114299132937305E-2</v>
-      </c>
-      <c r="CC10" s="10">
-        <f t="shared" si="32"/>
-        <v>3.6333708066740841E-2</v>
-      </c>
-      <c r="CD10" s="10">
-        <f t="shared" si="33"/>
-        <v>1.5871428571428571E-2</v>
-      </c>
-      <c r="CE10" s="10">
-        <f t="shared" si="34"/>
-        <v>0.32700337260066764</v>
-      </c>
-      <c r="CF10" s="10">
-        <f t="shared" si="35"/>
-        <v>0.20082311031222566</v>
-      </c>
-      <c r="CG10" s="10">
-        <f t="shared" si="36"/>
         <v>0.67299662739933241</v>
       </c>
     </row>
@@ -3516,30 +3510,30 @@
         <v>2.9463016839999998</v>
       </c>
       <c r="O11" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="P11" s="26">
         <v>1.01</v>
       </c>
       <c r="Q11" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11490329922799999</v>
       </c>
       <c r="S11" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T11" s="16">
-        <v>-6.0941159999999996</v>
+        <v>-6.0973139999999999</v>
       </c>
       <c r="U11" s="16">
-        <v>65.017885000000007</v>
+        <v>61.343403000000002</v>
       </c>
       <c r="V11" s="16">
-        <v>44.076763</v>
+        <v>33.004970999999998</v>
       </c>
       <c r="W11" s="16">
-        <v>42.359470999999999</v>
+        <v>42.195610000000002</v>
       </c>
       <c r="X11" s="26">
         <v>420</v>
@@ -3547,194 +3541,196 @@
       <c r="Y11" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z11" s="17"/>
+      <c r="Z11" s="17">
+        <v>51.423575999999997</v>
+      </c>
       <c r="AA11" s="17"/>
       <c r="AB11" s="16">
-        <v>23.169466</v>
+        <v>22.906690000000001</v>
       </c>
       <c r="AC11" s="16">
-        <v>8.136234</v>
+        <v>13.197062000000001</v>
       </c>
       <c r="AD11" s="16"/>
       <c r="AE11" s="17">
-        <v>0</v>
+        <v>-129.528977</v>
       </c>
       <c r="AF11" s="17">
-        <v>0</v>
+        <v>-129.528977</v>
       </c>
       <c r="AG11" s="17"/>
       <c r="AH11" s="17"/>
       <c r="AI11" s="17"/>
       <c r="AJ11" s="17"/>
       <c r="AK11" s="16">
-        <v>13.552455999999999</v>
+        <v>14.953878</v>
       </c>
       <c r="AL11" s="16">
         <v>0</v>
       </c>
       <c r="AM11" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN11" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AP11" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>NCEN_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="AQ11" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR11" s="12">
-        <f t="shared" si="4"/>
-        <v>1440.9303899096728</v>
+        <f t="shared" si="5"/>
+        <v>598.06642417112914</v>
       </c>
       <c r="AS11" s="12">
-        <f t="shared" si="5"/>
-        <v>1440.9303899096728</v>
+        <f t="shared" si="6"/>
+        <v>598.06642417112914</v>
       </c>
       <c r="AT11" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU11" s="12">
-        <f t="shared" si="7"/>
-        <v>1477.8262521594916</v>
+        <f t="shared" si="8"/>
+        <v>625.57059510243857</v>
       </c>
       <c r="AV11" s="12">
-        <f t="shared" si="8"/>
-        <v>1477.8262521594916</v>
+        <f t="shared" si="9"/>
+        <v>625.57059510243857</v>
       </c>
       <c r="AW11" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX11" s="5">
-        <f t="shared" si="10"/>
-        <v>389.23187904136739</v>
+        <f t="shared" si="11"/>
+        <v>631.33843496701627</v>
       </c>
       <c r="AY11" s="1">
-        <f t="shared" si="11"/>
-        <v>35.912672291853617</v>
+        <f t="shared" si="12"/>
+        <v>35.505369491946013</v>
       </c>
       <c r="AZ11" s="1">
-        <f t="shared" si="12"/>
-        <v>815.68627149707459</v>
+        <f t="shared" si="13"/>
+        <v>594.39321341398875</v>
       </c>
       <c r="BA11" s="1">
-        <f t="shared" si="13"/>
-        <v>-18.80731106364717</v>
+        <f t="shared" si="14"/>
+        <v>-20.752123095166663</v>
       </c>
       <c r="BB11" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-870.71704006818936</v>
       </c>
       <c r="BC11" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>194.26040330394619</v>
       </c>
       <c r="BD11" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>106.85542108065717</v>
       </c>
       <c r="BE11" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="BF11" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BG11" s="1">
         <v>0</v>
       </c>
       <c r="BH11" s="1">
-        <f t="shared" si="19"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="20"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BI11" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BJ11" s="1">
         <v>0</v>
       </c>
       <c r="BK11" s="1">
-        <f t="shared" si="21"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="22"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BL11" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM11" s="1">
         <v>0</v>
       </c>
       <c r="BN11" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO11" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP11" s="1">
         <v>0</v>
       </c>
       <c r="BQ11" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS11" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT11" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU11" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV11" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX11" s="10">
         <v>1</v>
       </c>
       <c r="BY11" s="10">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="CA11" s="10">
+        <f t="shared" si="32"/>
+        <v>0.35722411839200002</v>
+      </c>
+      <c r="CB11" s="10">
+        <f t="shared" si="33"/>
+        <v>2.8583416262839882E-2</v>
+      </c>
+      <c r="CC11" s="10">
+        <f t="shared" si="34"/>
+        <v>0.41383317371333478</v>
+      </c>
+      <c r="CD11" s="10">
+        <f t="shared" si="35"/>
+        <v>1.5871428571428571E-2</v>
+      </c>
+      <c r="CE11" s="10">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="CF11" s="10">
+        <f t="shared" si="37"/>
+        <v>0.1844878630603968</v>
+      </c>
+      <c r="CG11" s="10">
         <f t="shared" si="38"/>
-        <v>1</v>
-      </c>
-      <c r="CA11" s="10">
-        <f t="shared" si="30"/>
-        <v>0.35722411839200002</v>
-      </c>
-      <c r="CB11" s="10">
-        <f t="shared" si="31"/>
-        <v>2.8583416262839882E-2</v>
-      </c>
-      <c r="CC11" s="10">
-        <f t="shared" si="32"/>
-        <v>0.41383317371333478</v>
-      </c>
-      <c r="CD11" s="10">
-        <f t="shared" si="33"/>
-        <v>1.5871428571428571E-2</v>
-      </c>
-      <c r="CE11" s="10">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="CF11" s="10">
-        <f t="shared" si="35"/>
-        <v>0.1844878630603968</v>
-      </c>
-      <c r="CG11" s="10">
-        <f t="shared" si="36"/>
         <v>1</v>
       </c>
     </row>
@@ -3780,30 +3776,30 @@
         <v>3.542547876</v>
       </c>
       <c r="O12" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="P12" s="26">
         <v>1.01</v>
       </c>
       <c r="Q12" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125077268194</v>
       </c>
       <c r="S12" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T12" s="16">
-        <v>-6.0941159999999996</v>
+        <v>-6.0973139999999999</v>
       </c>
       <c r="U12" s="16">
-        <v>65.017885000000007</v>
+        <v>61.343403000000002</v>
       </c>
       <c r="V12" s="16">
-        <v>44.076763</v>
+        <v>33.004970999999998</v>
       </c>
       <c r="W12" s="16">
-        <v>42.359470999999999</v>
+        <v>42.195610000000002</v>
       </c>
       <c r="X12" s="26">
         <v>420</v>
@@ -3811,194 +3807,196 @@
       <c r="Y12" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z12" s="17"/>
+      <c r="Z12" s="17">
+        <v>51.423575999999997</v>
+      </c>
       <c r="AA12" s="17"/>
       <c r="AB12" s="16">
-        <v>23.169466</v>
+        <v>22.906690000000001</v>
       </c>
       <c r="AC12" s="16">
-        <v>8.136234</v>
+        <v>13.197062000000001</v>
       </c>
       <c r="AD12" s="16"/>
       <c r="AE12" s="17">
-        <v>0</v>
+        <v>-129.528977</v>
       </c>
       <c r="AF12" s="17">
-        <v>0</v>
+        <v>-129.528977</v>
       </c>
       <c r="AG12" s="17"/>
       <c r="AH12" s="17"/>
       <c r="AI12" s="17"/>
       <c r="AJ12" s="17"/>
       <c r="AK12" s="16">
-        <v>13.552455999999999</v>
+        <v>14.953878</v>
       </c>
       <c r="AL12" s="16">
         <v>0</v>
       </c>
       <c r="AM12" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN12" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AP12" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>NCEN_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="AQ12" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR12" s="12">
-        <f t="shared" si="4"/>
-        <v>1409.0538648629781</v>
+        <f t="shared" si="5"/>
+        <v>584.8745384096128</v>
       </c>
       <c r="AS12" s="12">
-        <f t="shared" si="5"/>
-        <v>1409.0538648629781</v>
+        <f t="shared" si="6"/>
+        <v>584.8745384096128</v>
       </c>
       <c r="AT12" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU12" s="12">
-        <f t="shared" si="7"/>
-        <v>1449.0776517543773</v>
+        <f t="shared" si="8"/>
+        <v>614.71043351692254</v>
       </c>
       <c r="AV12" s="12">
-        <f t="shared" si="8"/>
-        <v>1449.0776517543773</v>
+        <f t="shared" si="9"/>
+        <v>614.71043351692254</v>
       </c>
       <c r="AW12" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX12" s="5">
-        <f t="shared" si="10"/>
-        <v>389.23187918481403</v>
+        <f t="shared" si="11"/>
+        <v>631.33843519968821</v>
       </c>
       <c r="AY12" s="1">
-        <f t="shared" si="11"/>
-        <v>45.775913989188041</v>
+        <f t="shared" si="12"/>
+        <v>45.256747445840737</v>
       </c>
       <c r="AZ12" s="1">
-        <f t="shared" si="12"/>
-        <v>749.33715041352343</v>
+        <f t="shared" si="13"/>
+        <v>546.04439516593357</v>
       </c>
       <c r="BA12" s="1">
-        <f t="shared" si="13"/>
-        <v>-18.807311072766034</v>
+        <f t="shared" si="14"/>
+        <v>-20.752123105228485</v>
       </c>
       <c r="BB12" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-870.71704042892929</v>
       </c>
       <c r="BC12" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>214.57390798665784</v>
       </c>
       <c r="BD12" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>117.95601601844012</v>
       </c>
       <c r="BE12" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="BF12" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BG12" s="1">
         <v>0</v>
       </c>
       <c r="BH12" s="1">
-        <f t="shared" si="19"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="20"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BI12" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BJ12" s="1">
         <v>0</v>
       </c>
       <c r="BK12" s="1">
-        <f t="shared" si="21"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="22"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BL12" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM12" s="1">
         <v>0</v>
       </c>
       <c r="BN12" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO12" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP12" s="1">
         <v>0</v>
       </c>
       <c r="BQ12" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS12" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT12" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU12" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV12" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX12" s="10">
         <v>1</v>
       </c>
       <c r="BY12" s="10">
+        <f t="shared" si="31"/>
+        <v>0.67299662739933241</v>
+      </c>
+      <c r="CA12" s="10">
+        <f t="shared" si="32"/>
+        <v>0.38885408131600002</v>
+      </c>
+      <c r="CB12" s="10">
+        <f t="shared" si="33"/>
+        <v>3.1114299132937305E-2</v>
+      </c>
+      <c r="CC12" s="10">
+        <f t="shared" si="34"/>
+        <v>3.6333708066740841E-2</v>
+      </c>
+      <c r="CD12" s="10">
+        <f t="shared" si="35"/>
+        <v>1.5871428571428571E-2</v>
+      </c>
+      <c r="CE12" s="10">
+        <f t="shared" si="36"/>
+        <v>0.32700337260066764</v>
+      </c>
+      <c r="CF12" s="10">
+        <f t="shared" si="37"/>
+        <v>0.20082311031222566</v>
+      </c>
+      <c r="CG12" s="10">
         <f t="shared" si="38"/>
-        <v>0.67299662739933241</v>
-      </c>
-      <c r="CA12" s="10">
-        <f t="shared" si="30"/>
-        <v>0.38885408131600002</v>
-      </c>
-      <c r="CB12" s="10">
-        <f t="shared" si="31"/>
-        <v>3.1114299132937305E-2</v>
-      </c>
-      <c r="CC12" s="10">
-        <f t="shared" si="32"/>
-        <v>3.6333708066740841E-2</v>
-      </c>
-      <c r="CD12" s="10">
-        <f t="shared" si="33"/>
-        <v>1.5871428571428571E-2</v>
-      </c>
-      <c r="CE12" s="10">
-        <f t="shared" si="34"/>
-        <v>0.32700337260066764</v>
-      </c>
-      <c r="CF12" s="10">
-        <f t="shared" si="35"/>
-        <v>0.20082311031222566</v>
-      </c>
-      <c r="CG12" s="10">
-        <f t="shared" si="36"/>
         <v>0.67299662739933241</v>
       </c>
     </row>
@@ -4044,30 +4042,30 @@
         <v>2.9463016839999998</v>
       </c>
       <c r="O13" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="P13" s="26">
         <v>1.01</v>
       </c>
       <c r="Q13" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11490329922799999</v>
       </c>
       <c r="S13" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T13" s="16">
-        <v>-6.2004849999999996</v>
+        <v>-6.1992539999999998</v>
       </c>
       <c r="U13" s="16">
-        <v>65.557461000000004</v>
+        <v>65.59151</v>
       </c>
       <c r="V13" s="16">
-        <v>44.126296000000004</v>
+        <v>31.821489</v>
       </c>
       <c r="W13" s="16">
-        <v>40.622698999999997</v>
+        <v>37.986238999999998</v>
       </c>
       <c r="X13" s="26">
         <v>420</v>
@@ -4075,194 +4073,196 @@
       <c r="Y13" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z13" s="17"/>
+      <c r="Z13" s="17">
+        <v>51.417555</v>
+      </c>
       <c r="AA13" s="17"/>
       <c r="AB13" s="16">
-        <v>22.423241999999998</v>
+        <v>22.465142</v>
       </c>
       <c r="AC13" s="16">
-        <v>7.9492849999999997</v>
+        <v>13.285634</v>
       </c>
       <c r="AD13" s="16"/>
       <c r="AE13" s="17">
-        <v>0</v>
+        <v>-129.68144799999999</v>
       </c>
       <c r="AF13" s="17">
-        <v>0</v>
+        <v>-129.68144799999999</v>
       </c>
       <c r="AG13" s="17"/>
       <c r="AH13" s="17"/>
       <c r="AI13" s="17"/>
       <c r="AJ13" s="17"/>
       <c r="AK13" s="16">
-        <v>13.349734</v>
+        <v>15.046749</v>
       </c>
       <c r="AL13" s="16">
         <v>0</v>
       </c>
       <c r="AM13" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN13" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AP13" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>CEN_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="AQ13" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR13" s="12">
-        <f t="shared" si="4"/>
-        <v>1430.1765725049829</v>
+        <f t="shared" si="5"/>
+        <v>599.56937775741244</v>
       </c>
       <c r="AS13" s="12">
-        <f t="shared" si="5"/>
-        <v>1430.1765725049829</v>
+        <f t="shared" si="6"/>
+        <v>599.56937775741244</v>
       </c>
       <c r="AT13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU13" s="12">
-        <f t="shared" si="7"/>
-        <v>1467.0724347548016</v>
+        <f t="shared" si="8"/>
+        <v>627.07354868872187</v>
       </c>
       <c r="AV13" s="12">
-        <f t="shared" si="8"/>
-        <v>1467.0724347548016</v>
+        <f t="shared" si="9"/>
+        <v>627.07354868872187</v>
       </c>
       <c r="AW13" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX13" s="5">
-        <f t="shared" si="10"/>
-        <v>380.28836653239767</v>
+        <f t="shared" si="11"/>
+        <v>635.57565896898711</v>
       </c>
       <c r="AY13" s="1">
-        <f t="shared" si="11"/>
-        <v>34.756025092115991</v>
+        <f t="shared" si="12"/>
+        <v>34.820970092101263</v>
       </c>
       <c r="AZ13" s="1">
-        <f t="shared" si="12"/>
-        <v>814.7512879872728</v>
+        <f t="shared" si="13"/>
+        <v>593.49716081417864</v>
       </c>
       <c r="BA13" s="1">
-        <f t="shared" si="13"/>
-        <v>-18.525985249828281</v>
+        <f t="shared" si="14"/>
+        <v>-20.881004073329734</v>
       </c>
       <c r="BB13" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-871.74197750605879</v>
       </c>
       <c r="BC13" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>194.26040330394619</v>
       </c>
       <c r="BD13" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>106.85542108065717</v>
       </c>
       <c r="BE13" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="BF13" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BG13" s="1">
         <v>0</v>
       </c>
       <c r="BH13" s="1">
-        <f t="shared" si="19"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="20"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BI13" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BJ13" s="1">
         <v>0</v>
       </c>
       <c r="BK13" s="1">
-        <f t="shared" si="21"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="22"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BL13" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM13" s="1">
         <v>0</v>
       </c>
       <c r="BN13" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO13" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP13" s="1">
         <v>0</v>
       </c>
       <c r="BQ13" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS13" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT13" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU13" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV13" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX13" s="10">
         <v>1</v>
       </c>
       <c r="BY13" s="10">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="CA13" s="10">
+        <f t="shared" si="32"/>
+        <v>0.35722411839200002</v>
+      </c>
+      <c r="CB13" s="10">
+        <f t="shared" si="33"/>
+        <v>2.8583416262839882E-2</v>
+      </c>
+      <c r="CC13" s="10">
+        <f t="shared" si="34"/>
+        <v>0.41383317371333478</v>
+      </c>
+      <c r="CD13" s="10">
+        <f t="shared" si="35"/>
+        <v>1.5871428571428571E-2</v>
+      </c>
+      <c r="CE13" s="10">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="CF13" s="10">
+        <f t="shared" si="37"/>
+        <v>0.1844878630603968</v>
+      </c>
+      <c r="CG13" s="10">
         <f t="shared" si="38"/>
-        <v>1</v>
-      </c>
-      <c r="CA13" s="10">
-        <f t="shared" si="30"/>
-        <v>0.35722411839200002</v>
-      </c>
-      <c r="CB13" s="10">
-        <f t="shared" si="31"/>
-        <v>2.8583416262839882E-2</v>
-      </c>
-      <c r="CC13" s="10">
-        <f t="shared" si="32"/>
-        <v>0.41383317371333478</v>
-      </c>
-      <c r="CD13" s="10">
-        <f t="shared" si="33"/>
-        <v>1.5871428571428571E-2</v>
-      </c>
-      <c r="CE13" s="10">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="CF13" s="10">
-        <f t="shared" si="35"/>
-        <v>0.1844878630603968</v>
-      </c>
-      <c r="CG13" s="10">
-        <f t="shared" si="36"/>
         <v>1</v>
       </c>
     </row>
@@ -4308,30 +4308,30 @@
         <v>3.542547876</v>
       </c>
       <c r="O14" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="P14" s="26">
         <v>1.01</v>
       </c>
       <c r="Q14" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125077268194</v>
       </c>
       <c r="S14" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T14" s="16">
-        <v>-6.2004849999999996</v>
+        <v>-6.1992539999999998</v>
       </c>
       <c r="U14" s="16">
-        <v>65.557461000000004</v>
+        <v>65.59151</v>
       </c>
       <c r="V14" s="16">
-        <v>44.126296000000004</v>
+        <v>31.821489</v>
       </c>
       <c r="W14" s="16">
-        <v>40.622698999999997</v>
+        <v>37.986238999999998</v>
       </c>
       <c r="X14" s="26">
         <v>420</v>
@@ -4339,194 +4339,196 @@
       <c r="Y14" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z14" s="17"/>
+      <c r="Z14" s="17">
+        <v>51.417555</v>
+      </c>
       <c r="AA14" s="17"/>
       <c r="AB14" s="16">
-        <v>22.423241999999998</v>
+        <v>22.465142</v>
       </c>
       <c r="AC14" s="16">
-        <v>7.9492849999999997</v>
+        <v>13.285634</v>
       </c>
       <c r="AD14" s="16"/>
       <c r="AE14" s="17">
-        <v>0</v>
+        <v>-129.68144799999999</v>
       </c>
       <c r="AF14" s="17">
-        <v>0</v>
+        <v>-129.68144799999999</v>
       </c>
       <c r="AG14" s="17"/>
       <c r="AH14" s="17"/>
       <c r="AI14" s="17"/>
       <c r="AJ14" s="17"/>
       <c r="AK14" s="16">
-        <v>13.349734</v>
+        <v>15.046749</v>
       </c>
       <c r="AL14" s="16">
         <v>0</v>
       </c>
       <c r="AM14" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN14" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AP14" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>CEN_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="AQ14" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR14" s="12">
-        <f t="shared" si="4"/>
-        <v>1398.0584328315642</v>
+        <f t="shared" si="5"/>
+        <v>586.26241124940475</v>
       </c>
       <c r="AS14" s="12">
-        <f t="shared" si="5"/>
-        <v>1398.0584328315642</v>
+        <f t="shared" si="6"/>
+        <v>586.26241124940475</v>
       </c>
       <c r="AT14" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU14" s="12">
-        <f t="shared" si="7"/>
-        <v>1438.0822197229634</v>
+        <f t="shared" si="8"/>
+        <v>616.09830635671449</v>
       </c>
       <c r="AV14" s="12">
-        <f t="shared" si="8"/>
-        <v>1438.0822197229634</v>
+        <f t="shared" si="9"/>
+        <v>616.09830635671449</v>
       </c>
       <c r="AW14" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX14" s="5">
-        <f t="shared" si="10"/>
-        <v>380.28836667254831</v>
+        <f t="shared" si="11"/>
+        <v>635.57565920322077</v>
       </c>
       <c r="AY14" s="1">
-        <f t="shared" si="11"/>
-        <v>44.301599231969732</v>
+        <f t="shared" si="12"/>
+        <v>44.384381061993224</v>
       </c>
       <c r="AZ14" s="1">
-        <f t="shared" si="12"/>
-        <v>748.47821983763833</v>
+        <f t="shared" si="13"/>
+        <v>545.22122880255972</v>
       </c>
       <c r="BA14" s="1">
-        <f t="shared" si="13"/>
-        <v>-18.525985258810742</v>
+        <f t="shared" si="14"/>
+        <v>-20.881004083454044</v>
       </c>
       <c r="BB14" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-871.74197786722334</v>
       </c>
       <c r="BC14" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>214.57390798665784</v>
       </c>
       <c r="BD14" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>117.95601601844012</v>
       </c>
       <c r="BE14" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="BF14" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BG14" s="1">
         <v>0</v>
       </c>
       <c r="BH14" s="1">
-        <f t="shared" si="19"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="20"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BI14" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BJ14" s="1">
         <v>0</v>
       </c>
       <c r="BK14" s="1">
-        <f t="shared" si="21"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="22"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BL14" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM14" s="1">
         <v>0</v>
       </c>
       <c r="BN14" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO14" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP14" s="1">
         <v>0</v>
       </c>
       <c r="BQ14" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS14" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT14" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU14" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV14" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX14" s="10">
         <v>1</v>
       </c>
       <c r="BY14" s="10">
+        <f t="shared" si="31"/>
+        <v>0.67299662739933241</v>
+      </c>
+      <c r="CA14" s="10">
+        <f t="shared" si="32"/>
+        <v>0.38885408131600002</v>
+      </c>
+      <c r="CB14" s="10">
+        <f t="shared" si="33"/>
+        <v>3.1114299132937305E-2</v>
+      </c>
+      <c r="CC14" s="10">
+        <f t="shared" si="34"/>
+        <v>3.6333708066740841E-2</v>
+      </c>
+      <c r="CD14" s="10">
+        <f t="shared" si="35"/>
+        <v>1.5871428571428571E-2</v>
+      </c>
+      <c r="CE14" s="10">
+        <f t="shared" si="36"/>
+        <v>0.32700337260066764</v>
+      </c>
+      <c r="CF14" s="10">
+        <f t="shared" si="37"/>
+        <v>0.20082311031222566</v>
+      </c>
+      <c r="CG14" s="10">
         <f t="shared" si="38"/>
-        <v>0.67299662739933241</v>
-      </c>
-      <c r="CA14" s="10">
-        <f t="shared" si="30"/>
-        <v>0.38885408131600002</v>
-      </c>
-      <c r="CB14" s="10">
-        <f t="shared" si="31"/>
-        <v>3.1114299132937305E-2</v>
-      </c>
-      <c r="CC14" s="10">
-        <f t="shared" si="32"/>
-        <v>3.6333708066740841E-2</v>
-      </c>
-      <c r="CD14" s="10">
-        <f t="shared" si="33"/>
-        <v>1.5871428571428571E-2</v>
-      </c>
-      <c r="CE14" s="10">
-        <f t="shared" si="34"/>
-        <v>0.32700337260066764</v>
-      </c>
-      <c r="CF14" s="10">
-        <f t="shared" si="35"/>
-        <v>0.20082311031222566</v>
-      </c>
-      <c r="CG14" s="10">
-        <f t="shared" si="36"/>
         <v>0.67299662739933241</v>
       </c>
     </row>
@@ -4572,30 +4574,30 @@
         <v>2.9463016839999998</v>
       </c>
       <c r="O15" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="P15" s="26">
         <v>1.01</v>
       </c>
       <c r="Q15" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11490329922799999</v>
       </c>
       <c r="S15" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T15" s="16">
-        <v>-5.0171330000000003</v>
+        <v>-5.0000840000000002</v>
       </c>
       <c r="U15" s="16">
-        <v>65.195735999999997</v>
+        <v>62.617055000000001</v>
       </c>
       <c r="V15" s="16">
-        <v>49.284007000000003</v>
+        <v>37.705083000000002</v>
       </c>
       <c r="W15" s="16">
-        <v>40.025033000000001</v>
+        <v>30.684851999999999</v>
       </c>
       <c r="X15" s="26">
         <v>420</v>
@@ -4603,194 +4605,196 @@
       <c r="Y15" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z15" s="17"/>
+      <c r="Z15" s="17">
+        <v>-8.7269439999999996</v>
+      </c>
       <c r="AA15" s="17"/>
       <c r="AB15" s="16">
-        <v>21.347408999999999</v>
+        <v>21.357776999999999</v>
       </c>
       <c r="AC15" s="16">
-        <v>7.9738689999999997</v>
+        <v>7.5483099999999999</v>
       </c>
       <c r="AD15" s="16"/>
       <c r="AE15" s="17">
-        <v>0</v>
+        <v>-126.782873</v>
       </c>
       <c r="AF15" s="17">
-        <v>0</v>
+        <v>-126.782873</v>
       </c>
       <c r="AG15" s="17"/>
       <c r="AH15" s="17"/>
       <c r="AI15" s="17"/>
       <c r="AJ15" s="17"/>
       <c r="AK15" s="16">
-        <v>13.408868</v>
+        <v>8.6017200000000003</v>
       </c>
       <c r="AL15" s="16">
         <v>0</v>
       </c>
       <c r="AM15" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN15" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AP15" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>TX_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="AQ15" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR15" s="12">
-        <f t="shared" si="4"/>
-        <v>1440.0047144772827</v>
+        <f t="shared" si="5"/>
+        <v>362.35278204469142</v>
       </c>
       <c r="AS15" s="12">
-        <f t="shared" si="5"/>
-        <v>1440.0047144772827</v>
+        <f t="shared" si="6"/>
+        <v>362.35278204469142</v>
       </c>
       <c r="AT15" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU15" s="12">
-        <f t="shared" si="7"/>
-        <v>1476.9005767271015</v>
+        <f t="shared" si="8"/>
+        <v>389.85695297600091</v>
       </c>
       <c r="AV15" s="12">
-        <f t="shared" si="8"/>
-        <v>1476.9005767271015</v>
+        <f t="shared" si="9"/>
+        <v>389.85695297600091</v>
       </c>
       <c r="AW15" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX15" s="5">
-        <f t="shared" si="10"/>
-        <v>381.46444830614621</v>
+        <f t="shared" si="11"/>
+        <v>361.10599632296021</v>
       </c>
       <c r="AY15" s="1">
-        <f t="shared" si="11"/>
-        <v>33.08848394249425</v>
+        <f t="shared" si="12"/>
+        <v>33.104554342490609</v>
       </c>
       <c r="AZ15" s="1">
-        <f t="shared" si="12"/>
-        <v>825.15295206506767</v>
+        <f t="shared" si="13"/>
+        <v>604.03786511194403</v>
       </c>
       <c r="BA15" s="1">
-        <f t="shared" si="13"/>
-        <v>-18.608047979449964</v>
+        <f t="shared" si="14"/>
+        <v>-11.936967271643985</v>
       </c>
       <c r="BB15" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-852.25723592259328</v>
       </c>
       <c r="BC15" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>194.26040330394619</v>
       </c>
       <c r="BD15" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>106.85542108065717</v>
       </c>
       <c r="BE15" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="BF15" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BG15" s="1">
         <v>0</v>
       </c>
       <c r="BH15" s="1">
-        <f t="shared" si="19"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="20"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BI15" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BJ15" s="1">
         <v>0</v>
       </c>
       <c r="BK15" s="1">
-        <f t="shared" si="21"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="22"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BL15" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM15" s="1">
         <v>0</v>
       </c>
       <c r="BN15" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO15" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP15" s="1">
         <v>0</v>
       </c>
       <c r="BQ15" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS15" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT15" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU15" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV15" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX15" s="10">
         <v>1</v>
       </c>
       <c r="BY15" s="10">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="CA15" s="10">
+        <f t="shared" si="32"/>
+        <v>0.35722411839200002</v>
+      </c>
+      <c r="CB15" s="10">
+        <f t="shared" si="33"/>
+        <v>2.8583416262839882E-2</v>
+      </c>
+      <c r="CC15" s="10">
+        <f t="shared" si="34"/>
+        <v>0.41383317371333478</v>
+      </c>
+      <c r="CD15" s="10">
+        <f t="shared" si="35"/>
+        <v>1.5871428571428571E-2</v>
+      </c>
+      <c r="CE15" s="10">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="CF15" s="10">
+        <f t="shared" si="37"/>
+        <v>0.1844878630603968</v>
+      </c>
+      <c r="CG15" s="10">
         <f t="shared" si="38"/>
-        <v>1</v>
-      </c>
-      <c r="CA15" s="10">
-        <f t="shared" si="30"/>
-        <v>0.35722411839200002</v>
-      </c>
-      <c r="CB15" s="10">
-        <f t="shared" si="31"/>
-        <v>2.8583416262839882E-2</v>
-      </c>
-      <c r="CC15" s="10">
-        <f t="shared" si="32"/>
-        <v>0.41383317371333478</v>
-      </c>
-      <c r="CD15" s="10">
-        <f t="shared" si="33"/>
-        <v>1.5871428571428571E-2</v>
-      </c>
-      <c r="CE15" s="10">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="CF15" s="10">
-        <f t="shared" si="35"/>
-        <v>0.1844878630603968</v>
-      </c>
-      <c r="CG15" s="10">
-        <f t="shared" si="36"/>
         <v>1</v>
       </c>
     </row>
@@ -4836,30 +4840,30 @@
         <v>3.542547876</v>
       </c>
       <c r="O16" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="P16" s="26">
         <v>1.01</v>
       </c>
       <c r="Q16" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125077268194</v>
       </c>
       <c r="S16" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T16" s="16">
-        <v>-5.0171330000000003</v>
+        <v>-5.0000840000000002</v>
       </c>
       <c r="U16" s="16">
-        <v>65.195735999999997</v>
+        <v>62.617055000000001</v>
       </c>
       <c r="V16" s="16">
-        <v>49.284007000000003</v>
+        <v>37.705083000000002</v>
       </c>
       <c r="W16" s="16">
-        <v>40.025033000000001</v>
+        <v>30.684851999999999</v>
       </c>
       <c r="X16" s="26">
         <v>420</v>
@@ -4867,194 +4871,196 @@
       <c r="Y16" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z16" s="17"/>
+      <c r="Z16" s="17">
+        <v>-8.7269439999999996</v>
+      </c>
       <c r="AA16" s="17"/>
       <c r="AB16" s="16">
-        <v>21.347408999999999</v>
+        <v>21.357776999999999</v>
       </c>
       <c r="AC16" s="16">
-        <v>7.9738689999999997</v>
+        <v>7.5483099999999999</v>
       </c>
       <c r="AD16" s="16"/>
       <c r="AE16" s="17">
-        <v>0</v>
+        <v>-126.782873</v>
       </c>
       <c r="AF16" s="17">
-        <v>0</v>
+        <v>-126.782873</v>
       </c>
       <c r="AG16" s="17"/>
       <c r="AH16" s="17"/>
       <c r="AI16" s="17"/>
       <c r="AJ16" s="17"/>
       <c r="AK16" s="16">
-        <v>13.408868</v>
+        <v>8.6017200000000003</v>
       </c>
       <c r="AL16" s="16">
         <v>0</v>
       </c>
       <c r="AM16" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN16" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AP16" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>TX_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="AQ16" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR16" s="12">
-        <f t="shared" si="4"/>
-        <v>1406.5825060397012</v>
+        <f t="shared" si="5"/>
+        <v>347.7170137749539</v>
       </c>
       <c r="AS16" s="12">
-        <f t="shared" si="5"/>
-        <v>1406.5825060397012</v>
+        <f t="shared" si="6"/>
+        <v>347.7170137749539</v>
       </c>
       <c r="AT16" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU16" s="12">
-        <f t="shared" si="7"/>
-        <v>1446.6062929311004</v>
+        <f t="shared" si="8"/>
+        <v>377.55290888226364</v>
       </c>
       <c r="AV16" s="12">
-        <f t="shared" si="8"/>
-        <v>1446.6062929311004</v>
+        <f t="shared" si="9"/>
+        <v>377.55290888226364</v>
       </c>
       <c r="AW16" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX16" s="5">
-        <f t="shared" si="10"/>
-        <v>381.46444844673022</v>
+        <f t="shared" si="11"/>
+        <v>361.1059964560414</v>
       </c>
       <c r="AY16" s="1">
-        <f t="shared" si="11"/>
-        <v>42.176075973266656</v>
+        <f t="shared" si="12"/>
+        <v>42.196560030872469</v>
       </c>
       <c r="AZ16" s="1">
-        <f t="shared" si="12"/>
-        <v>758.03379725995796</v>
+        <f t="shared" si="13"/>
+        <v>554.9045367088487</v>
       </c>
       <c r="BA16" s="1">
-        <f t="shared" si="13"/>
-        <v>-18.608047988472212</v>
+        <f t="shared" si="14"/>
+        <v>-11.936967277431711</v>
       </c>
       <c r="BB16" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-852.25723627568527</v>
       </c>
       <c r="BC16" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>214.57390798665784</v>
       </c>
       <c r="BD16" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>117.95601601844012</v>
       </c>
       <c r="BE16" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="BF16" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BG16" s="1">
         <v>0</v>
       </c>
       <c r="BH16" s="1">
-        <f t="shared" si="19"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="20"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BI16" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BJ16" s="1">
         <v>0</v>
       </c>
       <c r="BK16" s="1">
-        <f t="shared" si="21"/>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="22"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BL16" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM16" s="1">
         <v>0</v>
       </c>
       <c r="BN16" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO16" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP16" s="1">
         <v>0</v>
       </c>
       <c r="BQ16" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS16" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT16" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU16" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV16" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX16" s="10">
         <v>1</v>
       </c>
       <c r="BY16" s="10">
+        <f t="shared" si="31"/>
+        <v>0.67299662739933241</v>
+      </c>
+      <c r="CA16" s="10">
+        <f t="shared" si="32"/>
+        <v>0.38885408131600002</v>
+      </c>
+      <c r="CB16" s="10">
+        <f t="shared" si="33"/>
+        <v>3.1114299132937305E-2</v>
+      </c>
+      <c r="CC16" s="10">
+        <f t="shared" si="34"/>
+        <v>3.6333708066740841E-2</v>
+      </c>
+      <c r="CD16" s="10">
+        <f t="shared" si="35"/>
+        <v>1.5871428571428571E-2</v>
+      </c>
+      <c r="CE16" s="10">
+        <f t="shared" si="36"/>
+        <v>0.32700337260066764</v>
+      </c>
+      <c r="CF16" s="10">
+        <f t="shared" si="37"/>
+        <v>0.20082311031222566</v>
+      </c>
+      <c r="CG16" s="10">
         <f t="shared" si="38"/>
-        <v>0.67299662739933241</v>
-      </c>
-      <c r="CA16" s="10">
-        <f t="shared" si="30"/>
-        <v>0.38885408131600002</v>
-      </c>
-      <c r="CB16" s="10">
-        <f t="shared" si="31"/>
-        <v>3.1114299132937305E-2</v>
-      </c>
-      <c r="CC16" s="10">
-        <f t="shared" si="32"/>
-        <v>3.6333708066740841E-2</v>
-      </c>
-      <c r="CD16" s="10">
-        <f t="shared" si="33"/>
-        <v>1.5871428571428571E-2</v>
-      </c>
-      <c r="CE16" s="10">
-        <f t="shared" si="34"/>
-        <v>0.32700337260066764</v>
-      </c>
-      <c r="CF16" s="10">
-        <f t="shared" si="35"/>
-        <v>0.20082311031222566</v>
-      </c>
-      <c r="CG16" s="10">
-        <f t="shared" si="36"/>
         <v>0.67299662739933241</v>
       </c>
     </row>
@@ -5100,30 +5106,30 @@
         <v>2.9463016839999998</v>
       </c>
       <c r="O17" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="P17" s="26">
         <v>1.01</v>
       </c>
       <c r="Q17" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11490329922799999</v>
       </c>
       <c r="S17" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T17" s="16">
-        <v>-4.0829269999999998</v>
+        <v>6.3412249999999997</v>
       </c>
       <c r="U17" s="16">
-        <v>67.847282000000007</v>
+        <v>64.329804999999993</v>
       </c>
       <c r="V17" s="16">
-        <v>43.850637999999996</v>
+        <v>37.865810000000003</v>
       </c>
       <c r="W17" s="16">
-        <v>41.097996000000002</v>
+        <v>42.137908000000003</v>
       </c>
       <c r="X17" s="26">
         <v>420</v>
@@ -5131,194 +5137,196 @@
       <c r="Y17" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z17" s="17"/>
+      <c r="Z17" s="17">
+        <v>-3.8794550000000001</v>
+      </c>
       <c r="AA17" s="17"/>
       <c r="AB17" s="16">
-        <v>20.094425000000001</v>
+        <v>20.232006999999999</v>
       </c>
       <c r="AC17" s="16">
-        <v>5.1886080000000003</v>
+        <v>8.1320359999999994</v>
       </c>
       <c r="AD17" s="16"/>
       <c r="AE17" s="17">
-        <v>0</v>
+        <v>-112.989964</v>
       </c>
       <c r="AF17" s="17">
-        <v>0</v>
+        <v>-112.989964</v>
       </c>
       <c r="AG17" s="17"/>
       <c r="AH17" s="17"/>
       <c r="AI17" s="17"/>
       <c r="AJ17" s="17"/>
       <c r="AK17" s="16">
-        <v>8.921977</v>
+        <v>12.309823</v>
       </c>
       <c r="AL17" s="16">
         <v>0</v>
       </c>
       <c r="AM17" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN17" s="16">
         <v>0</v>
       </c>
       <c r="AP17" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>NW_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="AQ17" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR17" s="12">
-        <f t="shared" si="4"/>
-        <v>1319.2559222353186</v>
+        <f t="shared" si="5"/>
+        <v>575.79551877727795</v>
       </c>
       <c r="AS17" s="12">
-        <f t="shared" si="5"/>
-        <v>1319.2559222353186</v>
+        <f t="shared" si="6"/>
+        <v>575.79551877727795</v>
       </c>
       <c r="AT17" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU17" s="12">
-        <f t="shared" si="7"/>
-        <v>1356.1517844851373</v>
+        <f t="shared" si="8"/>
+        <v>603.29968970858738</v>
       </c>
       <c r="AV17" s="12">
-        <f t="shared" si="8"/>
-        <v>1356.1517844851373</v>
+        <f t="shared" si="9"/>
+        <v>603.29968970858738</v>
       </c>
       <c r="AW17" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX17" s="5">
-        <f t="shared" si="10"/>
-        <v>248.21946387592484</v>
+        <f t="shared" si="11"/>
+        <v>389.03104958781239</v>
       </c>
       <c r="AY17" s="1">
-        <f t="shared" si="11"/>
-        <v>31.146358742934805</v>
+        <f t="shared" si="12"/>
+        <v>31.359610842886429</v>
       </c>
       <c r="AZ17" s="1">
-        <f t="shared" si="12"/>
-        <v>833.36462280332682</v>
+        <f t="shared" si="13"/>
+        <v>703.72797120080975</v>
       </c>
       <c r="BA17" s="1">
-        <f t="shared" si="13"/>
-        <v>-12.381401329892206</v>
+        <f t="shared" si="14"/>
+        <v>-17.082857180974312</v>
       </c>
       <c r="BB17" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-759.53882513479027</v>
       </c>
       <c r="BC17" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>194.26040330394619</v>
       </c>
       <c r="BD17" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>106.85542108065717</v>
       </c>
       <c r="BE17" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="BF17" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BG17" s="1">
         <v>0</v>
       </c>
       <c r="BH17" s="1">
-        <f t="shared" si="19"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="20"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BI17" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BJ17" s="1">
         <v>0</v>
       </c>
       <c r="BK17" s="1">
-        <f t="shared" si="21"/>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="22"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BL17" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM17" s="1">
         <v>0</v>
       </c>
       <c r="BN17" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO17" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP17" s="1">
         <v>0</v>
       </c>
       <c r="BQ17" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS17" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU17" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV17" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX17" s="10">
         <v>1</v>
       </c>
       <c r="BY17" s="10">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="CA17" s="10">
+        <f t="shared" si="32"/>
+        <v>0.35722411839200002</v>
+      </c>
+      <c r="CB17" s="10">
+        <f t="shared" si="33"/>
+        <v>2.8583416262839882E-2</v>
+      </c>
+      <c r="CC17" s="10">
+        <f t="shared" si="34"/>
+        <v>0.41383317371333478</v>
+      </c>
+      <c r="CD17" s="10">
+        <f t="shared" si="35"/>
+        <v>1.5871428571428571E-2</v>
+      </c>
+      <c r="CE17" s="10">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="CF17" s="10">
+        <f t="shared" si="37"/>
+        <v>0.1844878630603968</v>
+      </c>
+      <c r="CG17" s="10">
         <f t="shared" si="38"/>
-        <v>1</v>
-      </c>
-      <c r="CA17" s="10">
-        <f t="shared" si="30"/>
-        <v>0.35722411839200002</v>
-      </c>
-      <c r="CB17" s="10">
-        <f t="shared" si="31"/>
-        <v>2.8583416262839882E-2</v>
-      </c>
-      <c r="CC17" s="10">
-        <f t="shared" si="32"/>
-        <v>0.41383317371333478</v>
-      </c>
-      <c r="CD17" s="10">
-        <f t="shared" si="33"/>
-        <v>1.5871428571428571E-2</v>
-      </c>
-      <c r="CE17" s="10">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="CF17" s="10">
-        <f t="shared" si="35"/>
-        <v>0.1844878630603968</v>
-      </c>
-      <c r="CG17" s="10">
-        <f t="shared" si="36"/>
         <v>1</v>
       </c>
     </row>
@@ -5364,30 +5372,30 @@
         <v>3.542547876</v>
       </c>
       <c r="O18" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="P18" s="26">
         <v>1.01</v>
       </c>
       <c r="Q18" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125077268194</v>
       </c>
       <c r="S18" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T18" s="16">
-        <v>-4.0829269999999998</v>
+        <v>6.3412249999999997</v>
       </c>
       <c r="U18" s="16">
-        <v>67.847282000000007</v>
+        <v>64.329804999999993</v>
       </c>
       <c r="V18" s="16">
-        <v>43.850637999999996</v>
+        <v>37.865810000000003</v>
       </c>
       <c r="W18" s="16">
-        <v>41.097996000000002</v>
+        <v>42.137908000000003</v>
       </c>
       <c r="X18" s="26">
         <v>420</v>
@@ -5395,194 +5403,196 @@
       <c r="Y18" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z18" s="17"/>
+      <c r="Z18" s="17">
+        <v>-3.8794550000000001</v>
+      </c>
       <c r="AA18" s="17"/>
       <c r="AB18" s="16">
-        <v>20.094425000000001</v>
+        <v>20.232006999999999</v>
       </c>
       <c r="AC18" s="16">
-        <v>5.1886080000000003</v>
+        <v>8.1320359999999994</v>
       </c>
       <c r="AD18" s="16"/>
       <c r="AE18" s="17">
-        <v>0</v>
+        <v>-112.989964</v>
       </c>
       <c r="AF18" s="17">
-        <v>0</v>
+        <v>-112.989964</v>
       </c>
       <c r="AG18" s="17"/>
       <c r="AH18" s="17"/>
       <c r="AI18" s="17"/>
       <c r="AJ18" s="17"/>
       <c r="AK18" s="16">
-        <v>8.921977</v>
+        <v>12.309823</v>
       </c>
       <c r="AL18" s="16">
         <v>0</v>
       </c>
       <c r="AM18" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN18" s="16">
         <v>0</v>
       </c>
       <c r="AP18" s="1" t="str">
-        <f>B18</f>
+        <f t="shared" si="3"/>
         <v>NW_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="AQ18" s="1" t="str">
-        <f>C18</f>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR18" s="12">
-        <f>SUM(AX18:BE18)+BG18+BH18</f>
-        <v>1284.6323690856429</v>
+        <f t="shared" si="5"/>
+        <v>552.5715704043057</v>
       </c>
       <c r="AS18" s="12">
-        <f>SUM(AX18:BE18)+BJ18+BK18</f>
-        <v>1284.6323690856429</v>
+        <f t="shared" si="6"/>
+        <v>552.5715704043057</v>
       </c>
       <c r="AT18" s="5">
-        <f>AR18-AS18</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU18" s="12">
-        <f>SUM(AX18:BE18)+BM18+BN18</f>
-        <v>1324.6561559770421</v>
+        <f t="shared" si="8"/>
+        <v>582.40746551161544</v>
       </c>
       <c r="AV18" s="12">
-        <f>SUM(AX18:BE18)+BP18+BQ18</f>
-        <v>1324.6561559770421</v>
+        <f t="shared" si="9"/>
+        <v>582.40746551161544</v>
       </c>
       <c r="AW18" s="5">
-        <f>AU18-AV18</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX18" s="5">
-        <f>E18/G18*AC18</f>
-        <v>248.21946396740304</v>
+        <f t="shared" si="11"/>
+        <v>389.03104973118496</v>
       </c>
       <c r="AY18" s="1">
-        <f>F18/G18*AB18</f>
-        <v>39.700555483764276</v>
+        <f t="shared" si="12"/>
+        <v>39.972376241241399</v>
       </c>
       <c r="AZ18" s="1">
-        <f>1/G18*(S18+T18)</f>
-        <v>765.57751862215241</v>
+        <f t="shared" si="13"/>
+        <v>646.48570293829698</v>
       </c>
       <c r="BA18" s="1">
-        <f>H18/G18*AK18*-1</f>
-        <v>-12.381401335895418</v>
+        <f t="shared" si="14"/>
+        <v>-17.082857189257062</v>
       </c>
       <c r="BB18" s="1">
-        <f>I18/G18*AE18</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-759.53882544946885</v>
       </c>
       <c r="BC18" s="1">
-        <f>L18/G18/(0.9*8760)</f>
+        <f t="shared" si="16"/>
         <v>214.57390798665784</v>
       </c>
       <c r="BD18" s="1">
-        <f>M18/G18/(0.9*8760)</f>
+        <f t="shared" si="17"/>
         <v>117.95601601844012</v>
       </c>
       <c r="BE18" s="1">
-        <f>O18</f>
+        <f t="shared" si="18"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="BF18" s="1">
-        <f>CG18-BY18-CA18-CD18</f>
+        <f t="shared" si="19"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BG18" s="1">
         <v>0</v>
       </c>
       <c r="BH18" s="1">
-        <f>BF18*S18</f>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="20"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BI18" s="1">
-        <f>BY18-CG18-CA18-CD18</f>
+        <f t="shared" si="21"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BJ18" s="1">
         <v>0</v>
       </c>
       <c r="BK18" s="1">
-        <f>BI18*S18</f>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="22"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BL18" s="1">
-        <f>BY18-CG18</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM18" s="1">
         <v>0</v>
       </c>
       <c r="BN18" s="1">
-        <f>BL18*S18</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO18" s="1">
-        <f>BY18-CG18</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP18" s="1">
         <v>0</v>
       </c>
       <c r="BQ18" s="1">
-        <f>BO18*S18</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS18" s="9">
-        <f>$CJ$2</f>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT18" s="10">
-        <f>$CJ$3</f>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU18" s="9">
-        <f>$CJ$4</f>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV18" s="9">
-        <f>$CJ$5</f>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX18" s="10">
         <v>1</v>
       </c>
       <c r="BY18" s="10">
-        <f>BX18-CE18</f>
+        <f t="shared" si="31"/>
         <v>0.67299662739933241</v>
       </c>
       <c r="CA18" s="10">
-        <f>BS18*G18</f>
+        <f t="shared" si="32"/>
         <v>0.38885408131600002</v>
       </c>
       <c r="CB18" s="10">
-        <f>BU18*H18</f>
+        <f t="shared" si="33"/>
         <v>3.1114299132937305E-2</v>
       </c>
       <c r="CC18" s="10">
-        <f>(BX18-CA18-CB18-CF18-CD18)*(1-D18)</f>
+        <f t="shared" si="34"/>
         <v>3.6333708066740841E-2</v>
       </c>
       <c r="CD18" s="10">
-        <f>BV18*P18</f>
+        <f t="shared" si="35"/>
         <v>1.5871428571428571E-2</v>
       </c>
       <c r="CE18" s="10">
-        <f>(BX18-CA18-CB18-CF18-CD18)*(D18)</f>
+        <f t="shared" si="36"/>
         <v>0.32700337260066764</v>
       </c>
       <c r="CF18" s="10">
-        <f>BT18*I18</f>
+        <f t="shared" si="37"/>
         <v>0.20082311031222566</v>
       </c>
       <c r="CG18" s="10">
-        <f>SUM(CA18:CF18)-CE18</f>
+        <f t="shared" si="38"/>
         <v>0.67299662739933241</v>
       </c>
     </row>
@@ -5615,7 +5625,7 @@
         <v>0.41383317400000003</v>
       </c>
       <c r="K19" s="27">
-        <f>BY19-SUM(CA19+CD19+CB19+CF19)</f>
+        <f t="shared" si="0"/>
         <v>0.41383317371333472</v>
       </c>
       <c r="L19" s="13">
@@ -5628,30 +5638,30 @@
         <v>2.9463016839999998</v>
       </c>
       <c r="O19" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="P19" s="26">
         <v>1.01</v>
       </c>
       <c r="Q19" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11490329922799999</v>
       </c>
       <c r="S19" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T19" s="16">
-        <v>-5.5622189999999998</v>
+        <v>-4.302149</v>
       </c>
       <c r="U19" s="16">
-        <v>65.564085000000006</v>
+        <v>61.152786999999996</v>
       </c>
       <c r="V19" s="16">
-        <v>44.081525999999997</v>
+        <v>40.832245999999998</v>
       </c>
       <c r="W19" s="16">
-        <v>42.073737999999999</v>
+        <v>41.356794999999998</v>
       </c>
       <c r="X19" s="26">
         <v>420</v>
@@ -5659,194 +5669,196 @@
       <c r="Y19" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z19" s="17"/>
+      <c r="Z19" s="17">
+        <v>-1.8192109999999999</v>
+      </c>
       <c r="AA19" s="17"/>
       <c r="AB19" s="16">
-        <v>21.099150000000002</v>
+        <v>21.021514</v>
       </c>
       <c r="AC19" s="16">
-        <v>7.1014869999999997</v>
+        <v>9.0440679999999993</v>
       </c>
       <c r="AD19" s="16"/>
       <c r="AE19" s="17">
-        <v>0</v>
+        <v>-126.225199</v>
       </c>
       <c r="AF19" s="17">
-        <v>0</v>
+        <v>-126.225199</v>
       </c>
       <c r="AG19" s="17"/>
       <c r="AH19" s="17"/>
       <c r="AI19" s="17"/>
       <c r="AJ19" s="17"/>
       <c r="AK19" s="16">
-        <v>12.274521999999999</v>
+        <v>10.321106</v>
       </c>
       <c r="AL19" s="16">
         <v>0</v>
       </c>
       <c r="AM19" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN19" s="16">
         <v>0</v>
       </c>
       <c r="AP19" s="1" t="str">
-        <f t="shared" ref="AP19" si="39">B19</f>
+        <f t="shared" si="3"/>
         <v>SW_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="AQ19" s="1" t="str">
-        <f t="shared" ref="AQ19" si="40">C19</f>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR19" s="12">
-        <f t="shared" ref="AR19" si="41">SUM(AX19:BE19)+BG19+BH19</f>
-        <v>1394.6686273566809</v>
+        <f t="shared" si="5"/>
+        <v>440.88518520160773</v>
       </c>
       <c r="AS19" s="12">
-        <f t="shared" ref="AS19" si="42">SUM(AX19:BE19)+BJ19+BK19</f>
-        <v>1394.6686273566809</v>
+        <f t="shared" si="6"/>
+        <v>440.88518520160773</v>
       </c>
       <c r="AT19" s="5">
-        <f t="shared" ref="AT19" si="43">AR19-AS19</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU19" s="12">
-        <f t="shared" ref="AU19" si="44">SUM(AX19:BE19)+BM19+BN19</f>
-        <v>1431.5644896064996</v>
+        <f t="shared" si="8"/>
+        <v>468.38935613291721</v>
       </c>
       <c r="AV19" s="12">
-        <f t="shared" ref="AV19" si="45">SUM(AX19:BE19)+BP19+BQ19</f>
-        <v>1431.5644896064996</v>
+        <f t="shared" si="9"/>
+        <v>468.38935613291721</v>
       </c>
       <c r="AW19" s="5">
-        <f t="shared" ref="AW19" si="46">AU19-AV19</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX19" s="5">
-        <f t="shared" ref="AX19" si="47">E19/G19*AC19</f>
-        <v>339.7302890990897</v>
+        <f t="shared" si="11"/>
+        <v>432.66203772137101</v>
       </c>
       <c r="AY19" s="1">
-        <f t="shared" ref="AY19" si="48">F19/G19*AB19</f>
-        <v>32.703682492581542</v>
+        <f t="shared" si="12"/>
+        <v>32.583346692608842</v>
       </c>
       <c r="AZ19" s="1">
-        <f t="shared" ref="AZ19" si="49">1/G19*(S19+T19)</f>
-        <v>820.36164612608343</v>
+        <f t="shared" si="13"/>
+        <v>610.17271376064343</v>
       </c>
       <c r="BA19" s="1">
-        <f t="shared" ref="BA19" si="50">H19/G19*AK19*-1</f>
-        <v>-17.033868504098489</v>
+        <f t="shared" si="14"/>
+        <v>-14.323031269230848</v>
       </c>
       <c r="BB19" s="1">
-        <f t="shared" ref="BB19" si="51">I19/G19*AE19</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-848.50845116531866</v>
       </c>
       <c r="BC19" s="1">
-        <f t="shared" ref="BC19" si="52">L19/G19/(0.9*8760)</f>
+        <f t="shared" si="16"/>
         <v>194.26040330394619</v>
       </c>
       <c r="BD19" s="1">
-        <f t="shared" ref="BD19" si="53">M19/G19/(0.9*8760)</f>
+        <f t="shared" si="17"/>
         <v>106.85542108065717</v>
       </c>
       <c r="BE19" s="1">
-        <f t="shared" ref="BE19" si="54">O19</f>
+        <f t="shared" si="18"/>
         <v>-45.313083991760003</v>
       </c>
       <c r="BF19" s="1">
-        <f t="shared" ref="BF19" si="55">CG19-BY19-CA19-CD19</f>
+        <f t="shared" si="19"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BG19" s="1">
         <v>0</v>
       </c>
       <c r="BH19" s="1">
-        <f t="shared" ref="BH19" si="56">BF19*S19</f>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="20"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BI19" s="1">
-        <f t="shared" ref="BI19" si="57">BY19-CG19-CA19-CD19</f>
+        <f t="shared" si="21"/>
         <v>-0.37309554696342861</v>
       </c>
       <c r="BJ19" s="1">
         <v>0</v>
       </c>
       <c r="BK19" s="1">
-        <f t="shared" ref="BK19" si="58">BI19*S19</f>
-        <v>-36.895862249818791</v>
+        <f t="shared" si="22"/>
+        <v>-27.504170931309481</v>
       </c>
       <c r="BL19" s="1">
-        <f t="shared" ref="BL19" si="59">BY19-CG19</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM19" s="1">
         <v>0</v>
       </c>
       <c r="BN19" s="1">
-        <f t="shared" ref="BN19" si="60">BL19*S19</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO19" s="1">
-        <f t="shared" ref="BO19" si="61">BY19-CG19</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP19" s="1">
         <v>0</v>
       </c>
       <c r="BQ19" s="1">
-        <f t="shared" ref="BQ19" si="62">BO19*S19</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS19" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT19" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU19" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV19" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX19" s="10">
         <v>1</v>
       </c>
       <c r="BY19" s="10">
-        <f t="shared" ref="BY19" si="63">BX19-CE19</f>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="CA19" s="10">
-        <f t="shared" ref="CA19" si="64">BS19*G19</f>
+        <f t="shared" si="32"/>
         <v>0.35722411839200002</v>
       </c>
       <c r="CB19" s="10">
-        <f t="shared" ref="CB19" si="65">BU19*H19</f>
+        <f t="shared" si="33"/>
         <v>2.8583416262839882E-2</v>
       </c>
       <c r="CC19" s="10">
-        <f t="shared" ref="CC19" si="66">(BX19-CA19-CB19-CF19-CD19)*(1-D19)</f>
+        <f t="shared" si="34"/>
         <v>0.41383317371333478</v>
       </c>
       <c r="CD19" s="10">
-        <f t="shared" ref="CD19" si="67">BV19*P19</f>
+        <f t="shared" si="35"/>
         <v>1.5871428571428571E-2</v>
       </c>
       <c r="CE19" s="10">
-        <f t="shared" ref="CE19" si="68">(BX19-CA19-CB19-CF19-CD19)*(D19)</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="CF19" s="10">
-        <f t="shared" ref="CF19" si="69">BT19*I19</f>
+        <f t="shared" si="37"/>
         <v>0.1844878630603968</v>
       </c>
       <c r="CG19" s="10">
-        <f t="shared" ref="CG19" si="70">SUM(CA19:CF19)-CE19</f>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
     </row>
@@ -5892,30 +5904,30 @@
         <v>3.542547876</v>
       </c>
       <c r="O20" s="13">
-        <f t="shared" si="37"/>
+        <f t="shared" si="1"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="P20" s="26">
         <v>1.01</v>
       </c>
       <c r="Q20" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125077268194</v>
       </c>
       <c r="S20" s="16">
-        <v>98.891188999999997</v>
+        <v>73.71884</v>
       </c>
       <c r="T20" s="16">
-        <v>-5.5622189999999998</v>
+        <v>-4.302149</v>
       </c>
       <c r="U20" s="16">
-        <v>65.564085000000006</v>
+        <v>61.152786999999996</v>
       </c>
       <c r="V20" s="16">
-        <v>44.081525999999997</v>
+        <v>40.832245999999998</v>
       </c>
       <c r="W20" s="16">
-        <v>42.073737999999999</v>
+        <v>41.356794999999998</v>
       </c>
       <c r="X20" s="26">
         <v>420</v>
@@ -5923,194 +5935,196 @@
       <c r="Y20" s="11">
         <v>21.986353300000001</v>
       </c>
-      <c r="Z20" s="17"/>
+      <c r="Z20" s="17">
+        <v>-1.8192109999999999</v>
+      </c>
       <c r="AA20" s="17"/>
       <c r="AB20" s="16">
-        <v>21.099150000000002</v>
+        <v>21.021514</v>
       </c>
       <c r="AC20" s="16">
-        <v>7.1014869999999997</v>
+        <v>9.0440679999999993</v>
       </c>
       <c r="AD20" s="16"/>
       <c r="AE20" s="17">
-        <v>0</v>
+        <v>-126.225199</v>
       </c>
       <c r="AF20" s="17">
-        <v>0</v>
+        <v>-126.225199</v>
       </c>
       <c r="AG20" s="17"/>
       <c r="AH20" s="17"/>
       <c r="AI20" s="17"/>
       <c r="AJ20" s="17"/>
       <c r="AK20" s="16">
-        <v>12.274521999999999</v>
+        <v>10.321106</v>
       </c>
       <c r="AL20" s="16">
         <v>0</v>
       </c>
       <c r="AM20" s="16">
-        <v>828.55554299999994</v>
+        <v>822.26752199999999</v>
       </c>
       <c r="AN20" s="16">
         <v>0</v>
       </c>
       <c r="AP20" s="1" t="str">
-        <f>B20</f>
+        <f t="shared" si="3"/>
         <v>SW_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="AQ20" s="1" t="str">
-        <f>C20</f>
+        <f t="shared" si="4"/>
         <v>CO2Captured</v>
       </c>
       <c r="AR20" s="12">
-        <f>SUM(AX20:BE20)+BG20+BH20</f>
-        <v>1361.5304669203708</v>
+        <f t="shared" si="5"/>
+        <v>425.60725218664447</v>
       </c>
       <c r="AS20" s="12">
-        <f>SUM(AX20:BE20)+BJ20+BK20</f>
-        <v>1361.5304669203708</v>
+        <f t="shared" si="6"/>
+        <v>425.60725218664447</v>
       </c>
       <c r="AT20" s="5">
-        <f>AR20-AS20</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU20" s="12">
-        <f>SUM(AX20:BE20)+BM20+BN20</f>
-        <v>1401.55425381177</v>
+        <f t="shared" si="8"/>
+        <v>455.44314729395421</v>
       </c>
       <c r="AV20" s="12">
-        <f>SUM(AX20:BE20)+BP20+BQ20</f>
-        <v>1401.55425381177</v>
+        <f t="shared" si="9"/>
+        <v>455.44314729395421</v>
       </c>
       <c r="AW20" s="5">
-        <f>AU20-AV20</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX20" s="5">
-        <f>E20/G20*AC20</f>
-        <v>339.73028922429313</v>
+        <f t="shared" si="11"/>
+        <v>432.66203788082328</v>
       </c>
       <c r="AY20" s="1">
-        <f>F20/G20*AB20</f>
-        <v>41.685590666827494</v>
+        <f t="shared" si="12"/>
+        <v>41.532205221583972</v>
       </c>
       <c r="AZ20" s="1">
-        <f>1/G20*(S20+T20)</f>
-        <v>753.632223193389</v>
+        <f t="shared" si="13"/>
+        <v>560.54036774496194</v>
       </c>
       <c r="BA20" s="1">
-        <f>H20/G20*AK20*-1</f>
-        <v>-17.033868512357486</v>
+        <f t="shared" si="14"/>
+        <v>-14.323031276175474</v>
       </c>
       <c r="BB20" s="1">
-        <f>I20/G20*AE20</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>-848.50845151685746</v>
       </c>
       <c r="BC20" s="1">
-        <f>L20/G20/(0.9*8760)</f>
+        <f t="shared" si="16"/>
         <v>214.57390798665784</v>
       </c>
       <c r="BD20" s="1">
-        <f>M20/G20/(0.9*8760)</f>
+        <f t="shared" si="17"/>
         <v>117.95601601844012</v>
       </c>
       <c r="BE20" s="1">
-        <f>O20</f>
+        <f t="shared" si="18"/>
         <v>-48.989904765479999</v>
       </c>
       <c r="BF20" s="1">
-        <f>CG20-BY20-CA20-CD20</f>
+        <f t="shared" si="19"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BG20" s="1">
         <v>0</v>
       </c>
       <c r="BH20" s="1">
-        <f>BF20*S20</f>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="20"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BI20" s="1">
-        <f>BY20-CG20-CA20-CD20</f>
+        <f t="shared" si="21"/>
         <v>-0.40472550988742861</v>
       </c>
       <c r="BJ20" s="1">
         <v>0</v>
       </c>
       <c r="BK20" s="1">
-        <f>BI20*S20</f>
-        <v>-40.02378689139907</v>
+        <f t="shared" si="22"/>
+        <v>-29.835895107309767</v>
       </c>
       <c r="BL20" s="1">
-        <f>BY20-CG20</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BM20" s="1">
         <v>0</v>
       </c>
       <c r="BN20" s="1">
-        <f>BL20*S20</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BO20" s="1">
-        <f>BY20-CG20</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BP20" s="1">
         <v>0</v>
       </c>
       <c r="BQ20" s="1">
-        <f>BO20*S20</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BS20" s="9">
-        <f>$CJ$2</f>
+        <f t="shared" si="27"/>
         <v>3.14</v>
       </c>
       <c r="BT20" s="10">
-        <f>$CJ$3</f>
+        <f t="shared" si="28"/>
         <v>0.24123847100000001</v>
       </c>
       <c r="BU20" s="9">
-        <f>$CJ$4</f>
+        <f t="shared" si="29"/>
         <v>0.18104824</v>
       </c>
       <c r="BV20" s="9">
-        <f>$CJ$5</f>
+        <f t="shared" si="30"/>
         <v>1.5714285714285715E-2</v>
       </c>
       <c r="BX20" s="10">
         <v>1</v>
       </c>
       <c r="BY20" s="10">
-        <f>BX20-CE20</f>
+        <f t="shared" si="31"/>
         <v>0.67299662739933241</v>
       </c>
       <c r="CA20" s="10">
-        <f>BS20*G20</f>
+        <f t="shared" si="32"/>
         <v>0.38885408131600002</v>
       </c>
       <c r="CB20" s="10">
-        <f>BU20*H20</f>
+        <f t="shared" si="33"/>
         <v>3.1114299132937305E-2</v>
       </c>
       <c r="CC20" s="10">
-        <f>(BX20-CA20-CB20-CF20-CD20)*(1-D20)</f>
+        <f t="shared" si="34"/>
         <v>3.6333708066740841E-2</v>
       </c>
       <c r="CD20" s="10">
-        <f>BV20*P20</f>
+        <f t="shared" si="35"/>
         <v>1.5871428571428571E-2</v>
       </c>
       <c r="CE20" s="10">
-        <f>(BX20-CA20-CB20-CF20-CD20)*(D20)</f>
+        <f t="shared" si="36"/>
         <v>0.32700337260066764</v>
       </c>
       <c r="CF20" s="10">
-        <f>BT20*I20</f>
+        <f t="shared" si="37"/>
         <v>0.20082311031222566</v>
       </c>
       <c r="CG20" s="10">
-        <f>SUM(CA20:CF20)-CE20</f>
+        <f t="shared" si="38"/>
         <v>0.67299662739933241</v>
       </c>
     </row>
@@ -9523,7 +9537,7 @@
         <v>14</v>
       </c>
       <c r="U1" s="21" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -9567,19 +9581,19 @@
         <v>55</v>
       </c>
       <c r="N2" s="23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O2" s="23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R2">
         <v>45.6</v>
       </c>
       <c r="S2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>53</v>
@@ -9621,10 +9635,10 @@
         <v>55</v>
       </c>
       <c r="AH2" s="23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AI2" s="23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
@@ -9634,23 +9648,23 @@
       </c>
       <c r="B3" s="25">
         <f>lc_detailed!AX3/$R$2</f>
-        <v>7.4790582687141676</v>
+        <v>7.6246838779146486</v>
       </c>
       <c r="C3" s="25">
         <f>lc_detailed!AY3/$R$2</f>
-        <v>0.74873960070734991</v>
+        <v>0.72286564786234198</v>
       </c>
       <c r="D3" s="25">
         <f>lc_detailed!AZ3/$R$2</f>
-        <v>17.888005451470899</v>
+        <v>13.03615561171002</v>
       </c>
       <c r="E3" s="25">
         <f>lc_detailed!BA3/$R$2</f>
-        <v>-0.36969322532493909</v>
+        <v>-0.24235512400049214</v>
       </c>
       <c r="F3" s="25">
         <f>lc_detailed!BB3/$R$2</f>
-        <v>0</v>
+        <v>-18.880719992760021</v>
       </c>
       <c r="G3" s="25">
         <f>lc_detailed!BC3/$R$2</f>
@@ -9678,43 +9692,43 @@
       </c>
       <c r="M3" s="25">
         <f>lc_detailed!AU3</f>
-        <v>1429.8253607507204</v>
+        <v>358.88746933797165</v>
       </c>
       <c r="N3" s="25">
-        <f>M3/$R$2</f>
-        <v>31.355819314708778</v>
+        <f t="shared" ref="N3:N20" si="0">M3/$R$2</f>
+        <v>7.8703392398677989</v>
       </c>
       <c r="O3" s="25">
-        <f>SUM(B3:K3)</f>
-        <v>31.355819314708782</v>
-      </c>
-      <c r="U3" t="str" cm="1">
+        <f t="shared" ref="O3:O20" si="1">SUM(B3:K3)</f>
+        <v>7.8703392398677998</v>
+      </c>
+      <c r="U3" t="str">
         <f t="array" ref="U3:AI65">_xlfn._xlws.SORT(A3:O65, 13, 1)</f>
-        <v>CA_Synthetic_Ethylene_CCS_90</v>
+        <v>NE_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V3" s="25">
-        <v>5.2904756031087681</v>
+        <v>9.6475746507461988</v>
       </c>
       <c r="W3" s="25">
-        <v>0.87613997951393885</v>
+        <v>0.7066773254975931</v>
       </c>
       <c r="X3" s="25">
-        <v>16.655984750796321</v>
+        <v>9.7233651841228586</v>
       </c>
       <c r="Y3" s="25">
-        <v>-0.26046229524938447</v>
+        <v>-0.27269292708438991</v>
       </c>
       <c r="Z3" s="25">
-        <v>0</v>
+        <v>-22.223848279928063</v>
       </c>
       <c r="AA3" s="25">
-        <v>4.705568157602146</v>
+        <v>4.2600965636830308</v>
       </c>
       <c r="AB3" s="25">
-        <v>2.5867547372464941</v>
+        <v>2.3433206377337097</v>
       </c>
       <c r="AC3" s="25">
-        <v>-1.074340016786842</v>
+        <v>-0.99370798227543866</v>
       </c>
       <c r="AD3" s="25">
         <v>0</v>
@@ -9726,13 +9740,13 @@
         <v>0</v>
       </c>
       <c r="AG3" s="25">
-        <v>1312.3735137801536</v>
+        <v>145.49980386579475</v>
       </c>
       <c r="AH3" s="25">
-        <v>28.780120916231439</v>
+        <v>3.1907851724954988</v>
       </c>
       <c r="AI3" s="25">
-        <v>28.780120916231439</v>
+        <v>3.1907851724954996</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.2">
@@ -9742,23 +9756,23 @@
       </c>
       <c r="B4" s="25">
         <f>lc_detailed!AX4/$R$2</f>
-        <v>7.4790582714704827</v>
+        <v>7.624683880724632</v>
       </c>
       <c r="C4" s="25">
         <f>lc_detailed!AY4/$R$2</f>
-        <v>0.95437730959534783</v>
+        <v>0.9213972007811656</v>
       </c>
       <c r="D4" s="25">
         <f>lc_detailed!AZ4/$R$2</f>
-        <v>16.432968777303802</v>
+        <v>11.975775539898962</v>
       </c>
       <c r="E4" s="25">
         <f>lc_detailed!BA4/$R$2</f>
-        <v>-0.36969322550418754</v>
+        <v>-0.24235512411799978</v>
       </c>
       <c r="F4" s="25">
         <f>lc_detailed!BB4/$R$2</f>
-        <v>0</v>
+        <v>-18.880720000582343</v>
       </c>
       <c r="G4" s="25">
         <f>lc_detailed!BC4/$R$2</f>
@@ -9786,33 +9800,33 @@
       </c>
       <c r="M4" s="25">
         <f>lc_detailed!AU4</f>
-        <v>1400.590046898282</v>
+        <v>347.32445548933936</v>
       </c>
       <c r="N4" s="25">
-        <f>M4/$R$2</f>
-        <v>30.714694010927236</v>
+        <f t="shared" si="0"/>
+        <v>7.6167643747662135</v>
       </c>
       <c r="O4" s="25">
-        <f>SUM(B4:K4)</f>
-        <v>30.714694010927246</v>
+        <f t="shared" si="1"/>
+        <v>7.6167643747662144</v>
       </c>
       <c r="U4" t="str">
-        <v>NW_Synthetic_Ethylene_CCS_90</v>
+        <v>NE_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V4" s="25">
-        <v>5.443409297530768</v>
+        <v>9.6475746543016925</v>
       </c>
       <c r="W4" s="25">
-        <v>0.87062621674921659</v>
+        <v>0.90076283399899526</v>
       </c>
       <c r="X4" s="25">
-        <v>16.788980671538429</v>
+        <v>8.932452358341326</v>
       </c>
       <c r="Y4" s="25">
-        <v>-0.27152195912051358</v>
+        <v>-0.27269292721660704</v>
       </c>
       <c r="Z4" s="25">
-        <v>0</v>
+        <v>-22.22384828913545</v>
       </c>
       <c r="AA4" s="25">
         <v>4.705568157602146</v>
@@ -9833,13 +9847,13 @@
         <v>0</v>
       </c>
       <c r="AG4" s="25">
-        <v>1324.6561559770421</v>
+        <v>146.02175678084004</v>
       </c>
       <c r="AH4" s="25">
-        <v>29.049477104759696</v>
+        <v>3.2022315083517552</v>
       </c>
       <c r="AI4" s="25">
-        <v>29.049477104759696</v>
+        <v>3.2022315083517525</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
@@ -9849,23 +9863,23 @@
       </c>
       <c r="B5" s="25">
         <f>lc_detailed!AX5/$R$2</f>
-        <v>11.46912799200997</v>
+        <v>7.9023386587990325</v>
       </c>
       <c r="C5" s="25">
         <f>lc_detailed!AY5/$R$2</f>
-        <v>0.77235102943006417</v>
+        <v>0.73083594500965676</v>
       </c>
       <c r="D5" s="25">
         <f>lc_detailed!AZ5/$R$2</f>
-        <v>15.940764076883717</v>
+        <v>11.091536587122279</v>
       </c>
       <c r="E5" s="25">
         <f>lc_detailed!BA5/$R$2</f>
-        <v>-0.3699899768881969</v>
+        <v>-0.16457133828177642</v>
       </c>
       <c r="F5" s="25">
         <f>lc_detailed!BB5/$R$2</f>
-        <v>0</v>
+        <v>-20.74755519690644</v>
       </c>
       <c r="G5" s="25">
         <f>lc_detailed!BC5/$R$2</f>
@@ -9893,42 +9907,42 @@
       </c>
       <c r="M5" s="25">
         <f>lc_detailed!AU5</f>
-        <v>1524.0414827303043</v>
+        <v>201.65660069471286</v>
       </c>
       <c r="N5" s="25">
-        <f t="shared" ref="N5:N20" si="0">M5/$R$2</f>
-        <v>33.421962340576847</v>
+        <f t="shared" si="0"/>
+        <v>4.4222938748840539</v>
       </c>
       <c r="O5" s="25">
-        <f t="shared" ref="O5:O20" si="1">SUM(B5:K5)</f>
-        <v>33.421962340576862</v>
+        <f t="shared" si="1"/>
+        <v>4.4222938748840521</v>
       </c>
       <c r="U5" t="str">
-        <v>CA_Synthetic_Ethylene_Non_CCS</v>
+        <v>MIDAT_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V5" s="25">
-        <v>5.2904756011590282</v>
+        <v>7.9023386617113429</v>
       </c>
       <c r="W5" s="25">
-        <v>0.68735990664232594</v>
+        <v>0.93155650147922364</v>
       </c>
       <c r="X5" s="25">
-        <v>18.130768095498382</v>
+        <v>10.189334687032737</v>
       </c>
       <c r="Y5" s="25">
-        <v>-0.26046229512309738</v>
+        <v>-0.16457133836157006</v>
       </c>
       <c r="Z5" s="25">
-        <v>0</v>
+        <v>-20.747555205502195</v>
       </c>
       <c r="AA5" s="25">
-        <v>4.2600965636830308</v>
+        <v>4.705568157602146</v>
       </c>
       <c r="AB5" s="25">
-        <v>2.3433206377337097</v>
+        <v>2.5867547372464941</v>
       </c>
       <c r="AC5" s="25">
-        <v>-0.99370798227543866</v>
+        <v>-1.074340016786842</v>
       </c>
       <c r="AD5" s="25">
         <v>0</v>
@@ -9940,13 +9954,13 @@
         <v>0</v>
       </c>
       <c r="AG5" s="25">
-        <v>1343.2779840456978</v>
+        <v>197.40633000961301</v>
       </c>
       <c r="AH5" s="25">
-        <v>29.457850527317934</v>
+        <v>4.329086184421338</v>
       </c>
       <c r="AI5" s="25">
-        <v>29.457850527317937</v>
+        <v>4.3290861844213371</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.2">
@@ -9956,23 +9970,23 @@
       </c>
       <c r="B6" s="25">
         <f>lc_detailed!AX6/$R$2</f>
-        <v>11.469127996236775</v>
+        <v>7.9023386617113429</v>
       </c>
       <c r="C6" s="25">
         <f>lc_detailed!AY6/$R$2</f>
-        <v>0.98447350298327296</v>
+        <v>0.93155650147922364</v>
       </c>
       <c r="D6" s="25">
         <f>lc_detailed!AZ6/$R$2</f>
-        <v>14.644118880244196</v>
+        <v>10.189334687032737</v>
       </c>
       <c r="E6" s="25">
         <f>lc_detailed!BA6/$R$2</f>
-        <v>-0.36998997706758924</v>
+        <v>-0.16457133836157006</v>
       </c>
       <c r="F6" s="25">
         <f>lc_detailed!BB6/$R$2</f>
-        <v>0</v>
+        <v>-20.747555205502195</v>
       </c>
       <c r="G6" s="25">
         <f>lc_detailed!BC6/$R$2</f>
@@ -10000,33 +10014,33 @@
       </c>
       <c r="M6" s="25">
         <f>lc_detailed!AU6</f>
-        <v>1502.3245255889051</v>
+        <v>197.40633000961301</v>
       </c>
       <c r="N6" s="25">
         <f t="shared" si="0"/>
-        <v>32.945713280458442</v>
+        <v>4.329086184421338</v>
       </c>
       <c r="O6" s="25">
         <f t="shared" si="1"/>
-        <v>32.945713280458449</v>
+        <v>4.3290861844213371</v>
       </c>
       <c r="U6" t="str">
-        <v>NW_Synthetic_Ethylene_Non_CCS</v>
+        <v>MIDAT_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V6" s="25">
-        <v>5.4434092955246678</v>
+        <v>7.9023386587990325</v>
       </c>
       <c r="W6" s="25">
-        <v>0.68303418295909657</v>
+        <v>0.73083594500965676</v>
       </c>
       <c r="X6" s="25">
-        <v>18.275539973757166</v>
+        <v>11.091536587122279</v>
       </c>
       <c r="Y6" s="25">
-        <v>-0.27152195898886416</v>
+        <v>-0.16457133828177642</v>
       </c>
       <c r="Z6" s="25">
-        <v>0</v>
+        <v>-20.74755519690644</v>
       </c>
       <c r="AA6" s="25">
         <v>4.2600965636830308</v>
@@ -10047,13 +10061,13 @@
         <v>0</v>
       </c>
       <c r="AG6" s="25">
-        <v>1356.1517844851373</v>
+        <v>201.65660069471286</v>
       </c>
       <c r="AH6" s="25">
-        <v>29.740170712393361</v>
+        <v>4.4222938748840539</v>
       </c>
       <c r="AI6" s="25">
-        <v>29.740170712393372</v>
+        <v>4.4222938748840521</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
@@ -10063,23 +10077,23 @@
       </c>
       <c r="B7" s="25">
         <f>lc_detailed!AX7/$R$2</f>
-        <v>10.596217819504876</v>
+        <v>9.6475746507461988</v>
       </c>
       <c r="C7" s="25">
         <f>lc_detailed!AY7/$R$2</f>
-        <v>0.7459629592606114</v>
+        <v>0.7066773254975931</v>
       </c>
       <c r="D7" s="25">
         <f>lc_detailed!AZ7/$R$2</f>
-        <v>14.590879921906732</v>
+        <v>9.7233651841228586</v>
       </c>
       <c r="E7" s="25">
         <f>lc_detailed!BA7/$R$2</f>
-        <v>-0.33797477121342173</v>
+        <v>-0.27269292708438991</v>
       </c>
       <c r="F7" s="25">
         <f>lc_detailed!BB7/$R$2</f>
-        <v>0</v>
+        <v>-22.223848279928063</v>
       </c>
       <c r="G7" s="25">
         <f>lc_detailed!BC7/$R$2</f>
@@ -10107,33 +10121,33 @@
       </c>
       <c r="M7" s="25">
         <f>lc_detailed!AU7</f>
-        <v>1422.9386587761646</v>
+        <v>145.49980386579475</v>
       </c>
       <c r="N7" s="25">
         <f t="shared" si="0"/>
-        <v>31.204795148600102</v>
+        <v>3.1907851724954988</v>
       </c>
       <c r="O7" s="25">
         <f t="shared" si="1"/>
-        <v>31.204795148600098</v>
+        <v>3.1907851724954996</v>
       </c>
       <c r="U7" t="str">
         <v>SE_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V7" s="25">
-        <v>7.4790582714704827</v>
+        <v>7.624683880724632</v>
       </c>
       <c r="W7" s="25">
-        <v>0.95437730959534783</v>
+        <v>0.9213972007811656</v>
       </c>
       <c r="X7" s="25">
-        <v>16.432968777303802</v>
+        <v>11.975775539898962</v>
       </c>
       <c r="Y7" s="25">
-        <v>-0.36969322550418754</v>
+        <v>-0.24235512411799978</v>
       </c>
       <c r="Z7" s="25">
-        <v>0</v>
+        <v>-18.880720000582343</v>
       </c>
       <c r="AA7" s="25">
         <v>4.705568157602146</v>
@@ -10154,13 +10168,13 @@
         <v>0</v>
       </c>
       <c r="AG7" s="25">
-        <v>1400.590046898282</v>
+        <v>347.32445548933936</v>
       </c>
       <c r="AH7" s="25">
-        <v>30.714694010927236</v>
+        <v>7.6167643747662135</v>
       </c>
       <c r="AI7" s="25">
-        <v>30.714694010927246</v>
+        <v>7.6167643747662144</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
@@ -10170,23 +10184,23 @@
       </c>
       <c r="B8" s="25">
         <f>lc_detailed!AX8/$R$2</f>
-        <v>10.596217823409981</v>
+        <v>9.6475746543016925</v>
       </c>
       <c r="C8" s="25">
         <f>lc_detailed!AY8/$R$2</f>
-        <v>0.95083807700881717</v>
+        <v>0.90076283399899526</v>
       </c>
       <c r="D8" s="25">
         <f>lc_detailed!AZ8/$R$2</f>
-        <v>13.404036287923102</v>
+        <v>8.932452358341326</v>
       </c>
       <c r="E8" s="25">
         <f>lc_detailed!BA8/$R$2</f>
-        <v>-0.33797477137729132</v>
+        <v>-0.27269292721660704</v>
       </c>
       <c r="F8" s="25">
         <f>lc_detailed!BB8/$R$2</f>
-        <v>0</v>
+        <v>-22.22384828913545</v>
       </c>
       <c r="G8" s="25">
         <f>lc_detailed!BC8/$R$2</f>
@@ -10214,42 +10228,42 @@
       </c>
       <c r="M8" s="25">
         <f>lc_detailed!AU8</f>
-        <v>1405.898173453204</v>
+        <v>146.02175678084004</v>
       </c>
       <c r="N8" s="25">
         <f t="shared" si="0"/>
-        <v>30.831100295026403</v>
+        <v>3.2022315083517552</v>
       </c>
       <c r="O8" s="25">
         <f t="shared" si="1"/>
-        <v>30.83110029502641</v>
+        <v>3.2022315083517525</v>
       </c>
       <c r="U8" t="str">
-        <v>SW_Synthetic_Ethylene_CCS_90</v>
+        <v>SE_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V8" s="25">
-        <v>7.4502256408836214</v>
+        <v>7.6246838779146486</v>
       </c>
       <c r="W8" s="25">
-        <v>0.91415769006200642</v>
+        <v>0.72286564786234198</v>
       </c>
       <c r="X8" s="25">
-        <v>16.527022438451514</v>
+        <v>13.03615561171002</v>
       </c>
       <c r="Y8" s="25">
-        <v>-0.37354974807801505</v>
+        <v>-0.24235512400049214</v>
       </c>
       <c r="Z8" s="25">
-        <v>0</v>
+        <v>-18.880719992760021</v>
       </c>
       <c r="AA8" s="25">
-        <v>4.705568157602146</v>
+        <v>4.2600965636830308</v>
       </c>
       <c r="AB8" s="25">
-        <v>2.5867547372464941</v>
+        <v>2.3433206377337097</v>
       </c>
       <c r="AC8" s="25">
-        <v>-1.074340016786842</v>
+        <v>-0.99370798227543866</v>
       </c>
       <c r="AD8" s="25">
         <v>0</v>
@@ -10261,13 +10275,13 @@
         <v>0</v>
       </c>
       <c r="AG8" s="25">
-        <v>1401.55425381177</v>
+        <v>358.88746933797165</v>
       </c>
       <c r="AH8" s="25">
-        <v>30.735838899380919</v>
+        <v>7.8703392398677989</v>
       </c>
       <c r="AI8" s="25">
-        <v>30.735838899380923</v>
+        <v>7.8703392398677998</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
@@ -10277,23 +10291,23 @@
       </c>
       <c r="B9" s="25">
         <f>lc_detailed!AX9/$R$2</f>
-        <v>5.2904756011590282</v>
+        <v>8.882221111503009</v>
       </c>
       <c r="C9" s="25">
         <f>lc_detailed!AY9/$R$2</f>
-        <v>0.68735990664232594</v>
+        <v>0.68916970159805557</v>
       </c>
       <c r="D9" s="25">
         <f>lc_detailed!AZ9/$R$2</f>
-        <v>18.130768095498382</v>
+        <v>14.948219637620451</v>
       </c>
       <c r="E9" s="25">
         <f>lc_detailed!BA9/$R$2</f>
-        <v>-0.26046229512309738</v>
+        <v>-0.39450878949359602</v>
       </c>
       <c r="F9" s="25">
         <f>lc_detailed!BB9/$R$2</f>
-        <v>0</v>
+        <v>-17.122469805914761</v>
       </c>
       <c r="G9" s="25">
         <f>lc_detailed!BC9/$R$2</f>
@@ -10321,33 +10335,33 @@
       </c>
       <c r="M9" s="25">
         <f>lc_detailed!AU9</f>
-        <v>1343.2779840456978</v>
+        <v>575.12275299512351</v>
       </c>
       <c r="N9" s="25">
         <f t="shared" si="0"/>
-        <v>29.457850527317934</v>
+        <v>12.612341074454463</v>
       </c>
       <c r="O9" s="25">
         <f t="shared" si="1"/>
-        <v>29.457850527317937</v>
+        <v>12.612341074454461</v>
       </c>
       <c r="U9" t="str">
-        <v>NE_Synthetic_Ethylene_CCS_90</v>
+        <v>TX_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V9" s="25">
-        <v>10.596217823409981</v>
+        <v>7.9189911503517845</v>
       </c>
       <c r="W9" s="25">
-        <v>0.95083807700881717</v>
+        <v>0.92536315857176465</v>
       </c>
       <c r="X9" s="25">
-        <v>13.404036287923102</v>
+        <v>12.168959138351944</v>
       </c>
       <c r="Y9" s="25">
-        <v>-0.33797477137729132</v>
+        <v>-0.26177559818929191</v>
       </c>
       <c r="Z9" s="25">
-        <v>0</v>
+        <v>-18.689851672712397</v>
       </c>
       <c r="AA9" s="25">
         <v>4.705568157602146</v>
@@ -10368,13 +10382,13 @@
         <v>0</v>
       </c>
       <c r="AG9" s="25">
-        <v>1405.898173453204</v>
+        <v>377.55290888226364</v>
       </c>
       <c r="AH9" s="25">
-        <v>30.831100295026403</v>
+        <v>8.2796690544356064</v>
       </c>
       <c r="AI9" s="25">
-        <v>30.83110029502641</v>
+        <v>8.2796690544356029</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.2">
@@ -10384,23 +10398,23 @@
       </c>
       <c r="B10" s="25">
         <f>lc_detailed!AX10/$R$2</f>
-        <v>5.2904756031087681</v>
+        <v>8.8822211147764421</v>
       </c>
       <c r="C10" s="25">
         <f>lc_detailed!AY10/$R$2</f>
-        <v>0.87613997951393885</v>
+        <v>0.87844682589836531</v>
       </c>
       <c r="D10" s="25">
         <f>lc_detailed!AZ10/$R$2</f>
-        <v>16.655984750796321</v>
+        <v>13.73230946556412</v>
       </c>
       <c r="E10" s="25">
         <f>lc_detailed!BA10/$R$2</f>
-        <v>-0.26046229524938447</v>
+        <v>-0.39450878968487657</v>
       </c>
       <c r="F10" s="25">
         <f>lc_detailed!BB10/$R$2</f>
-        <v>0</v>
+        <v>-17.122469813008635</v>
       </c>
       <c r="G10" s="25">
         <f>lc_detailed!BC10/$R$2</f>
@@ -10428,33 +10442,33 @@
       </c>
       <c r="M10" s="25">
         <f>lc_detailed!AU10</f>
-        <v>1312.3735137801536</v>
+        <v>556.04556468128874</v>
       </c>
       <c r="N10" s="25">
         <f t="shared" si="0"/>
-        <v>28.780120916231439</v>
+        <v>12.193981681607209</v>
       </c>
       <c r="O10" s="25">
         <f t="shared" si="1"/>
-        <v>28.780120916231439</v>
+        <v>12.193981681607214</v>
       </c>
       <c r="U10" t="str">
-        <v>NE_Synthetic_Ethylene_Non_CCS</v>
+        <v>TX_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V10" s="25">
-        <v>10.596217819504876</v>
+        <v>7.9189911474333377</v>
       </c>
       <c r="W10" s="25">
-        <v>0.7459629592606114</v>
+        <v>0.72597706891426772</v>
       </c>
       <c r="X10" s="25">
-        <v>14.590879921906732</v>
+        <v>13.24644441034965</v>
       </c>
       <c r="Y10" s="25">
-        <v>-0.33797477121342173</v>
+        <v>-0.26177559806236805</v>
       </c>
       <c r="Z10" s="25">
-        <v>0</v>
+        <v>-18.689851664969151</v>
       </c>
       <c r="AA10" s="25">
         <v>4.2600965636830308</v>
@@ -10475,13 +10489,13 @@
         <v>0</v>
       </c>
       <c r="AG10" s="25">
-        <v>1422.9386587761646</v>
+        <v>389.85695297600091</v>
       </c>
       <c r="AH10" s="25">
-        <v>31.204795148600102</v>
+        <v>8.5494945828070374</v>
       </c>
       <c r="AI10" s="25">
-        <v>31.204795148600098</v>
+        <v>8.5494945828070357</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.2">
@@ -10491,23 +10505,23 @@
       </c>
       <c r="B11" s="25">
         <f>lc_detailed!AX11/$R$2</f>
-        <v>8.5357868210826187</v>
+        <v>13.845141117697725</v>
       </c>
       <c r="C11" s="25">
         <f>lc_detailed!AY11/$R$2</f>
-        <v>0.78755860289152668</v>
+        <v>0.77862652394618448</v>
       </c>
       <c r="D11" s="25">
         <f>lc_detailed!AZ11/$R$2</f>
-        <v>17.887856831076196</v>
+        <v>13.034938890657648</v>
       </c>
       <c r="E11" s="25">
         <f>lc_detailed!BA11/$R$2</f>
-        <v>-0.41244103209752564</v>
+        <v>-0.45509041875365486</v>
       </c>
       <c r="F11" s="25">
         <f>lc_detailed!BB11/$R$2</f>
-        <v>0</v>
+        <v>-19.09467193131994</v>
       </c>
       <c r="G11" s="25">
         <f>lc_detailed!BC11/$R$2</f>
@@ -10535,42 +10549,42 @@
       </c>
       <c r="M11" s="25">
         <f>lc_detailed!AU11</f>
-        <v>1477.8262521594916</v>
+        <v>625.57059510243857</v>
       </c>
       <c r="N11" s="25">
         <f t="shared" si="0"/>
-        <v>32.408470442094114</v>
+        <v>13.718653401369266</v>
       </c>
       <c r="O11" s="25">
         <f t="shared" si="1"/>
-        <v>32.408470442094121</v>
+        <v>13.718653401369265</v>
       </c>
       <c r="U11" t="str">
-        <v>SE_Synthetic_Ethylene_Non_CCS</v>
+        <v>SW_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V11" s="25">
-        <v>7.4790582687141676</v>
+        <v>9.488202585105773</v>
       </c>
       <c r="W11" s="25">
-        <v>0.74873960070734991</v>
+        <v>0.91079397415754326</v>
       </c>
       <c r="X11" s="25">
-        <v>17.888005451470899</v>
+        <v>12.292551924231621</v>
       </c>
       <c r="Y11" s="25">
-        <v>-0.36969322532493909</v>
+        <v>-0.31410156307402354</v>
       </c>
       <c r="Z11" s="25">
-        <v>0</v>
+        <v>-18.607641480632839</v>
       </c>
       <c r="AA11" s="25">
-        <v>4.2600965636830308</v>
+        <v>4.705568157602146</v>
       </c>
       <c r="AB11" s="25">
-        <v>2.3433206377337097</v>
+        <v>2.5867547372464941</v>
       </c>
       <c r="AC11" s="25">
-        <v>-0.99370798227543866</v>
+        <v>-1.074340016786842</v>
       </c>
       <c r="AD11" s="25">
         <v>0</v>
@@ -10582,13 +10596,13 @@
         <v>0</v>
       </c>
       <c r="AG11" s="25">
-        <v>1429.8253607507204</v>
+        <v>455.44314729395421</v>
       </c>
       <c r="AH11" s="25">
-        <v>31.355819314708778</v>
+        <v>9.9877883178498728</v>
       </c>
       <c r="AI11" s="25">
-        <v>31.355819314708782</v>
+        <v>9.9877883178498745</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.2">
@@ -10598,23 +10612,23 @@
       </c>
       <c r="B12" s="25">
         <f>lc_detailed!AX12/$R$2</f>
-        <v>8.5357868242283779</v>
+        <v>13.845141122800179</v>
       </c>
       <c r="C12" s="25">
         <f>lc_detailed!AY12/$R$2</f>
-        <v>1.0038577629207903</v>
+        <v>0.99247253170703364</v>
       </c>
       <c r="D12" s="25">
         <f>lc_detailed!AZ12/$R$2</f>
-        <v>16.4328322459106</v>
+        <v>11.974657788726613</v>
       </c>
       <c r="E12" s="25">
         <f>lc_detailed!BA12/$R$2</f>
-        <v>-0.41244103229750073</v>
+        <v>-0.45509041897430885</v>
       </c>
       <c r="F12" s="25">
         <f>lc_detailed!BB12/$R$2</f>
-        <v>0</v>
+        <v>-19.094671939230906</v>
       </c>
       <c r="G12" s="25">
         <f>lc_detailed!BC12/$R$2</f>
@@ -10642,33 +10656,33 @@
       </c>
       <c r="M12" s="25">
         <f>lc_detailed!AU12</f>
-        <v>1449.0776517543773</v>
+        <v>614.71043351692254</v>
       </c>
       <c r="N12" s="25">
         <f t="shared" si="0"/>
-        <v>31.778018678824061</v>
+        <v>13.480491963090406</v>
       </c>
       <c r="O12" s="25">
         <f t="shared" si="1"/>
-        <v>31.778018678824061</v>
+        <v>13.48049196309041</v>
       </c>
       <c r="U12" t="str">
         <v>SW_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V12" s="25">
-        <v>7.4502256381379315</v>
+        <v>9.4882025816090128</v>
       </c>
       <c r="W12" s="25">
-        <v>0.71718601957415662</v>
+        <v>0.7145470765922991</v>
       </c>
       <c r="X12" s="25">
-        <v>17.990386976449198</v>
+        <v>13.380980564926391</v>
       </c>
       <c r="Y12" s="25">
-        <v>-0.37354974789689666</v>
+        <v>-0.31410156292172908</v>
       </c>
       <c r="Z12" s="25">
-        <v>0</v>
+        <v>-18.607641472923653</v>
       </c>
       <c r="AA12" s="25">
         <v>4.2600965636830308</v>
@@ -10689,13 +10703,13 @@
         <v>0</v>
       </c>
       <c r="AG12" s="25">
-        <v>1431.5644896064996</v>
+        <v>468.38935613291721</v>
       </c>
       <c r="AH12" s="25">
-        <v>31.393958105405691</v>
+        <v>10.271696406423622</v>
       </c>
       <c r="AI12" s="25">
-        <v>31.393958105405694</v>
+        <v>10.271696406423624</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
@@ -10705,23 +10719,23 @@
       </c>
       <c r="B13" s="25">
         <f>lc_detailed!AX13/$R$2</f>
-        <v>8.3396571607981951</v>
+        <v>13.938062696688313</v>
       </c>
       <c r="C13" s="25">
         <f>lc_detailed!AY13/$R$2</f>
-        <v>0.76219353272184187</v>
+        <v>0.76361776517765922</v>
       </c>
       <c r="D13" s="25">
         <f>lc_detailed!AZ13/$R$2</f>
-        <v>17.867352806738438</v>
+        <v>13.015288614346023</v>
       </c>
       <c r="E13" s="25">
         <f>lc_detailed!BA13/$R$2</f>
-        <v>-0.40627160635588333</v>
+        <v>-0.45791675599407311</v>
       </c>
       <c r="F13" s="25">
         <f>lc_detailed!BB13/$R$2</f>
-        <v>0</v>
+        <v>-19.117148629518834</v>
       </c>
       <c r="G13" s="25">
         <f>lc_detailed!BC13/$R$2</f>
@@ -10749,33 +10763,33 @@
       </c>
       <c r="M13" s="25">
         <f>lc_detailed!AU13</f>
-        <v>1467.0724347548016</v>
+        <v>627.07354868872187</v>
       </c>
       <c r="N13" s="25">
         <f t="shared" si="0"/>
-        <v>32.172641113043895</v>
+        <v>13.751612909840391</v>
       </c>
       <c r="O13" s="25">
         <f t="shared" si="1"/>
-        <v>32.172641113043895</v>
+        <v>13.751612909840391</v>
       </c>
       <c r="U13" t="str">
-        <v>CEN_Synthetic_Ethylene_CCS_90</v>
+        <v>CA_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V13" s="25">
-        <v>8.3396571638716726</v>
+        <v>8.8822211147764421</v>
       </c>
       <c r="W13" s="25">
-        <v>0.97152629894670461</v>
+        <v>0.87844682589836531</v>
       </c>
       <c r="X13" s="25">
-        <v>16.413996049071017</v>
+        <v>13.73230946556412</v>
       </c>
       <c r="Y13" s="25">
-        <v>-0.40627160655286715</v>
+        <v>-0.39450878968487657</v>
       </c>
       <c r="Z13" s="25">
-        <v>0</v>
+        <v>-17.122469813008635</v>
       </c>
       <c r="AA13" s="25">
         <v>4.705568157602146</v>
@@ -10796,13 +10810,13 @@
         <v>0</v>
       </c>
       <c r="AG13" s="25">
-        <v>1438.0822197229634</v>
+        <v>556.04556468128874</v>
       </c>
       <c r="AH13" s="25">
-        <v>31.53689078339832</v>
+        <v>12.193981681607209</v>
       </c>
       <c r="AI13" s="25">
-        <v>31.536890783398327</v>
+        <v>12.193981681607214</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.2">
@@ -10812,23 +10826,23 @@
       </c>
       <c r="B14" s="25">
         <f>lc_detailed!AX14/$R$2</f>
-        <v>8.3396571638716726</v>
+        <v>13.938062701825016</v>
       </c>
       <c r="C14" s="25">
         <f>lc_detailed!AY14/$R$2</f>
-        <v>0.97152629894670461</v>
+        <v>0.97334168995599168</v>
       </c>
       <c r="D14" s="25">
         <f>lc_detailed!AZ14/$R$2</f>
-        <v>16.413996049071017</v>
+        <v>11.956605894792975</v>
       </c>
       <c r="E14" s="25">
         <f>lc_detailed!BA14/$R$2</f>
-        <v>-0.40627160655286715</v>
+        <v>-0.45791675621609745</v>
       </c>
       <c r="F14" s="25">
         <f>lc_detailed!BB14/$R$2</f>
-        <v>0</v>
+        <v>-19.117148637439108</v>
       </c>
       <c r="G14" s="25">
         <f>lc_detailed!BC14/$R$2</f>
@@ -10856,42 +10870,42 @@
       </c>
       <c r="M14" s="25">
         <f>lc_detailed!AU14</f>
-        <v>1438.0822197229634</v>
+        <v>616.09830635671449</v>
       </c>
       <c r="N14" s="25">
         <f t="shared" si="0"/>
-        <v>31.53689078339832</v>
+        <v>13.510927770980581</v>
       </c>
       <c r="O14" s="25">
         <f t="shared" si="1"/>
-        <v>31.536890783398327</v>
+        <v>13.510927770980578</v>
       </c>
       <c r="U14" t="str">
-        <v>TX_Synthetic_Ethylene_CCS_90</v>
+        <v>CA_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V14" s="25">
-        <v>8.3654484308493462</v>
+        <v>8.882221111503009</v>
       </c>
       <c r="W14" s="25">
-        <v>0.92491394678216343</v>
+        <v>0.68916970159805557</v>
       </c>
       <c r="X14" s="25">
-        <v>16.623548185525394</v>
+        <v>14.948219637620451</v>
       </c>
       <c r="Y14" s="25">
-        <v>-0.40807122781737304</v>
+        <v>-0.39450878949359602</v>
       </c>
       <c r="Z14" s="25">
-        <v>0</v>
+        <v>-17.122469805914761</v>
       </c>
       <c r="AA14" s="25">
-        <v>4.705568157602146</v>
+        <v>4.2600965636830308</v>
       </c>
       <c r="AB14" s="25">
-        <v>2.5867547372464941</v>
+        <v>2.3433206377337097</v>
       </c>
       <c r="AC14" s="25">
-        <v>-1.074340016786842</v>
+        <v>-0.99370798227543866</v>
       </c>
       <c r="AD14" s="25">
         <v>0</v>
@@ -10903,13 +10917,13 @@
         <v>0</v>
       </c>
       <c r="AG14" s="25">
-        <v>1446.6062929311004</v>
+        <v>575.12275299512351</v>
       </c>
       <c r="AH14" s="25">
-        <v>31.723822213401323</v>
+        <v>12.612341074454463</v>
       </c>
       <c r="AI14" s="25">
-        <v>31.723822213401327</v>
+        <v>12.612341074454461</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.2">
@@ -10919,23 +10933,23 @@
       </c>
       <c r="B15" s="25">
         <f>lc_detailed!AX15/$R$2</f>
-        <v>8.3654484277663634</v>
+        <v>7.9189911474333377</v>
       </c>
       <c r="C15" s="25">
         <f>lc_detailed!AY15/$R$2</f>
-        <v>0.72562464786171599</v>
+        <v>0.72597706891426772</v>
       </c>
       <c r="D15" s="25">
         <f>lc_detailed!AZ15/$R$2</f>
-        <v>18.095459475111131</v>
+        <v>13.24644441034965</v>
       </c>
       <c r="E15" s="25">
         <f>lc_detailed!BA15/$R$2</f>
-        <v>-0.40807122761951675</v>
+        <v>-0.26177559806236805</v>
       </c>
       <c r="F15" s="25">
         <f>lc_detailed!BB15/$R$2</f>
-        <v>0</v>
+        <v>-18.689851664969151</v>
       </c>
       <c r="G15" s="25">
         <f>lc_detailed!BC15/$R$2</f>
@@ -10963,33 +10977,33 @@
       </c>
       <c r="M15" s="25">
         <f>lc_detailed!AU15</f>
-        <v>1476.9005767271015</v>
+        <v>389.85695297600091</v>
       </c>
       <c r="N15" s="25">
         <f t="shared" si="0"/>
-        <v>32.388170542260994</v>
+        <v>8.5494945828070374</v>
       </c>
       <c r="O15" s="25">
         <f t="shared" si="1"/>
-        <v>32.388170542260994</v>
+        <v>8.5494945828070357</v>
       </c>
       <c r="U15" t="str">
-        <v>NCEN_Synthetic_Ethylene_CCS_90</v>
+        <v>NW_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V15" s="25">
-        <v>8.5357868242283779</v>
+        <v>8.5313826695435289</v>
       </c>
       <c r="W15" s="25">
-        <v>1.0038577629207903</v>
+        <v>0.87658719827283771</v>
       </c>
       <c r="X15" s="25">
-        <v>16.4328322459106</v>
+        <v>14.177318046892477</v>
       </c>
       <c r="Y15" s="25">
-        <v>-0.41244103229750073</v>
+        <v>-0.37462406116791802</v>
       </c>
       <c r="Z15" s="25">
-        <v>0</v>
+        <v>-16.656553189681333</v>
       </c>
       <c r="AA15" s="25">
         <v>4.705568157602146</v>
@@ -11010,13 +11024,13 @@
         <v>0</v>
       </c>
       <c r="AG15" s="25">
-        <v>1449.0776517543773</v>
+        <v>582.40746551161544</v>
       </c>
       <c r="AH15" s="25">
-        <v>31.778018678824061</v>
+        <v>12.772093541921391</v>
       </c>
       <c r="AI15" s="25">
-        <v>31.778018678824061</v>
+        <v>12.772093541921391</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.2">
@@ -11026,23 +11040,23 @@
       </c>
       <c r="B16" s="25">
         <f>lc_detailed!AX16/$R$2</f>
-        <v>8.3654484308493462</v>
+        <v>7.9189911503517845</v>
       </c>
       <c r="C16" s="25">
         <f>lc_detailed!AY16/$R$2</f>
-        <v>0.92491394678216343</v>
+        <v>0.92536315857176465</v>
       </c>
       <c r="D16" s="25">
         <f>lc_detailed!AZ16/$R$2</f>
-        <v>16.623548185525394</v>
+        <v>12.168959138351944</v>
       </c>
       <c r="E16" s="25">
         <f>lc_detailed!BA16/$R$2</f>
-        <v>-0.40807122781737304</v>
+        <v>-0.26177559818929191</v>
       </c>
       <c r="F16" s="25">
         <f>lc_detailed!BB16/$R$2</f>
-        <v>0</v>
+        <v>-18.689851672712397</v>
       </c>
       <c r="G16" s="25">
         <f>lc_detailed!BC16/$R$2</f>
@@ -11070,33 +11084,33 @@
       </c>
       <c r="M16" s="25">
         <f>lc_detailed!AU16</f>
-        <v>1446.6062929311004</v>
+        <v>377.55290888226364</v>
       </c>
       <c r="N16" s="25">
         <f t="shared" si="0"/>
-        <v>31.723822213401323</v>
+        <v>8.2796690544356064</v>
       </c>
       <c r="O16" s="25">
         <f t="shared" si="1"/>
-        <v>31.723822213401327</v>
+        <v>8.2796690544356029</v>
       </c>
       <c r="U16" t="str">
-        <v>CEN_Synthetic_Ethylene_Non_CCS</v>
+        <v>NW_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V16" s="25">
-        <v>8.3396571607981951</v>
+        <v>8.531382666399395</v>
       </c>
       <c r="W16" s="25">
-        <v>0.76219353272184187</v>
+        <v>0.68771076409838661</v>
       </c>
       <c r="X16" s="25">
-        <v>17.867352806738438</v>
+        <v>15.432630947386178</v>
       </c>
       <c r="Y16" s="25">
-        <v>-0.40627160635588333</v>
+        <v>-0.37462406098627876</v>
       </c>
       <c r="Z16" s="25">
-        <v>0</v>
+        <v>-16.656553182780488</v>
       </c>
       <c r="AA16" s="25">
         <v>4.2600965636830308</v>
@@ -11117,13 +11131,13 @@
         <v>0</v>
       </c>
       <c r="AG16" s="25">
-        <v>1467.0724347548016</v>
+        <v>603.29968970858738</v>
       </c>
       <c r="AH16" s="25">
-        <v>32.172641113043895</v>
+        <v>13.230256353258495</v>
       </c>
       <c r="AI16" s="25">
-        <v>32.172641113043895</v>
+        <v>13.230256353258495</v>
       </c>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.2">
@@ -11133,23 +11147,23 @@
       </c>
       <c r="B17" s="25">
         <f>lc_detailed!AX17/$R$2</f>
-        <v>5.4434092955246678</v>
+        <v>8.531382666399395</v>
       </c>
       <c r="C17" s="25">
         <f>lc_detailed!AY17/$R$2</f>
-        <v>0.68303418295909657</v>
+        <v>0.68771076409838661</v>
       </c>
       <c r="D17" s="25">
         <f>lc_detailed!AZ17/$R$2</f>
-        <v>18.275539973757166</v>
+        <v>15.432630947386178</v>
       </c>
       <c r="E17" s="25">
         <f>lc_detailed!BA17/$R$2</f>
-        <v>-0.27152195898886416</v>
+        <v>-0.37462406098627876</v>
       </c>
       <c r="F17" s="25">
         <f>lc_detailed!BB17/$R$2</f>
-        <v>0</v>
+        <v>-16.656553182780488</v>
       </c>
       <c r="G17" s="25">
         <f>lc_detailed!BC17/$R$2</f>
@@ -11177,42 +11191,42 @@
       </c>
       <c r="M17" s="25">
         <f>lc_detailed!AU17</f>
-        <v>1356.1517844851373</v>
+        <v>603.29968970858738</v>
       </c>
       <c r="N17" s="25">
         <f t="shared" si="0"/>
-        <v>29.740170712393361</v>
+        <v>13.230256353258495</v>
       </c>
       <c r="O17" s="25">
         <f t="shared" si="1"/>
-        <v>29.740170712393372</v>
+        <v>13.230256353258495</v>
       </c>
       <c r="U17" t="str">
-        <v>TX_Synthetic_Ethylene_Non_CCS</v>
+        <v>NCEN_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V17" s="25">
-        <v>8.3654484277663634</v>
+        <v>13.845141122800179</v>
       </c>
       <c r="W17" s="25">
-        <v>0.72562464786171599</v>
+        <v>0.99247253170703364</v>
       </c>
       <c r="X17" s="25">
-        <v>18.095459475111131</v>
+        <v>11.974657788726613</v>
       </c>
       <c r="Y17" s="25">
-        <v>-0.40807122761951675</v>
+        <v>-0.45509041897430885</v>
       </c>
       <c r="Z17" s="25">
-        <v>0</v>
+        <v>-19.094671939230906</v>
       </c>
       <c r="AA17" s="25">
-        <v>4.2600965636830308</v>
+        <v>4.705568157602146</v>
       </c>
       <c r="AB17" s="25">
-        <v>2.3433206377337097</v>
+        <v>2.5867547372464941</v>
       </c>
       <c r="AC17" s="25">
-        <v>-0.99370798227543866</v>
+        <v>-1.074340016786842</v>
       </c>
       <c r="AD17" s="25">
         <v>0</v>
@@ -11224,13 +11238,13 @@
         <v>0</v>
       </c>
       <c r="AG17" s="25">
-        <v>1476.9005767271015</v>
+        <v>614.71043351692254</v>
       </c>
       <c r="AH17" s="25">
-        <v>32.388170542260994</v>
+        <v>13.480491963090406</v>
       </c>
       <c r="AI17" s="25">
-        <v>32.388170542260994</v>
+        <v>13.48049196309041</v>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.2">
@@ -11240,23 +11254,23 @@
       </c>
       <c r="B18" s="25">
         <f>lc_detailed!AX18/$R$2</f>
-        <v>5.443409297530768</v>
+        <v>8.5313826695435289</v>
       </c>
       <c r="C18" s="25">
         <f>lc_detailed!AY18/$R$2</f>
-        <v>0.87062621674921659</v>
+        <v>0.87658719827283771</v>
       </c>
       <c r="D18" s="25">
         <f>lc_detailed!AZ18/$R$2</f>
-        <v>16.788980671538429</v>
+        <v>14.177318046892477</v>
       </c>
       <c r="E18" s="25">
         <f>lc_detailed!BA18/$R$2</f>
-        <v>-0.27152195912051358</v>
+        <v>-0.37462406116791802</v>
       </c>
       <c r="F18" s="25">
         <f>lc_detailed!BB18/$R$2</f>
-        <v>0</v>
+        <v>-16.656553189681333</v>
       </c>
       <c r="G18" s="25">
         <f>lc_detailed!BC18/$R$2</f>
@@ -11284,42 +11298,42 @@
       </c>
       <c r="M18" s="25">
         <f>lc_detailed!AU18</f>
-        <v>1324.6561559770421</v>
+        <v>582.40746551161544</v>
       </c>
       <c r="N18" s="25">
         <f t="shared" si="0"/>
-        <v>29.049477104759696</v>
+        <v>12.772093541921391</v>
       </c>
       <c r="O18" s="25">
         <f t="shared" si="1"/>
-        <v>29.049477104759696</v>
+        <v>12.772093541921391</v>
       </c>
       <c r="U18" t="str">
-        <v>NCEN_Synthetic_Ethylene_Non_CCS</v>
+        <v>CEN_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V18" s="25">
-        <v>8.5357868210826187</v>
+        <v>13.938062701825016</v>
       </c>
       <c r="W18" s="25">
-        <v>0.78755860289152668</v>
+        <v>0.97334168995599168</v>
       </c>
       <c r="X18" s="25">
-        <v>17.887856831076196</v>
+        <v>11.956605894792975</v>
       </c>
       <c r="Y18" s="25">
-        <v>-0.41244103209752564</v>
+        <v>-0.45791675621609745</v>
       </c>
       <c r="Z18" s="25">
-        <v>0</v>
+        <v>-19.117148637439108</v>
       </c>
       <c r="AA18" s="25">
-        <v>4.2600965636830308</v>
+        <v>4.705568157602146</v>
       </c>
       <c r="AB18" s="25">
-        <v>2.3433206377337097</v>
+        <v>2.5867547372464941</v>
       </c>
       <c r="AC18" s="25">
-        <v>-0.99370798227543866</v>
+        <v>-1.074340016786842</v>
       </c>
       <c r="AD18" s="25">
         <v>0</v>
@@ -11331,13 +11345,13 @@
         <v>0</v>
       </c>
       <c r="AG18" s="25">
-        <v>1477.8262521594916</v>
+        <v>616.09830635671449</v>
       </c>
       <c r="AH18" s="25">
-        <v>32.408470442094114</v>
+        <v>13.510927770980581</v>
       </c>
       <c r="AI18" s="25">
-        <v>32.408470442094121</v>
+        <v>13.510927770980578</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.2">
@@ -11347,23 +11361,23 @@
       </c>
       <c r="B19" s="25">
         <f>lc_detailed!AX19/$R$2</f>
-        <v>7.4502256381379315</v>
+        <v>9.4882025816090128</v>
       </c>
       <c r="C19" s="25">
         <f>lc_detailed!AY19/$R$2</f>
-        <v>0.71718601957415662</v>
+        <v>0.7145470765922991</v>
       </c>
       <c r="D19" s="25">
         <f>lc_detailed!AZ19/$R$2</f>
-        <v>17.990386976449198</v>
+        <v>13.380980564926391</v>
       </c>
       <c r="E19" s="25">
         <f>lc_detailed!BA19/$R$2</f>
-        <v>-0.37354974789689666</v>
+        <v>-0.31410156292172908</v>
       </c>
       <c r="F19" s="25">
         <f>lc_detailed!BB19/$R$2</f>
-        <v>0</v>
+        <v>-18.607641472923653</v>
       </c>
       <c r="G19" s="25">
         <f>lc_detailed!BC19/$R$2</f>
@@ -11391,42 +11405,42 @@
       </c>
       <c r="M19" s="25">
         <f>lc_detailed!AU19</f>
-        <v>1431.5644896064996</v>
+        <v>468.38935613291721</v>
       </c>
       <c r="N19" s="25">
         <f t="shared" si="0"/>
-        <v>31.393958105405691</v>
+        <v>10.271696406423622</v>
       </c>
       <c r="O19" s="25">
         <f t="shared" si="1"/>
-        <v>31.393958105405694</v>
+        <v>10.271696406423624</v>
       </c>
       <c r="U19" t="str">
-        <v>MIDAT_Synthetic_Ethylene_CCS_90</v>
+        <v>NCEN_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V19" s="25">
-        <v>11.469127996236775</v>
+        <v>13.845141117697725</v>
       </c>
       <c r="W19" s="25">
-        <v>0.98447350298327296</v>
+        <v>0.77862652394618448</v>
       </c>
       <c r="X19" s="25">
-        <v>14.644118880244196</v>
+        <v>13.034938890657648</v>
       </c>
       <c r="Y19" s="25">
-        <v>-0.36998997706758924</v>
+        <v>-0.45509041875365486</v>
       </c>
       <c r="Z19" s="25">
-        <v>0</v>
+        <v>-19.09467193131994</v>
       </c>
       <c r="AA19" s="25">
-        <v>4.705568157602146</v>
+        <v>4.2600965636830308</v>
       </c>
       <c r="AB19" s="25">
-        <v>2.5867547372464941</v>
+        <v>2.3433206377337097</v>
       </c>
       <c r="AC19" s="25">
-        <v>-1.074340016786842</v>
+        <v>-0.99370798227543866</v>
       </c>
       <c r="AD19" s="25">
         <v>0</v>
@@ -11438,13 +11452,13 @@
         <v>0</v>
       </c>
       <c r="AG19" s="25">
-        <v>1502.3245255889051</v>
+        <v>625.57059510243857</v>
       </c>
       <c r="AH19" s="25">
-        <v>32.945713280458442</v>
+        <v>13.718653401369266</v>
       </c>
       <c r="AI19" s="25">
-        <v>32.945713280458449</v>
+        <v>13.718653401369265</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.2">
@@ -11454,23 +11468,23 @@
       </c>
       <c r="B20" s="25">
         <f>lc_detailed!AX20/$R$2</f>
-        <v>7.4502256408836214</v>
+        <v>9.488202585105773</v>
       </c>
       <c r="C20" s="25">
         <f>lc_detailed!AY20/$R$2</f>
-        <v>0.91415769006200642</v>
+        <v>0.91079397415754326</v>
       </c>
       <c r="D20" s="25">
         <f>lc_detailed!AZ20/$R$2</f>
-        <v>16.527022438451514</v>
+        <v>12.292551924231621</v>
       </c>
       <c r="E20" s="25">
         <f>lc_detailed!BA20/$R$2</f>
-        <v>-0.37354974807801505</v>
+        <v>-0.31410156307402354</v>
       </c>
       <c r="F20" s="25">
         <f>lc_detailed!BB20/$R$2</f>
-        <v>0</v>
+        <v>-18.607641480632839</v>
       </c>
       <c r="G20" s="25">
         <f>lc_detailed!BC20/$R$2</f>
@@ -11498,33 +11512,33 @@
       </c>
       <c r="M20" s="25">
         <f>lc_detailed!AU20</f>
-        <v>1401.55425381177</v>
+        <v>455.44314729395421</v>
       </c>
       <c r="N20" s="25">
         <f t="shared" si="0"/>
-        <v>30.735838899380919</v>
+        <v>9.9877883178498728</v>
       </c>
       <c r="O20" s="25">
         <f t="shared" si="1"/>
-        <v>30.735838899380923</v>
+        <v>9.9877883178498745</v>
       </c>
       <c r="U20" t="str">
-        <v>MIDAT_Synthetic_Ethylene_Non_CCS</v>
+        <v>CEN_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V20" s="25">
-        <v>11.46912799200997</v>
+        <v>13.938062696688313</v>
       </c>
       <c r="W20" s="25">
-        <v>0.77235102943006417</v>
+        <v>0.76361776517765922</v>
       </c>
       <c r="X20" s="25">
-        <v>15.940764076883717</v>
+        <v>13.015288614346023</v>
       </c>
       <c r="Y20" s="25">
-        <v>-0.3699899768881969</v>
+        <v>-0.45791675599407311</v>
       </c>
       <c r="Z20" s="25">
-        <v>0</v>
+        <v>-19.117148629518834</v>
       </c>
       <c r="AA20" s="25">
         <v>4.2600965636830308</v>
@@ -11545,13 +11559,13 @@
         <v>0</v>
       </c>
       <c r="AG20" s="25">
-        <v>1524.0414827303043</v>
+        <v>627.07354868872187</v>
       </c>
       <c r="AH20" s="25">
-        <v>33.421962340576847</v>
+        <v>13.751612909840391</v>
       </c>
       <c r="AI20" s="25">
-        <v>33.421962340576862</v>
+        <v>13.751612909840391</v>
       </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.2">
@@ -13802,7 +13816,7 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q1" s="24" t="s">
         <v>14</v>
@@ -13852,19 +13866,19 @@
         <v>55</v>
       </c>
       <c r="N2" s="23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O2" s="23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R2">
         <v>45.6</v>
       </c>
       <c r="S2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>53</v>
@@ -13906,10 +13920,10 @@
         <v>55</v>
       </c>
       <c r="AH2" s="23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AI2" s="23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
@@ -13919,23 +13933,23 @@
       </c>
       <c r="B3" s="25">
         <f>lc_detailed!AX3/$R$2</f>
-        <v>7.4790582687141676</v>
+        <v>7.6246838779146486</v>
       </c>
       <c r="C3" s="25">
         <f>lc_detailed!AY3/$R$2</f>
-        <v>0.74873960070734991</v>
+        <v>0.72286564786234198</v>
       </c>
       <c r="D3" s="25">
         <f>lc_detailed!AZ3/$R$2</f>
-        <v>17.888005451470899</v>
+        <v>13.03615561171002</v>
       </c>
       <c r="E3" s="25">
         <f>lc_detailed!BA3/$R$2</f>
-        <v>-0.36969322532493909</v>
+        <v>-0.24235512400049214</v>
       </c>
       <c r="F3" s="25">
         <f>lc_detailed!BB3/$R$2</f>
-        <v>0</v>
+        <v>-18.880719992760021</v>
       </c>
       <c r="G3" s="25">
         <f>lc_detailed!BC3/$R$2</f>
@@ -13955,7 +13969,7 @@
       </c>
       <c r="K3" s="25">
         <f>lc_detailed!BH3/$R$2</f>
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="L3" s="25">
         <f>lc_detailed!BI3</f>
@@ -13963,34 +13977,34 @@
       </c>
       <c r="M3" s="25">
         <f>lc_detailed!AR3</f>
-        <v>1392.9294985009017</v>
+        <v>331.38329840666216</v>
       </c>
       <c r="N3" s="25">
-        <f>M3/$R$2</f>
-        <v>30.546699528528546</v>
+        <f t="shared" ref="N3:N20" si="0">M3/$R$2</f>
+        <v>7.2671775966373282</v>
       </c>
       <c r="O3" s="25">
-        <f>SUM(B3:K3)</f>
-        <v>30.546699528528546</v>
-      </c>
-      <c r="U3" t="str" cm="1">
+        <f t="shared" ref="O3:O20" si="1">SUM(B3:K3)</f>
+        <v>7.2671775966373291</v>
+      </c>
+      <c r="U3" t="str">
         <f t="array" ref="U3:AI65">_xlfn._xlws.SORT(A3:O65, 13, 1)</f>
-        <v>CA_Synthetic_Ethylene_CCS_90</v>
+        <v>NE_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V3">
-        <v>5.2904756031087681</v>
+        <v>9.6475746543016925</v>
       </c>
       <c r="W3">
-        <v>0.87613997951393885</v>
+        <v>0.90076283399899526</v>
       </c>
       <c r="X3">
-        <v>16.655984750796321</v>
+        <v>8.932452358341326</v>
       </c>
       <c r="Y3">
-        <v>-0.26046229524938447</v>
+        <v>-0.27269292721660704</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>-22.22384828913545</v>
       </c>
       <c r="AA3">
         <v>4.705568157602146</v>
@@ -14005,19 +14019,19 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="AF3">
         <v>-0.40472550988742861</v>
       </c>
       <c r="AG3">
-        <v>1272.3497268887545</v>
+        <v>116.18586167353027</v>
       </c>
       <c r="AH3">
-        <v>27.902406291420053</v>
+        <v>2.5479355630160145</v>
       </c>
       <c r="AI3">
-        <v>27.902406291420057</v>
+        <v>2.5479355630160119</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.2">
@@ -14027,23 +14041,23 @@
       </c>
       <c r="B4" s="25">
         <f>lc_detailed!AX4/$R$2</f>
-        <v>7.4790582714704827</v>
+        <v>7.624683880724632</v>
       </c>
       <c r="C4" s="25">
         <f>lc_detailed!AY4/$R$2</f>
-        <v>0.95437730959534783</v>
+        <v>0.9213972007811656</v>
       </c>
       <c r="D4" s="25">
         <f>lc_detailed!AZ4/$R$2</f>
-        <v>16.432968777303802</v>
+        <v>11.975775539898962</v>
       </c>
       <c r="E4" s="25">
         <f>lc_detailed!BA4/$R$2</f>
-        <v>-0.36969322550418754</v>
+        <v>-0.24235512411799978</v>
       </c>
       <c r="F4" s="25">
         <f>lc_detailed!BB4/$R$2</f>
-        <v>0</v>
+        <v>-18.880720000582343</v>
       </c>
       <c r="G4" s="25">
         <f>lc_detailed!BC4/$R$2</f>
@@ -14063,7 +14077,7 @@
       </c>
       <c r="K4" s="25">
         <f>lc_detailed!BH4/$R$2</f>
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="L4" s="25">
         <f>lc_detailed!BI4</f>
@@ -14071,60 +14085,60 @@
       </c>
       <c r="M4" s="25">
         <f>lc_detailed!AR4</f>
-        <v>1360.5662600068829</v>
+        <v>317.48856038202962</v>
       </c>
       <c r="N4" s="25">
-        <f>M4/$R$2</f>
-        <v>29.836979386115853</v>
+        <f t="shared" si="0"/>
+        <v>6.9624684294304737</v>
       </c>
       <c r="O4" s="25">
-        <f>SUM(B4:K4)</f>
-        <v>29.836979386115864</v>
+        <f t="shared" si="1"/>
+        <v>6.9624684294304737</v>
       </c>
       <c r="U4" t="str">
-        <v>NW_Synthetic_Ethylene_CCS_90</v>
+        <v>NE_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V4">
-        <v>5.443409297530768</v>
+        <v>9.6475746507461988</v>
       </c>
       <c r="W4">
-        <v>0.87062621674921659</v>
+        <v>0.7066773254975931</v>
       </c>
       <c r="X4">
-        <v>16.788980671538429</v>
+        <v>9.7233651841228586</v>
       </c>
       <c r="Y4">
-        <v>-0.27152195912051358</v>
+        <v>-0.27269292708438991</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>-22.223848279928063</v>
       </c>
       <c r="AA4">
-        <v>4.705568157602146</v>
+        <v>4.2600965636830308</v>
       </c>
       <c r="AB4">
-        <v>2.5867547372464941</v>
+        <v>2.3433206377337097</v>
       </c>
       <c r="AC4">
-        <v>-1.074340016786842</v>
+        <v>-0.99370798227543866</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>-0.87771462481138307</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="AF4">
-        <v>-0.40472550988742861</v>
+        <v>-0.37309554696342861</v>
       </c>
       <c r="AG4">
-        <v>1284.6323690856429</v>
+        <v>117.99563293448526</v>
       </c>
       <c r="AH4">
-        <v>28.17176247994831</v>
+        <v>2.5876235292650276</v>
       </c>
       <c r="AI4">
-        <v>28.171762479948313</v>
+        <v>2.5876235292650285</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
@@ -14134,23 +14148,23 @@
       </c>
       <c r="B5" s="25">
         <f>lc_detailed!AX5/$R$2</f>
-        <v>11.46912799200997</v>
+        <v>7.9023386587990325</v>
       </c>
       <c r="C5" s="25">
         <f>lc_detailed!AY5/$R$2</f>
-        <v>0.77235102943006417</v>
+        <v>0.73083594500965676</v>
       </c>
       <c r="D5" s="25">
         <f>lc_detailed!AZ5/$R$2</f>
-        <v>15.940764076883717</v>
+        <v>11.091536587122279</v>
       </c>
       <c r="E5" s="25">
         <f>lc_detailed!BA5/$R$2</f>
-        <v>-0.3699899768881969</v>
+        <v>-0.16457133828177642</v>
       </c>
       <c r="F5" s="25">
         <f>lc_detailed!BB5/$R$2</f>
-        <v>0</v>
+        <v>-20.74755519690644</v>
       </c>
       <c r="G5" s="25">
         <f>lc_detailed!BC5/$R$2</f>
@@ -14170,7 +14184,7 @@
       </c>
       <c r="K5" s="25">
         <f>lc_detailed!BH5/$R$2</f>
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="L5" s="25">
         <f>lc_detailed!BI5</f>
@@ -14178,60 +14192,60 @@
       </c>
       <c r="M5" s="25">
         <f>lc_detailed!AR5</f>
-        <v>1487.1456204804856</v>
+        <v>174.15242976340338</v>
       </c>
       <c r="N5" s="25">
-        <f t="shared" ref="N5:N29" si="0">M5/$R$2</f>
-        <v>32.612842554396615</v>
+        <f t="shared" si="0"/>
+        <v>3.8191322316535827</v>
       </c>
       <c r="O5" s="25">
-        <f t="shared" ref="O5:O29" si="1">SUM(B5:K5)</f>
-        <v>32.612842554396622</v>
+        <f t="shared" si="1"/>
+        <v>3.819132231653581</v>
       </c>
       <c r="U5" t="str">
-        <v>CA_Synthetic_Ethylene_Non_CCS</v>
+        <v>MIDAT_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V5">
-        <v>5.2904756011590282</v>
+        <v>7.9023386617113429</v>
       </c>
       <c r="W5">
-        <v>0.68735990664232594</v>
+        <v>0.93155650147922364</v>
       </c>
       <c r="X5">
-        <v>18.130768095498382</v>
+        <v>10.189334687032737</v>
       </c>
       <c r="Y5">
-        <v>-0.26046229512309738</v>
+        <v>-0.16457133836157006</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>-20.747555205502195</v>
       </c>
       <c r="AA5">
-        <v>4.2600965636830308</v>
+        <v>4.705568157602146</v>
       </c>
       <c r="AB5">
-        <v>2.3433206377337097</v>
+        <v>2.5867547372464941</v>
       </c>
       <c r="AC5">
-        <v>-0.99370798227543866</v>
+        <v>-1.074340016786842</v>
       </c>
       <c r="AD5">
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>-0.80911978618023661</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="AF5">
-        <v>-0.37309554696342861</v>
+        <v>-0.40472550988742861</v>
       </c>
       <c r="AG5">
-        <v>1306.3821217958791</v>
+        <v>167.57043490230325</v>
       </c>
       <c r="AH5">
-        <v>28.648730741137701</v>
+        <v>3.6747902390855973</v>
       </c>
       <c r="AI5">
-        <v>28.648730741137701</v>
+        <v>3.6747902390855964</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.2">
@@ -14241,23 +14255,23 @@
       </c>
       <c r="B6" s="25">
         <f>lc_detailed!AX6/$R$2</f>
-        <v>11.469127996236775</v>
+        <v>7.9023386617113429</v>
       </c>
       <c r="C6" s="25">
         <f>lc_detailed!AY6/$R$2</f>
-        <v>0.98447350298327296</v>
+        <v>0.93155650147922364</v>
       </c>
       <c r="D6" s="25">
         <f>lc_detailed!AZ6/$R$2</f>
-        <v>14.644118880244196</v>
+        <v>10.189334687032737</v>
       </c>
       <c r="E6" s="25">
         <f>lc_detailed!BA6/$R$2</f>
-        <v>-0.36998997706758924</v>
+        <v>-0.16457133836157006</v>
       </c>
       <c r="F6" s="25">
         <f>lc_detailed!BB6/$R$2</f>
-        <v>0</v>
+        <v>-20.747555205502195</v>
       </c>
       <c r="G6" s="25">
         <f>lc_detailed!BC6/$R$2</f>
@@ -14277,7 +14291,7 @@
       </c>
       <c r="K6" s="25">
         <f>lc_detailed!BH6/$R$2</f>
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="L6" s="25">
         <f>lc_detailed!BI6</f>
@@ -14285,33 +14299,33 @@
       </c>
       <c r="M6" s="25">
         <f>lc_detailed!AR6</f>
-        <v>1462.3007386975059</v>
+        <v>167.57043490230325</v>
       </c>
       <c r="N6" s="25">
         <f t="shared" si="0"/>
-        <v>32.06799865564706</v>
+        <v>3.6747902390855973</v>
       </c>
       <c r="O6" s="25">
         <f t="shared" si="1"/>
-        <v>32.067998655647067</v>
+        <v>3.6747902390855964</v>
       </c>
       <c r="U6" t="str">
-        <v>NW_Synthetic_Ethylene_Non_CCS</v>
+        <v>MIDAT_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V6">
-        <v>5.4434092955246678</v>
+        <v>7.9023386587990325</v>
       </c>
       <c r="W6">
-        <v>0.68303418295909657</v>
+        <v>0.73083594500965676</v>
       </c>
       <c r="X6">
-        <v>18.275539973757166</v>
+        <v>11.091536587122279</v>
       </c>
       <c r="Y6">
-        <v>-0.27152195898886416</v>
+        <v>-0.16457133828177642</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>-20.74755519690644</v>
       </c>
       <c r="AA6">
         <v>4.2600965636830308</v>
@@ -14326,19 +14340,19 @@
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="AF6">
         <v>-0.37309554696342861</v>
       </c>
       <c r="AG6">
-        <v>1319.2559222353186</v>
+        <v>174.15242976340338</v>
       </c>
       <c r="AH6">
-        <v>28.931050926213128</v>
+        <v>3.8191322316535827</v>
       </c>
       <c r="AI6">
-        <v>28.931050926213135</v>
+        <v>3.819132231653581</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
@@ -14348,23 +14362,23 @@
       </c>
       <c r="B7" s="25">
         <f>lc_detailed!AX7/$R$2</f>
-        <v>10.596217819504876</v>
+        <v>9.6475746507461988</v>
       </c>
       <c r="C7" s="25">
         <f>lc_detailed!AY7/$R$2</f>
-        <v>0.7459629592606114</v>
+        <v>0.7066773254975931</v>
       </c>
       <c r="D7" s="25">
         <f>lc_detailed!AZ7/$R$2</f>
-        <v>14.590879921906732</v>
+        <v>9.7233651841228586</v>
       </c>
       <c r="E7" s="25">
         <f>lc_detailed!BA7/$R$2</f>
-        <v>-0.33797477121342173</v>
+        <v>-0.27269292708438991</v>
       </c>
       <c r="F7" s="25">
         <f>lc_detailed!BB7/$R$2</f>
-        <v>0</v>
+        <v>-22.223848279928063</v>
       </c>
       <c r="G7" s="25">
         <f>lc_detailed!BC7/$R$2</f>
@@ -14384,7 +14398,7 @@
       </c>
       <c r="K7" s="25">
         <f>lc_detailed!BH7/$R$2</f>
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="L7" s="25">
         <f>lc_detailed!BI7</f>
@@ -14392,33 +14406,33 @@
       </c>
       <c r="M7" s="25">
         <f>lc_detailed!AR7</f>
-        <v>1386.0427965263459</v>
+        <v>117.99563293448526</v>
       </c>
       <c r="N7" s="25">
         <f t="shared" si="0"/>
-        <v>30.395675362419865</v>
+        <v>2.5876235292650276</v>
       </c>
       <c r="O7" s="25">
         <f t="shared" si="1"/>
-        <v>30.395675362419862</v>
+        <v>2.5876235292650285</v>
       </c>
       <c r="U7" t="str">
         <v>SE_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V7">
-        <v>7.4790582714704827</v>
+        <v>7.624683880724632</v>
       </c>
       <c r="W7">
-        <v>0.95437730959534783</v>
+        <v>0.9213972007811656</v>
       </c>
       <c r="X7">
-        <v>16.432968777303802</v>
+        <v>11.975775539898962</v>
       </c>
       <c r="Y7">
-        <v>-0.36969322550418754</v>
+        <v>-0.24235512411799978</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>-18.880720000582343</v>
       </c>
       <c r="AA7">
         <v>4.705568157602146</v>
@@ -14433,19 +14447,19 @@
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="AF7">
         <v>-0.40472550988742861</v>
       </c>
       <c r="AG7">
-        <v>1360.5662600068829</v>
+        <v>317.48856038202962</v>
       </c>
       <c r="AH7">
-        <v>29.836979386115853</v>
+        <v>6.9624684294304737</v>
       </c>
       <c r="AI7">
-        <v>29.836979386115864</v>
+        <v>6.9624684294304737</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
@@ -14455,23 +14469,23 @@
       </c>
       <c r="B8" s="25">
         <f>lc_detailed!AX8/$R$2</f>
-        <v>10.596217823409981</v>
+        <v>9.6475746543016925</v>
       </c>
       <c r="C8" s="25">
         <f>lc_detailed!AY8/$R$2</f>
-        <v>0.95083807700881717</v>
+        <v>0.90076283399899526</v>
       </c>
       <c r="D8" s="25">
         <f>lc_detailed!AZ8/$R$2</f>
-        <v>13.404036287923102</v>
+        <v>8.932452358341326</v>
       </c>
       <c r="E8" s="25">
         <f>lc_detailed!BA8/$R$2</f>
-        <v>-0.33797477137729132</v>
+        <v>-0.27269292721660704</v>
       </c>
       <c r="F8" s="25">
         <f>lc_detailed!BB8/$R$2</f>
-        <v>0</v>
+        <v>-22.22384828913545</v>
       </c>
       <c r="G8" s="25">
         <f>lc_detailed!BC8/$R$2</f>
@@ -14491,7 +14505,7 @@
       </c>
       <c r="K8" s="25">
         <f>lc_detailed!BH8/$R$2</f>
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="L8" s="25">
         <f>lc_detailed!BI8</f>
@@ -14499,60 +14513,60 @@
       </c>
       <c r="M8" s="25">
         <f>lc_detailed!AR8</f>
-        <v>1365.8743865618048</v>
+        <v>116.18586167353027</v>
       </c>
       <c r="N8" s="25">
         <f t="shared" si="0"/>
-        <v>29.953385670215017</v>
+        <v>2.5479355630160145</v>
       </c>
       <c r="O8" s="25">
         <f t="shared" si="1"/>
-        <v>29.953385670215027</v>
+        <v>2.5479355630160119</v>
       </c>
       <c r="U8" t="str">
-        <v>SW_Synthetic_Ethylene_CCS_90</v>
+        <v>SE_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V8">
-        <v>7.4502256408836214</v>
+        <v>7.6246838779146486</v>
       </c>
       <c r="W8">
-        <v>0.91415769006200642</v>
+        <v>0.72286564786234198</v>
       </c>
       <c r="X8">
-        <v>16.527022438451514</v>
+        <v>13.03615561171002</v>
       </c>
       <c r="Y8">
-        <v>-0.37354974807801505</v>
+        <v>-0.24235512400049214</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>-18.880719992760021</v>
       </c>
       <c r="AA8">
-        <v>4.705568157602146</v>
+        <v>4.2600965636830308</v>
       </c>
       <c r="AB8">
-        <v>2.5867547372464941</v>
+        <v>2.3433206377337097</v>
       </c>
       <c r="AC8">
-        <v>-1.074340016786842</v>
+        <v>-0.99370798227543866</v>
       </c>
       <c r="AD8">
         <v>0</v>
       </c>
       <c r="AE8">
-        <v>-0.87771462481138307</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="AF8">
-        <v>-0.40472550988742861</v>
+        <v>-0.37309554696342861</v>
       </c>
       <c r="AG8">
-        <v>1361.5304669203708</v>
+        <v>331.38329840666216</v>
       </c>
       <c r="AH8">
-        <v>29.858124274569533</v>
+        <v>7.2671775966373282</v>
       </c>
       <c r="AI8">
-        <v>29.858124274569541</v>
+        <v>7.2671775966373291</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
@@ -14562,23 +14576,23 @@
       </c>
       <c r="B9" s="25">
         <f>lc_detailed!AX9/$R$2</f>
-        <v>5.2904756011590282</v>
+        <v>8.882221111503009</v>
       </c>
       <c r="C9" s="25">
         <f>lc_detailed!AY9/$R$2</f>
-        <v>0.68735990664232594</v>
+        <v>0.68916970159805557</v>
       </c>
       <c r="D9" s="25">
         <f>lc_detailed!AZ9/$R$2</f>
-        <v>18.130768095498382</v>
+        <v>14.948219637620451</v>
       </c>
       <c r="E9" s="25">
         <f>lc_detailed!BA9/$R$2</f>
-        <v>-0.26046229512309738</v>
+        <v>-0.39450878949359602</v>
       </c>
       <c r="F9" s="25">
         <f>lc_detailed!BB9/$R$2</f>
-        <v>0</v>
+        <v>-17.122469805914761</v>
       </c>
       <c r="G9" s="25">
         <f>lc_detailed!BC9/$R$2</f>
@@ -14598,7 +14612,7 @@
       </c>
       <c r="K9" s="25">
         <f>lc_detailed!BH9/$R$2</f>
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="L9" s="25">
         <f>lc_detailed!BI9</f>
@@ -14606,33 +14620,33 @@
       </c>
       <c r="M9" s="25">
         <f>lc_detailed!AR9</f>
-        <v>1306.3821217958791</v>
+        <v>547.61858206381407</v>
       </c>
       <c r="N9" s="25">
         <f t="shared" si="0"/>
-        <v>28.648730741137701</v>
+        <v>12.009179431223993</v>
       </c>
       <c r="O9" s="25">
         <f t="shared" si="1"/>
-        <v>28.648730741137701</v>
+        <v>12.009179431223989</v>
       </c>
       <c r="U9" t="str">
-        <v>NE_Synthetic_Ethylene_CCS_90</v>
+        <v>TX_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V9">
-        <v>10.596217823409981</v>
+        <v>7.9189911503517845</v>
       </c>
       <c r="W9">
-        <v>0.95083807700881717</v>
+        <v>0.92536315857176465</v>
       </c>
       <c r="X9">
-        <v>13.404036287923102</v>
+        <v>12.168959138351944</v>
       </c>
       <c r="Y9">
-        <v>-0.33797477137729132</v>
+        <v>-0.26177559818929191</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>-18.689851672712397</v>
       </c>
       <c r="AA9">
         <v>4.705568157602146</v>
@@ -14647,19 +14661,19 @@
         <v>0</v>
       </c>
       <c r="AE9">
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="AF9">
         <v>-0.40472550988742861</v>
       </c>
       <c r="AG9">
-        <v>1365.8743865618048</v>
+        <v>347.7170137749539</v>
       </c>
       <c r="AH9">
-        <v>29.953385670215017</v>
+        <v>7.6253731090998658</v>
       </c>
       <c r="AI9">
-        <v>29.953385670215027</v>
+        <v>7.6253731090998622</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.2">
@@ -14669,23 +14683,23 @@
       </c>
       <c r="B10" s="25">
         <f>lc_detailed!AX10/$R$2</f>
-        <v>5.2904756031087681</v>
+        <v>8.8822211147764421</v>
       </c>
       <c r="C10" s="25">
         <f>lc_detailed!AY10/$R$2</f>
-        <v>0.87613997951393885</v>
+        <v>0.87844682589836531</v>
       </c>
       <c r="D10" s="25">
         <f>lc_detailed!AZ10/$R$2</f>
-        <v>16.655984750796321</v>
+        <v>13.73230946556412</v>
       </c>
       <c r="E10" s="25">
         <f>lc_detailed!BA10/$R$2</f>
-        <v>-0.26046229524938447</v>
+        <v>-0.39450878968487657</v>
       </c>
       <c r="F10" s="25">
         <f>lc_detailed!BB10/$R$2</f>
-        <v>0</v>
+        <v>-17.122469813008635</v>
       </c>
       <c r="G10" s="25">
         <f>lc_detailed!BC10/$R$2</f>
@@ -14705,7 +14719,7 @@
       </c>
       <c r="K10" s="25">
         <f>lc_detailed!BH10/$R$2</f>
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="L10" s="25">
         <f>lc_detailed!BI10</f>
@@ -14713,33 +14727,33 @@
       </c>
       <c r="M10" s="25">
         <f>lc_detailed!AR10</f>
-        <v>1272.3497268887545</v>
+        <v>526.209669573979</v>
       </c>
       <c r="N10" s="25">
         <f t="shared" si="0"/>
-        <v>27.902406291420053</v>
+        <v>11.539685736271469</v>
       </c>
       <c r="O10" s="25">
         <f t="shared" si="1"/>
-        <v>27.902406291420057</v>
+        <v>11.539685736271474</v>
       </c>
       <c r="U10" t="str">
-        <v>NE_Synthetic_Ethylene_Non_CCS</v>
+        <v>TX_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V10">
-        <v>10.596217819504876</v>
+        <v>7.9189911474333377</v>
       </c>
       <c r="W10">
-        <v>0.7459629592606114</v>
+        <v>0.72597706891426772</v>
       </c>
       <c r="X10">
-        <v>14.590879921906732</v>
+        <v>13.24644441034965</v>
       </c>
       <c r="Y10">
-        <v>-0.33797477121342173</v>
+        <v>-0.26177559806236805</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>-18.689851664969151</v>
       </c>
       <c r="AA10">
         <v>4.2600965636830308</v>
@@ -14754,19 +14768,19 @@
         <v>0</v>
       </c>
       <c r="AE10">
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="AF10">
         <v>-0.37309554696342861</v>
       </c>
       <c r="AG10">
-        <v>1386.0427965263459</v>
+        <v>362.35278204469142</v>
       </c>
       <c r="AH10">
-        <v>30.395675362419865</v>
+        <v>7.9463329395765658</v>
       </c>
       <c r="AI10">
-        <v>30.395675362419862</v>
+        <v>7.9463329395765649</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.2">
@@ -14776,23 +14790,23 @@
       </c>
       <c r="B11" s="25">
         <f>lc_detailed!AX11/$R$2</f>
-        <v>8.5357868210826187</v>
+        <v>13.845141117697725</v>
       </c>
       <c r="C11" s="25">
         <f>lc_detailed!AY11/$R$2</f>
-        <v>0.78755860289152668</v>
+        <v>0.77862652394618448</v>
       </c>
       <c r="D11" s="25">
         <f>lc_detailed!AZ11/$R$2</f>
-        <v>17.887856831076196</v>
+        <v>13.034938890657648</v>
       </c>
       <c r="E11" s="25">
         <f>lc_detailed!BA11/$R$2</f>
-        <v>-0.41244103209752564</v>
+        <v>-0.45509041875365486</v>
       </c>
       <c r="F11" s="25">
         <f>lc_detailed!BB11/$R$2</f>
-        <v>0</v>
+        <v>-19.09467193131994</v>
       </c>
       <c r="G11" s="25">
         <f>lc_detailed!BC11/$R$2</f>
@@ -14812,7 +14826,7 @@
       </c>
       <c r="K11" s="25">
         <f>lc_detailed!BH11/$R$2</f>
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="L11" s="25">
         <f>lc_detailed!BI11</f>
@@ -14820,60 +14834,60 @@
       </c>
       <c r="M11" s="25">
         <f>lc_detailed!AR11</f>
-        <v>1440.9303899096728</v>
+        <v>598.06642417112914</v>
       </c>
       <c r="N11" s="25">
         <f t="shared" si="0"/>
-        <v>31.599350655913877</v>
+        <v>13.115491758138797</v>
       </c>
       <c r="O11" s="25">
         <f t="shared" si="1"/>
-        <v>31.599350655913884</v>
+        <v>13.115491758138793</v>
       </c>
       <c r="U11" t="str">
-        <v>SE_Synthetic_Ethylene_Non_CCS</v>
+        <v>SW_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V11">
-        <v>7.4790582687141676</v>
+        <v>9.488202585105773</v>
       </c>
       <c r="W11">
-        <v>0.74873960070734991</v>
+        <v>0.91079397415754326</v>
       </c>
       <c r="X11">
-        <v>17.888005451470899</v>
+        <v>12.292551924231621</v>
       </c>
       <c r="Y11">
-        <v>-0.36969322532493909</v>
+        <v>-0.31410156307402354</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>-18.607641480632839</v>
       </c>
       <c r="AA11">
-        <v>4.2600965636830308</v>
+        <v>4.705568157602146</v>
       </c>
       <c r="AB11">
-        <v>2.3433206377337097</v>
+        <v>2.5867547372464941</v>
       </c>
       <c r="AC11">
-        <v>-0.99370798227543866</v>
+        <v>-1.074340016786842</v>
       </c>
       <c r="AD11">
         <v>0</v>
       </c>
       <c r="AE11">
-        <v>-0.80911978618023661</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="AF11">
-        <v>-0.37309554696342861</v>
+        <v>-0.40472550988742861</v>
       </c>
       <c r="AG11">
-        <v>1392.9294985009017</v>
+        <v>425.60725218664447</v>
       </c>
       <c r="AH11">
-        <v>30.546699528528546</v>
+        <v>9.333492372514133</v>
       </c>
       <c r="AI11">
-        <v>30.546699528528546</v>
+        <v>9.3334923725141348</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.2">
@@ -14883,23 +14897,23 @@
       </c>
       <c r="B12" s="25">
         <f>lc_detailed!AX12/$R$2</f>
-        <v>8.5357868242283779</v>
+        <v>13.845141122800179</v>
       </c>
       <c r="C12" s="25">
         <f>lc_detailed!AY12/$R$2</f>
-        <v>1.0038577629207903</v>
+        <v>0.99247253170703364</v>
       </c>
       <c r="D12" s="25">
         <f>lc_detailed!AZ12/$R$2</f>
-        <v>16.4328322459106</v>
+        <v>11.974657788726613</v>
       </c>
       <c r="E12" s="25">
         <f>lc_detailed!BA12/$R$2</f>
-        <v>-0.41244103229750073</v>
+        <v>-0.45509041897430885</v>
       </c>
       <c r="F12" s="25">
         <f>lc_detailed!BB12/$R$2</f>
-        <v>0</v>
+        <v>-19.094671939230906</v>
       </c>
       <c r="G12" s="25">
         <f>lc_detailed!BC12/$R$2</f>
@@ -14919,7 +14933,7 @@
       </c>
       <c r="K12" s="25">
         <f>lc_detailed!BH12/$R$2</f>
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="L12" s="25">
         <f>lc_detailed!BI12</f>
@@ -14927,33 +14941,33 @@
       </c>
       <c r="M12" s="25">
         <f>lc_detailed!AR12</f>
-        <v>1409.0538648629781</v>
+        <v>584.8745384096128</v>
       </c>
       <c r="N12" s="25">
         <f t="shared" si="0"/>
-        <v>30.900304054012675</v>
+        <v>12.826196017754667</v>
       </c>
       <c r="O12" s="25">
         <f t="shared" si="1"/>
-        <v>30.900304054012679</v>
+        <v>12.82619601775467</v>
       </c>
       <c r="U12" t="str">
         <v>SW_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V12">
-        <v>7.4502256381379315</v>
+        <v>9.4882025816090128</v>
       </c>
       <c r="W12">
-        <v>0.71718601957415662</v>
+        <v>0.7145470765922991</v>
       </c>
       <c r="X12">
-        <v>17.990386976449198</v>
+        <v>13.380980564926391</v>
       </c>
       <c r="Y12">
-        <v>-0.37354974789689666</v>
+        <v>-0.31410156292172908</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>-18.607641472923653</v>
       </c>
       <c r="AA12">
         <v>4.2600965636830308</v>
@@ -14968,19 +14982,19 @@
         <v>0</v>
       </c>
       <c r="AE12">
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="AF12">
         <v>-0.37309554696342861</v>
       </c>
       <c r="AG12">
-        <v>1394.6686273566809</v>
+        <v>440.88518520160773</v>
       </c>
       <c r="AH12">
-        <v>30.584838319225458</v>
+        <v>9.6685347631931524</v>
       </c>
       <c r="AI12">
-        <v>30.584838319225458</v>
+        <v>9.6685347631931524</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
@@ -14990,23 +15004,23 @@
       </c>
       <c r="B13" s="25">
         <f>lc_detailed!AX13/$R$2</f>
-        <v>8.3396571607981951</v>
+        <v>13.938062696688313</v>
       </c>
       <c r="C13" s="25">
         <f>lc_detailed!AY13/$R$2</f>
-        <v>0.76219353272184187</v>
+        <v>0.76361776517765922</v>
       </c>
       <c r="D13" s="25">
         <f>lc_detailed!AZ13/$R$2</f>
-        <v>17.867352806738438</v>
+        <v>13.015288614346023</v>
       </c>
       <c r="E13" s="25">
         <f>lc_detailed!BA13/$R$2</f>
-        <v>-0.40627160635588333</v>
+        <v>-0.45791675599407311</v>
       </c>
       <c r="F13" s="25">
         <f>lc_detailed!BB13/$R$2</f>
-        <v>0</v>
+        <v>-19.117148629518834</v>
       </c>
       <c r="G13" s="25">
         <f>lc_detailed!BC13/$R$2</f>
@@ -15026,7 +15040,7 @@
       </c>
       <c r="K13" s="25">
         <f>lc_detailed!BH13/$R$2</f>
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="L13" s="25">
         <f>lc_detailed!BI13</f>
@@ -15034,33 +15048,33 @@
       </c>
       <c r="M13" s="25">
         <f>lc_detailed!AR13</f>
-        <v>1430.1765725049829</v>
+        <v>599.56937775741244</v>
       </c>
       <c r="N13" s="25">
         <f t="shared" si="0"/>
-        <v>31.363521326863658</v>
+        <v>13.148451266609921</v>
       </c>
       <c r="O13" s="25">
         <f t="shared" si="1"/>
-        <v>31.363521326863658</v>
+        <v>13.14845126660992</v>
       </c>
       <c r="U13" t="str">
-        <v>CEN_Synthetic_Ethylene_CCS_90</v>
+        <v>CA_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V13">
-        <v>8.3396571638716726</v>
+        <v>8.8822211147764421</v>
       </c>
       <c r="W13">
-        <v>0.97152629894670461</v>
+        <v>0.87844682589836531</v>
       </c>
       <c r="X13">
-        <v>16.413996049071017</v>
+        <v>13.73230946556412</v>
       </c>
       <c r="Y13">
-        <v>-0.40627160655286715</v>
+        <v>-0.39450878968487657</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>-17.122469813008635</v>
       </c>
       <c r="AA13">
         <v>4.705568157602146</v>
@@ -15075,19 +15089,19 @@
         <v>0</v>
       </c>
       <c r="AE13">
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="AF13">
         <v>-0.40472550988742861</v>
       </c>
       <c r="AG13">
-        <v>1398.0584328315642</v>
+        <v>526.209669573979</v>
       </c>
       <c r="AH13">
-        <v>30.659176158586934</v>
+        <v>11.539685736271469</v>
       </c>
       <c r="AI13">
-        <v>30.659176158586945</v>
+        <v>11.539685736271474</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.2">
@@ -15097,23 +15111,23 @@
       </c>
       <c r="B14" s="25">
         <f>lc_detailed!AX14/$R$2</f>
-        <v>8.3396571638716726</v>
+        <v>13.938062701825016</v>
       </c>
       <c r="C14" s="25">
         <f>lc_detailed!AY14/$R$2</f>
-        <v>0.97152629894670461</v>
+        <v>0.97334168995599168</v>
       </c>
       <c r="D14" s="25">
         <f>lc_detailed!AZ14/$R$2</f>
-        <v>16.413996049071017</v>
+        <v>11.956605894792975</v>
       </c>
       <c r="E14" s="25">
         <f>lc_detailed!BA14/$R$2</f>
-        <v>-0.40627160655286715</v>
+        <v>-0.45791675621609745</v>
       </c>
       <c r="F14" s="25">
         <f>lc_detailed!BB14/$R$2</f>
-        <v>0</v>
+        <v>-19.117148637439108</v>
       </c>
       <c r="G14" s="25">
         <f>lc_detailed!BC14/$R$2</f>
@@ -15133,7 +15147,7 @@
       </c>
       <c r="K14" s="25">
         <f>lc_detailed!BH14/$R$2</f>
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="L14" s="25">
         <f>lc_detailed!BI14</f>
@@ -15141,60 +15155,60 @@
       </c>
       <c r="M14" s="25">
         <f>lc_detailed!AR14</f>
-        <v>1398.0584328315642</v>
+        <v>586.26241124940475</v>
       </c>
       <c r="N14" s="25">
         <f t="shared" si="0"/>
-        <v>30.659176158586934</v>
+        <v>12.85663182564484</v>
       </c>
       <c r="O14" s="25">
         <f t="shared" si="1"/>
-        <v>30.659176158586945</v>
+        <v>12.856631825644838</v>
       </c>
       <c r="U14" t="str">
-        <v>TX_Synthetic_Ethylene_CCS_90</v>
+        <v>CA_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V14">
-        <v>8.3654484308493462</v>
+        <v>8.882221111503009</v>
       </c>
       <c r="W14">
-        <v>0.92491394678216343</v>
+        <v>0.68916970159805557</v>
       </c>
       <c r="X14">
-        <v>16.623548185525394</v>
+        <v>14.948219637620451</v>
       </c>
       <c r="Y14">
-        <v>-0.40807122781737304</v>
+        <v>-0.39450878949359602</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>-17.122469805914761</v>
       </c>
       <c r="AA14">
-        <v>4.705568157602146</v>
+        <v>4.2600965636830308</v>
       </c>
       <c r="AB14">
-        <v>2.5867547372464941</v>
+        <v>2.3433206377337097</v>
       </c>
       <c r="AC14">
-        <v>-1.074340016786842</v>
+        <v>-0.99370798227543866</v>
       </c>
       <c r="AD14">
         <v>0</v>
       </c>
       <c r="AE14">
-        <v>-0.87771462481138307</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="AF14">
-        <v>-0.40472550988742861</v>
+        <v>-0.37309554696342861</v>
       </c>
       <c r="AG14">
-        <v>1406.5825060397012</v>
+        <v>547.61858206381407</v>
       </c>
       <c r="AH14">
-        <v>30.846107588589938</v>
+        <v>12.009179431223993</v>
       </c>
       <c r="AI14">
-        <v>30.846107588589945</v>
+        <v>12.009179431223989</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.2">
@@ -15204,23 +15218,23 @@
       </c>
       <c r="B15" s="25">
         <f>lc_detailed!AX15/$R$2</f>
-        <v>8.3654484277663634</v>
+        <v>7.9189911474333377</v>
       </c>
       <c r="C15" s="25">
         <f>lc_detailed!AY15/$R$2</f>
-        <v>0.72562464786171599</v>
+        <v>0.72597706891426772</v>
       </c>
       <c r="D15" s="25">
         <f>lc_detailed!AZ15/$R$2</f>
-        <v>18.095459475111131</v>
+        <v>13.24644441034965</v>
       </c>
       <c r="E15" s="25">
         <f>lc_detailed!BA15/$R$2</f>
-        <v>-0.40807122761951675</v>
+        <v>-0.26177559806236805</v>
       </c>
       <c r="F15" s="25">
         <f>lc_detailed!BB15/$R$2</f>
-        <v>0</v>
+        <v>-18.689851664969151</v>
       </c>
       <c r="G15" s="25">
         <f>lc_detailed!BC15/$R$2</f>
@@ -15240,7 +15254,7 @@
       </c>
       <c r="K15" s="25">
         <f>lc_detailed!BH15/$R$2</f>
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="L15" s="25">
         <f>lc_detailed!BI15</f>
@@ -15248,33 +15262,33 @@
       </c>
       <c r="M15" s="25">
         <f>lc_detailed!AR15</f>
-        <v>1440.0047144772827</v>
+        <v>362.35278204469142</v>
       </c>
       <c r="N15" s="25">
         <f t="shared" si="0"/>
-        <v>31.579050756080761</v>
+        <v>7.9463329395765658</v>
       </c>
       <c r="O15" s="25">
         <f t="shared" si="1"/>
-        <v>31.579050756080758</v>
+        <v>7.9463329395765649</v>
       </c>
       <c r="U15" t="str">
-        <v>NCEN_Synthetic_Ethylene_CCS_90</v>
+        <v>NW_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V15">
-        <v>8.5357868242283779</v>
+        <v>8.5313826695435289</v>
       </c>
       <c r="W15">
-        <v>1.0038577629207903</v>
+        <v>0.87658719827283771</v>
       </c>
       <c r="X15">
-        <v>16.4328322459106</v>
+        <v>14.177318046892477</v>
       </c>
       <c r="Y15">
-        <v>-0.41244103229750073</v>
+        <v>-0.37462406116791802</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>-16.656553189681333</v>
       </c>
       <c r="AA15">
         <v>4.705568157602146</v>
@@ -15289,19 +15303,19 @@
         <v>0</v>
       </c>
       <c r="AE15">
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="AF15">
         <v>-0.40472550988742861</v>
       </c>
       <c r="AG15">
-        <v>1409.0538648629781</v>
+        <v>552.5715704043057</v>
       </c>
       <c r="AH15">
-        <v>30.900304054012675</v>
+        <v>12.117797596585651</v>
       </c>
       <c r="AI15">
-        <v>30.900304054012679</v>
+        <v>12.117797596585651</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.2">
@@ -15311,23 +15325,23 @@
       </c>
       <c r="B16" s="25">
         <f>lc_detailed!AX16/$R$2</f>
-        <v>8.3654484308493462</v>
+        <v>7.9189911503517845</v>
       </c>
       <c r="C16" s="25">
         <f>lc_detailed!AY16/$R$2</f>
-        <v>0.92491394678216343</v>
+        <v>0.92536315857176465</v>
       </c>
       <c r="D16" s="25">
         <f>lc_detailed!AZ16/$R$2</f>
-        <v>16.623548185525394</v>
+        <v>12.168959138351944</v>
       </c>
       <c r="E16" s="25">
         <f>lc_detailed!BA16/$R$2</f>
-        <v>-0.40807122781737304</v>
+        <v>-0.26177559818929191</v>
       </c>
       <c r="F16" s="25">
         <f>lc_detailed!BB16/$R$2</f>
-        <v>0</v>
+        <v>-18.689851672712397</v>
       </c>
       <c r="G16" s="25">
         <f>lc_detailed!BC16/$R$2</f>
@@ -15347,7 +15361,7 @@
       </c>
       <c r="K16" s="25">
         <f>lc_detailed!BH16/$R$2</f>
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="L16" s="25">
         <f>lc_detailed!BI16</f>
@@ -15355,33 +15369,33 @@
       </c>
       <c r="M16" s="25">
         <f>lc_detailed!AR16</f>
-        <v>1406.5825060397012</v>
+        <v>347.7170137749539</v>
       </c>
       <c r="N16" s="25">
         <f t="shared" si="0"/>
-        <v>30.846107588589938</v>
+        <v>7.6253731090998658</v>
       </c>
       <c r="O16" s="25">
         <f t="shared" si="1"/>
-        <v>30.846107588589945</v>
+        <v>7.6253731090998622</v>
       </c>
       <c r="U16" t="str">
-        <v>CEN_Synthetic_Ethylene_Non_CCS</v>
+        <v>NW_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V16">
-        <v>8.3396571607981951</v>
+        <v>8.531382666399395</v>
       </c>
       <c r="W16">
-        <v>0.76219353272184187</v>
+        <v>0.68771076409838661</v>
       </c>
       <c r="X16">
-        <v>17.867352806738438</v>
+        <v>15.432630947386178</v>
       </c>
       <c r="Y16">
-        <v>-0.40627160635588333</v>
+        <v>-0.37462406098627876</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>-16.656553182780488</v>
       </c>
       <c r="AA16">
         <v>4.2600965636830308</v>
@@ -15396,19 +15410,19 @@
         <v>0</v>
       </c>
       <c r="AE16">
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="AF16">
         <v>-0.37309554696342861</v>
       </c>
       <c r="AG16">
-        <v>1430.1765725049829</v>
+        <v>575.79551877727795</v>
       </c>
       <c r="AH16">
-        <v>31.363521326863658</v>
+        <v>12.627094710028025</v>
       </c>
       <c r="AI16">
-        <v>31.363521326863658</v>
+        <v>12.627094710028024</v>
       </c>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.2">
@@ -15418,23 +15432,23 @@
       </c>
       <c r="B17" s="25">
         <f>lc_detailed!AX17/$R$2</f>
-        <v>5.4434092955246678</v>
+        <v>8.531382666399395</v>
       </c>
       <c r="C17" s="25">
         <f>lc_detailed!AY17/$R$2</f>
-        <v>0.68303418295909657</v>
+        <v>0.68771076409838661</v>
       </c>
       <c r="D17" s="25">
         <f>lc_detailed!AZ17/$R$2</f>
-        <v>18.275539973757166</v>
+        <v>15.432630947386178</v>
       </c>
       <c r="E17" s="25">
         <f>lc_detailed!BA17/$R$2</f>
-        <v>-0.27152195898886416</v>
+        <v>-0.37462406098627876</v>
       </c>
       <c r="F17" s="25">
         <f>lc_detailed!BB17/$R$2</f>
-        <v>0</v>
+        <v>-16.656553182780488</v>
       </c>
       <c r="G17" s="25">
         <f>lc_detailed!BC17/$R$2</f>
@@ -15454,7 +15468,7 @@
       </c>
       <c r="K17" s="25">
         <f>lc_detailed!BH17/$R$2</f>
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="L17" s="25">
         <f>lc_detailed!BI17</f>
@@ -15462,60 +15476,60 @@
       </c>
       <c r="M17" s="25">
         <f>lc_detailed!AR17</f>
-        <v>1319.2559222353186</v>
+        <v>575.79551877727795</v>
       </c>
       <c r="N17" s="25">
         <f t="shared" si="0"/>
-        <v>28.931050926213128</v>
+        <v>12.627094710028025</v>
       </c>
       <c r="O17" s="25">
         <f t="shared" si="1"/>
-        <v>28.931050926213135</v>
+        <v>12.627094710028024</v>
       </c>
       <c r="U17" t="str">
-        <v>TX_Synthetic_Ethylene_Non_CCS</v>
+        <v>NCEN_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V17">
-        <v>8.3654484277663634</v>
+        <v>13.845141122800179</v>
       </c>
       <c r="W17">
-        <v>0.72562464786171599</v>
+        <v>0.99247253170703364</v>
       </c>
       <c r="X17">
-        <v>18.095459475111131</v>
+        <v>11.974657788726613</v>
       </c>
       <c r="Y17">
-        <v>-0.40807122761951675</v>
+        <v>-0.45509041897430885</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>-19.094671939230906</v>
       </c>
       <c r="AA17">
-        <v>4.2600965636830308</v>
+        <v>4.705568157602146</v>
       </c>
       <c r="AB17">
-        <v>2.3433206377337097</v>
+        <v>2.5867547372464941</v>
       </c>
       <c r="AC17">
-        <v>-0.99370798227543866</v>
+        <v>-1.074340016786842</v>
       </c>
       <c r="AD17">
         <v>0</v>
       </c>
       <c r="AE17">
-        <v>-0.80911978618023661</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="AF17">
-        <v>-0.37309554696342861</v>
+        <v>-0.40472550988742861</v>
       </c>
       <c r="AG17">
-        <v>1440.0047144772827</v>
+        <v>584.8745384096128</v>
       </c>
       <c r="AH17">
-        <v>31.579050756080761</v>
+        <v>12.826196017754667</v>
       </c>
       <c r="AI17">
-        <v>31.579050756080758</v>
+        <v>12.82619601775467</v>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.2">
@@ -15525,23 +15539,23 @@
       </c>
       <c r="B18" s="25">
         <f>lc_detailed!AX18/$R$2</f>
-        <v>5.443409297530768</v>
+        <v>8.5313826695435289</v>
       </c>
       <c r="C18" s="25">
         <f>lc_detailed!AY18/$R$2</f>
-        <v>0.87062621674921659</v>
+        <v>0.87658719827283771</v>
       </c>
       <c r="D18" s="25">
         <f>lc_detailed!AZ18/$R$2</f>
-        <v>16.788980671538429</v>
+        <v>14.177318046892477</v>
       </c>
       <c r="E18" s="25">
         <f>lc_detailed!BA18/$R$2</f>
-        <v>-0.27152195912051358</v>
+        <v>-0.37462406116791802</v>
       </c>
       <c r="F18" s="25">
         <f>lc_detailed!BB18/$R$2</f>
-        <v>0</v>
+        <v>-16.656553189681333</v>
       </c>
       <c r="G18" s="25">
         <f>lc_detailed!BC18/$R$2</f>
@@ -15561,7 +15575,7 @@
       </c>
       <c r="K18" s="25">
         <f>lc_detailed!BH18/$R$2</f>
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="L18" s="25">
         <f>lc_detailed!BI18</f>
@@ -15569,60 +15583,60 @@
       </c>
       <c r="M18" s="25">
         <f>lc_detailed!AR18</f>
-        <v>1284.6323690856429</v>
+        <v>552.5715704043057</v>
       </c>
       <c r="N18" s="25">
         <f t="shared" si="0"/>
-        <v>28.17176247994831</v>
+        <v>12.117797596585651</v>
       </c>
       <c r="O18" s="25">
         <f t="shared" si="1"/>
-        <v>28.171762479948313</v>
+        <v>12.117797596585651</v>
       </c>
       <c r="U18" t="str">
-        <v>NCEN_Synthetic_Ethylene_Non_CCS</v>
+        <v>CEN_Synthetic_Ethylene_CCS_90</v>
       </c>
       <c r="V18">
-        <v>8.5357868210826187</v>
+        <v>13.938062701825016</v>
       </c>
       <c r="W18">
-        <v>0.78755860289152668</v>
+        <v>0.97334168995599168</v>
       </c>
       <c r="X18">
-        <v>17.887856831076196</v>
+        <v>11.956605894792975</v>
       </c>
       <c r="Y18">
-        <v>-0.41244103209752564</v>
+        <v>-0.45791675621609745</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>-19.117148637439108</v>
       </c>
       <c r="AA18">
-        <v>4.2600965636830308</v>
+        <v>4.705568157602146</v>
       </c>
       <c r="AB18">
-        <v>2.3433206377337097</v>
+        <v>2.5867547372464941</v>
       </c>
       <c r="AC18">
-        <v>-0.99370798227543866</v>
+        <v>-1.074340016786842</v>
       </c>
       <c r="AD18">
         <v>0</v>
       </c>
       <c r="AE18">
-        <v>-0.80911978618023661</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="AF18">
-        <v>-0.37309554696342861</v>
+        <v>-0.40472550988742861</v>
       </c>
       <c r="AG18">
-        <v>1440.9303899096728</v>
+        <v>586.26241124940475</v>
       </c>
       <c r="AH18">
-        <v>31.599350655913877</v>
+        <v>12.85663182564484</v>
       </c>
       <c r="AI18">
-        <v>31.599350655913884</v>
+        <v>12.856631825644838</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.2">
@@ -15632,23 +15646,23 @@
       </c>
       <c r="B19" s="25">
         <f>lc_detailed!AX19/$R$2</f>
-        <v>7.4502256381379315</v>
+        <v>9.4882025816090128</v>
       </c>
       <c r="C19" s="25">
         <f>lc_detailed!AY19/$R$2</f>
-        <v>0.71718601957415662</v>
+        <v>0.7145470765922991</v>
       </c>
       <c r="D19" s="25">
         <f>lc_detailed!AZ19/$R$2</f>
-        <v>17.990386976449198</v>
+        <v>13.380980564926391</v>
       </c>
       <c r="E19" s="25">
         <f>lc_detailed!BA19/$R$2</f>
-        <v>-0.37354974789689666</v>
+        <v>-0.31410156292172908</v>
       </c>
       <c r="F19" s="25">
         <f>lc_detailed!BB19/$R$2</f>
-        <v>0</v>
+        <v>-18.607641472923653</v>
       </c>
       <c r="G19" s="25">
         <f>lc_detailed!BC19/$R$2</f>
@@ -15668,7 +15682,7 @@
       </c>
       <c r="K19" s="25">
         <f>lc_detailed!BH19/$R$2</f>
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="L19" s="25">
         <f>lc_detailed!BI19</f>
@@ -15676,60 +15690,60 @@
       </c>
       <c r="M19" s="25">
         <f>lc_detailed!AR19</f>
-        <v>1394.6686273566809</v>
+        <v>440.88518520160773</v>
       </c>
       <c r="N19" s="25">
         <f t="shared" si="0"/>
-        <v>30.584838319225458</v>
+        <v>9.6685347631931524</v>
       </c>
       <c r="O19" s="25">
         <f t="shared" si="1"/>
-        <v>30.584838319225458</v>
+        <v>9.6685347631931524</v>
       </c>
       <c r="U19" t="str">
-        <v>MIDAT_Synthetic_Ethylene_CCS_90</v>
+        <v>NCEN_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V19">
-        <v>11.469127996236775</v>
+        <v>13.845141117697725</v>
       </c>
       <c r="W19">
-        <v>0.98447350298327296</v>
+        <v>0.77862652394618448</v>
       </c>
       <c r="X19">
-        <v>14.644118880244196</v>
+        <v>13.034938890657648</v>
       </c>
       <c r="Y19">
-        <v>-0.36998997706758924</v>
+        <v>-0.45509041875365486</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>-19.09467193131994</v>
       </c>
       <c r="AA19">
-        <v>4.705568157602146</v>
+        <v>4.2600965636830308</v>
       </c>
       <c r="AB19">
-        <v>2.5867547372464941</v>
+        <v>2.3433206377337097</v>
       </c>
       <c r="AC19">
-        <v>-1.074340016786842</v>
+        <v>-0.99370798227543866</v>
       </c>
       <c r="AD19">
         <v>0</v>
       </c>
       <c r="AE19">
-        <v>-0.87771462481138307</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="AF19">
-        <v>-0.40472550988742861</v>
+        <v>-0.37309554696342861</v>
       </c>
       <c r="AG19">
-        <v>1462.3007386975059</v>
+        <v>598.06642417112914</v>
       </c>
       <c r="AH19">
-        <v>32.06799865564706</v>
+        <v>13.115491758138797</v>
       </c>
       <c r="AI19">
-        <v>32.067998655647067</v>
+        <v>13.115491758138793</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.2">
@@ -15739,23 +15753,23 @@
       </c>
       <c r="B20" s="25">
         <f>lc_detailed!AX20/$R$2</f>
-        <v>7.4502256408836214</v>
+        <v>9.488202585105773</v>
       </c>
       <c r="C20" s="25">
         <f>lc_detailed!AY20/$R$2</f>
-        <v>0.91415769006200642</v>
+        <v>0.91079397415754326</v>
       </c>
       <c r="D20" s="25">
         <f>lc_detailed!AZ20/$R$2</f>
-        <v>16.527022438451514</v>
+        <v>12.292551924231621</v>
       </c>
       <c r="E20" s="25">
         <f>lc_detailed!BA20/$R$2</f>
-        <v>-0.37354974807801505</v>
+        <v>-0.31410156307402354</v>
       </c>
       <c r="F20" s="25">
         <f>lc_detailed!BB20/$R$2</f>
-        <v>0</v>
+        <v>-18.607641480632839</v>
       </c>
       <c r="G20" s="25">
         <f>lc_detailed!BC20/$R$2</f>
@@ -15775,7 +15789,7 @@
       </c>
       <c r="K20" s="25">
         <f>lc_detailed!BH20/$R$2</f>
-        <v>-0.87771462481138307</v>
+        <v>-0.65429594533574054</v>
       </c>
       <c r="L20" s="25">
         <f>lc_detailed!BI20</f>
@@ -15783,33 +15797,33 @@
       </c>
       <c r="M20" s="25">
         <f>lc_detailed!AR20</f>
-        <v>1361.5304669203708</v>
+        <v>425.60725218664447</v>
       </c>
       <c r="N20" s="25">
         <f t="shared" si="0"/>
-        <v>29.858124274569533</v>
+        <v>9.333492372514133</v>
       </c>
       <c r="O20" s="25">
         <f t="shared" si="1"/>
-        <v>29.858124274569541</v>
+        <v>9.3334923725141348</v>
       </c>
       <c r="U20" t="str">
-        <v>MIDAT_Synthetic_Ethylene_Non_CCS</v>
+        <v>CEN_Synthetic_Ethylene_Non_CCS</v>
       </c>
       <c r="V20">
-        <v>11.46912799200997</v>
+        <v>13.938062696688313</v>
       </c>
       <c r="W20">
-        <v>0.77235102943006417</v>
+        <v>0.76361776517765922</v>
       </c>
       <c r="X20">
-        <v>15.940764076883717</v>
+        <v>13.015288614346023</v>
       </c>
       <c r="Y20">
-        <v>-0.3699899768881969</v>
+        <v>-0.45791675599407311</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>-19.117148629518834</v>
       </c>
       <c r="AA20">
         <v>4.2600965636830308</v>
@@ -15824,19 +15838,19 @@
         <v>0</v>
       </c>
       <c r="AE20">
-        <v>-0.80911978618023661</v>
+        <v>-0.60316164323047106</v>
       </c>
       <c r="AF20">
         <v>-0.37309554696342861</v>
       </c>
       <c r="AG20">
-        <v>1487.1456204804856</v>
+        <v>599.56937775741244</v>
       </c>
       <c r="AH20">
-        <v>32.612842554396615</v>
+        <v>13.148451266609921</v>
       </c>
       <c r="AI20">
-        <v>32.612842554396622</v>
+        <v>13.14845126660992</v>
       </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.2">
